--- a/Archivos/Archivos_origen/Planeación contenido blog Aciertala 2025.xlsx
+++ b/Archivos/Archivos_origen/Planeación contenido blog Aciertala 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/jhor_caro_virtualsoft_tech/Documents/Documentos/Proyectos QuotaMedia/SEO/Planeacion SEO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/jhor_caro_virtualsoft_tech/Documents/Documentos/GitHub/Planeaci-n_SEO/Archivos/Archivos_origen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="11_D2D46AE609F6779E136FF9258C46CEF0CFAB49D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE88B081-82ED-49E2-A5C2-B0FB41876257}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_D2D46AE609F6779E136FF9258C46CEF0CFAB49D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BCF48C9-B13C-42E0-BF96-EBDB786B464C}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Abril" sheetId="1" r:id="rId1"/>
@@ -4434,10 +4434,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -28761,7 +28757,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AG992"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="12.453125" customWidth="1"/>
     <col min="2" max="2" width="18.6328125" customWidth="1"/>
@@ -28847,7 +28843,7 @@
       <c r="AF1" s="5"/>
       <c r="AG1" s="5"/>
     </row>
-    <row r="2" spans="1:33" ht="15.75" customHeight="1">
+    <row r="2" spans="1:33" ht="112.5">
       <c r="A2" s="14" t="s">
         <v>27</v>
       </c>
@@ -28896,7 +28892,7 @@
       </c>
       <c r="Q2" s="8"/>
     </row>
-    <row r="3" spans="1:33" ht="15.75" customHeight="1">
+    <row r="3" spans="1:33" ht="50">
       <c r="A3" s="14" t="s">
         <v>27</v>
       </c>
@@ -28937,7 +28933,7 @@
       </c>
       <c r="P3" s="7"/>
     </row>
-    <row r="4" spans="1:33" ht="15.75" customHeight="1">
+    <row r="4" spans="1:33" ht="62.5">
       <c r="A4" s="14" t="s">
         <v>65</v>
       </c>
@@ -28986,7 +28982,7 @@
       </c>
       <c r="Q4" s="7"/>
     </row>
-    <row r="5" spans="1:33" ht="15.75" customHeight="1">
+    <row r="5" spans="1:33" ht="112.5">
       <c r="A5" s="14" t="s">
         <v>27</v>
       </c>
@@ -29035,7 +29031,7 @@
       </c>
       <c r="Q5" s="7"/>
     </row>
-    <row r="6" spans="1:33" ht="15.75" customHeight="1">
+    <row r="6" spans="1:33" ht="62.5">
       <c r="A6" s="14" t="s">
         <v>27</v>
       </c>
@@ -29084,7 +29080,7 @@
       </c>
       <c r="Q6" s="7"/>
     </row>
-    <row r="7" spans="1:33" ht="15.75" customHeight="1">
+    <row r="7" spans="1:33" ht="125">
       <c r="A7" s="14" t="s">
         <v>27</v>
       </c>
@@ -29133,7 +29129,7 @@
       </c>
       <c r="Q7" s="7"/>
     </row>
-    <row r="8" spans="1:33" ht="15.75" customHeight="1">
+    <row r="8" spans="1:33" ht="62.5">
       <c r="A8" s="14" t="s">
         <v>27</v>
       </c>
@@ -29180,7 +29176,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="15.75" customHeight="1">
+    <row r="9" spans="1:33" ht="125">
       <c r="A9" s="14" t="s">
         <v>27</v>
       </c>
@@ -29228,7 +29224,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="15.75" customHeight="1">
+    <row r="10" spans="1:33" ht="112.5">
       <c r="A10" s="23" t="s">
         <v>16</v>
       </c>
@@ -29275,7 +29271,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="15.75" customHeight="1">
+    <row r="11" spans="1:33" ht="87.5">
       <c r="A11" s="14" t="s">
         <v>27</v>
       </c>
@@ -29324,7 +29320,7 @@
       </c>
       <c r="Q11" s="8"/>
     </row>
-    <row r="12" spans="1:33" ht="15.75" customHeight="1">
+    <row r="12" spans="1:33" ht="93">
       <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
@@ -29373,7 +29369,7 @@
       </c>
       <c r="Q12" s="7"/>
     </row>
-    <row r="13" spans="1:33" ht="15.75" customHeight="1">
+    <row r="13" spans="1:33" ht="124">
       <c r="A13" s="14" t="s">
         <v>27</v>
       </c>
@@ -29422,7 +29418,7 @@
       </c>
       <c r="Q13" s="7"/>
     </row>
-    <row r="14" spans="1:33" ht="15.75" customHeight="1">
+    <row r="14" spans="1:33" ht="50">
       <c r="A14" s="14" t="s">
         <v>27</v>
       </c>
@@ -29469,7 +29465,7 @@
       </c>
       <c r="Q14" s="7"/>
     </row>
-    <row r="15" spans="1:33" ht="15.75" customHeight="1">
+    <row r="15" spans="1:33" ht="50">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -29517,7 +29513,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="15.75" customHeight="1">
+    <row r="16" spans="1:33">
       <c r="D16" s="7"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
@@ -29526,7 +29522,7 @@
       <c r="K16" s="18"/>
       <c r="L16" s="7"/>
     </row>
-    <row r="17" spans="4:12" ht="15.75" customHeight="1">
+    <row r="17" spans="4:12">
       <c r="D17" s="7"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
@@ -29534,7 +29530,7 @@
       <c r="J17" s="7"/>
       <c r="L17" s="7"/>
     </row>
-    <row r="18" spans="4:12" ht="15.75" customHeight="1">
+    <row r="18" spans="4:12">
       <c r="D18" s="7"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
@@ -29542,7 +29538,7 @@
       <c r="J18" s="7"/>
       <c r="L18" s="7"/>
     </row>
-    <row r="19" spans="4:12" ht="15.75" customHeight="1">
+    <row r="19" spans="4:12">
       <c r="D19" s="7"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
@@ -29550,7 +29546,7 @@
       <c r="J19" s="7"/>
       <c r="L19" s="7"/>
     </row>
-    <row r="20" spans="4:12" ht="15.75" customHeight="1">
+    <row r="20" spans="4:12">
       <c r="D20" s="7"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
@@ -29558,7 +29554,7 @@
       <c r="J20" s="7"/>
       <c r="L20" s="7"/>
     </row>
-    <row r="21" spans="4:12" ht="15.75" customHeight="1">
+    <row r="21" spans="4:12">
       <c r="D21" s="7"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
@@ -29566,7 +29562,7 @@
       <c r="J21" s="7"/>
       <c r="L21" s="7"/>
     </row>
-    <row r="22" spans="4:12" ht="15.75" customHeight="1">
+    <row r="22" spans="4:12">
       <c r="D22" s="7"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
@@ -29574,7 +29570,7 @@
       <c r="J22" s="7"/>
       <c r="L22" s="7"/>
     </row>
-    <row r="23" spans="4:12" ht="15.75" customHeight="1">
+    <row r="23" spans="4:12">
       <c r="D23" s="7"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
@@ -29582,7 +29578,7 @@
       <c r="J23" s="7"/>
       <c r="L23" s="7"/>
     </row>
-    <row r="24" spans="4:12" ht="15.75" customHeight="1">
+    <row r="24" spans="4:12">
       <c r="D24" s="7"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
@@ -29590,7 +29586,7 @@
       <c r="J24" s="7"/>
       <c r="L24" s="7"/>
     </row>
-    <row r="25" spans="4:12" ht="15.75" customHeight="1">
+    <row r="25" spans="4:12">
       <c r="D25" s="7"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
@@ -29598,7 +29594,7 @@
       <c r="J25" s="7"/>
       <c r="L25" s="7"/>
     </row>
-    <row r="26" spans="4:12" ht="15.75" customHeight="1">
+    <row r="26" spans="4:12">
       <c r="D26" s="7"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
@@ -29606,7 +29602,7 @@
       <c r="J26" s="7"/>
       <c r="L26" s="7"/>
     </row>
-    <row r="27" spans="4:12" ht="15.75" customHeight="1">
+    <row r="27" spans="4:12">
       <c r="D27" s="7"/>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
@@ -29614,7 +29610,7 @@
       <c r="J27" s="7"/>
       <c r="L27" s="7"/>
     </row>
-    <row r="28" spans="4:12" ht="15.75" customHeight="1">
+    <row r="28" spans="4:12">
       <c r="D28" s="7"/>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
@@ -29622,7 +29618,7 @@
       <c r="J28" s="7"/>
       <c r="L28" s="7"/>
     </row>
-    <row r="29" spans="4:12" ht="15.75" customHeight="1">
+    <row r="29" spans="4:12">
       <c r="D29" s="7"/>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
@@ -29630,7 +29626,7 @@
       <c r="J29" s="7"/>
       <c r="L29" s="7"/>
     </row>
-    <row r="30" spans="4:12" ht="15.75" customHeight="1">
+    <row r="30" spans="4:12">
       <c r="D30" s="7"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
@@ -29638,7 +29634,7 @@
       <c r="J30" s="7"/>
       <c r="L30" s="7"/>
     </row>
-    <row r="31" spans="4:12" ht="15.75" customHeight="1">
+    <row r="31" spans="4:12">
       <c r="D31" s="7"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
@@ -29646,7 +29642,7 @@
       <c r="J31" s="7"/>
       <c r="L31" s="7"/>
     </row>
-    <row r="32" spans="4:12" ht="12.5">
+    <row r="32" spans="4:12">
       <c r="D32" s="7"/>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
@@ -29654,7 +29650,7 @@
       <c r="J32" s="7"/>
       <c r="L32" s="7"/>
     </row>
-    <row r="33" spans="4:12" ht="12.5">
+    <row r="33" spans="4:12">
       <c r="D33" s="7"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
@@ -29662,7 +29658,7 @@
       <c r="J33" s="7"/>
       <c r="L33" s="7"/>
     </row>
-    <row r="34" spans="4:12" ht="12.5">
+    <row r="34" spans="4:12">
       <c r="D34" s="7"/>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
@@ -29670,7 +29666,7 @@
       <c r="J34" s="7"/>
       <c r="L34" s="7"/>
     </row>
-    <row r="35" spans="4:12" ht="12.5">
+    <row r="35" spans="4:12">
       <c r="D35" s="7"/>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
@@ -29678,7 +29674,7 @@
       <c r="J35" s="7"/>
       <c r="L35" s="7"/>
     </row>
-    <row r="36" spans="4:12" ht="12.5">
+    <row r="36" spans="4:12">
       <c r="D36" s="7"/>
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
@@ -29686,7 +29682,7 @@
       <c r="J36" s="7"/>
       <c r="L36" s="7"/>
     </row>
-    <row r="37" spans="4:12" ht="12.5">
+    <row r="37" spans="4:12">
       <c r="D37" s="7"/>
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
@@ -29694,7 +29690,7 @@
       <c r="J37" s="7"/>
       <c r="L37" s="7"/>
     </row>
-    <row r="38" spans="4:12" ht="12.5">
+    <row r="38" spans="4:12">
       <c r="D38" s="7"/>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
@@ -29702,7 +29698,7 @@
       <c r="J38" s="7"/>
       <c r="L38" s="7"/>
     </row>
-    <row r="39" spans="4:12" ht="12.5">
+    <row r="39" spans="4:12">
       <c r="D39" s="7"/>
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
@@ -29710,7 +29706,7 @@
       <c r="J39" s="7"/>
       <c r="L39" s="7"/>
     </row>
-    <row r="40" spans="4:12" ht="12.5">
+    <row r="40" spans="4:12">
       <c r="D40" s="7"/>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
@@ -29718,7 +29714,7 @@
       <c r="J40" s="7"/>
       <c r="L40" s="7"/>
     </row>
-    <row r="41" spans="4:12" ht="12.5">
+    <row r="41" spans="4:12">
       <c r="D41" s="7"/>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
@@ -29726,7 +29722,7 @@
       <c r="J41" s="7"/>
       <c r="L41" s="7"/>
     </row>
-    <row r="42" spans="4:12" ht="12.5">
+    <row r="42" spans="4:12">
       <c r="D42" s="7"/>
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
@@ -29734,7 +29730,7 @@
       <c r="J42" s="7"/>
       <c r="L42" s="7"/>
     </row>
-    <row r="43" spans="4:12" ht="12.5">
+    <row r="43" spans="4:12">
       <c r="D43" s="7"/>
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
@@ -29742,7 +29738,7 @@
       <c r="J43" s="7"/>
       <c r="L43" s="7"/>
     </row>
-    <row r="44" spans="4:12" ht="12.5">
+    <row r="44" spans="4:12">
       <c r="D44" s="7"/>
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
@@ -29750,7 +29746,7 @@
       <c r="J44" s="7"/>
       <c r="L44" s="7"/>
     </row>
-    <row r="45" spans="4:12" ht="12.5">
+    <row r="45" spans="4:12">
       <c r="D45" s="7"/>
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
@@ -29758,7 +29754,7 @@
       <c r="J45" s="7"/>
       <c r="L45" s="7"/>
     </row>
-    <row r="46" spans="4:12" ht="12.5">
+    <row r="46" spans="4:12">
       <c r="D46" s="7"/>
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
@@ -29766,7 +29762,7 @@
       <c r="J46" s="7"/>
       <c r="L46" s="7"/>
     </row>
-    <row r="47" spans="4:12" ht="12.5">
+    <row r="47" spans="4:12">
       <c r="D47" s="7"/>
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
@@ -29774,7 +29770,7 @@
       <c r="J47" s="7"/>
       <c r="L47" s="7"/>
     </row>
-    <row r="48" spans="4:12" ht="12.5">
+    <row r="48" spans="4:12">
       <c r="D48" s="7"/>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
@@ -29782,7 +29778,7 @@
       <c r="J48" s="7"/>
       <c r="L48" s="7"/>
     </row>
-    <row r="49" spans="4:12" ht="12.5">
+    <row r="49" spans="4:12">
       <c r="D49" s="7"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
@@ -29790,7 +29786,7 @@
       <c r="J49" s="7"/>
       <c r="L49" s="7"/>
     </row>
-    <row r="50" spans="4:12" ht="12.5">
+    <row r="50" spans="4:12">
       <c r="D50" s="7"/>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
@@ -29798,7 +29794,7 @@
       <c r="J50" s="7"/>
       <c r="L50" s="7"/>
     </row>
-    <row r="51" spans="4:12" ht="12.5">
+    <row r="51" spans="4:12">
       <c r="D51" s="7"/>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
@@ -29806,7 +29802,7 @@
       <c r="J51" s="7"/>
       <c r="L51" s="7"/>
     </row>
-    <row r="52" spans="4:12" ht="12.5">
+    <row r="52" spans="4:12">
       <c r="D52" s="7"/>
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
@@ -29814,7 +29810,7 @@
       <c r="J52" s="7"/>
       <c r="L52" s="7"/>
     </row>
-    <row r="53" spans="4:12" ht="12.5">
+    <row r="53" spans="4:12">
       <c r="D53" s="7"/>
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
@@ -29822,7 +29818,7 @@
       <c r="J53" s="7"/>
       <c r="L53" s="7"/>
     </row>
-    <row r="54" spans="4:12" ht="12.5">
+    <row r="54" spans="4:12">
       <c r="D54" s="7"/>
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
@@ -29830,7 +29826,7 @@
       <c r="J54" s="7"/>
       <c r="L54" s="7"/>
     </row>
-    <row r="55" spans="4:12" ht="12.5">
+    <row r="55" spans="4:12">
       <c r="D55" s="7"/>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
@@ -29838,7 +29834,7 @@
       <c r="J55" s="7"/>
       <c r="L55" s="7"/>
     </row>
-    <row r="56" spans="4:12" ht="12.5">
+    <row r="56" spans="4:12">
       <c r="D56" s="7"/>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
@@ -29846,7 +29842,7 @@
       <c r="J56" s="7"/>
       <c r="L56" s="7"/>
     </row>
-    <row r="57" spans="4:12" ht="12.5">
+    <row r="57" spans="4:12">
       <c r="D57" s="7"/>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
@@ -29854,7 +29850,7 @@
       <c r="J57" s="7"/>
       <c r="L57" s="7"/>
     </row>
-    <row r="58" spans="4:12" ht="12.5">
+    <row r="58" spans="4:12">
       <c r="D58" s="7"/>
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
@@ -29862,7 +29858,7 @@
       <c r="J58" s="7"/>
       <c r="L58" s="7"/>
     </row>
-    <row r="59" spans="4:12" ht="12.5">
+    <row r="59" spans="4:12">
       <c r="D59" s="7"/>
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
@@ -29870,7 +29866,7 @@
       <c r="J59" s="7"/>
       <c r="L59" s="7"/>
     </row>
-    <row r="60" spans="4:12" ht="12.5">
+    <row r="60" spans="4:12">
       <c r="D60" s="7"/>
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
@@ -29878,7 +29874,7 @@
       <c r="J60" s="7"/>
       <c r="L60" s="7"/>
     </row>
-    <row r="61" spans="4:12" ht="12.5">
+    <row r="61" spans="4:12">
       <c r="D61" s="7"/>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
@@ -29886,7 +29882,7 @@
       <c r="J61" s="7"/>
       <c r="L61" s="7"/>
     </row>
-    <row r="62" spans="4:12" ht="12.5">
+    <row r="62" spans="4:12">
       <c r="D62" s="7"/>
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
@@ -29894,7 +29890,7 @@
       <c r="J62" s="7"/>
       <c r="L62" s="7"/>
     </row>
-    <row r="63" spans="4:12" ht="12.5">
+    <row r="63" spans="4:12">
       <c r="D63" s="7"/>
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
@@ -29902,7 +29898,7 @@
       <c r="J63" s="7"/>
       <c r="L63" s="7"/>
     </row>
-    <row r="64" spans="4:12" ht="12.5">
+    <row r="64" spans="4:12">
       <c r="D64" s="7"/>
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
@@ -29910,7 +29906,7 @@
       <c r="J64" s="7"/>
       <c r="L64" s="7"/>
     </row>
-    <row r="65" spans="4:12" ht="12.5">
+    <row r="65" spans="4:12">
       <c r="D65" s="7"/>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
@@ -29918,7 +29914,7 @@
       <c r="J65" s="7"/>
       <c r="L65" s="7"/>
     </row>
-    <row r="66" spans="4:12" ht="12.5">
+    <row r="66" spans="4:12">
       <c r="D66" s="7"/>
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
@@ -29926,7 +29922,7 @@
       <c r="J66" s="7"/>
       <c r="L66" s="7"/>
     </row>
-    <row r="67" spans="4:12" ht="12.5">
+    <row r="67" spans="4:12">
       <c r="D67" s="7"/>
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
@@ -29934,7 +29930,7 @@
       <c r="J67" s="7"/>
       <c r="L67" s="7"/>
     </row>
-    <row r="68" spans="4:12" ht="12.5">
+    <row r="68" spans="4:12">
       <c r="D68" s="7"/>
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
@@ -29942,7 +29938,7 @@
       <c r="J68" s="7"/>
       <c r="L68" s="7"/>
     </row>
-    <row r="69" spans="4:12" ht="12.5">
+    <row r="69" spans="4:12">
       <c r="D69" s="7"/>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
@@ -29950,7 +29946,7 @@
       <c r="J69" s="7"/>
       <c r="L69" s="7"/>
     </row>
-    <row r="70" spans="4:12" ht="12.5">
+    <row r="70" spans="4:12">
       <c r="D70" s="7"/>
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
@@ -29958,7 +29954,7 @@
       <c r="J70" s="7"/>
       <c r="L70" s="7"/>
     </row>
-    <row r="71" spans="4:12" ht="12.5">
+    <row r="71" spans="4:12">
       <c r="D71" s="7"/>
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
@@ -29966,7 +29962,7 @@
       <c r="J71" s="7"/>
       <c r="L71" s="7"/>
     </row>
-    <row r="72" spans="4:12" ht="12.5">
+    <row r="72" spans="4:12">
       <c r="D72" s="7"/>
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
@@ -29974,7 +29970,7 @@
       <c r="J72" s="7"/>
       <c r="L72" s="7"/>
     </row>
-    <row r="73" spans="4:12" ht="12.5">
+    <row r="73" spans="4:12">
       <c r="D73" s="7"/>
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
@@ -29982,7 +29978,7 @@
       <c r="J73" s="7"/>
       <c r="L73" s="7"/>
     </row>
-    <row r="74" spans="4:12" ht="12.5">
+    <row r="74" spans="4:12">
       <c r="D74" s="7"/>
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
@@ -29990,7 +29986,7 @@
       <c r="J74" s="7"/>
       <c r="L74" s="7"/>
     </row>
-    <row r="75" spans="4:12" ht="12.5">
+    <row r="75" spans="4:12">
       <c r="D75" s="7"/>
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
@@ -29998,7 +29994,7 @@
       <c r="J75" s="7"/>
       <c r="L75" s="7"/>
     </row>
-    <row r="76" spans="4:12" ht="12.5">
+    <row r="76" spans="4:12">
       <c r="D76" s="7"/>
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
@@ -30006,7 +30002,7 @@
       <c r="J76" s="7"/>
       <c r="L76" s="7"/>
     </row>
-    <row r="77" spans="4:12" ht="12.5">
+    <row r="77" spans="4:12">
       <c r="D77" s="7"/>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
@@ -30014,7 +30010,7 @@
       <c r="J77" s="7"/>
       <c r="L77" s="7"/>
     </row>
-    <row r="78" spans="4:12" ht="12.5">
+    <row r="78" spans="4:12">
       <c r="D78" s="7"/>
       <c r="G78" s="8"/>
       <c r="H78" s="8"/>
@@ -30022,7 +30018,7 @@
       <c r="J78" s="7"/>
       <c r="L78" s="7"/>
     </row>
-    <row r="79" spans="4:12" ht="12.5">
+    <row r="79" spans="4:12">
       <c r="D79" s="7"/>
       <c r="G79" s="8"/>
       <c r="H79" s="8"/>
@@ -30030,7 +30026,7 @@
       <c r="J79" s="7"/>
       <c r="L79" s="7"/>
     </row>
-    <row r="80" spans="4:12" ht="12.5">
+    <row r="80" spans="4:12">
       <c r="D80" s="7"/>
       <c r="G80" s="8"/>
       <c r="H80" s="8"/>
@@ -30038,7 +30034,7 @@
       <c r="J80" s="7"/>
       <c r="L80" s="7"/>
     </row>
-    <row r="81" spans="4:12" ht="12.5">
+    <row r="81" spans="4:12">
       <c r="D81" s="7"/>
       <c r="G81" s="8"/>
       <c r="H81" s="8"/>
@@ -30046,7 +30042,7 @@
       <c r="J81" s="7"/>
       <c r="L81" s="7"/>
     </row>
-    <row r="82" spans="4:12" ht="12.5">
+    <row r="82" spans="4:12">
       <c r="D82" s="7"/>
       <c r="G82" s="8"/>
       <c r="H82" s="8"/>
@@ -30054,7 +30050,7 @@
       <c r="J82" s="7"/>
       <c r="L82" s="7"/>
     </row>
-    <row r="83" spans="4:12" ht="12.5">
+    <row r="83" spans="4:12">
       <c r="D83" s="7"/>
       <c r="G83" s="8"/>
       <c r="H83" s="8"/>
@@ -30062,7 +30058,7 @@
       <c r="J83" s="7"/>
       <c r="L83" s="7"/>
     </row>
-    <row r="84" spans="4:12" ht="12.5">
+    <row r="84" spans="4:12">
       <c r="D84" s="7"/>
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
@@ -30070,7 +30066,7 @@
       <c r="J84" s="7"/>
       <c r="L84" s="7"/>
     </row>
-    <row r="85" spans="4:12" ht="12.5">
+    <row r="85" spans="4:12">
       <c r="D85" s="7"/>
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
@@ -30078,7 +30074,7 @@
       <c r="J85" s="7"/>
       <c r="L85" s="7"/>
     </row>
-    <row r="86" spans="4:12" ht="12.5">
+    <row r="86" spans="4:12">
       <c r="D86" s="7"/>
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
@@ -30086,7 +30082,7 @@
       <c r="J86" s="7"/>
       <c r="L86" s="7"/>
     </row>
-    <row r="87" spans="4:12" ht="12.5">
+    <row r="87" spans="4:12">
       <c r="D87" s="7"/>
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
@@ -30094,7 +30090,7 @@
       <c r="J87" s="7"/>
       <c r="L87" s="7"/>
     </row>
-    <row r="88" spans="4:12" ht="12.5">
+    <row r="88" spans="4:12">
       <c r="D88" s="7"/>
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
@@ -30102,7 +30098,7 @@
       <c r="J88" s="7"/>
       <c r="L88" s="7"/>
     </row>
-    <row r="89" spans="4:12" ht="12.5">
+    <row r="89" spans="4:12">
       <c r="D89" s="7"/>
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
@@ -30110,7 +30106,7 @@
       <c r="J89" s="7"/>
       <c r="L89" s="7"/>
     </row>
-    <row r="90" spans="4:12" ht="12.5">
+    <row r="90" spans="4:12">
       <c r="D90" s="7"/>
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
@@ -30118,7 +30114,7 @@
       <c r="J90" s="7"/>
       <c r="L90" s="7"/>
     </row>
-    <row r="91" spans="4:12" ht="12.5">
+    <row r="91" spans="4:12">
       <c r="D91" s="7"/>
       <c r="G91" s="8"/>
       <c r="H91" s="8"/>
@@ -30126,7 +30122,7 @@
       <c r="J91" s="7"/>
       <c r="L91" s="7"/>
     </row>
-    <row r="92" spans="4:12" ht="12.5">
+    <row r="92" spans="4:12">
       <c r="D92" s="7"/>
       <c r="G92" s="8"/>
       <c r="H92" s="8"/>
@@ -30134,7 +30130,7 @@
       <c r="J92" s="7"/>
       <c r="L92" s="7"/>
     </row>
-    <row r="93" spans="4:12" ht="12.5">
+    <row r="93" spans="4:12">
       <c r="D93" s="7"/>
       <c r="G93" s="8"/>
       <c r="H93" s="8"/>
@@ -30142,7 +30138,7 @@
       <c r="J93" s="7"/>
       <c r="L93" s="7"/>
     </row>
-    <row r="94" spans="4:12" ht="12.5">
+    <row r="94" spans="4:12">
       <c r="D94" s="7"/>
       <c r="G94" s="8"/>
       <c r="H94" s="8"/>
@@ -30150,7 +30146,7 @@
       <c r="J94" s="7"/>
       <c r="L94" s="7"/>
     </row>
-    <row r="95" spans="4:12" ht="12.5">
+    <row r="95" spans="4:12">
       <c r="D95" s="7"/>
       <c r="G95" s="8"/>
       <c r="H95" s="8"/>
@@ -30158,7 +30154,7 @@
       <c r="J95" s="7"/>
       <c r="L95" s="7"/>
     </row>
-    <row r="96" spans="4:12" ht="12.5">
+    <row r="96" spans="4:12">
       <c r="D96" s="7"/>
       <c r="G96" s="8"/>
       <c r="H96" s="8"/>
@@ -30166,7 +30162,7 @@
       <c r="J96" s="7"/>
       <c r="L96" s="7"/>
     </row>
-    <row r="97" spans="4:12" ht="12.5">
+    <row r="97" spans="4:12">
       <c r="D97" s="7"/>
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
@@ -30174,7 +30170,7 @@
       <c r="J97" s="7"/>
       <c r="L97" s="7"/>
     </row>
-    <row r="98" spans="4:12" ht="12.5">
+    <row r="98" spans="4:12">
       <c r="D98" s="7"/>
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
@@ -30182,7 +30178,7 @@
       <c r="J98" s="7"/>
       <c r="L98" s="7"/>
     </row>
-    <row r="99" spans="4:12" ht="12.5">
+    <row r="99" spans="4:12">
       <c r="D99" s="7"/>
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
@@ -30190,7 +30186,7 @@
       <c r="J99" s="7"/>
       <c r="L99" s="7"/>
     </row>
-    <row r="100" spans="4:12" ht="12.5">
+    <row r="100" spans="4:12">
       <c r="D100" s="7"/>
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
@@ -30198,7 +30194,7 @@
       <c r="J100" s="7"/>
       <c r="L100" s="7"/>
     </row>
-    <row r="101" spans="4:12" ht="12.5">
+    <row r="101" spans="4:12">
       <c r="D101" s="7"/>
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
@@ -30206,7 +30202,7 @@
       <c r="J101" s="7"/>
       <c r="L101" s="7"/>
     </row>
-    <row r="102" spans="4:12" ht="12.5">
+    <row r="102" spans="4:12">
       <c r="D102" s="7"/>
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
@@ -30214,7 +30210,7 @@
       <c r="J102" s="7"/>
       <c r="L102" s="7"/>
     </row>
-    <row r="103" spans="4:12" ht="12.5">
+    <row r="103" spans="4:12">
       <c r="D103" s="7"/>
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
@@ -30222,7 +30218,7 @@
       <c r="J103" s="7"/>
       <c r="L103" s="7"/>
     </row>
-    <row r="104" spans="4:12" ht="12.5">
+    <row r="104" spans="4:12">
       <c r="D104" s="7"/>
       <c r="G104" s="8"/>
       <c r="H104" s="8"/>
@@ -30230,7 +30226,7 @@
       <c r="J104" s="7"/>
       <c r="L104" s="7"/>
     </row>
-    <row r="105" spans="4:12" ht="12.5">
+    <row r="105" spans="4:12">
       <c r="D105" s="7"/>
       <c r="G105" s="8"/>
       <c r="H105" s="8"/>
@@ -30238,7 +30234,7 @@
       <c r="J105" s="7"/>
       <c r="L105" s="7"/>
     </row>
-    <row r="106" spans="4:12" ht="12.5">
+    <row r="106" spans="4:12">
       <c r="D106" s="7"/>
       <c r="G106" s="8"/>
       <c r="H106" s="8"/>
@@ -30246,7 +30242,7 @@
       <c r="J106" s="7"/>
       <c r="L106" s="7"/>
     </row>
-    <row r="107" spans="4:12" ht="12.5">
+    <row r="107" spans="4:12">
       <c r="D107" s="7"/>
       <c r="G107" s="8"/>
       <c r="H107" s="8"/>
@@ -30254,7 +30250,7 @@
       <c r="J107" s="7"/>
       <c r="L107" s="7"/>
     </row>
-    <row r="108" spans="4:12" ht="12.5">
+    <row r="108" spans="4:12">
       <c r="D108" s="7"/>
       <c r="G108" s="8"/>
       <c r="H108" s="8"/>
@@ -30262,7 +30258,7 @@
       <c r="J108" s="7"/>
       <c r="L108" s="7"/>
     </row>
-    <row r="109" spans="4:12" ht="12.5">
+    <row r="109" spans="4:12">
       <c r="D109" s="7"/>
       <c r="G109" s="8"/>
       <c r="H109" s="8"/>
@@ -30270,7 +30266,7 @@
       <c r="J109" s="7"/>
       <c r="L109" s="7"/>
     </row>
-    <row r="110" spans="4:12" ht="12.5">
+    <row r="110" spans="4:12">
       <c r="D110" s="7"/>
       <c r="G110" s="8"/>
       <c r="H110" s="8"/>
@@ -30278,7 +30274,7 @@
       <c r="J110" s="7"/>
       <c r="L110" s="7"/>
     </row>
-    <row r="111" spans="4:12" ht="12.5">
+    <row r="111" spans="4:12">
       <c r="D111" s="7"/>
       <c r="G111" s="8"/>
       <c r="H111" s="8"/>
@@ -30286,7 +30282,7 @@
       <c r="J111" s="7"/>
       <c r="L111" s="7"/>
     </row>
-    <row r="112" spans="4:12" ht="12.5">
+    <row r="112" spans="4:12">
       <c r="D112" s="7"/>
       <c r="G112" s="8"/>
       <c r="H112" s="8"/>
@@ -30294,7 +30290,7 @@
       <c r="J112" s="7"/>
       <c r="L112" s="7"/>
     </row>
-    <row r="113" spans="4:12" ht="12.5">
+    <row r="113" spans="4:12">
       <c r="D113" s="7"/>
       <c r="G113" s="8"/>
       <c r="H113" s="8"/>
@@ -30302,7 +30298,7 @@
       <c r="J113" s="7"/>
       <c r="L113" s="7"/>
     </row>
-    <row r="114" spans="4:12" ht="12.5">
+    <row r="114" spans="4:12">
       <c r="D114" s="7"/>
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
@@ -30310,7 +30306,7 @@
       <c r="J114" s="7"/>
       <c r="L114" s="7"/>
     </row>
-    <row r="115" spans="4:12" ht="12.5">
+    <row r="115" spans="4:12">
       <c r="D115" s="7"/>
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
@@ -30318,7 +30314,7 @@
       <c r="J115" s="7"/>
       <c r="L115" s="7"/>
     </row>
-    <row r="116" spans="4:12" ht="12.5">
+    <row r="116" spans="4:12">
       <c r="D116" s="7"/>
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
@@ -30326,7 +30322,7 @@
       <c r="J116" s="7"/>
       <c r="L116" s="7"/>
     </row>
-    <row r="117" spans="4:12" ht="12.5">
+    <row r="117" spans="4:12">
       <c r="D117" s="7"/>
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
@@ -30334,7 +30330,7 @@
       <c r="J117" s="7"/>
       <c r="L117" s="7"/>
     </row>
-    <row r="118" spans="4:12" ht="12.5">
+    <row r="118" spans="4:12">
       <c r="D118" s="7"/>
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
@@ -30342,7 +30338,7 @@
       <c r="J118" s="7"/>
       <c r="L118" s="7"/>
     </row>
-    <row r="119" spans="4:12" ht="12.5">
+    <row r="119" spans="4:12">
       <c r="D119" s="7"/>
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
@@ -30350,7 +30346,7 @@
       <c r="J119" s="7"/>
       <c r="L119" s="7"/>
     </row>
-    <row r="120" spans="4:12" ht="12.5">
+    <row r="120" spans="4:12">
       <c r="D120" s="7"/>
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
@@ -30358,7 +30354,7 @@
       <c r="J120" s="7"/>
       <c r="L120" s="7"/>
     </row>
-    <row r="121" spans="4:12" ht="12.5">
+    <row r="121" spans="4:12">
       <c r="D121" s="7"/>
       <c r="G121" s="8"/>
       <c r="H121" s="8"/>
@@ -30366,7 +30362,7 @@
       <c r="J121" s="7"/>
       <c r="L121" s="7"/>
     </row>
-    <row r="122" spans="4:12" ht="12.5">
+    <row r="122" spans="4:12">
       <c r="D122" s="7"/>
       <c r="G122" s="8"/>
       <c r="H122" s="8"/>
@@ -30374,7 +30370,7 @@
       <c r="J122" s="7"/>
       <c r="L122" s="7"/>
     </row>
-    <row r="123" spans="4:12" ht="12.5">
+    <row r="123" spans="4:12">
       <c r="D123" s="7"/>
       <c r="G123" s="8"/>
       <c r="H123" s="8"/>
@@ -30382,7 +30378,7 @@
       <c r="J123" s="7"/>
       <c r="L123" s="7"/>
     </row>
-    <row r="124" spans="4:12" ht="12.5">
+    <row r="124" spans="4:12">
       <c r="D124" s="7"/>
       <c r="G124" s="8"/>
       <c r="H124" s="8"/>
@@ -30390,7 +30386,7 @@
       <c r="J124" s="7"/>
       <c r="L124" s="7"/>
     </row>
-    <row r="125" spans="4:12" ht="12.5">
+    <row r="125" spans="4:12">
       <c r="D125" s="7"/>
       <c r="G125" s="8"/>
       <c r="H125" s="8"/>
@@ -30398,7 +30394,7 @@
       <c r="J125" s="7"/>
       <c r="L125" s="7"/>
     </row>
-    <row r="126" spans="4:12" ht="12.5">
+    <row r="126" spans="4:12">
       <c r="D126" s="7"/>
       <c r="G126" s="8"/>
       <c r="H126" s="8"/>
@@ -30406,7 +30402,7 @@
       <c r="J126" s="7"/>
       <c r="L126" s="7"/>
     </row>
-    <row r="127" spans="4:12" ht="12.5">
+    <row r="127" spans="4:12">
       <c r="D127" s="7"/>
       <c r="G127" s="8"/>
       <c r="H127" s="8"/>
@@ -30414,7 +30410,7 @@
       <c r="J127" s="7"/>
       <c r="L127" s="7"/>
     </row>
-    <row r="128" spans="4:12" ht="12.5">
+    <row r="128" spans="4:12">
       <c r="D128" s="7"/>
       <c r="G128" s="8"/>
       <c r="H128" s="8"/>
@@ -30422,7 +30418,7 @@
       <c r="J128" s="7"/>
       <c r="L128" s="7"/>
     </row>
-    <row r="129" spans="4:12" ht="12.5">
+    <row r="129" spans="4:12">
       <c r="D129" s="7"/>
       <c r="G129" s="8"/>
       <c r="H129" s="8"/>
@@ -30430,7 +30426,7 @@
       <c r="J129" s="7"/>
       <c r="L129" s="7"/>
     </row>
-    <row r="130" spans="4:12" ht="12.5">
+    <row r="130" spans="4:12">
       <c r="D130" s="7"/>
       <c r="G130" s="8"/>
       <c r="H130" s="8"/>
@@ -30438,7 +30434,7 @@
       <c r="J130" s="7"/>
       <c r="L130" s="7"/>
     </row>
-    <row r="131" spans="4:12" ht="12.5">
+    <row r="131" spans="4:12">
       <c r="D131" s="7"/>
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
@@ -30446,7 +30442,7 @@
       <c r="J131" s="7"/>
       <c r="L131" s="7"/>
     </row>
-    <row r="132" spans="4:12" ht="12.5">
+    <row r="132" spans="4:12">
       <c r="D132" s="7"/>
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
@@ -30454,7 +30450,7 @@
       <c r="J132" s="7"/>
       <c r="L132" s="7"/>
     </row>
-    <row r="133" spans="4:12" ht="12.5">
+    <row r="133" spans="4:12">
       <c r="D133" s="7"/>
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
@@ -30462,7 +30458,7 @@
       <c r="J133" s="7"/>
       <c r="L133" s="7"/>
     </row>
-    <row r="134" spans="4:12" ht="12.5">
+    <row r="134" spans="4:12">
       <c r="D134" s="7"/>
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
@@ -30470,7 +30466,7 @@
       <c r="J134" s="7"/>
       <c r="L134" s="7"/>
     </row>
-    <row r="135" spans="4:12" ht="12.5">
+    <row r="135" spans="4:12">
       <c r="D135" s="7"/>
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
@@ -30478,7 +30474,7 @@
       <c r="J135" s="7"/>
       <c r="L135" s="7"/>
     </row>
-    <row r="136" spans="4:12" ht="12.5">
+    <row r="136" spans="4:12">
       <c r="D136" s="7"/>
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
@@ -30486,7 +30482,7 @@
       <c r="J136" s="7"/>
       <c r="L136" s="7"/>
     </row>
-    <row r="137" spans="4:12" ht="12.5">
+    <row r="137" spans="4:12">
       <c r="D137" s="7"/>
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
@@ -30494,7 +30490,7 @@
       <c r="J137" s="7"/>
       <c r="L137" s="7"/>
     </row>
-    <row r="138" spans="4:12" ht="12.5">
+    <row r="138" spans="4:12">
       <c r="D138" s="7"/>
       <c r="G138" s="8"/>
       <c r="H138" s="8"/>
@@ -30502,7 +30498,7 @@
       <c r="J138" s="7"/>
       <c r="L138" s="7"/>
     </row>
-    <row r="139" spans="4:12" ht="12.5">
+    <row r="139" spans="4:12">
       <c r="D139" s="7"/>
       <c r="G139" s="8"/>
       <c r="H139" s="8"/>
@@ -30510,7 +30506,7 @@
       <c r="J139" s="7"/>
       <c r="L139" s="7"/>
     </row>
-    <row r="140" spans="4:12" ht="12.5">
+    <row r="140" spans="4:12">
       <c r="D140" s="7"/>
       <c r="G140" s="8"/>
       <c r="H140" s="8"/>
@@ -30518,7 +30514,7 @@
       <c r="J140" s="7"/>
       <c r="L140" s="7"/>
     </row>
-    <row r="141" spans="4:12" ht="12.5">
+    <row r="141" spans="4:12">
       <c r="D141" s="7"/>
       <c r="G141" s="8"/>
       <c r="H141" s="8"/>
@@ -30526,7 +30522,7 @@
       <c r="J141" s="7"/>
       <c r="L141" s="7"/>
     </row>
-    <row r="142" spans="4:12" ht="12.5">
+    <row r="142" spans="4:12">
       <c r="D142" s="7"/>
       <c r="G142" s="8"/>
       <c r="H142" s="8"/>
@@ -30534,7 +30530,7 @@
       <c r="J142" s="7"/>
       <c r="L142" s="7"/>
     </row>
-    <row r="143" spans="4:12" ht="12.5">
+    <row r="143" spans="4:12">
       <c r="D143" s="7"/>
       <c r="G143" s="8"/>
       <c r="H143" s="8"/>
@@ -30542,7 +30538,7 @@
       <c r="J143" s="7"/>
       <c r="L143" s="7"/>
     </row>
-    <row r="144" spans="4:12" ht="12.5">
+    <row r="144" spans="4:12">
       <c r="D144" s="7"/>
       <c r="G144" s="8"/>
       <c r="H144" s="8"/>
@@ -30550,7 +30546,7 @@
       <c r="J144" s="7"/>
       <c r="L144" s="7"/>
     </row>
-    <row r="145" spans="4:12" ht="12.5">
+    <row r="145" spans="4:12">
       <c r="D145" s="7"/>
       <c r="G145" s="8"/>
       <c r="H145" s="8"/>
@@ -30558,7 +30554,7 @@
       <c r="J145" s="7"/>
       <c r="L145" s="7"/>
     </row>
-    <row r="146" spans="4:12" ht="12.5">
+    <row r="146" spans="4:12">
       <c r="D146" s="7"/>
       <c r="G146" s="8"/>
       <c r="H146" s="8"/>
@@ -30566,7 +30562,7 @@
       <c r="J146" s="7"/>
       <c r="L146" s="7"/>
     </row>
-    <row r="147" spans="4:12" ht="12.5">
+    <row r="147" spans="4:12">
       <c r="D147" s="7"/>
       <c r="G147" s="8"/>
       <c r="H147" s="8"/>
@@ -30574,7 +30570,7 @@
       <c r="J147" s="7"/>
       <c r="L147" s="7"/>
     </row>
-    <row r="148" spans="4:12" ht="12.5">
+    <row r="148" spans="4:12">
       <c r="D148" s="7"/>
       <c r="G148" s="8"/>
       <c r="H148" s="8"/>
@@ -30582,7 +30578,7 @@
       <c r="J148" s="7"/>
       <c r="L148" s="7"/>
     </row>
-    <row r="149" spans="4:12" ht="12.5">
+    <row r="149" spans="4:12">
       <c r="D149" s="7"/>
       <c r="G149" s="8"/>
       <c r="H149" s="8"/>
@@ -30590,7 +30586,7 @@
       <c r="J149" s="7"/>
       <c r="L149" s="7"/>
     </row>
-    <row r="150" spans="4:12" ht="12.5">
+    <row r="150" spans="4:12">
       <c r="D150" s="7"/>
       <c r="G150" s="8"/>
       <c r="H150" s="8"/>
@@ -30598,7 +30594,7 @@
       <c r="J150" s="7"/>
       <c r="L150" s="7"/>
     </row>
-    <row r="151" spans="4:12" ht="12.5">
+    <row r="151" spans="4:12">
       <c r="D151" s="7"/>
       <c r="G151" s="8"/>
       <c r="H151" s="8"/>
@@ -30606,7 +30602,7 @@
       <c r="J151" s="7"/>
       <c r="L151" s="7"/>
     </row>
-    <row r="152" spans="4:12" ht="12.5">
+    <row r="152" spans="4:12">
       <c r="D152" s="7"/>
       <c r="G152" s="8"/>
       <c r="H152" s="8"/>
@@ -30614,7 +30610,7 @@
       <c r="J152" s="7"/>
       <c r="L152" s="7"/>
     </row>
-    <row r="153" spans="4:12" ht="12.5">
+    <row r="153" spans="4:12">
       <c r="D153" s="7"/>
       <c r="G153" s="8"/>
       <c r="H153" s="8"/>
@@ -30622,7 +30618,7 @@
       <c r="J153" s="7"/>
       <c r="L153" s="7"/>
     </row>
-    <row r="154" spans="4:12" ht="12.5">
+    <row r="154" spans="4:12">
       <c r="D154" s="7"/>
       <c r="G154" s="8"/>
       <c r="H154" s="8"/>
@@ -30630,7 +30626,7 @@
       <c r="J154" s="7"/>
       <c r="L154" s="7"/>
     </row>
-    <row r="155" spans="4:12" ht="12.5">
+    <row r="155" spans="4:12">
       <c r="D155" s="7"/>
       <c r="G155" s="8"/>
       <c r="H155" s="8"/>
@@ -30638,7 +30634,7 @@
       <c r="J155" s="7"/>
       <c r="L155" s="7"/>
     </row>
-    <row r="156" spans="4:12" ht="12.5">
+    <row r="156" spans="4:12">
       <c r="D156" s="7"/>
       <c r="G156" s="8"/>
       <c r="H156" s="8"/>
@@ -30646,7 +30642,7 @@
       <c r="J156" s="7"/>
       <c r="L156" s="7"/>
     </row>
-    <row r="157" spans="4:12" ht="12.5">
+    <row r="157" spans="4:12">
       <c r="D157" s="7"/>
       <c r="G157" s="8"/>
       <c r="H157" s="8"/>
@@ -30654,7 +30650,7 @@
       <c r="J157" s="7"/>
       <c r="L157" s="7"/>
     </row>
-    <row r="158" spans="4:12" ht="12.5">
+    <row r="158" spans="4:12">
       <c r="D158" s="7"/>
       <c r="G158" s="8"/>
       <c r="H158" s="8"/>
@@ -30662,7 +30658,7 @@
       <c r="J158" s="7"/>
       <c r="L158" s="7"/>
     </row>
-    <row r="159" spans="4:12" ht="12.5">
+    <row r="159" spans="4:12">
       <c r="D159" s="7"/>
       <c r="G159" s="8"/>
       <c r="H159" s="8"/>
@@ -30670,7 +30666,7 @@
       <c r="J159" s="7"/>
       <c r="L159" s="7"/>
     </row>
-    <row r="160" spans="4:12" ht="12.5">
+    <row r="160" spans="4:12">
       <c r="D160" s="7"/>
       <c r="G160" s="8"/>
       <c r="H160" s="8"/>
@@ -30678,7 +30674,7 @@
       <c r="J160" s="7"/>
       <c r="L160" s="7"/>
     </row>
-    <row r="161" spans="4:12" ht="12.5">
+    <row r="161" spans="4:12">
       <c r="D161" s="7"/>
       <c r="G161" s="8"/>
       <c r="H161" s="8"/>
@@ -30686,7 +30682,7 @@
       <c r="J161" s="7"/>
       <c r="L161" s="7"/>
     </row>
-    <row r="162" spans="4:12" ht="12.5">
+    <row r="162" spans="4:12">
       <c r="D162" s="7"/>
       <c r="G162" s="8"/>
       <c r="H162" s="8"/>
@@ -30694,7 +30690,7 @@
       <c r="J162" s="7"/>
       <c r="L162" s="7"/>
     </row>
-    <row r="163" spans="4:12" ht="12.5">
+    <row r="163" spans="4:12">
       <c r="D163" s="7"/>
       <c r="G163" s="8"/>
       <c r="H163" s="8"/>
@@ -30702,7 +30698,7 @@
       <c r="J163" s="7"/>
       <c r="L163" s="7"/>
     </row>
-    <row r="164" spans="4:12" ht="12.5">
+    <row r="164" spans="4:12">
       <c r="D164" s="7"/>
       <c r="G164" s="8"/>
       <c r="H164" s="8"/>
@@ -30710,7 +30706,7 @@
       <c r="J164" s="7"/>
       <c r="L164" s="7"/>
     </row>
-    <row r="165" spans="4:12" ht="12.5">
+    <row r="165" spans="4:12">
       <c r="D165" s="7"/>
       <c r="G165" s="8"/>
       <c r="H165" s="8"/>
@@ -30718,7 +30714,7 @@
       <c r="J165" s="7"/>
       <c r="L165" s="7"/>
     </row>
-    <row r="166" spans="4:12" ht="12.5">
+    <row r="166" spans="4:12">
       <c r="D166" s="7"/>
       <c r="G166" s="8"/>
       <c r="H166" s="8"/>
@@ -30726,7 +30722,7 @@
       <c r="J166" s="7"/>
       <c r="L166" s="7"/>
     </row>
-    <row r="167" spans="4:12" ht="12.5">
+    <row r="167" spans="4:12">
       <c r="D167" s="7"/>
       <c r="G167" s="8"/>
       <c r="H167" s="8"/>
@@ -30734,7 +30730,7 @@
       <c r="J167" s="7"/>
       <c r="L167" s="7"/>
     </row>
-    <row r="168" spans="4:12" ht="12.5">
+    <row r="168" spans="4:12">
       <c r="D168" s="7"/>
       <c r="G168" s="8"/>
       <c r="H168" s="8"/>
@@ -30742,7 +30738,7 @@
       <c r="J168" s="7"/>
       <c r="L168" s="7"/>
     </row>
-    <row r="169" spans="4:12" ht="12.5">
+    <row r="169" spans="4:12">
       <c r="D169" s="7"/>
       <c r="G169" s="8"/>
       <c r="H169" s="8"/>
@@ -30750,7 +30746,7 @@
       <c r="J169" s="7"/>
       <c r="L169" s="7"/>
     </row>
-    <row r="170" spans="4:12" ht="12.5">
+    <row r="170" spans="4:12">
       <c r="D170" s="7"/>
       <c r="G170" s="8"/>
       <c r="H170" s="8"/>
@@ -30758,7 +30754,7 @@
       <c r="J170" s="7"/>
       <c r="L170" s="7"/>
     </row>
-    <row r="171" spans="4:12" ht="12.5">
+    <row r="171" spans="4:12">
       <c r="D171" s="7"/>
       <c r="G171" s="8"/>
       <c r="H171" s="8"/>
@@ -30766,7 +30762,7 @@
       <c r="J171" s="7"/>
       <c r="L171" s="7"/>
     </row>
-    <row r="172" spans="4:12" ht="12.5">
+    <row r="172" spans="4:12">
       <c r="D172" s="7"/>
       <c r="G172" s="8"/>
       <c r="H172" s="8"/>
@@ -30774,7 +30770,7 @@
       <c r="J172" s="7"/>
       <c r="L172" s="7"/>
     </row>
-    <row r="173" spans="4:12" ht="12.5">
+    <row r="173" spans="4:12">
       <c r="D173" s="7"/>
       <c r="G173" s="8"/>
       <c r="H173" s="8"/>
@@ -30782,7 +30778,7 @@
       <c r="J173" s="7"/>
       <c r="L173" s="7"/>
     </row>
-    <row r="174" spans="4:12" ht="12.5">
+    <row r="174" spans="4:12">
       <c r="D174" s="7"/>
       <c r="G174" s="8"/>
       <c r="H174" s="8"/>
@@ -30790,7 +30786,7 @@
       <c r="J174" s="7"/>
       <c r="L174" s="7"/>
     </row>
-    <row r="175" spans="4:12" ht="12.5">
+    <row r="175" spans="4:12">
       <c r="D175" s="7"/>
       <c r="G175" s="8"/>
       <c r="H175" s="8"/>
@@ -30798,7 +30794,7 @@
       <c r="J175" s="7"/>
       <c r="L175" s="7"/>
     </row>
-    <row r="176" spans="4:12" ht="12.5">
+    <row r="176" spans="4:12">
       <c r="D176" s="7"/>
       <c r="G176" s="8"/>
       <c r="H176" s="8"/>
@@ -30806,7 +30802,7 @@
       <c r="J176" s="7"/>
       <c r="L176" s="7"/>
     </row>
-    <row r="177" spans="4:12" ht="12.5">
+    <row r="177" spans="4:12">
       <c r="D177" s="7"/>
       <c r="G177" s="8"/>
       <c r="H177" s="8"/>
@@ -30814,7 +30810,7 @@
       <c r="J177" s="7"/>
       <c r="L177" s="7"/>
     </row>
-    <row r="178" spans="4:12" ht="12.5">
+    <row r="178" spans="4:12">
       <c r="D178" s="7"/>
       <c r="G178" s="8"/>
       <c r="H178" s="8"/>
@@ -30822,7 +30818,7 @@
       <c r="J178" s="7"/>
       <c r="L178" s="7"/>
     </row>
-    <row r="179" spans="4:12" ht="12.5">
+    <row r="179" spans="4:12">
       <c r="D179" s="7"/>
       <c r="G179" s="8"/>
       <c r="H179" s="8"/>
@@ -30830,7 +30826,7 @@
       <c r="J179" s="7"/>
       <c r="L179" s="7"/>
     </row>
-    <row r="180" spans="4:12" ht="12.5">
+    <row r="180" spans="4:12">
       <c r="D180" s="7"/>
       <c r="G180" s="8"/>
       <c r="H180" s="8"/>
@@ -30838,7 +30834,7 @@
       <c r="J180" s="7"/>
       <c r="L180" s="7"/>
     </row>
-    <row r="181" spans="4:12" ht="12.5">
+    <row r="181" spans="4:12">
       <c r="D181" s="7"/>
       <c r="G181" s="8"/>
       <c r="H181" s="8"/>
@@ -30846,7 +30842,7 @@
       <c r="J181" s="7"/>
       <c r="L181" s="7"/>
     </row>
-    <row r="182" spans="4:12" ht="12.5">
+    <row r="182" spans="4:12">
       <c r="D182" s="7"/>
       <c r="G182" s="8"/>
       <c r="H182" s="8"/>
@@ -30854,7 +30850,7 @@
       <c r="J182" s="7"/>
       <c r="L182" s="7"/>
     </row>
-    <row r="183" spans="4:12" ht="12.5">
+    <row r="183" spans="4:12">
       <c r="D183" s="7"/>
       <c r="G183" s="8"/>
       <c r="H183" s="8"/>
@@ -30862,7 +30858,7 @@
       <c r="J183" s="7"/>
       <c r="L183" s="7"/>
     </row>
-    <row r="184" spans="4:12" ht="12.5">
+    <row r="184" spans="4:12">
       <c r="D184" s="7"/>
       <c r="G184" s="8"/>
       <c r="H184" s="8"/>
@@ -30870,7 +30866,7 @@
       <c r="J184" s="7"/>
       <c r="L184" s="7"/>
     </row>
-    <row r="185" spans="4:12" ht="12.5">
+    <row r="185" spans="4:12">
       <c r="D185" s="7"/>
       <c r="G185" s="8"/>
       <c r="H185" s="8"/>
@@ -30878,7 +30874,7 @@
       <c r="J185" s="7"/>
       <c r="L185" s="7"/>
     </row>
-    <row r="186" spans="4:12" ht="12.5">
+    <row r="186" spans="4:12">
       <c r="D186" s="7"/>
       <c r="G186" s="8"/>
       <c r="H186" s="8"/>
@@ -30886,7 +30882,7 @@
       <c r="J186" s="7"/>
       <c r="L186" s="7"/>
     </row>
-    <row r="187" spans="4:12" ht="12.5">
+    <row r="187" spans="4:12">
       <c r="D187" s="7"/>
       <c r="G187" s="8"/>
       <c r="H187" s="8"/>
@@ -30894,7 +30890,7 @@
       <c r="J187" s="7"/>
       <c r="L187" s="7"/>
     </row>
-    <row r="188" spans="4:12" ht="12.5">
+    <row r="188" spans="4:12">
       <c r="D188" s="7"/>
       <c r="G188" s="8"/>
       <c r="H188" s="8"/>
@@ -30902,7 +30898,7 @@
       <c r="J188" s="7"/>
       <c r="L188" s="7"/>
     </row>
-    <row r="189" spans="4:12" ht="12.5">
+    <row r="189" spans="4:12">
       <c r="D189" s="7"/>
       <c r="G189" s="8"/>
       <c r="H189" s="8"/>
@@ -30910,7 +30906,7 @@
       <c r="J189" s="7"/>
       <c r="L189" s="7"/>
     </row>
-    <row r="190" spans="4:12" ht="12.5">
+    <row r="190" spans="4:12">
       <c r="D190" s="7"/>
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
@@ -30918,7 +30914,7 @@
       <c r="J190" s="7"/>
       <c r="L190" s="7"/>
     </row>
-    <row r="191" spans="4:12" ht="12.5">
+    <row r="191" spans="4:12">
       <c r="D191" s="7"/>
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
@@ -30926,7 +30922,7 @@
       <c r="J191" s="7"/>
       <c r="L191" s="7"/>
     </row>
-    <row r="192" spans="4:12" ht="12.5">
+    <row r="192" spans="4:12">
       <c r="D192" s="7"/>
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
@@ -30934,7 +30930,7 @@
       <c r="J192" s="7"/>
       <c r="L192" s="7"/>
     </row>
-    <row r="193" spans="4:12" ht="12.5">
+    <row r="193" spans="4:12">
       <c r="D193" s="7"/>
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
@@ -30942,7 +30938,7 @@
       <c r="J193" s="7"/>
       <c r="L193" s="7"/>
     </row>
-    <row r="194" spans="4:12" ht="12.5">
+    <row r="194" spans="4:12">
       <c r="D194" s="7"/>
       <c r="G194" s="8"/>
       <c r="H194" s="8"/>
@@ -30950,7 +30946,7 @@
       <c r="J194" s="7"/>
       <c r="L194" s="7"/>
     </row>
-    <row r="195" spans="4:12" ht="12.5">
+    <row r="195" spans="4:12">
       <c r="D195" s="7"/>
       <c r="G195" s="8"/>
       <c r="H195" s="8"/>
@@ -30958,7 +30954,7 @@
       <c r="J195" s="7"/>
       <c r="L195" s="7"/>
     </row>
-    <row r="196" spans="4:12" ht="12.5">
+    <row r="196" spans="4:12">
       <c r="D196" s="7"/>
       <c r="G196" s="8"/>
       <c r="H196" s="8"/>
@@ -30966,7 +30962,7 @@
       <c r="J196" s="7"/>
       <c r="L196" s="7"/>
     </row>
-    <row r="197" spans="4:12" ht="12.5">
+    <row r="197" spans="4:12">
       <c r="D197" s="7"/>
       <c r="G197" s="8"/>
       <c r="H197" s="8"/>
@@ -30974,7 +30970,7 @@
       <c r="J197" s="7"/>
       <c r="L197" s="7"/>
     </row>
-    <row r="198" spans="4:12" ht="12.5">
+    <row r="198" spans="4:12">
       <c r="D198" s="7"/>
       <c r="G198" s="8"/>
       <c r="H198" s="8"/>
@@ -30982,7 +30978,7 @@
       <c r="J198" s="7"/>
       <c r="L198" s="7"/>
     </row>
-    <row r="199" spans="4:12" ht="12.5">
+    <row r="199" spans="4:12">
       <c r="D199" s="7"/>
       <c r="G199" s="8"/>
       <c r="H199" s="8"/>
@@ -30990,7 +30986,7 @@
       <c r="J199" s="7"/>
       <c r="L199" s="7"/>
     </row>
-    <row r="200" spans="4:12" ht="12.5">
+    <row r="200" spans="4:12">
       <c r="D200" s="7"/>
       <c r="G200" s="8"/>
       <c r="H200" s="8"/>
@@ -30998,7 +30994,7 @@
       <c r="J200" s="7"/>
       <c r="L200" s="7"/>
     </row>
-    <row r="201" spans="4:12" ht="12.5">
+    <row r="201" spans="4:12">
       <c r="D201" s="7"/>
       <c r="G201" s="8"/>
       <c r="H201" s="8"/>
@@ -31006,7 +31002,7 @@
       <c r="J201" s="7"/>
       <c r="L201" s="7"/>
     </row>
-    <row r="202" spans="4:12" ht="12.5">
+    <row r="202" spans="4:12">
       <c r="D202" s="7"/>
       <c r="G202" s="8"/>
       <c r="H202" s="8"/>
@@ -31014,7 +31010,7 @@
       <c r="J202" s="7"/>
       <c r="L202" s="7"/>
     </row>
-    <row r="203" spans="4:12" ht="12.5">
+    <row r="203" spans="4:12">
       <c r="D203" s="7"/>
       <c r="G203" s="8"/>
       <c r="H203" s="8"/>
@@ -31022,7 +31018,7 @@
       <c r="J203" s="7"/>
       <c r="L203" s="7"/>
     </row>
-    <row r="204" spans="4:12" ht="12.5">
+    <row r="204" spans="4:12">
       <c r="D204" s="7"/>
       <c r="G204" s="8"/>
       <c r="H204" s="8"/>
@@ -31030,7 +31026,7 @@
       <c r="J204" s="7"/>
       <c r="L204" s="7"/>
     </row>
-    <row r="205" spans="4:12" ht="12.5">
+    <row r="205" spans="4:12">
       <c r="D205" s="7"/>
       <c r="G205" s="8"/>
       <c r="H205" s="8"/>
@@ -31038,7 +31034,7 @@
       <c r="J205" s="7"/>
       <c r="L205" s="7"/>
     </row>
-    <row r="206" spans="4:12" ht="12.5">
+    <row r="206" spans="4:12">
       <c r="D206" s="7"/>
       <c r="G206" s="8"/>
       <c r="H206" s="8"/>
@@ -31046,7 +31042,7 @@
       <c r="J206" s="7"/>
       <c r="L206" s="7"/>
     </row>
-    <row r="207" spans="4:12" ht="12.5">
+    <row r="207" spans="4:12">
       <c r="D207" s="7"/>
       <c r="G207" s="8"/>
       <c r="H207" s="8"/>
@@ -31054,7 +31050,7 @@
       <c r="J207" s="7"/>
       <c r="L207" s="7"/>
     </row>
-    <row r="208" spans="4:12" ht="12.5">
+    <row r="208" spans="4:12">
       <c r="D208" s="7"/>
       <c r="G208" s="8"/>
       <c r="H208" s="8"/>
@@ -31062,7 +31058,7 @@
       <c r="J208" s="7"/>
       <c r="L208" s="7"/>
     </row>
-    <row r="209" spans="4:12" ht="12.5">
+    <row r="209" spans="4:12">
       <c r="D209" s="7"/>
       <c r="G209" s="8"/>
       <c r="H209" s="8"/>
@@ -31070,7 +31066,7 @@
       <c r="J209" s="7"/>
       <c r="L209" s="7"/>
     </row>
-    <row r="210" spans="4:12" ht="12.5">
+    <row r="210" spans="4:12">
       <c r="D210" s="7"/>
       <c r="G210" s="8"/>
       <c r="H210" s="8"/>
@@ -31078,7 +31074,7 @@
       <c r="J210" s="7"/>
       <c r="L210" s="7"/>
     </row>
-    <row r="211" spans="4:12" ht="12.5">
+    <row r="211" spans="4:12">
       <c r="D211" s="7"/>
       <c r="G211" s="8"/>
       <c r="H211" s="8"/>
@@ -31086,7 +31082,7 @@
       <c r="J211" s="7"/>
       <c r="L211" s="7"/>
     </row>
-    <row r="212" spans="4:12" ht="12.5">
+    <row r="212" spans="4:12">
       <c r="D212" s="7"/>
       <c r="G212" s="8"/>
       <c r="H212" s="8"/>
@@ -31094,7 +31090,7 @@
       <c r="J212" s="7"/>
       <c r="L212" s="7"/>
     </row>
-    <row r="213" spans="4:12" ht="12.5">
+    <row r="213" spans="4:12">
       <c r="D213" s="7"/>
       <c r="G213" s="8"/>
       <c r="H213" s="8"/>
@@ -31102,7 +31098,7 @@
       <c r="J213" s="7"/>
       <c r="L213" s="7"/>
     </row>
-    <row r="214" spans="4:12" ht="12.5">
+    <row r="214" spans="4:12">
       <c r="D214" s="7"/>
       <c r="G214" s="8"/>
       <c r="H214" s="8"/>
@@ -31110,7 +31106,7 @@
       <c r="J214" s="7"/>
       <c r="L214" s="7"/>
     </row>
-    <row r="215" spans="4:12" ht="12.5">
+    <row r="215" spans="4:12">
       <c r="D215" s="7"/>
       <c r="G215" s="8"/>
       <c r="H215" s="8"/>
@@ -31118,7 +31114,7 @@
       <c r="J215" s="7"/>
       <c r="L215" s="7"/>
     </row>
-    <row r="216" spans="4:12" ht="12.5">
+    <row r="216" spans="4:12">
       <c r="D216" s="7"/>
       <c r="G216" s="8"/>
       <c r="H216" s="8"/>
@@ -31126,7 +31122,7 @@
       <c r="J216" s="7"/>
       <c r="L216" s="7"/>
     </row>
-    <row r="217" spans="4:12" ht="12.5">
+    <row r="217" spans="4:12">
       <c r="D217" s="7"/>
       <c r="G217" s="8"/>
       <c r="H217" s="8"/>
@@ -31134,7 +31130,7 @@
       <c r="J217" s="7"/>
       <c r="L217" s="7"/>
     </row>
-    <row r="218" spans="4:12" ht="12.5">
+    <row r="218" spans="4:12">
       <c r="D218" s="7"/>
       <c r="G218" s="8"/>
       <c r="H218" s="8"/>
@@ -31142,7 +31138,7 @@
       <c r="J218" s="7"/>
       <c r="L218" s="7"/>
     </row>
-    <row r="219" spans="4:12" ht="12.5">
+    <row r="219" spans="4:12">
       <c r="D219" s="7"/>
       <c r="G219" s="8"/>
       <c r="H219" s="8"/>
@@ -31150,7 +31146,7 @@
       <c r="J219" s="7"/>
       <c r="L219" s="7"/>
     </row>
-    <row r="220" spans="4:12" ht="12.5">
+    <row r="220" spans="4:12">
       <c r="D220" s="7"/>
       <c r="G220" s="8"/>
       <c r="H220" s="8"/>
@@ -31158,7 +31154,7 @@
       <c r="J220" s="7"/>
       <c r="L220" s="7"/>
     </row>
-    <row r="221" spans="4:12" ht="12.5">
+    <row r="221" spans="4:12">
       <c r="D221" s="7"/>
       <c r="G221" s="8"/>
       <c r="H221" s="8"/>
@@ -31166,7 +31162,7 @@
       <c r="J221" s="7"/>
       <c r="L221" s="7"/>
     </row>
-    <row r="222" spans="4:12" ht="12.5">
+    <row r="222" spans="4:12">
       <c r="D222" s="7"/>
       <c r="G222" s="8"/>
       <c r="H222" s="8"/>
@@ -31174,7 +31170,7 @@
       <c r="J222" s="7"/>
       <c r="L222" s="7"/>
     </row>
-    <row r="223" spans="4:12" ht="12.5">
+    <row r="223" spans="4:12">
       <c r="D223" s="7"/>
       <c r="G223" s="8"/>
       <c r="H223" s="8"/>
@@ -31182,7 +31178,7 @@
       <c r="J223" s="7"/>
       <c r="L223" s="7"/>
     </row>
-    <row r="224" spans="4:12" ht="12.5">
+    <row r="224" spans="4:12">
       <c r="D224" s="7"/>
       <c r="G224" s="8"/>
       <c r="H224" s="8"/>
@@ -31190,7 +31186,7 @@
       <c r="J224" s="7"/>
       <c r="L224" s="7"/>
     </row>
-    <row r="225" spans="4:12" ht="12.5">
+    <row r="225" spans="4:12">
       <c r="D225" s="7"/>
       <c r="G225" s="8"/>
       <c r="H225" s="8"/>
@@ -31198,7 +31194,7 @@
       <c r="J225" s="7"/>
       <c r="L225" s="7"/>
     </row>
-    <row r="226" spans="4:12" ht="12.5">
+    <row r="226" spans="4:12">
       <c r="D226" s="7"/>
       <c r="G226" s="8"/>
       <c r="H226" s="8"/>
@@ -31206,7 +31202,7 @@
       <c r="J226" s="7"/>
       <c r="L226" s="7"/>
     </row>
-    <row r="227" spans="4:12" ht="12.5">
+    <row r="227" spans="4:12">
       <c r="D227" s="7"/>
       <c r="G227" s="8"/>
       <c r="H227" s="8"/>
@@ -31214,7 +31210,7 @@
       <c r="J227" s="7"/>
       <c r="L227" s="7"/>
     </row>
-    <row r="228" spans="4:12" ht="12.5">
+    <row r="228" spans="4:12">
       <c r="D228" s="7"/>
       <c r="G228" s="8"/>
       <c r="H228" s="8"/>
@@ -31222,7 +31218,7 @@
       <c r="J228" s="7"/>
       <c r="L228" s="7"/>
     </row>
-    <row r="229" spans="4:12" ht="12.5">
+    <row r="229" spans="4:12">
       <c r="D229" s="7"/>
       <c r="G229" s="8"/>
       <c r="H229" s="8"/>
@@ -31230,7 +31226,7 @@
       <c r="J229" s="7"/>
       <c r="L229" s="7"/>
     </row>
-    <row r="230" spans="4:12" ht="12.5">
+    <row r="230" spans="4:12">
       <c r="D230" s="7"/>
       <c r="G230" s="8"/>
       <c r="H230" s="8"/>
@@ -31238,7 +31234,7 @@
       <c r="J230" s="7"/>
       <c r="L230" s="7"/>
     </row>
-    <row r="231" spans="4:12" ht="12.5">
+    <row r="231" spans="4:12">
       <c r="D231" s="7"/>
       <c r="G231" s="8"/>
       <c r="H231" s="8"/>
@@ -31246,7 +31242,7 @@
       <c r="J231" s="7"/>
       <c r="L231" s="7"/>
     </row>
-    <row r="232" spans="4:12" ht="12.5">
+    <row r="232" spans="4:12">
       <c r="D232" s="7"/>
       <c r="G232" s="8"/>
       <c r="H232" s="8"/>
@@ -31254,7 +31250,7 @@
       <c r="J232" s="7"/>
       <c r="L232" s="7"/>
     </row>
-    <row r="233" spans="4:12" ht="12.5">
+    <row r="233" spans="4:12">
       <c r="D233" s="7"/>
       <c r="G233" s="8"/>
       <c r="H233" s="8"/>
@@ -31262,7 +31258,7 @@
       <c r="J233" s="7"/>
       <c r="L233" s="7"/>
     </row>
-    <row r="234" spans="4:12" ht="12.5">
+    <row r="234" spans="4:12">
       <c r="D234" s="7"/>
       <c r="G234" s="8"/>
       <c r="H234" s="8"/>
@@ -31270,7 +31266,7 @@
       <c r="J234" s="7"/>
       <c r="L234" s="7"/>
     </row>
-    <row r="235" spans="4:12" ht="12.5">
+    <row r="235" spans="4:12">
       <c r="D235" s="7"/>
       <c r="G235" s="8"/>
       <c r="H235" s="8"/>
@@ -31278,7 +31274,7 @@
       <c r="J235" s="7"/>
       <c r="L235" s="7"/>
     </row>
-    <row r="236" spans="4:12" ht="12.5">
+    <row r="236" spans="4:12">
       <c r="D236" s="7"/>
       <c r="G236" s="8"/>
       <c r="H236" s="8"/>
@@ -31286,7 +31282,7 @@
       <c r="J236" s="7"/>
       <c r="L236" s="7"/>
     </row>
-    <row r="237" spans="4:12" ht="12.5">
+    <row r="237" spans="4:12">
       <c r="D237" s="7"/>
       <c r="G237" s="8"/>
       <c r="H237" s="8"/>
@@ -31294,7 +31290,7 @@
       <c r="J237" s="7"/>
       <c r="L237" s="7"/>
     </row>
-    <row r="238" spans="4:12" ht="12.5">
+    <row r="238" spans="4:12">
       <c r="D238" s="7"/>
       <c r="G238" s="8"/>
       <c r="H238" s="8"/>
@@ -31302,7 +31298,7 @@
       <c r="J238" s="7"/>
       <c r="L238" s="7"/>
     </row>
-    <row r="239" spans="4:12" ht="12.5">
+    <row r="239" spans="4:12">
       <c r="D239" s="7"/>
       <c r="G239" s="8"/>
       <c r="H239" s="8"/>
@@ -31310,7 +31306,7 @@
       <c r="J239" s="7"/>
       <c r="L239" s="7"/>
     </row>
-    <row r="240" spans="4:12" ht="12.5">
+    <row r="240" spans="4:12">
       <c r="D240" s="7"/>
       <c r="G240" s="8"/>
       <c r="H240" s="8"/>
@@ -31318,7 +31314,7 @@
       <c r="J240" s="7"/>
       <c r="L240" s="7"/>
     </row>
-    <row r="241" spans="4:12" ht="12.5">
+    <row r="241" spans="4:12">
       <c r="D241" s="7"/>
       <c r="G241" s="8"/>
       <c r="H241" s="8"/>
@@ -31326,7 +31322,7 @@
       <c r="J241" s="7"/>
       <c r="L241" s="7"/>
     </row>
-    <row r="242" spans="4:12" ht="12.5">
+    <row r="242" spans="4:12">
       <c r="D242" s="7"/>
       <c r="G242" s="8"/>
       <c r="H242" s="8"/>
@@ -31334,7 +31330,7 @@
       <c r="J242" s="7"/>
       <c r="L242" s="7"/>
     </row>
-    <row r="243" spans="4:12" ht="12.5">
+    <row r="243" spans="4:12">
       <c r="D243" s="7"/>
       <c r="G243" s="8"/>
       <c r="H243" s="8"/>
@@ -31342,7 +31338,7 @@
       <c r="J243" s="7"/>
       <c r="L243" s="7"/>
     </row>
-    <row r="244" spans="4:12" ht="12.5">
+    <row r="244" spans="4:12">
       <c r="D244" s="7"/>
       <c r="G244" s="8"/>
       <c r="H244" s="8"/>
@@ -31350,7 +31346,7 @@
       <c r="J244" s="7"/>
       <c r="L244" s="7"/>
     </row>
-    <row r="245" spans="4:12" ht="12.5">
+    <row r="245" spans="4:12">
       <c r="D245" s="7"/>
       <c r="G245" s="8"/>
       <c r="H245" s="8"/>
@@ -31358,7 +31354,7 @@
       <c r="J245" s="7"/>
       <c r="L245" s="7"/>
     </row>
-    <row r="246" spans="4:12" ht="12.5">
+    <row r="246" spans="4:12">
       <c r="D246" s="7"/>
       <c r="G246" s="8"/>
       <c r="H246" s="8"/>
@@ -31366,7 +31362,7 @@
       <c r="J246" s="7"/>
       <c r="L246" s="7"/>
     </row>
-    <row r="247" spans="4:12" ht="12.5">
+    <row r="247" spans="4:12">
       <c r="D247" s="7"/>
       <c r="G247" s="8"/>
       <c r="H247" s="8"/>
@@ -31374,7 +31370,7 @@
       <c r="J247" s="7"/>
       <c r="L247" s="7"/>
     </row>
-    <row r="248" spans="4:12" ht="12.5">
+    <row r="248" spans="4:12">
       <c r="D248" s="7"/>
       <c r="G248" s="8"/>
       <c r="H248" s="8"/>
@@ -31382,7 +31378,7 @@
       <c r="J248" s="7"/>
       <c r="L248" s="7"/>
     </row>
-    <row r="249" spans="4:12" ht="12.5">
+    <row r="249" spans="4:12">
       <c r="D249" s="7"/>
       <c r="G249" s="8"/>
       <c r="H249" s="8"/>
@@ -31390,7 +31386,7 @@
       <c r="J249" s="7"/>
       <c r="L249" s="7"/>
     </row>
-    <row r="250" spans="4:12" ht="12.5">
+    <row r="250" spans="4:12">
       <c r="D250" s="7"/>
       <c r="G250" s="8"/>
       <c r="H250" s="8"/>
@@ -31398,7 +31394,7 @@
       <c r="J250" s="7"/>
       <c r="L250" s="7"/>
     </row>
-    <row r="251" spans="4:12" ht="12.5">
+    <row r="251" spans="4:12">
       <c r="D251" s="7"/>
       <c r="G251" s="8"/>
       <c r="H251" s="8"/>
@@ -31406,7 +31402,7 @@
       <c r="J251" s="7"/>
       <c r="L251" s="7"/>
     </row>
-    <row r="252" spans="4:12" ht="12.5">
+    <row r="252" spans="4:12">
       <c r="D252" s="7"/>
       <c r="G252" s="8"/>
       <c r="H252" s="8"/>
@@ -31414,7 +31410,7 @@
       <c r="J252" s="7"/>
       <c r="L252" s="7"/>
     </row>
-    <row r="253" spans="4:12" ht="12.5">
+    <row r="253" spans="4:12">
       <c r="D253" s="7"/>
       <c r="G253" s="8"/>
       <c r="H253" s="8"/>
@@ -31422,7 +31418,7 @@
       <c r="J253" s="7"/>
       <c r="L253" s="7"/>
     </row>
-    <row r="254" spans="4:12" ht="12.5">
+    <row r="254" spans="4:12">
       <c r="D254" s="7"/>
       <c r="G254" s="8"/>
       <c r="H254" s="8"/>
@@ -31430,7 +31426,7 @@
       <c r="J254" s="7"/>
       <c r="L254" s="7"/>
     </row>
-    <row r="255" spans="4:12" ht="12.5">
+    <row r="255" spans="4:12">
       <c r="D255" s="7"/>
       <c r="G255" s="8"/>
       <c r="H255" s="8"/>
@@ -31438,7 +31434,7 @@
       <c r="J255" s="7"/>
       <c r="L255" s="7"/>
     </row>
-    <row r="256" spans="4:12" ht="12.5">
+    <row r="256" spans="4:12">
       <c r="D256" s="7"/>
       <c r="G256" s="8"/>
       <c r="H256" s="8"/>
@@ -31446,7 +31442,7 @@
       <c r="J256" s="7"/>
       <c r="L256" s="7"/>
     </row>
-    <row r="257" spans="4:12" ht="12.5">
+    <row r="257" spans="4:12">
       <c r="D257" s="7"/>
       <c r="G257" s="8"/>
       <c r="H257" s="8"/>
@@ -31454,7 +31450,7 @@
       <c r="J257" s="7"/>
       <c r="L257" s="7"/>
     </row>
-    <row r="258" spans="4:12" ht="12.5">
+    <row r="258" spans="4:12">
       <c r="D258" s="7"/>
       <c r="G258" s="8"/>
       <c r="H258" s="8"/>
@@ -31462,7 +31458,7 @@
       <c r="J258" s="7"/>
       <c r="L258" s="7"/>
     </row>
-    <row r="259" spans="4:12" ht="12.5">
+    <row r="259" spans="4:12">
       <c r="D259" s="7"/>
       <c r="G259" s="8"/>
       <c r="H259" s="8"/>
@@ -31470,7 +31466,7 @@
       <c r="J259" s="7"/>
       <c r="L259" s="7"/>
     </row>
-    <row r="260" spans="4:12" ht="12.5">
+    <row r="260" spans="4:12">
       <c r="D260" s="7"/>
       <c r="G260" s="8"/>
       <c r="H260" s="8"/>
@@ -31478,7 +31474,7 @@
       <c r="J260" s="7"/>
       <c r="L260" s="7"/>
     </row>
-    <row r="261" spans="4:12" ht="12.5">
+    <row r="261" spans="4:12">
       <c r="D261" s="7"/>
       <c r="G261" s="8"/>
       <c r="H261" s="8"/>
@@ -31486,7 +31482,7 @@
       <c r="J261" s="7"/>
       <c r="L261" s="7"/>
     </row>
-    <row r="262" spans="4:12" ht="12.5">
+    <row r="262" spans="4:12">
       <c r="D262" s="7"/>
       <c r="G262" s="8"/>
       <c r="H262" s="8"/>
@@ -31494,7 +31490,7 @@
       <c r="J262" s="7"/>
       <c r="L262" s="7"/>
     </row>
-    <row r="263" spans="4:12" ht="12.5">
+    <row r="263" spans="4:12">
       <c r="D263" s="7"/>
       <c r="G263" s="8"/>
       <c r="H263" s="8"/>
@@ -31502,7 +31498,7 @@
       <c r="J263" s="7"/>
       <c r="L263" s="7"/>
     </row>
-    <row r="264" spans="4:12" ht="12.5">
+    <row r="264" spans="4:12">
       <c r="D264" s="7"/>
       <c r="G264" s="8"/>
       <c r="H264" s="8"/>
@@ -31510,7 +31506,7 @@
       <c r="J264" s="7"/>
       <c r="L264" s="7"/>
     </row>
-    <row r="265" spans="4:12" ht="12.5">
+    <row r="265" spans="4:12">
       <c r="D265" s="7"/>
       <c r="G265" s="8"/>
       <c r="H265" s="8"/>
@@ -31518,7 +31514,7 @@
       <c r="J265" s="7"/>
       <c r="L265" s="7"/>
     </row>
-    <row r="266" spans="4:12" ht="12.5">
+    <row r="266" spans="4:12">
       <c r="D266" s="7"/>
       <c r="G266" s="8"/>
       <c r="H266" s="8"/>
@@ -31526,7 +31522,7 @@
       <c r="J266" s="7"/>
       <c r="L266" s="7"/>
     </row>
-    <row r="267" spans="4:12" ht="12.5">
+    <row r="267" spans="4:12">
       <c r="D267" s="7"/>
       <c r="G267" s="8"/>
       <c r="H267" s="8"/>
@@ -31534,7 +31530,7 @@
       <c r="J267" s="7"/>
       <c r="L267" s="7"/>
     </row>
-    <row r="268" spans="4:12" ht="12.5">
+    <row r="268" spans="4:12">
       <c r="D268" s="7"/>
       <c r="G268" s="8"/>
       <c r="H268" s="8"/>
@@ -31542,7 +31538,7 @@
       <c r="J268" s="7"/>
       <c r="L268" s="7"/>
     </row>
-    <row r="269" spans="4:12" ht="12.5">
+    <row r="269" spans="4:12">
       <c r="D269" s="7"/>
       <c r="G269" s="8"/>
       <c r="H269" s="8"/>
@@ -31550,7 +31546,7 @@
       <c r="J269" s="7"/>
       <c r="L269" s="7"/>
     </row>
-    <row r="270" spans="4:12" ht="12.5">
+    <row r="270" spans="4:12">
       <c r="D270" s="7"/>
       <c r="G270" s="8"/>
       <c r="H270" s="8"/>
@@ -31558,7 +31554,7 @@
       <c r="J270" s="7"/>
       <c r="L270" s="7"/>
     </row>
-    <row r="271" spans="4:12" ht="12.5">
+    <row r="271" spans="4:12">
       <c r="D271" s="7"/>
       <c r="G271" s="8"/>
       <c r="H271" s="8"/>
@@ -31566,7 +31562,7 @@
       <c r="J271" s="7"/>
       <c r="L271" s="7"/>
     </row>
-    <row r="272" spans="4:12" ht="12.5">
+    <row r="272" spans="4:12">
       <c r="D272" s="7"/>
       <c r="G272" s="8"/>
       <c r="H272" s="8"/>
@@ -31574,7 +31570,7 @@
       <c r="J272" s="7"/>
       <c r="L272" s="7"/>
     </row>
-    <row r="273" spans="4:12" ht="12.5">
+    <row r="273" spans="4:12">
       <c r="D273" s="7"/>
       <c r="G273" s="8"/>
       <c r="H273" s="8"/>
@@ -31582,7 +31578,7 @@
       <c r="J273" s="7"/>
       <c r="L273" s="7"/>
     </row>
-    <row r="274" spans="4:12" ht="12.5">
+    <row r="274" spans="4:12">
       <c r="D274" s="7"/>
       <c r="G274" s="8"/>
       <c r="H274" s="8"/>
@@ -31590,7 +31586,7 @@
       <c r="J274" s="7"/>
       <c r="L274" s="7"/>
     </row>
-    <row r="275" spans="4:12" ht="12.5">
+    <row r="275" spans="4:12">
       <c r="D275" s="7"/>
       <c r="G275" s="8"/>
       <c r="H275" s="8"/>
@@ -31598,7 +31594,7 @@
       <c r="J275" s="7"/>
       <c r="L275" s="7"/>
     </row>
-    <row r="276" spans="4:12" ht="12.5">
+    <row r="276" spans="4:12">
       <c r="D276" s="7"/>
       <c r="G276" s="8"/>
       <c r="H276" s="8"/>
@@ -31606,7 +31602,7 @@
       <c r="J276" s="7"/>
       <c r="L276" s="7"/>
     </row>
-    <row r="277" spans="4:12" ht="12.5">
+    <row r="277" spans="4:12">
       <c r="D277" s="7"/>
       <c r="G277" s="8"/>
       <c r="H277" s="8"/>
@@ -31614,7 +31610,7 @@
       <c r="J277" s="7"/>
       <c r="L277" s="7"/>
     </row>
-    <row r="278" spans="4:12" ht="12.5">
+    <row r="278" spans="4:12">
       <c r="D278" s="7"/>
       <c r="G278" s="8"/>
       <c r="H278" s="8"/>
@@ -31622,7 +31618,7 @@
       <c r="J278" s="7"/>
       <c r="L278" s="7"/>
     </row>
-    <row r="279" spans="4:12" ht="12.5">
+    <row r="279" spans="4:12">
       <c r="D279" s="7"/>
       <c r="G279" s="8"/>
       <c r="H279" s="8"/>
@@ -31630,7 +31626,7 @@
       <c r="J279" s="7"/>
       <c r="L279" s="7"/>
     </row>
-    <row r="280" spans="4:12" ht="12.5">
+    <row r="280" spans="4:12">
       <c r="D280" s="7"/>
       <c r="G280" s="8"/>
       <c r="H280" s="8"/>
@@ -31638,7 +31634,7 @@
       <c r="J280" s="7"/>
       <c r="L280" s="7"/>
     </row>
-    <row r="281" spans="4:12" ht="12.5">
+    <row r="281" spans="4:12">
       <c r="D281" s="7"/>
       <c r="G281" s="8"/>
       <c r="H281" s="8"/>
@@ -31646,7 +31642,7 @@
       <c r="J281" s="7"/>
       <c r="L281" s="7"/>
     </row>
-    <row r="282" spans="4:12" ht="12.5">
+    <row r="282" spans="4:12">
       <c r="D282" s="7"/>
       <c r="G282" s="8"/>
       <c r="H282" s="8"/>
@@ -31654,7 +31650,7 @@
       <c r="J282" s="7"/>
       <c r="L282" s="7"/>
     </row>
-    <row r="283" spans="4:12" ht="12.5">
+    <row r="283" spans="4:12">
       <c r="D283" s="7"/>
       <c r="G283" s="8"/>
       <c r="H283" s="8"/>
@@ -31662,7 +31658,7 @@
       <c r="J283" s="7"/>
       <c r="L283" s="7"/>
     </row>
-    <row r="284" spans="4:12" ht="12.5">
+    <row r="284" spans="4:12">
       <c r="D284" s="7"/>
       <c r="G284" s="8"/>
       <c r="H284" s="8"/>
@@ -31670,7 +31666,7 @@
       <c r="J284" s="7"/>
       <c r="L284" s="7"/>
     </row>
-    <row r="285" spans="4:12" ht="12.5">
+    <row r="285" spans="4:12">
       <c r="D285" s="7"/>
       <c r="G285" s="8"/>
       <c r="H285" s="8"/>
@@ -31678,7 +31674,7 @@
       <c r="J285" s="7"/>
       <c r="L285" s="7"/>
     </row>
-    <row r="286" spans="4:12" ht="12.5">
+    <row r="286" spans="4:12">
       <c r="D286" s="7"/>
       <c r="G286" s="8"/>
       <c r="H286" s="8"/>
@@ -31686,7 +31682,7 @@
       <c r="J286" s="7"/>
       <c r="L286" s="7"/>
     </row>
-    <row r="287" spans="4:12" ht="12.5">
+    <row r="287" spans="4:12">
       <c r="D287" s="7"/>
       <c r="G287" s="8"/>
       <c r="H287" s="8"/>
@@ -31694,7 +31690,7 @@
       <c r="J287" s="7"/>
       <c r="L287" s="7"/>
     </row>
-    <row r="288" spans="4:12" ht="12.5">
+    <row r="288" spans="4:12">
       <c r="D288" s="7"/>
       <c r="G288" s="8"/>
       <c r="H288" s="8"/>
@@ -31702,7 +31698,7 @@
       <c r="J288" s="7"/>
       <c r="L288" s="7"/>
     </row>
-    <row r="289" spans="4:12" ht="12.5">
+    <row r="289" spans="4:12">
       <c r="D289" s="7"/>
       <c r="G289" s="8"/>
       <c r="H289" s="8"/>
@@ -31710,7 +31706,7 @@
       <c r="J289" s="7"/>
       <c r="L289" s="7"/>
     </row>
-    <row r="290" spans="4:12" ht="12.5">
+    <row r="290" spans="4:12">
       <c r="D290" s="7"/>
       <c r="G290" s="8"/>
       <c r="H290" s="8"/>
@@ -31718,7 +31714,7 @@
       <c r="J290" s="7"/>
       <c r="L290" s="7"/>
     </row>
-    <row r="291" spans="4:12" ht="12.5">
+    <row r="291" spans="4:12">
       <c r="D291" s="7"/>
       <c r="G291" s="8"/>
       <c r="H291" s="8"/>
@@ -31726,7 +31722,7 @@
       <c r="J291" s="7"/>
       <c r="L291" s="7"/>
     </row>
-    <row r="292" spans="4:12" ht="12.5">
+    <row r="292" spans="4:12">
       <c r="D292" s="7"/>
       <c r="G292" s="8"/>
       <c r="H292" s="8"/>
@@ -31734,7 +31730,7 @@
       <c r="J292" s="7"/>
       <c r="L292" s="7"/>
     </row>
-    <row r="293" spans="4:12" ht="12.5">
+    <row r="293" spans="4:12">
       <c r="D293" s="7"/>
       <c r="G293" s="8"/>
       <c r="H293" s="8"/>
@@ -31742,7 +31738,7 @@
       <c r="J293" s="7"/>
       <c r="L293" s="7"/>
     </row>
-    <row r="294" spans="4:12" ht="12.5">
+    <row r="294" spans="4:12">
       <c r="D294" s="7"/>
       <c r="G294" s="8"/>
       <c r="H294" s="8"/>
@@ -31750,7 +31746,7 @@
       <c r="J294" s="7"/>
       <c r="L294" s="7"/>
     </row>
-    <row r="295" spans="4:12" ht="12.5">
+    <row r="295" spans="4:12">
       <c r="D295" s="7"/>
       <c r="G295" s="8"/>
       <c r="H295" s="8"/>
@@ -31758,7 +31754,7 @@
       <c r="J295" s="7"/>
       <c r="L295" s="7"/>
     </row>
-    <row r="296" spans="4:12" ht="12.5">
+    <row r="296" spans="4:12">
       <c r="D296" s="7"/>
       <c r="G296" s="8"/>
       <c r="H296" s="8"/>
@@ -31766,7 +31762,7 @@
       <c r="J296" s="7"/>
       <c r="L296" s="7"/>
     </row>
-    <row r="297" spans="4:12" ht="12.5">
+    <row r="297" spans="4:12">
       <c r="D297" s="7"/>
       <c r="G297" s="8"/>
       <c r="H297" s="8"/>
@@ -31774,7 +31770,7 @@
       <c r="J297" s="7"/>
       <c r="L297" s="7"/>
     </row>
-    <row r="298" spans="4:12" ht="12.5">
+    <row r="298" spans="4:12">
       <c r="D298" s="7"/>
       <c r="G298" s="8"/>
       <c r="H298" s="8"/>
@@ -31782,7 +31778,7 @@
       <c r="J298" s="7"/>
       <c r="L298" s="7"/>
     </row>
-    <row r="299" spans="4:12" ht="12.5">
+    <row r="299" spans="4:12">
       <c r="D299" s="7"/>
       <c r="G299" s="8"/>
       <c r="H299" s="8"/>
@@ -31790,7 +31786,7 @@
       <c r="J299" s="7"/>
       <c r="L299" s="7"/>
     </row>
-    <row r="300" spans="4:12" ht="12.5">
+    <row r="300" spans="4:12">
       <c r="D300" s="7"/>
       <c r="G300" s="8"/>
       <c r="H300" s="8"/>
@@ -31798,7 +31794,7 @@
       <c r="J300" s="7"/>
       <c r="L300" s="7"/>
     </row>
-    <row r="301" spans="4:12" ht="12.5">
+    <row r="301" spans="4:12">
       <c r="D301" s="7"/>
       <c r="G301" s="8"/>
       <c r="H301" s="8"/>
@@ -31806,7 +31802,7 @@
       <c r="J301" s="7"/>
       <c r="L301" s="7"/>
     </row>
-    <row r="302" spans="4:12" ht="12.5">
+    <row r="302" spans="4:12">
       <c r="D302" s="7"/>
       <c r="G302" s="8"/>
       <c r="H302" s="8"/>
@@ -31814,7 +31810,7 @@
       <c r="J302" s="7"/>
       <c r="L302" s="7"/>
     </row>
-    <row r="303" spans="4:12" ht="12.5">
+    <row r="303" spans="4:12">
       <c r="D303" s="7"/>
       <c r="G303" s="8"/>
       <c r="H303" s="8"/>
@@ -31822,7 +31818,7 @@
       <c r="J303" s="7"/>
       <c r="L303" s="7"/>
     </row>
-    <row r="304" spans="4:12" ht="12.5">
+    <row r="304" spans="4:12">
       <c r="D304" s="7"/>
       <c r="G304" s="8"/>
       <c r="H304" s="8"/>
@@ -31830,7 +31826,7 @@
       <c r="J304" s="7"/>
       <c r="L304" s="7"/>
     </row>
-    <row r="305" spans="4:12" ht="12.5">
+    <row r="305" spans="4:12">
       <c r="D305" s="7"/>
       <c r="G305" s="8"/>
       <c r="H305" s="8"/>
@@ -31838,7 +31834,7 @@
       <c r="J305" s="7"/>
       <c r="L305" s="7"/>
     </row>
-    <row r="306" spans="4:12" ht="12.5">
+    <row r="306" spans="4:12">
       <c r="D306" s="7"/>
       <c r="G306" s="8"/>
       <c r="H306" s="8"/>
@@ -31846,7 +31842,7 @@
       <c r="J306" s="7"/>
       <c r="L306" s="7"/>
     </row>
-    <row r="307" spans="4:12" ht="12.5">
+    <row r="307" spans="4:12">
       <c r="D307" s="7"/>
       <c r="G307" s="8"/>
       <c r="H307" s="8"/>
@@ -31854,7 +31850,7 @@
       <c r="J307" s="7"/>
       <c r="L307" s="7"/>
     </row>
-    <row r="308" spans="4:12" ht="12.5">
+    <row r="308" spans="4:12">
       <c r="D308" s="7"/>
       <c r="G308" s="8"/>
       <c r="H308" s="8"/>
@@ -31862,7 +31858,7 @@
       <c r="J308" s="7"/>
       <c r="L308" s="7"/>
     </row>
-    <row r="309" spans="4:12" ht="12.5">
+    <row r="309" spans="4:12">
       <c r="D309" s="7"/>
       <c r="G309" s="8"/>
       <c r="H309" s="8"/>
@@ -31870,7 +31866,7 @@
       <c r="J309" s="7"/>
       <c r="L309" s="7"/>
     </row>
-    <row r="310" spans="4:12" ht="12.5">
+    <row r="310" spans="4:12">
       <c r="D310" s="7"/>
       <c r="G310" s="8"/>
       <c r="H310" s="8"/>
@@ -31878,7 +31874,7 @@
       <c r="J310" s="7"/>
       <c r="L310" s="7"/>
     </row>
-    <row r="311" spans="4:12" ht="12.5">
+    <row r="311" spans="4:12">
       <c r="D311" s="7"/>
       <c r="G311" s="8"/>
       <c r="H311" s="8"/>
@@ -31886,7 +31882,7 @@
       <c r="J311" s="7"/>
       <c r="L311" s="7"/>
     </row>
-    <row r="312" spans="4:12" ht="12.5">
+    <row r="312" spans="4:12">
       <c r="D312" s="7"/>
       <c r="G312" s="8"/>
       <c r="H312" s="8"/>
@@ -31894,7 +31890,7 @@
       <c r="J312" s="7"/>
       <c r="L312" s="7"/>
     </row>
-    <row r="313" spans="4:12" ht="12.5">
+    <row r="313" spans="4:12">
       <c r="D313" s="7"/>
       <c r="G313" s="8"/>
       <c r="H313" s="8"/>
@@ -31902,7 +31898,7 @@
       <c r="J313" s="7"/>
       <c r="L313" s="7"/>
     </row>
-    <row r="314" spans="4:12" ht="12.5">
+    <row r="314" spans="4:12">
       <c r="D314" s="7"/>
       <c r="G314" s="8"/>
       <c r="H314" s="8"/>
@@ -31910,7 +31906,7 @@
       <c r="J314" s="7"/>
       <c r="L314" s="7"/>
     </row>
-    <row r="315" spans="4:12" ht="12.5">
+    <row r="315" spans="4:12">
       <c r="D315" s="7"/>
       <c r="G315" s="8"/>
       <c r="H315" s="8"/>
@@ -31918,7 +31914,7 @@
       <c r="J315" s="7"/>
       <c r="L315" s="7"/>
     </row>
-    <row r="316" spans="4:12" ht="12.5">
+    <row r="316" spans="4:12">
       <c r="D316" s="7"/>
       <c r="G316" s="8"/>
       <c r="H316" s="8"/>
@@ -31926,7 +31922,7 @@
       <c r="J316" s="7"/>
       <c r="L316" s="7"/>
     </row>
-    <row r="317" spans="4:12" ht="12.5">
+    <row r="317" spans="4:12">
       <c r="D317" s="7"/>
       <c r="G317" s="8"/>
       <c r="H317" s="8"/>
@@ -31934,7 +31930,7 @@
       <c r="J317" s="7"/>
       <c r="L317" s="7"/>
     </row>
-    <row r="318" spans="4:12" ht="12.5">
+    <row r="318" spans="4:12">
       <c r="D318" s="7"/>
       <c r="G318" s="8"/>
       <c r="H318" s="8"/>
@@ -31942,7 +31938,7 @@
       <c r="J318" s="7"/>
       <c r="L318" s="7"/>
     </row>
-    <row r="319" spans="4:12" ht="12.5">
+    <row r="319" spans="4:12">
       <c r="D319" s="7"/>
       <c r="G319" s="8"/>
       <c r="H319" s="8"/>
@@ -31950,7 +31946,7 @@
       <c r="J319" s="7"/>
       <c r="L319" s="7"/>
     </row>
-    <row r="320" spans="4:12" ht="12.5">
+    <row r="320" spans="4:12">
       <c r="D320" s="7"/>
       <c r="G320" s="8"/>
       <c r="H320" s="8"/>
@@ -31958,7 +31954,7 @@
       <c r="J320" s="7"/>
       <c r="L320" s="7"/>
     </row>
-    <row r="321" spans="4:12" ht="12.5">
+    <row r="321" spans="4:12">
       <c r="D321" s="7"/>
       <c r="G321" s="8"/>
       <c r="H321" s="8"/>
@@ -31966,7 +31962,7 @@
       <c r="J321" s="7"/>
       <c r="L321" s="7"/>
     </row>
-    <row r="322" spans="4:12" ht="12.5">
+    <row r="322" spans="4:12">
       <c r="D322" s="7"/>
       <c r="G322" s="8"/>
       <c r="H322" s="8"/>
@@ -31974,7 +31970,7 @@
       <c r="J322" s="7"/>
       <c r="L322" s="7"/>
     </row>
-    <row r="323" spans="4:12" ht="12.5">
+    <row r="323" spans="4:12">
       <c r="D323" s="7"/>
       <c r="G323" s="8"/>
       <c r="H323" s="8"/>
@@ -31982,7 +31978,7 @@
       <c r="J323" s="7"/>
       <c r="L323" s="7"/>
     </row>
-    <row r="324" spans="4:12" ht="12.5">
+    <row r="324" spans="4:12">
       <c r="D324" s="7"/>
       <c r="G324" s="8"/>
       <c r="H324" s="8"/>
@@ -31990,7 +31986,7 @@
       <c r="J324" s="7"/>
       <c r="L324" s="7"/>
     </row>
-    <row r="325" spans="4:12" ht="12.5">
+    <row r="325" spans="4:12">
       <c r="D325" s="7"/>
       <c r="G325" s="8"/>
       <c r="H325" s="8"/>
@@ -31998,7 +31994,7 @@
       <c r="J325" s="7"/>
       <c r="L325" s="7"/>
     </row>
-    <row r="326" spans="4:12" ht="12.5">
+    <row r="326" spans="4:12">
       <c r="D326" s="7"/>
       <c r="G326" s="8"/>
       <c r="H326" s="8"/>
@@ -32006,7 +32002,7 @@
       <c r="J326" s="7"/>
       <c r="L326" s="7"/>
     </row>
-    <row r="327" spans="4:12" ht="12.5">
+    <row r="327" spans="4:12">
       <c r="D327" s="7"/>
       <c r="G327" s="8"/>
       <c r="H327" s="8"/>
@@ -32014,7 +32010,7 @@
       <c r="J327" s="7"/>
       <c r="L327" s="7"/>
     </row>
-    <row r="328" spans="4:12" ht="12.5">
+    <row r="328" spans="4:12">
       <c r="D328" s="7"/>
       <c r="G328" s="8"/>
       <c r="H328" s="8"/>
@@ -32022,7 +32018,7 @@
       <c r="J328" s="7"/>
       <c r="L328" s="7"/>
     </row>
-    <row r="329" spans="4:12" ht="12.5">
+    <row r="329" spans="4:12">
       <c r="D329" s="7"/>
       <c r="G329" s="8"/>
       <c r="H329" s="8"/>
@@ -32030,7 +32026,7 @@
       <c r="J329" s="7"/>
       <c r="L329" s="7"/>
     </row>
-    <row r="330" spans="4:12" ht="12.5">
+    <row r="330" spans="4:12">
       <c r="D330" s="7"/>
       <c r="G330" s="8"/>
       <c r="H330" s="8"/>
@@ -32038,7 +32034,7 @@
       <c r="J330" s="7"/>
       <c r="L330" s="7"/>
     </row>
-    <row r="331" spans="4:12" ht="12.5">
+    <row r="331" spans="4:12">
       <c r="D331" s="7"/>
       <c r="G331" s="8"/>
       <c r="H331" s="8"/>
@@ -32046,7 +32042,7 @@
       <c r="J331" s="7"/>
       <c r="L331" s="7"/>
     </row>
-    <row r="332" spans="4:12" ht="12.5">
+    <row r="332" spans="4:12">
       <c r="D332" s="7"/>
       <c r="G332" s="8"/>
       <c r="H332" s="8"/>
@@ -32054,7 +32050,7 @@
       <c r="J332" s="7"/>
       <c r="L332" s="7"/>
     </row>
-    <row r="333" spans="4:12" ht="12.5">
+    <row r="333" spans="4:12">
       <c r="D333" s="7"/>
       <c r="G333" s="8"/>
       <c r="H333" s="8"/>
@@ -32062,7 +32058,7 @@
       <c r="J333" s="7"/>
       <c r="L333" s="7"/>
     </row>
-    <row r="334" spans="4:12" ht="12.5">
+    <row r="334" spans="4:12">
       <c r="D334" s="7"/>
       <c r="G334" s="8"/>
       <c r="H334" s="8"/>
@@ -32070,7 +32066,7 @@
       <c r="J334" s="7"/>
       <c r="L334" s="7"/>
     </row>
-    <row r="335" spans="4:12" ht="12.5">
+    <row r="335" spans="4:12">
       <c r="D335" s="7"/>
       <c r="G335" s="8"/>
       <c r="H335" s="8"/>
@@ -32078,7 +32074,7 @@
       <c r="J335" s="7"/>
       <c r="L335" s="7"/>
     </row>
-    <row r="336" spans="4:12" ht="12.5">
+    <row r="336" spans="4:12">
       <c r="D336" s="7"/>
       <c r="G336" s="8"/>
       <c r="H336" s="8"/>
@@ -32086,7 +32082,7 @@
       <c r="J336" s="7"/>
       <c r="L336" s="7"/>
     </row>
-    <row r="337" spans="4:12" ht="12.5">
+    <row r="337" spans="4:12">
       <c r="D337" s="7"/>
       <c r="G337" s="8"/>
       <c r="H337" s="8"/>
@@ -32094,7 +32090,7 @@
       <c r="J337" s="7"/>
       <c r="L337" s="7"/>
     </row>
-    <row r="338" spans="4:12" ht="12.5">
+    <row r="338" spans="4:12">
       <c r="D338" s="7"/>
       <c r="G338" s="8"/>
       <c r="H338" s="8"/>
@@ -32102,7 +32098,7 @@
       <c r="J338" s="7"/>
       <c r="L338" s="7"/>
     </row>
-    <row r="339" spans="4:12" ht="12.5">
+    <row r="339" spans="4:12">
       <c r="D339" s="7"/>
       <c r="G339" s="8"/>
       <c r="H339" s="8"/>
@@ -32110,7 +32106,7 @@
       <c r="J339" s="7"/>
       <c r="L339" s="7"/>
     </row>
-    <row r="340" spans="4:12" ht="12.5">
+    <row r="340" spans="4:12">
       <c r="D340" s="7"/>
       <c r="G340" s="8"/>
       <c r="H340" s="8"/>
@@ -32118,7 +32114,7 @@
       <c r="J340" s="7"/>
       <c r="L340" s="7"/>
     </row>
-    <row r="341" spans="4:12" ht="12.5">
+    <row r="341" spans="4:12">
       <c r="D341" s="7"/>
       <c r="G341" s="8"/>
       <c r="H341" s="8"/>
@@ -32126,7 +32122,7 @@
       <c r="J341" s="7"/>
       <c r="L341" s="7"/>
     </row>
-    <row r="342" spans="4:12" ht="12.5">
+    <row r="342" spans="4:12">
       <c r="D342" s="7"/>
       <c r="G342" s="8"/>
       <c r="H342" s="8"/>
@@ -32134,7 +32130,7 @@
       <c r="J342" s="7"/>
       <c r="L342" s="7"/>
     </row>
-    <row r="343" spans="4:12" ht="12.5">
+    <row r="343" spans="4:12">
       <c r="D343" s="7"/>
       <c r="G343" s="8"/>
       <c r="H343" s="8"/>
@@ -32142,7 +32138,7 @@
       <c r="J343" s="7"/>
       <c r="L343" s="7"/>
     </row>
-    <row r="344" spans="4:12" ht="12.5">
+    <row r="344" spans="4:12">
       <c r="D344" s="7"/>
       <c r="G344" s="8"/>
       <c r="H344" s="8"/>
@@ -32150,7 +32146,7 @@
       <c r="J344" s="7"/>
       <c r="L344" s="7"/>
     </row>
-    <row r="345" spans="4:12" ht="12.5">
+    <row r="345" spans="4:12">
       <c r="D345" s="7"/>
       <c r="G345" s="8"/>
       <c r="H345" s="8"/>
@@ -32158,7 +32154,7 @@
       <c r="J345" s="7"/>
       <c r="L345" s="7"/>
     </row>
-    <row r="346" spans="4:12" ht="12.5">
+    <row r="346" spans="4:12">
       <c r="D346" s="7"/>
       <c r="G346" s="8"/>
       <c r="H346" s="8"/>
@@ -32166,7 +32162,7 @@
       <c r="J346" s="7"/>
       <c r="L346" s="7"/>
     </row>
-    <row r="347" spans="4:12" ht="12.5">
+    <row r="347" spans="4:12">
       <c r="D347" s="7"/>
       <c r="G347" s="8"/>
       <c r="H347" s="8"/>
@@ -32174,7 +32170,7 @@
       <c r="J347" s="7"/>
       <c r="L347" s="7"/>
     </row>
-    <row r="348" spans="4:12" ht="12.5">
+    <row r="348" spans="4:12">
       <c r="D348" s="7"/>
       <c r="G348" s="8"/>
       <c r="H348" s="8"/>
@@ -32182,7 +32178,7 @@
       <c r="J348" s="7"/>
       <c r="L348" s="7"/>
     </row>
-    <row r="349" spans="4:12" ht="12.5">
+    <row r="349" spans="4:12">
       <c r="D349" s="7"/>
       <c r="G349" s="8"/>
       <c r="H349" s="8"/>
@@ -32190,7 +32186,7 @@
       <c r="J349" s="7"/>
       <c r="L349" s="7"/>
     </row>
-    <row r="350" spans="4:12" ht="12.5">
+    <row r="350" spans="4:12">
       <c r="D350" s="7"/>
       <c r="G350" s="8"/>
       <c r="H350" s="8"/>
@@ -32198,7 +32194,7 @@
       <c r="J350" s="7"/>
       <c r="L350" s="7"/>
     </row>
-    <row r="351" spans="4:12" ht="12.5">
+    <row r="351" spans="4:12">
       <c r="D351" s="7"/>
       <c r="G351" s="8"/>
       <c r="H351" s="8"/>
@@ -32206,7 +32202,7 @@
       <c r="J351" s="7"/>
       <c r="L351" s="7"/>
     </row>
-    <row r="352" spans="4:12" ht="12.5">
+    <row r="352" spans="4:12">
       <c r="D352" s="7"/>
       <c r="G352" s="8"/>
       <c r="H352" s="8"/>
@@ -32214,7 +32210,7 @@
       <c r="J352" s="7"/>
       <c r="L352" s="7"/>
     </row>
-    <row r="353" spans="4:12" ht="12.5">
+    <row r="353" spans="4:12">
       <c r="D353" s="7"/>
       <c r="G353" s="8"/>
       <c r="H353" s="8"/>
@@ -32222,7 +32218,7 @@
       <c r="J353" s="7"/>
       <c r="L353" s="7"/>
     </row>
-    <row r="354" spans="4:12" ht="12.5">
+    <row r="354" spans="4:12">
       <c r="D354" s="7"/>
       <c r="G354" s="8"/>
       <c r="H354" s="8"/>
@@ -32230,7 +32226,7 @@
       <c r="J354" s="7"/>
       <c r="L354" s="7"/>
     </row>
-    <row r="355" spans="4:12" ht="12.5">
+    <row r="355" spans="4:12">
       <c r="D355" s="7"/>
       <c r="G355" s="8"/>
       <c r="H355" s="8"/>
@@ -32238,7 +32234,7 @@
       <c r="J355" s="7"/>
       <c r="L355" s="7"/>
     </row>
-    <row r="356" spans="4:12" ht="12.5">
+    <row r="356" spans="4:12">
       <c r="D356" s="7"/>
       <c r="G356" s="8"/>
       <c r="H356" s="8"/>
@@ -32246,7 +32242,7 @@
       <c r="J356" s="7"/>
       <c r="L356" s="7"/>
     </row>
-    <row r="357" spans="4:12" ht="12.5">
+    <row r="357" spans="4:12">
       <c r="D357" s="7"/>
       <c r="G357" s="8"/>
       <c r="H357" s="8"/>
@@ -32254,7 +32250,7 @@
       <c r="J357" s="7"/>
       <c r="L357" s="7"/>
     </row>
-    <row r="358" spans="4:12" ht="12.5">
+    <row r="358" spans="4:12">
       <c r="D358" s="7"/>
       <c r="G358" s="8"/>
       <c r="H358" s="8"/>
@@ -32262,7 +32258,7 @@
       <c r="J358" s="7"/>
       <c r="L358" s="7"/>
     </row>
-    <row r="359" spans="4:12" ht="12.5">
+    <row r="359" spans="4:12">
       <c r="D359" s="7"/>
       <c r="G359" s="8"/>
       <c r="H359" s="8"/>
@@ -32270,7 +32266,7 @@
       <c r="J359" s="7"/>
       <c r="L359" s="7"/>
     </row>
-    <row r="360" spans="4:12" ht="12.5">
+    <row r="360" spans="4:12">
       <c r="D360" s="7"/>
       <c r="G360" s="8"/>
       <c r="H360" s="8"/>
@@ -32278,7 +32274,7 @@
       <c r="J360" s="7"/>
       <c r="L360" s="7"/>
     </row>
-    <row r="361" spans="4:12" ht="12.5">
+    <row r="361" spans="4:12">
       <c r="D361" s="7"/>
       <c r="G361" s="8"/>
       <c r="H361" s="8"/>
@@ -32286,7 +32282,7 @@
       <c r="J361" s="7"/>
       <c r="L361" s="7"/>
     </row>
-    <row r="362" spans="4:12" ht="12.5">
+    <row r="362" spans="4:12">
       <c r="D362" s="7"/>
       <c r="G362" s="8"/>
       <c r="H362" s="8"/>
@@ -32294,7 +32290,7 @@
       <c r="J362" s="7"/>
       <c r="L362" s="7"/>
     </row>
-    <row r="363" spans="4:12" ht="12.5">
+    <row r="363" spans="4:12">
       <c r="D363" s="7"/>
       <c r="G363" s="8"/>
       <c r="H363" s="8"/>
@@ -32302,7 +32298,7 @@
       <c r="J363" s="7"/>
       <c r="L363" s="7"/>
     </row>
-    <row r="364" spans="4:12" ht="12.5">
+    <row r="364" spans="4:12">
       <c r="D364" s="7"/>
       <c r="G364" s="8"/>
       <c r="H364" s="8"/>
@@ -32310,7 +32306,7 @@
       <c r="J364" s="7"/>
       <c r="L364" s="7"/>
     </row>
-    <row r="365" spans="4:12" ht="12.5">
+    <row r="365" spans="4:12">
       <c r="D365" s="7"/>
       <c r="G365" s="8"/>
       <c r="H365" s="8"/>
@@ -32318,7 +32314,7 @@
       <c r="J365" s="7"/>
       <c r="L365" s="7"/>
     </row>
-    <row r="366" spans="4:12" ht="12.5">
+    <row r="366" spans="4:12">
       <c r="D366" s="7"/>
       <c r="G366" s="8"/>
       <c r="H366" s="8"/>
@@ -32326,7 +32322,7 @@
       <c r="J366" s="7"/>
       <c r="L366" s="7"/>
     </row>
-    <row r="367" spans="4:12" ht="12.5">
+    <row r="367" spans="4:12">
       <c r="D367" s="7"/>
       <c r="G367" s="8"/>
       <c r="H367" s="8"/>
@@ -32334,7 +32330,7 @@
       <c r="J367" s="7"/>
       <c r="L367" s="7"/>
     </row>
-    <row r="368" spans="4:12" ht="12.5">
+    <row r="368" spans="4:12">
       <c r="D368" s="7"/>
       <c r="G368" s="8"/>
       <c r="H368" s="8"/>
@@ -32342,7 +32338,7 @@
       <c r="J368" s="7"/>
       <c r="L368" s="7"/>
     </row>
-    <row r="369" spans="4:12" ht="12.5">
+    <row r="369" spans="4:12">
       <c r="D369" s="7"/>
       <c r="G369" s="8"/>
       <c r="H369" s="8"/>
@@ -32350,7 +32346,7 @@
       <c r="J369" s="7"/>
       <c r="L369" s="7"/>
     </row>
-    <row r="370" spans="4:12" ht="12.5">
+    <row r="370" spans="4:12">
       <c r="D370" s="7"/>
       <c r="G370" s="8"/>
       <c r="H370" s="8"/>
@@ -32358,7 +32354,7 @@
       <c r="J370" s="7"/>
       <c r="L370" s="7"/>
     </row>
-    <row r="371" spans="4:12" ht="12.5">
+    <row r="371" spans="4:12">
       <c r="D371" s="7"/>
       <c r="G371" s="8"/>
       <c r="H371" s="8"/>
@@ -32366,7 +32362,7 @@
       <c r="J371" s="7"/>
       <c r="L371" s="7"/>
     </row>
-    <row r="372" spans="4:12" ht="12.5">
+    <row r="372" spans="4:12">
       <c r="D372" s="7"/>
       <c r="G372" s="8"/>
       <c r="H372" s="8"/>
@@ -32374,7 +32370,7 @@
       <c r="J372" s="7"/>
       <c r="L372" s="7"/>
     </row>
-    <row r="373" spans="4:12" ht="12.5">
+    <row r="373" spans="4:12">
       <c r="D373" s="7"/>
       <c r="G373" s="8"/>
       <c r="H373" s="8"/>
@@ -32382,7 +32378,7 @@
       <c r="J373" s="7"/>
       <c r="L373" s="7"/>
     </row>
-    <row r="374" spans="4:12" ht="12.5">
+    <row r="374" spans="4:12">
       <c r="D374" s="7"/>
       <c r="G374" s="8"/>
       <c r="H374" s="8"/>
@@ -32390,7 +32386,7 @@
       <c r="J374" s="7"/>
       <c r="L374" s="7"/>
     </row>
-    <row r="375" spans="4:12" ht="12.5">
+    <row r="375" spans="4:12">
       <c r="D375" s="7"/>
       <c r="G375" s="8"/>
       <c r="H375" s="8"/>
@@ -32398,7 +32394,7 @@
       <c r="J375" s="7"/>
       <c r="L375" s="7"/>
     </row>
-    <row r="376" spans="4:12" ht="12.5">
+    <row r="376" spans="4:12">
       <c r="D376" s="7"/>
       <c r="G376" s="8"/>
       <c r="H376" s="8"/>
@@ -32406,7 +32402,7 @@
       <c r="J376" s="7"/>
       <c r="L376" s="7"/>
     </row>
-    <row r="377" spans="4:12" ht="12.5">
+    <row r="377" spans="4:12">
       <c r="D377" s="7"/>
       <c r="G377" s="8"/>
       <c r="H377" s="8"/>
@@ -32414,7 +32410,7 @@
       <c r="J377" s="7"/>
       <c r="L377" s="7"/>
     </row>
-    <row r="378" spans="4:12" ht="12.5">
+    <row r="378" spans="4:12">
       <c r="D378" s="7"/>
       <c r="G378" s="8"/>
       <c r="H378" s="8"/>
@@ -32422,7 +32418,7 @@
       <c r="J378" s="7"/>
       <c r="L378" s="7"/>
     </row>
-    <row r="379" spans="4:12" ht="12.5">
+    <row r="379" spans="4:12">
       <c r="D379" s="7"/>
       <c r="G379" s="8"/>
       <c r="H379" s="8"/>
@@ -32430,7 +32426,7 @@
       <c r="J379" s="7"/>
       <c r="L379" s="7"/>
     </row>
-    <row r="380" spans="4:12" ht="12.5">
+    <row r="380" spans="4:12">
       <c r="D380" s="7"/>
       <c r="G380" s="8"/>
       <c r="H380" s="8"/>
@@ -32438,7 +32434,7 @@
       <c r="J380" s="7"/>
       <c r="L380" s="7"/>
     </row>
-    <row r="381" spans="4:12" ht="12.5">
+    <row r="381" spans="4:12">
       <c r="D381" s="7"/>
       <c r="G381" s="8"/>
       <c r="H381" s="8"/>
@@ -32446,7 +32442,7 @@
       <c r="J381" s="7"/>
       <c r="L381" s="7"/>
     </row>
-    <row r="382" spans="4:12" ht="12.5">
+    <row r="382" spans="4:12">
       <c r="D382" s="7"/>
       <c r="G382" s="8"/>
       <c r="H382" s="8"/>
@@ -32454,7 +32450,7 @@
       <c r="J382" s="7"/>
       <c r="L382" s="7"/>
     </row>
-    <row r="383" spans="4:12" ht="12.5">
+    <row r="383" spans="4:12">
       <c r="D383" s="7"/>
       <c r="G383" s="8"/>
       <c r="H383" s="8"/>
@@ -32462,7 +32458,7 @@
       <c r="J383" s="7"/>
       <c r="L383" s="7"/>
     </row>
-    <row r="384" spans="4:12" ht="12.5">
+    <row r="384" spans="4:12">
       <c r="D384" s="7"/>
       <c r="G384" s="8"/>
       <c r="H384" s="8"/>
@@ -32470,7 +32466,7 @@
       <c r="J384" s="7"/>
       <c r="L384" s="7"/>
     </row>
-    <row r="385" spans="4:12" ht="12.5">
+    <row r="385" spans="4:12">
       <c r="D385" s="7"/>
       <c r="G385" s="8"/>
       <c r="H385" s="8"/>
@@ -32478,7 +32474,7 @@
       <c r="J385" s="7"/>
       <c r="L385" s="7"/>
     </row>
-    <row r="386" spans="4:12" ht="12.5">
+    <row r="386" spans="4:12">
       <c r="D386" s="7"/>
       <c r="G386" s="8"/>
       <c r="H386" s="8"/>
@@ -32486,7 +32482,7 @@
       <c r="J386" s="7"/>
       <c r="L386" s="7"/>
     </row>
-    <row r="387" spans="4:12" ht="12.5">
+    <row r="387" spans="4:12">
       <c r="D387" s="7"/>
       <c r="G387" s="8"/>
       <c r="H387" s="8"/>
@@ -32494,7 +32490,7 @@
       <c r="J387" s="7"/>
       <c r="L387" s="7"/>
     </row>
-    <row r="388" spans="4:12" ht="12.5">
+    <row r="388" spans="4:12">
       <c r="D388" s="7"/>
       <c r="G388" s="8"/>
       <c r="H388" s="8"/>
@@ -32502,7 +32498,7 @@
       <c r="J388" s="7"/>
       <c r="L388" s="7"/>
     </row>
-    <row r="389" spans="4:12" ht="12.5">
+    <row r="389" spans="4:12">
       <c r="D389" s="7"/>
       <c r="G389" s="8"/>
       <c r="H389" s="8"/>
@@ -32510,7 +32506,7 @@
       <c r="J389" s="7"/>
       <c r="L389" s="7"/>
     </row>
-    <row r="390" spans="4:12" ht="12.5">
+    <row r="390" spans="4:12">
       <c r="D390" s="7"/>
       <c r="G390" s="8"/>
       <c r="H390" s="8"/>
@@ -32518,7 +32514,7 @@
       <c r="J390" s="7"/>
       <c r="L390" s="7"/>
     </row>
-    <row r="391" spans="4:12" ht="12.5">
+    <row r="391" spans="4:12">
       <c r="D391" s="7"/>
       <c r="G391" s="8"/>
       <c r="H391" s="8"/>
@@ -32526,7 +32522,7 @@
       <c r="J391" s="7"/>
       <c r="L391" s="7"/>
     </row>
-    <row r="392" spans="4:12" ht="12.5">
+    <row r="392" spans="4:12">
       <c r="D392" s="7"/>
       <c r="G392" s="8"/>
       <c r="H392" s="8"/>
@@ -32534,7 +32530,7 @@
       <c r="J392" s="7"/>
       <c r="L392" s="7"/>
     </row>
-    <row r="393" spans="4:12" ht="12.5">
+    <row r="393" spans="4:12">
       <c r="D393" s="7"/>
       <c r="G393" s="8"/>
       <c r="H393" s="8"/>
@@ -32542,7 +32538,7 @@
       <c r="J393" s="7"/>
       <c r="L393" s="7"/>
     </row>
-    <row r="394" spans="4:12" ht="12.5">
+    <row r="394" spans="4:12">
       <c r="D394" s="7"/>
       <c r="G394" s="8"/>
       <c r="H394" s="8"/>
@@ -32550,7 +32546,7 @@
       <c r="J394" s="7"/>
       <c r="L394" s="7"/>
     </row>
-    <row r="395" spans="4:12" ht="12.5">
+    <row r="395" spans="4:12">
       <c r="D395" s="7"/>
       <c r="G395" s="8"/>
       <c r="H395" s="8"/>
@@ -32558,7 +32554,7 @@
       <c r="J395" s="7"/>
       <c r="L395" s="7"/>
     </row>
-    <row r="396" spans="4:12" ht="12.5">
+    <row r="396" spans="4:12">
       <c r="D396" s="7"/>
       <c r="G396" s="8"/>
       <c r="H396" s="8"/>
@@ -32566,7 +32562,7 @@
       <c r="J396" s="7"/>
       <c r="L396" s="7"/>
     </row>
-    <row r="397" spans="4:12" ht="12.5">
+    <row r="397" spans="4:12">
       <c r="D397" s="7"/>
       <c r="G397" s="8"/>
       <c r="H397" s="8"/>
@@ -32574,7 +32570,7 @@
       <c r="J397" s="7"/>
       <c r="L397" s="7"/>
     </row>
-    <row r="398" spans="4:12" ht="12.5">
+    <row r="398" spans="4:12">
       <c r="D398" s="7"/>
       <c r="G398" s="8"/>
       <c r="H398" s="8"/>
@@ -32582,7 +32578,7 @@
       <c r="J398" s="7"/>
       <c r="L398" s="7"/>
     </row>
-    <row r="399" spans="4:12" ht="12.5">
+    <row r="399" spans="4:12">
       <c r="D399" s="7"/>
       <c r="G399" s="8"/>
       <c r="H399" s="8"/>
@@ -32590,7 +32586,7 @@
       <c r="J399" s="7"/>
       <c r="L399" s="7"/>
     </row>
-    <row r="400" spans="4:12" ht="12.5">
+    <row r="400" spans="4:12">
       <c r="D400" s="7"/>
       <c r="G400" s="8"/>
       <c r="H400" s="8"/>
@@ -32598,7 +32594,7 @@
       <c r="J400" s="7"/>
       <c r="L400" s="7"/>
     </row>
-    <row r="401" spans="4:12" ht="12.5">
+    <row r="401" spans="4:12">
       <c r="D401" s="7"/>
       <c r="G401" s="8"/>
       <c r="H401" s="8"/>
@@ -32606,7 +32602,7 @@
       <c r="J401" s="7"/>
       <c r="L401" s="7"/>
     </row>
-    <row r="402" spans="4:12" ht="12.5">
+    <row r="402" spans="4:12">
       <c r="D402" s="7"/>
       <c r="G402" s="8"/>
       <c r="H402" s="8"/>
@@ -32614,7 +32610,7 @@
       <c r="J402" s="7"/>
       <c r="L402" s="7"/>
     </row>
-    <row r="403" spans="4:12" ht="12.5">
+    <row r="403" spans="4:12">
       <c r="D403" s="7"/>
       <c r="G403" s="8"/>
       <c r="H403" s="8"/>
@@ -32622,7 +32618,7 @@
       <c r="J403" s="7"/>
       <c r="L403" s="7"/>
     </row>
-    <row r="404" spans="4:12" ht="12.5">
+    <row r="404" spans="4:12">
       <c r="D404" s="7"/>
       <c r="G404" s="8"/>
       <c r="H404" s="8"/>
@@ -32630,7 +32626,7 @@
       <c r="J404" s="7"/>
       <c r="L404" s="7"/>
     </row>
-    <row r="405" spans="4:12" ht="12.5">
+    <row r="405" spans="4:12">
       <c r="D405" s="7"/>
       <c r="G405" s="8"/>
       <c r="H405" s="8"/>
@@ -32638,7 +32634,7 @@
       <c r="J405" s="7"/>
       <c r="L405" s="7"/>
     </row>
-    <row r="406" spans="4:12" ht="12.5">
+    <row r="406" spans="4:12">
       <c r="D406" s="7"/>
       <c r="G406" s="8"/>
       <c r="H406" s="8"/>
@@ -32646,7 +32642,7 @@
       <c r="J406" s="7"/>
       <c r="L406" s="7"/>
     </row>
-    <row r="407" spans="4:12" ht="12.5">
+    <row r="407" spans="4:12">
       <c r="D407" s="7"/>
       <c r="G407" s="8"/>
       <c r="H407" s="8"/>
@@ -32654,7 +32650,7 @@
       <c r="J407" s="7"/>
       <c r="L407" s="7"/>
     </row>
-    <row r="408" spans="4:12" ht="12.5">
+    <row r="408" spans="4:12">
       <c r="D408" s="7"/>
       <c r="G408" s="8"/>
       <c r="H408" s="8"/>
@@ -32662,7 +32658,7 @@
       <c r="J408" s="7"/>
       <c r="L408" s="7"/>
     </row>
-    <row r="409" spans="4:12" ht="12.5">
+    <row r="409" spans="4:12">
       <c r="D409" s="7"/>
       <c r="G409" s="8"/>
       <c r="H409" s="8"/>
@@ -32670,7 +32666,7 @@
       <c r="J409" s="7"/>
       <c r="L409" s="7"/>
     </row>
-    <row r="410" spans="4:12" ht="12.5">
+    <row r="410" spans="4:12">
       <c r="D410" s="7"/>
       <c r="G410" s="8"/>
       <c r="H410" s="8"/>
@@ -32678,7 +32674,7 @@
       <c r="J410" s="7"/>
       <c r="L410" s="7"/>
     </row>
-    <row r="411" spans="4:12" ht="12.5">
+    <row r="411" spans="4:12">
       <c r="D411" s="7"/>
       <c r="G411" s="8"/>
       <c r="H411" s="8"/>
@@ -32686,7 +32682,7 @@
       <c r="J411" s="7"/>
       <c r="L411" s="7"/>
     </row>
-    <row r="412" spans="4:12" ht="12.5">
+    <row r="412" spans="4:12">
       <c r="D412" s="7"/>
       <c r="G412" s="8"/>
       <c r="H412" s="8"/>
@@ -32694,7 +32690,7 @@
       <c r="J412" s="7"/>
       <c r="L412" s="7"/>
     </row>
-    <row r="413" spans="4:12" ht="12.5">
+    <row r="413" spans="4:12">
       <c r="D413" s="7"/>
       <c r="G413" s="8"/>
       <c r="H413" s="8"/>
@@ -32702,7 +32698,7 @@
       <c r="J413" s="7"/>
       <c r="L413" s="7"/>
     </row>
-    <row r="414" spans="4:12" ht="12.5">
+    <row r="414" spans="4:12">
       <c r="D414" s="7"/>
       <c r="G414" s="8"/>
       <c r="H414" s="8"/>
@@ -32710,7 +32706,7 @@
       <c r="J414" s="7"/>
       <c r="L414" s="7"/>
     </row>
-    <row r="415" spans="4:12" ht="12.5">
+    <row r="415" spans="4:12">
       <c r="D415" s="7"/>
       <c r="G415" s="8"/>
       <c r="H415" s="8"/>
@@ -32718,7 +32714,7 @@
       <c r="J415" s="7"/>
       <c r="L415" s="7"/>
     </row>
-    <row r="416" spans="4:12" ht="12.5">
+    <row r="416" spans="4:12">
       <c r="D416" s="7"/>
       <c r="G416" s="8"/>
       <c r="H416" s="8"/>
@@ -32726,7 +32722,7 @@
       <c r="J416" s="7"/>
       <c r="L416" s="7"/>
     </row>
-    <row r="417" spans="4:12" ht="12.5">
+    <row r="417" spans="4:12">
       <c r="D417" s="7"/>
       <c r="G417" s="8"/>
       <c r="H417" s="8"/>
@@ -32734,7 +32730,7 @@
       <c r="J417" s="7"/>
       <c r="L417" s="7"/>
     </row>
-    <row r="418" spans="4:12" ht="12.5">
+    <row r="418" spans="4:12">
       <c r="D418" s="7"/>
       <c r="G418" s="8"/>
       <c r="H418" s="8"/>
@@ -32742,7 +32738,7 @@
       <c r="J418" s="7"/>
       <c r="L418" s="7"/>
     </row>
-    <row r="419" spans="4:12" ht="12.5">
+    <row r="419" spans="4:12">
       <c r="D419" s="7"/>
       <c r="G419" s="8"/>
       <c r="H419" s="8"/>
@@ -32750,7 +32746,7 @@
       <c r="J419" s="7"/>
       <c r="L419" s="7"/>
     </row>
-    <row r="420" spans="4:12" ht="12.5">
+    <row r="420" spans="4:12">
       <c r="D420" s="7"/>
       <c r="G420" s="8"/>
       <c r="H420" s="8"/>
@@ -32758,7 +32754,7 @@
       <c r="J420" s="7"/>
       <c r="L420" s="7"/>
     </row>
-    <row r="421" spans="4:12" ht="12.5">
+    <row r="421" spans="4:12">
       <c r="D421" s="7"/>
       <c r="G421" s="8"/>
       <c r="H421" s="8"/>
@@ -32766,7 +32762,7 @@
       <c r="J421" s="7"/>
       <c r="L421" s="7"/>
     </row>
-    <row r="422" spans="4:12" ht="12.5">
+    <row r="422" spans="4:12">
       <c r="D422" s="7"/>
       <c r="G422" s="8"/>
       <c r="H422" s="8"/>
@@ -32774,7 +32770,7 @@
       <c r="J422" s="7"/>
       <c r="L422" s="7"/>
     </row>
-    <row r="423" spans="4:12" ht="12.5">
+    <row r="423" spans="4:12">
       <c r="D423" s="7"/>
       <c r="G423" s="8"/>
       <c r="H423" s="8"/>
@@ -32782,7 +32778,7 @@
       <c r="J423" s="7"/>
       <c r="L423" s="7"/>
     </row>
-    <row r="424" spans="4:12" ht="12.5">
+    <row r="424" spans="4:12">
       <c r="D424" s="7"/>
       <c r="G424" s="8"/>
       <c r="H424" s="8"/>
@@ -32790,7 +32786,7 @@
       <c r="J424" s="7"/>
       <c r="L424" s="7"/>
     </row>
-    <row r="425" spans="4:12" ht="12.5">
+    <row r="425" spans="4:12">
       <c r="D425" s="7"/>
       <c r="G425" s="8"/>
       <c r="H425" s="8"/>
@@ -32798,7 +32794,7 @@
       <c r="J425" s="7"/>
       <c r="L425" s="7"/>
     </row>
-    <row r="426" spans="4:12" ht="12.5">
+    <row r="426" spans="4:12">
       <c r="D426" s="7"/>
       <c r="G426" s="8"/>
       <c r="H426" s="8"/>
@@ -32806,7 +32802,7 @@
       <c r="J426" s="7"/>
       <c r="L426" s="7"/>
     </row>
-    <row r="427" spans="4:12" ht="12.5">
+    <row r="427" spans="4:12">
       <c r="D427" s="7"/>
       <c r="G427" s="8"/>
       <c r="H427" s="8"/>
@@ -32814,7 +32810,7 @@
       <c r="J427" s="7"/>
       <c r="L427" s="7"/>
     </row>
-    <row r="428" spans="4:12" ht="12.5">
+    <row r="428" spans="4:12">
       <c r="D428" s="7"/>
       <c r="G428" s="8"/>
       <c r="H428" s="8"/>
@@ -32822,7 +32818,7 @@
       <c r="J428" s="7"/>
       <c r="L428" s="7"/>
     </row>
-    <row r="429" spans="4:12" ht="12.5">
+    <row r="429" spans="4:12">
       <c r="D429" s="7"/>
       <c r="G429" s="8"/>
       <c r="H429" s="8"/>
@@ -32830,7 +32826,7 @@
       <c r="J429" s="7"/>
       <c r="L429" s="7"/>
     </row>
-    <row r="430" spans="4:12" ht="12.5">
+    <row r="430" spans="4:12">
       <c r="D430" s="7"/>
       <c r="G430" s="8"/>
       <c r="H430" s="8"/>
@@ -32838,7 +32834,7 @@
       <c r="J430" s="7"/>
       <c r="L430" s="7"/>
     </row>
-    <row r="431" spans="4:12" ht="12.5">
+    <row r="431" spans="4:12">
       <c r="D431" s="7"/>
       <c r="G431" s="8"/>
       <c r="H431" s="8"/>
@@ -32846,7 +32842,7 @@
       <c r="J431" s="7"/>
       <c r="L431" s="7"/>
     </row>
-    <row r="432" spans="4:12" ht="12.5">
+    <row r="432" spans="4:12">
       <c r="D432" s="7"/>
       <c r="G432" s="8"/>
       <c r="H432" s="8"/>
@@ -32854,7 +32850,7 @@
       <c r="J432" s="7"/>
       <c r="L432" s="7"/>
     </row>
-    <row r="433" spans="4:12" ht="12.5">
+    <row r="433" spans="4:12">
       <c r="D433" s="7"/>
       <c r="G433" s="8"/>
       <c r="H433" s="8"/>
@@ -32862,7 +32858,7 @@
       <c r="J433" s="7"/>
       <c r="L433" s="7"/>
     </row>
-    <row r="434" spans="4:12" ht="12.5">
+    <row r="434" spans="4:12">
       <c r="D434" s="7"/>
       <c r="G434" s="8"/>
       <c r="H434" s="8"/>
@@ -32870,7 +32866,7 @@
       <c r="J434" s="7"/>
       <c r="L434" s="7"/>
     </row>
-    <row r="435" spans="4:12" ht="12.5">
+    <row r="435" spans="4:12">
       <c r="D435" s="7"/>
       <c r="G435" s="8"/>
       <c r="H435" s="8"/>
@@ -32878,7 +32874,7 @@
       <c r="J435" s="7"/>
       <c r="L435" s="7"/>
     </row>
-    <row r="436" spans="4:12" ht="12.5">
+    <row r="436" spans="4:12">
       <c r="D436" s="7"/>
       <c r="G436" s="8"/>
       <c r="H436" s="8"/>
@@ -32886,7 +32882,7 @@
       <c r="J436" s="7"/>
       <c r="L436" s="7"/>
     </row>
-    <row r="437" spans="4:12" ht="12.5">
+    <row r="437" spans="4:12">
       <c r="D437" s="7"/>
       <c r="G437" s="8"/>
       <c r="H437" s="8"/>
@@ -32894,7 +32890,7 @@
       <c r="J437" s="7"/>
       <c r="L437" s="7"/>
     </row>
-    <row r="438" spans="4:12" ht="12.5">
+    <row r="438" spans="4:12">
       <c r="D438" s="7"/>
       <c r="G438" s="8"/>
       <c r="H438" s="8"/>
@@ -32902,7 +32898,7 @@
       <c r="J438" s="7"/>
       <c r="L438" s="7"/>
     </row>
-    <row r="439" spans="4:12" ht="12.5">
+    <row r="439" spans="4:12">
       <c r="D439" s="7"/>
       <c r="G439" s="8"/>
       <c r="H439" s="8"/>
@@ -32910,7 +32906,7 @@
       <c r="J439" s="7"/>
       <c r="L439" s="7"/>
     </row>
-    <row r="440" spans="4:12" ht="12.5">
+    <row r="440" spans="4:12">
       <c r="D440" s="7"/>
       <c r="G440" s="8"/>
       <c r="H440" s="8"/>
@@ -32918,7 +32914,7 @@
       <c r="J440" s="7"/>
       <c r="L440" s="7"/>
     </row>
-    <row r="441" spans="4:12" ht="12.5">
+    <row r="441" spans="4:12">
       <c r="D441" s="7"/>
       <c r="G441" s="8"/>
       <c r="H441" s="8"/>
@@ -32926,7 +32922,7 @@
       <c r="J441" s="7"/>
       <c r="L441" s="7"/>
     </row>
-    <row r="442" spans="4:12" ht="12.5">
+    <row r="442" spans="4:12">
       <c r="D442" s="7"/>
       <c r="G442" s="8"/>
       <c r="H442" s="8"/>
@@ -32934,7 +32930,7 @@
       <c r="J442" s="7"/>
       <c r="L442" s="7"/>
     </row>
-    <row r="443" spans="4:12" ht="12.5">
+    <row r="443" spans="4:12">
       <c r="D443" s="7"/>
       <c r="G443" s="8"/>
       <c r="H443" s="8"/>
@@ -32942,7 +32938,7 @@
       <c r="J443" s="7"/>
       <c r="L443" s="7"/>
     </row>
-    <row r="444" spans="4:12" ht="12.5">
+    <row r="444" spans="4:12">
       <c r="D444" s="7"/>
       <c r="G444" s="8"/>
       <c r="H444" s="8"/>
@@ -32950,7 +32946,7 @@
       <c r="J444" s="7"/>
       <c r="L444" s="7"/>
     </row>
-    <row r="445" spans="4:12" ht="12.5">
+    <row r="445" spans="4:12">
       <c r="D445" s="7"/>
       <c r="G445" s="8"/>
       <c r="H445" s="8"/>
@@ -32958,7 +32954,7 @@
       <c r="J445" s="7"/>
       <c r="L445" s="7"/>
     </row>
-    <row r="446" spans="4:12" ht="12.5">
+    <row r="446" spans="4:12">
       <c r="D446" s="7"/>
       <c r="G446" s="8"/>
       <c r="H446" s="8"/>
@@ -32966,7 +32962,7 @@
       <c r="J446" s="7"/>
       <c r="L446" s="7"/>
     </row>
-    <row r="447" spans="4:12" ht="12.5">
+    <row r="447" spans="4:12">
       <c r="D447" s="7"/>
       <c r="G447" s="8"/>
       <c r="H447" s="8"/>
@@ -32974,7 +32970,7 @@
       <c r="J447" s="7"/>
       <c r="L447" s="7"/>
     </row>
-    <row r="448" spans="4:12" ht="12.5">
+    <row r="448" spans="4:12">
       <c r="D448" s="7"/>
       <c r="G448" s="8"/>
       <c r="H448" s="8"/>
@@ -32982,7 +32978,7 @@
       <c r="J448" s="7"/>
       <c r="L448" s="7"/>
     </row>
-    <row r="449" spans="4:12" ht="12.5">
+    <row r="449" spans="4:12">
       <c r="D449" s="7"/>
       <c r="G449" s="8"/>
       <c r="H449" s="8"/>
@@ -32990,7 +32986,7 @@
       <c r="J449" s="7"/>
       <c r="L449" s="7"/>
     </row>
-    <row r="450" spans="4:12" ht="12.5">
+    <row r="450" spans="4:12">
       <c r="D450" s="7"/>
       <c r="G450" s="8"/>
       <c r="H450" s="8"/>
@@ -32998,7 +32994,7 @@
       <c r="J450" s="7"/>
       <c r="L450" s="7"/>
     </row>
-    <row r="451" spans="4:12" ht="12.5">
+    <row r="451" spans="4:12">
       <c r="D451" s="7"/>
       <c r="G451" s="8"/>
       <c r="H451" s="8"/>
@@ -33006,7 +33002,7 @@
       <c r="J451" s="7"/>
       <c r="L451" s="7"/>
     </row>
-    <row r="452" spans="4:12" ht="12.5">
+    <row r="452" spans="4:12">
       <c r="D452" s="7"/>
       <c r="G452" s="8"/>
       <c r="H452" s="8"/>
@@ -33014,7 +33010,7 @@
       <c r="J452" s="7"/>
       <c r="L452" s="7"/>
     </row>
-    <row r="453" spans="4:12" ht="12.5">
+    <row r="453" spans="4:12">
       <c r="D453" s="7"/>
       <c r="G453" s="8"/>
       <c r="H453" s="8"/>
@@ -33022,7 +33018,7 @@
       <c r="J453" s="7"/>
       <c r="L453" s="7"/>
     </row>
-    <row r="454" spans="4:12" ht="12.5">
+    <row r="454" spans="4:12">
       <c r="D454" s="7"/>
       <c r="G454" s="8"/>
       <c r="H454" s="8"/>
@@ -33030,7 +33026,7 @@
       <c r="J454" s="7"/>
       <c r="L454" s="7"/>
     </row>
-    <row r="455" spans="4:12" ht="12.5">
+    <row r="455" spans="4:12">
       <c r="D455" s="7"/>
       <c r="G455" s="8"/>
       <c r="H455" s="8"/>
@@ -33038,7 +33034,7 @@
       <c r="J455" s="7"/>
       <c r="L455" s="7"/>
     </row>
-    <row r="456" spans="4:12" ht="12.5">
+    <row r="456" spans="4:12">
       <c r="D456" s="7"/>
       <c r="G456" s="8"/>
       <c r="H456" s="8"/>
@@ -33046,7 +33042,7 @@
       <c r="J456" s="7"/>
       <c r="L456" s="7"/>
     </row>
-    <row r="457" spans="4:12" ht="12.5">
+    <row r="457" spans="4:12">
       <c r="D457" s="7"/>
       <c r="G457" s="8"/>
       <c r="H457" s="8"/>
@@ -33054,7 +33050,7 @@
       <c r="J457" s="7"/>
       <c r="L457" s="7"/>
     </row>
-    <row r="458" spans="4:12" ht="12.5">
+    <row r="458" spans="4:12">
       <c r="D458" s="7"/>
       <c r="G458" s="8"/>
       <c r="H458" s="8"/>
@@ -33062,7 +33058,7 @@
       <c r="J458" s="7"/>
       <c r="L458" s="7"/>
     </row>
-    <row r="459" spans="4:12" ht="12.5">
+    <row r="459" spans="4:12">
       <c r="D459" s="7"/>
       <c r="G459" s="8"/>
       <c r="H459" s="8"/>
@@ -33070,7 +33066,7 @@
       <c r="J459" s="7"/>
       <c r="L459" s="7"/>
     </row>
-    <row r="460" spans="4:12" ht="12.5">
+    <row r="460" spans="4:12">
       <c r="D460" s="7"/>
       <c r="G460" s="8"/>
       <c r="H460" s="8"/>
@@ -33078,7 +33074,7 @@
       <c r="J460" s="7"/>
       <c r="L460" s="7"/>
     </row>
-    <row r="461" spans="4:12" ht="12.5">
+    <row r="461" spans="4:12">
       <c r="D461" s="7"/>
       <c r="G461" s="8"/>
       <c r="H461" s="8"/>
@@ -33086,7 +33082,7 @@
       <c r="J461" s="7"/>
       <c r="L461" s="7"/>
     </row>
-    <row r="462" spans="4:12" ht="12.5">
+    <row r="462" spans="4:12">
       <c r="D462" s="7"/>
       <c r="G462" s="8"/>
       <c r="H462" s="8"/>
@@ -33094,7 +33090,7 @@
       <c r="J462" s="7"/>
       <c r="L462" s="7"/>
     </row>
-    <row r="463" spans="4:12" ht="12.5">
+    <row r="463" spans="4:12">
       <c r="D463" s="7"/>
       <c r="G463" s="8"/>
       <c r="H463" s="8"/>
@@ -33102,7 +33098,7 @@
       <c r="J463" s="7"/>
       <c r="L463" s="7"/>
     </row>
-    <row r="464" spans="4:12" ht="12.5">
+    <row r="464" spans="4:12">
       <c r="D464" s="7"/>
       <c r="G464" s="8"/>
       <c r="H464" s="8"/>
@@ -33110,7 +33106,7 @@
       <c r="J464" s="7"/>
       <c r="L464" s="7"/>
     </row>
-    <row r="465" spans="4:12" ht="12.5">
+    <row r="465" spans="4:12">
       <c r="D465" s="7"/>
       <c r="G465" s="8"/>
       <c r="H465" s="8"/>
@@ -33118,7 +33114,7 @@
       <c r="J465" s="7"/>
       <c r="L465" s="7"/>
     </row>
-    <row r="466" spans="4:12" ht="12.5">
+    <row r="466" spans="4:12">
       <c r="D466" s="7"/>
       <c r="G466" s="8"/>
       <c r="H466" s="8"/>
@@ -33126,7 +33122,7 @@
       <c r="J466" s="7"/>
       <c r="L466" s="7"/>
     </row>
-    <row r="467" spans="4:12" ht="12.5">
+    <row r="467" spans="4:12">
       <c r="D467" s="7"/>
       <c r="G467" s="8"/>
       <c r="H467" s="8"/>
@@ -33134,7 +33130,7 @@
       <c r="J467" s="7"/>
       <c r="L467" s="7"/>
     </row>
-    <row r="468" spans="4:12" ht="12.5">
+    <row r="468" spans="4:12">
       <c r="D468" s="7"/>
       <c r="G468" s="8"/>
       <c r="H468" s="8"/>
@@ -33142,7 +33138,7 @@
       <c r="J468" s="7"/>
       <c r="L468" s="7"/>
     </row>
-    <row r="469" spans="4:12" ht="12.5">
+    <row r="469" spans="4:12">
       <c r="D469" s="7"/>
       <c r="G469" s="8"/>
       <c r="H469" s="8"/>
@@ -33150,7 +33146,7 @@
       <c r="J469" s="7"/>
       <c r="L469" s="7"/>
     </row>
-    <row r="470" spans="4:12" ht="12.5">
+    <row r="470" spans="4:12">
       <c r="D470" s="7"/>
       <c r="G470" s="8"/>
       <c r="H470" s="8"/>
@@ -33158,7 +33154,7 @@
       <c r="J470" s="7"/>
       <c r="L470" s="7"/>
     </row>
-    <row r="471" spans="4:12" ht="12.5">
+    <row r="471" spans="4:12">
       <c r="D471" s="7"/>
       <c r="G471" s="8"/>
       <c r="H471" s="8"/>
@@ -33166,7 +33162,7 @@
       <c r="J471" s="7"/>
       <c r="L471" s="7"/>
     </row>
-    <row r="472" spans="4:12" ht="12.5">
+    <row r="472" spans="4:12">
       <c r="D472" s="7"/>
       <c r="G472" s="8"/>
       <c r="H472" s="8"/>
@@ -33174,7 +33170,7 @@
       <c r="J472" s="7"/>
       <c r="L472" s="7"/>
     </row>
-    <row r="473" spans="4:12" ht="12.5">
+    <row r="473" spans="4:12">
       <c r="D473" s="7"/>
       <c r="G473" s="8"/>
       <c r="H473" s="8"/>
@@ -33182,7 +33178,7 @@
       <c r="J473" s="7"/>
       <c r="L473" s="7"/>
     </row>
-    <row r="474" spans="4:12" ht="12.5">
+    <row r="474" spans="4:12">
       <c r="D474" s="7"/>
       <c r="G474" s="8"/>
       <c r="H474" s="8"/>
@@ -33190,7 +33186,7 @@
       <c r="J474" s="7"/>
       <c r="L474" s="7"/>
     </row>
-    <row r="475" spans="4:12" ht="12.5">
+    <row r="475" spans="4:12">
       <c r="D475" s="7"/>
       <c r="G475" s="8"/>
       <c r="H475" s="8"/>
@@ -33198,7 +33194,7 @@
       <c r="J475" s="7"/>
       <c r="L475" s="7"/>
     </row>
-    <row r="476" spans="4:12" ht="12.5">
+    <row r="476" spans="4:12">
       <c r="D476" s="7"/>
       <c r="G476" s="8"/>
       <c r="H476" s="8"/>
@@ -33206,7 +33202,7 @@
       <c r="J476" s="7"/>
       <c r="L476" s="7"/>
     </row>
-    <row r="477" spans="4:12" ht="12.5">
+    <row r="477" spans="4:12">
       <c r="D477" s="7"/>
       <c r="G477" s="8"/>
       <c r="H477" s="8"/>
@@ -33214,7 +33210,7 @@
       <c r="J477" s="7"/>
       <c r="L477" s="7"/>
     </row>
-    <row r="478" spans="4:12" ht="12.5">
+    <row r="478" spans="4:12">
       <c r="D478" s="7"/>
       <c r="G478" s="8"/>
       <c r="H478" s="8"/>
@@ -33222,7 +33218,7 @@
       <c r="J478" s="7"/>
       <c r="L478" s="7"/>
     </row>
-    <row r="479" spans="4:12" ht="12.5">
+    <row r="479" spans="4:12">
       <c r="D479" s="7"/>
       <c r="G479" s="8"/>
       <c r="H479" s="8"/>
@@ -33230,7 +33226,7 @@
       <c r="J479" s="7"/>
       <c r="L479" s="7"/>
     </row>
-    <row r="480" spans="4:12" ht="12.5">
+    <row r="480" spans="4:12">
       <c r="D480" s="7"/>
       <c r="G480" s="8"/>
       <c r="H480" s="8"/>
@@ -33238,7 +33234,7 @@
       <c r="J480" s="7"/>
       <c r="L480" s="7"/>
     </row>
-    <row r="481" spans="4:12" ht="12.5">
+    <row r="481" spans="4:12">
       <c r="D481" s="7"/>
       <c r="G481" s="8"/>
       <c r="H481" s="8"/>
@@ -33246,7 +33242,7 @@
       <c r="J481" s="7"/>
       <c r="L481" s="7"/>
     </row>
-    <row r="482" spans="4:12" ht="12.5">
+    <row r="482" spans="4:12">
       <c r="D482" s="7"/>
       <c r="G482" s="8"/>
       <c r="H482" s="8"/>
@@ -33254,7 +33250,7 @@
       <c r="J482" s="7"/>
       <c r="L482" s="7"/>
     </row>
-    <row r="483" spans="4:12" ht="12.5">
+    <row r="483" spans="4:12">
       <c r="D483" s="7"/>
       <c r="G483" s="8"/>
       <c r="H483" s="8"/>
@@ -33262,7 +33258,7 @@
       <c r="J483" s="7"/>
       <c r="L483" s="7"/>
     </row>
-    <row r="484" spans="4:12" ht="12.5">
+    <row r="484" spans="4:12">
       <c r="D484" s="7"/>
       <c r="G484" s="8"/>
       <c r="H484" s="8"/>
@@ -33270,7 +33266,7 @@
       <c r="J484" s="7"/>
       <c r="L484" s="7"/>
     </row>
-    <row r="485" spans="4:12" ht="12.5">
+    <row r="485" spans="4:12">
       <c r="D485" s="7"/>
       <c r="G485" s="8"/>
       <c r="H485" s="8"/>
@@ -33278,7 +33274,7 @@
       <c r="J485" s="7"/>
       <c r="L485" s="7"/>
     </row>
-    <row r="486" spans="4:12" ht="12.5">
+    <row r="486" spans="4:12">
       <c r="D486" s="7"/>
       <c r="G486" s="8"/>
       <c r="H486" s="8"/>
@@ -33286,7 +33282,7 @@
       <c r="J486" s="7"/>
       <c r="L486" s="7"/>
     </row>
-    <row r="487" spans="4:12" ht="12.5">
+    <row r="487" spans="4:12">
       <c r="D487" s="7"/>
       <c r="G487" s="8"/>
       <c r="H487" s="8"/>
@@ -33294,7 +33290,7 @@
       <c r="J487" s="7"/>
       <c r="L487" s="7"/>
     </row>
-    <row r="488" spans="4:12" ht="12.5">
+    <row r="488" spans="4:12">
       <c r="D488" s="7"/>
       <c r="G488" s="8"/>
       <c r="H488" s="8"/>
@@ -33302,7 +33298,7 @@
       <c r="J488" s="7"/>
       <c r="L488" s="7"/>
     </row>
-    <row r="489" spans="4:12" ht="12.5">
+    <row r="489" spans="4:12">
       <c r="D489" s="7"/>
       <c r="G489" s="8"/>
       <c r="H489" s="8"/>
@@ -33310,7 +33306,7 @@
       <c r="J489" s="7"/>
       <c r="L489" s="7"/>
     </row>
-    <row r="490" spans="4:12" ht="12.5">
+    <row r="490" spans="4:12">
       <c r="D490" s="7"/>
       <c r="G490" s="8"/>
       <c r="H490" s="8"/>
@@ -33318,7 +33314,7 @@
       <c r="J490" s="7"/>
       <c r="L490" s="7"/>
     </row>
-    <row r="491" spans="4:12" ht="12.5">
+    <row r="491" spans="4:12">
       <c r="D491" s="7"/>
       <c r="G491" s="8"/>
       <c r="H491" s="8"/>
@@ -33326,7 +33322,7 @@
       <c r="J491" s="7"/>
       <c r="L491" s="7"/>
     </row>
-    <row r="492" spans="4:12" ht="12.5">
+    <row r="492" spans="4:12">
       <c r="D492" s="7"/>
       <c r="G492" s="8"/>
       <c r="H492" s="8"/>
@@ -33334,7 +33330,7 @@
       <c r="J492" s="7"/>
       <c r="L492" s="7"/>
     </row>
-    <row r="493" spans="4:12" ht="12.5">
+    <row r="493" spans="4:12">
       <c r="D493" s="7"/>
       <c r="G493" s="8"/>
       <c r="H493" s="8"/>
@@ -33342,7 +33338,7 @@
       <c r="J493" s="7"/>
       <c r="L493" s="7"/>
     </row>
-    <row r="494" spans="4:12" ht="12.5">
+    <row r="494" spans="4:12">
       <c r="D494" s="7"/>
       <c r="G494" s="8"/>
       <c r="H494" s="8"/>
@@ -33350,7 +33346,7 @@
       <c r="J494" s="7"/>
       <c r="L494" s="7"/>
     </row>
-    <row r="495" spans="4:12" ht="12.5">
+    <row r="495" spans="4:12">
       <c r="D495" s="7"/>
       <c r="G495" s="8"/>
       <c r="H495" s="8"/>
@@ -33358,7 +33354,7 @@
       <c r="J495" s="7"/>
       <c r="L495" s="7"/>
     </row>
-    <row r="496" spans="4:12" ht="12.5">
+    <row r="496" spans="4:12">
       <c r="D496" s="7"/>
       <c r="G496" s="8"/>
       <c r="H496" s="8"/>
@@ -33366,7 +33362,7 @@
       <c r="J496" s="7"/>
       <c r="L496" s="7"/>
     </row>
-    <row r="497" spans="4:12" ht="12.5">
+    <row r="497" spans="4:12">
       <c r="D497" s="7"/>
       <c r="G497" s="8"/>
       <c r="H497" s="8"/>
@@ -33374,7 +33370,7 @@
       <c r="J497" s="7"/>
       <c r="L497" s="7"/>
     </row>
-    <row r="498" spans="4:12" ht="12.5">
+    <row r="498" spans="4:12">
       <c r="D498" s="7"/>
       <c r="G498" s="8"/>
       <c r="H498" s="8"/>
@@ -33382,7 +33378,7 @@
       <c r="J498" s="7"/>
       <c r="L498" s="7"/>
     </row>
-    <row r="499" spans="4:12" ht="12.5">
+    <row r="499" spans="4:12">
       <c r="D499" s="7"/>
       <c r="G499" s="8"/>
       <c r="H499" s="8"/>
@@ -33390,7 +33386,7 @@
       <c r="J499" s="7"/>
       <c r="L499" s="7"/>
     </row>
-    <row r="500" spans="4:12" ht="12.5">
+    <row r="500" spans="4:12">
       <c r="D500" s="7"/>
       <c r="G500" s="8"/>
       <c r="H500" s="8"/>
@@ -33398,7 +33394,7 @@
       <c r="J500" s="7"/>
       <c r="L500" s="7"/>
     </row>
-    <row r="501" spans="4:12" ht="12.5">
+    <row r="501" spans="4:12">
       <c r="D501" s="7"/>
       <c r="G501" s="8"/>
       <c r="H501" s="8"/>
@@ -33406,7 +33402,7 @@
       <c r="J501" s="7"/>
       <c r="L501" s="7"/>
     </row>
-    <row r="502" spans="4:12" ht="12.5">
+    <row r="502" spans="4:12">
       <c r="D502" s="7"/>
       <c r="G502" s="8"/>
       <c r="H502" s="8"/>
@@ -33414,7 +33410,7 @@
       <c r="J502" s="7"/>
       <c r="L502" s="7"/>
     </row>
-    <row r="503" spans="4:12" ht="12.5">
+    <row r="503" spans="4:12">
       <c r="D503" s="7"/>
       <c r="G503" s="8"/>
       <c r="H503" s="8"/>
@@ -33422,7 +33418,7 @@
       <c r="J503" s="7"/>
       <c r="L503" s="7"/>
     </row>
-    <row r="504" spans="4:12" ht="12.5">
+    <row r="504" spans="4:12">
       <c r="D504" s="7"/>
       <c r="G504" s="8"/>
       <c r="H504" s="8"/>
@@ -33430,7 +33426,7 @@
       <c r="J504" s="7"/>
       <c r="L504" s="7"/>
     </row>
-    <row r="505" spans="4:12" ht="12.5">
+    <row r="505" spans="4:12">
       <c r="D505" s="7"/>
       <c r="G505" s="8"/>
       <c r="H505" s="8"/>
@@ -33438,7 +33434,7 @@
       <c r="J505" s="7"/>
       <c r="L505" s="7"/>
     </row>
-    <row r="506" spans="4:12" ht="12.5">
+    <row r="506" spans="4:12">
       <c r="D506" s="7"/>
       <c r="G506" s="8"/>
       <c r="H506" s="8"/>
@@ -33446,7 +33442,7 @@
       <c r="J506" s="7"/>
       <c r="L506" s="7"/>
     </row>
-    <row r="507" spans="4:12" ht="12.5">
+    <row r="507" spans="4:12">
       <c r="D507" s="7"/>
       <c r="G507" s="8"/>
       <c r="H507" s="8"/>
@@ -33454,7 +33450,7 @@
       <c r="J507" s="7"/>
       <c r="L507" s="7"/>
     </row>
-    <row r="508" spans="4:12" ht="12.5">
+    <row r="508" spans="4:12">
       <c r="D508" s="7"/>
       <c r="G508" s="8"/>
       <c r="H508" s="8"/>
@@ -33462,7 +33458,7 @@
       <c r="J508" s="7"/>
       <c r="L508" s="7"/>
     </row>
-    <row r="509" spans="4:12" ht="12.5">
+    <row r="509" spans="4:12">
       <c r="D509" s="7"/>
       <c r="G509" s="8"/>
       <c r="H509" s="8"/>
@@ -33470,7 +33466,7 @@
       <c r="J509" s="7"/>
       <c r="L509" s="7"/>
     </row>
-    <row r="510" spans="4:12" ht="12.5">
+    <row r="510" spans="4:12">
       <c r="D510" s="7"/>
       <c r="G510" s="8"/>
       <c r="H510" s="8"/>
@@ -33478,7 +33474,7 @@
       <c r="J510" s="7"/>
       <c r="L510" s="7"/>
     </row>
-    <row r="511" spans="4:12" ht="12.5">
+    <row r="511" spans="4:12">
       <c r="D511" s="7"/>
       <c r="G511" s="8"/>
       <c r="H511" s="8"/>
@@ -33486,7 +33482,7 @@
       <c r="J511" s="7"/>
       <c r="L511" s="7"/>
     </row>
-    <row r="512" spans="4:12" ht="12.5">
+    <row r="512" spans="4:12">
       <c r="D512" s="7"/>
       <c r="G512" s="8"/>
       <c r="H512" s="8"/>
@@ -33494,7 +33490,7 @@
       <c r="J512" s="7"/>
       <c r="L512" s="7"/>
     </row>
-    <row r="513" spans="4:12" ht="12.5">
+    <row r="513" spans="4:12">
       <c r="D513" s="7"/>
       <c r="G513" s="8"/>
       <c r="H513" s="8"/>
@@ -33502,7 +33498,7 @@
       <c r="J513" s="7"/>
       <c r="L513" s="7"/>
     </row>
-    <row r="514" spans="4:12" ht="12.5">
+    <row r="514" spans="4:12">
       <c r="D514" s="7"/>
       <c r="G514" s="8"/>
       <c r="H514" s="8"/>
@@ -33510,7 +33506,7 @@
       <c r="J514" s="7"/>
       <c r="L514" s="7"/>
     </row>
-    <row r="515" spans="4:12" ht="12.5">
+    <row r="515" spans="4:12">
       <c r="D515" s="7"/>
       <c r="G515" s="8"/>
       <c r="H515" s="8"/>
@@ -33518,7 +33514,7 @@
       <c r="J515" s="7"/>
       <c r="L515" s="7"/>
     </row>
-    <row r="516" spans="4:12" ht="12.5">
+    <row r="516" spans="4:12">
       <c r="D516" s="7"/>
       <c r="G516" s="8"/>
       <c r="H516" s="8"/>
@@ -33526,7 +33522,7 @@
       <c r="J516" s="7"/>
       <c r="L516" s="7"/>
     </row>
-    <row r="517" spans="4:12" ht="12.5">
+    <row r="517" spans="4:12">
       <c r="D517" s="7"/>
       <c r="G517" s="8"/>
       <c r="H517" s="8"/>
@@ -33534,7 +33530,7 @@
       <c r="J517" s="7"/>
       <c r="L517" s="7"/>
     </row>
-    <row r="518" spans="4:12" ht="12.5">
+    <row r="518" spans="4:12">
       <c r="D518" s="7"/>
       <c r="G518" s="8"/>
       <c r="H518" s="8"/>
@@ -33542,7 +33538,7 @@
       <c r="J518" s="7"/>
       <c r="L518" s="7"/>
     </row>
-    <row r="519" spans="4:12" ht="12.5">
+    <row r="519" spans="4:12">
       <c r="D519" s="7"/>
       <c r="G519" s="8"/>
       <c r="H519" s="8"/>
@@ -33550,7 +33546,7 @@
       <c r="J519" s="7"/>
       <c r="L519" s="7"/>
     </row>
-    <row r="520" spans="4:12" ht="12.5">
+    <row r="520" spans="4:12">
       <c r="D520" s="7"/>
       <c r="G520" s="8"/>
       <c r="H520" s="8"/>
@@ -33558,7 +33554,7 @@
       <c r="J520" s="7"/>
       <c r="L520" s="7"/>
     </row>
-    <row r="521" spans="4:12" ht="12.5">
+    <row r="521" spans="4:12">
       <c r="D521" s="7"/>
       <c r="G521" s="8"/>
       <c r="H521" s="8"/>
@@ -33566,7 +33562,7 @@
       <c r="J521" s="7"/>
       <c r="L521" s="7"/>
     </row>
-    <row r="522" spans="4:12" ht="12.5">
+    <row r="522" spans="4:12">
       <c r="D522" s="7"/>
       <c r="G522" s="8"/>
       <c r="H522" s="8"/>
@@ -33574,7 +33570,7 @@
       <c r="J522" s="7"/>
       <c r="L522" s="7"/>
     </row>
-    <row r="523" spans="4:12" ht="12.5">
+    <row r="523" spans="4:12">
       <c r="D523" s="7"/>
       <c r="G523" s="8"/>
       <c r="H523" s="8"/>
@@ -33582,7 +33578,7 @@
       <c r="J523" s="7"/>
       <c r="L523" s="7"/>
     </row>
-    <row r="524" spans="4:12" ht="12.5">
+    <row r="524" spans="4:12">
       <c r="D524" s="7"/>
       <c r="G524" s="8"/>
       <c r="H524" s="8"/>
@@ -33590,7 +33586,7 @@
       <c r="J524" s="7"/>
       <c r="L524" s="7"/>
     </row>
-    <row r="525" spans="4:12" ht="12.5">
+    <row r="525" spans="4:12">
       <c r="D525" s="7"/>
       <c r="G525" s="8"/>
       <c r="H525" s="8"/>
@@ -33598,7 +33594,7 @@
       <c r="J525" s="7"/>
       <c r="L525" s="7"/>
     </row>
-    <row r="526" spans="4:12" ht="12.5">
+    <row r="526" spans="4:12">
       <c r="D526" s="7"/>
       <c r="G526" s="8"/>
       <c r="H526" s="8"/>
@@ -33606,7 +33602,7 @@
       <c r="J526" s="7"/>
       <c r="L526" s="7"/>
     </row>
-    <row r="527" spans="4:12" ht="12.5">
+    <row r="527" spans="4:12">
       <c r="D527" s="7"/>
       <c r="G527" s="8"/>
       <c r="H527" s="8"/>
@@ -33614,7 +33610,7 @@
       <c r="J527" s="7"/>
       <c r="L527" s="7"/>
     </row>
-    <row r="528" spans="4:12" ht="12.5">
+    <row r="528" spans="4:12">
       <c r="D528" s="7"/>
       <c r="G528" s="8"/>
       <c r="H528" s="8"/>
@@ -33622,7 +33618,7 @@
       <c r="J528" s="7"/>
       <c r="L528" s="7"/>
     </row>
-    <row r="529" spans="4:12" ht="12.5">
+    <row r="529" spans="4:12">
       <c r="D529" s="7"/>
       <c r="G529" s="8"/>
       <c r="H529" s="8"/>
@@ -33630,7 +33626,7 @@
       <c r="J529" s="7"/>
       <c r="L529" s="7"/>
     </row>
-    <row r="530" spans="4:12" ht="12.5">
+    <row r="530" spans="4:12">
       <c r="D530" s="7"/>
       <c r="G530" s="8"/>
       <c r="H530" s="8"/>
@@ -33638,7 +33634,7 @@
       <c r="J530" s="7"/>
       <c r="L530" s="7"/>
     </row>
-    <row r="531" spans="4:12" ht="12.5">
+    <row r="531" spans="4:12">
       <c r="D531" s="7"/>
       <c r="G531" s="8"/>
       <c r="H531" s="8"/>
@@ -33646,7 +33642,7 @@
       <c r="J531" s="7"/>
       <c r="L531" s="7"/>
     </row>
-    <row r="532" spans="4:12" ht="12.5">
+    <row r="532" spans="4:12">
       <c r="D532" s="7"/>
       <c r="G532" s="8"/>
       <c r="H532" s="8"/>
@@ -33654,7 +33650,7 @@
       <c r="J532" s="7"/>
       <c r="L532" s="7"/>
     </row>
-    <row r="533" spans="4:12" ht="12.5">
+    <row r="533" spans="4:12">
       <c r="D533" s="7"/>
       <c r="G533" s="8"/>
       <c r="H533" s="8"/>
@@ -33662,7 +33658,7 @@
       <c r="J533" s="7"/>
       <c r="L533" s="7"/>
     </row>
-    <row r="534" spans="4:12" ht="12.5">
+    <row r="534" spans="4:12">
       <c r="D534" s="7"/>
       <c r="G534" s="8"/>
       <c r="H534" s="8"/>
@@ -33670,7 +33666,7 @@
       <c r="J534" s="7"/>
       <c r="L534" s="7"/>
     </row>
-    <row r="535" spans="4:12" ht="12.5">
+    <row r="535" spans="4:12">
       <c r="D535" s="7"/>
       <c r="G535" s="8"/>
       <c r="H535" s="8"/>
@@ -33678,7 +33674,7 @@
       <c r="J535" s="7"/>
       <c r="L535" s="7"/>
     </row>
-    <row r="536" spans="4:12" ht="12.5">
+    <row r="536" spans="4:12">
       <c r="D536" s="7"/>
       <c r="G536" s="8"/>
       <c r="H536" s="8"/>
@@ -33686,7 +33682,7 @@
       <c r="J536" s="7"/>
       <c r="L536" s="7"/>
     </row>
-    <row r="537" spans="4:12" ht="12.5">
+    <row r="537" spans="4:12">
       <c r="D537" s="7"/>
       <c r="G537" s="8"/>
       <c r="H537" s="8"/>
@@ -33694,7 +33690,7 @@
       <c r="J537" s="7"/>
       <c r="L537" s="7"/>
     </row>
-    <row r="538" spans="4:12" ht="12.5">
+    <row r="538" spans="4:12">
       <c r="D538" s="7"/>
       <c r="G538" s="8"/>
       <c r="H538" s="8"/>
@@ -33702,7 +33698,7 @@
       <c r="J538" s="7"/>
       <c r="L538" s="7"/>
     </row>
-    <row r="539" spans="4:12" ht="12.5">
+    <row r="539" spans="4:12">
       <c r="D539" s="7"/>
       <c r="G539" s="8"/>
       <c r="H539" s="8"/>
@@ -33710,7 +33706,7 @@
       <c r="J539" s="7"/>
       <c r="L539" s="7"/>
     </row>
-    <row r="540" spans="4:12" ht="12.5">
+    <row r="540" spans="4:12">
       <c r="D540" s="7"/>
       <c r="G540" s="8"/>
       <c r="H540" s="8"/>
@@ -33718,7 +33714,7 @@
       <c r="J540" s="7"/>
       <c r="L540" s="7"/>
     </row>
-    <row r="541" spans="4:12" ht="12.5">
+    <row r="541" spans="4:12">
       <c r="D541" s="7"/>
       <c r="G541" s="8"/>
       <c r="H541" s="8"/>
@@ -33726,7 +33722,7 @@
       <c r="J541" s="7"/>
       <c r="L541" s="7"/>
     </row>
-    <row r="542" spans="4:12" ht="12.5">
+    <row r="542" spans="4:12">
       <c r="D542" s="7"/>
       <c r="G542" s="8"/>
       <c r="H542" s="8"/>
@@ -33734,7 +33730,7 @@
       <c r="J542" s="7"/>
       <c r="L542" s="7"/>
     </row>
-    <row r="543" spans="4:12" ht="12.5">
+    <row r="543" spans="4:12">
       <c r="D543" s="7"/>
       <c r="G543" s="8"/>
       <c r="H543" s="8"/>
@@ -33742,7 +33738,7 @@
       <c r="J543" s="7"/>
       <c r="L543" s="7"/>
     </row>
-    <row r="544" spans="4:12" ht="12.5">
+    <row r="544" spans="4:12">
       <c r="D544" s="7"/>
       <c r="G544" s="8"/>
       <c r="H544" s="8"/>
@@ -33750,7 +33746,7 @@
       <c r="J544" s="7"/>
       <c r="L544" s="7"/>
     </row>
-    <row r="545" spans="4:12" ht="12.5">
+    <row r="545" spans="4:12">
       <c r="D545" s="7"/>
       <c r="G545" s="8"/>
       <c r="H545" s="8"/>
@@ -33758,7 +33754,7 @@
       <c r="J545" s="7"/>
       <c r="L545" s="7"/>
     </row>
-    <row r="546" spans="4:12" ht="12.5">
+    <row r="546" spans="4:12">
       <c r="D546" s="7"/>
       <c r="G546" s="8"/>
       <c r="H546" s="8"/>
@@ -33766,7 +33762,7 @@
       <c r="J546" s="7"/>
       <c r="L546" s="7"/>
     </row>
-    <row r="547" spans="4:12" ht="12.5">
+    <row r="547" spans="4:12">
       <c r="D547" s="7"/>
       <c r="G547" s="8"/>
       <c r="H547" s="8"/>
@@ -33774,7 +33770,7 @@
       <c r="J547" s="7"/>
       <c r="L547" s="7"/>
     </row>
-    <row r="548" spans="4:12" ht="12.5">
+    <row r="548" spans="4:12">
       <c r="D548" s="7"/>
       <c r="G548" s="8"/>
       <c r="H548" s="8"/>
@@ -33782,7 +33778,7 @@
       <c r="J548" s="7"/>
       <c r="L548" s="7"/>
     </row>
-    <row r="549" spans="4:12" ht="12.5">
+    <row r="549" spans="4:12">
       <c r="D549" s="7"/>
       <c r="G549" s="8"/>
       <c r="H549" s="8"/>
@@ -33790,7 +33786,7 @@
       <c r="J549" s="7"/>
       <c r="L549" s="7"/>
     </row>
-    <row r="550" spans="4:12" ht="12.5">
+    <row r="550" spans="4:12">
       <c r="D550" s="7"/>
       <c r="G550" s="8"/>
       <c r="H550" s="8"/>
@@ -33798,7 +33794,7 @@
       <c r="J550" s="7"/>
       <c r="L550" s="7"/>
     </row>
-    <row r="551" spans="4:12" ht="12.5">
+    <row r="551" spans="4:12">
       <c r="D551" s="7"/>
       <c r="G551" s="8"/>
       <c r="H551" s="8"/>
@@ -33806,7 +33802,7 @@
       <c r="J551" s="7"/>
       <c r="L551" s="7"/>
     </row>
-    <row r="552" spans="4:12" ht="12.5">
+    <row r="552" spans="4:12">
       <c r="D552" s="7"/>
       <c r="G552" s="8"/>
       <c r="H552" s="8"/>
@@ -33814,7 +33810,7 @@
       <c r="J552" s="7"/>
       <c r="L552" s="7"/>
     </row>
-    <row r="553" spans="4:12" ht="12.5">
+    <row r="553" spans="4:12">
       <c r="D553" s="7"/>
       <c r="G553" s="8"/>
       <c r="H553" s="8"/>
@@ -33822,7 +33818,7 @@
       <c r="J553" s="7"/>
       <c r="L553" s="7"/>
     </row>
-    <row r="554" spans="4:12" ht="12.5">
+    <row r="554" spans="4:12">
       <c r="D554" s="7"/>
       <c r="G554" s="8"/>
       <c r="H554" s="8"/>
@@ -33830,7 +33826,7 @@
       <c r="J554" s="7"/>
       <c r="L554" s="7"/>
     </row>
-    <row r="555" spans="4:12" ht="12.5">
+    <row r="555" spans="4:12">
       <c r="D555" s="7"/>
       <c r="G555" s="8"/>
       <c r="H555" s="8"/>
@@ -33838,7 +33834,7 @@
       <c r="J555" s="7"/>
       <c r="L555" s="7"/>
     </row>
-    <row r="556" spans="4:12" ht="12.5">
+    <row r="556" spans="4:12">
       <c r="D556" s="7"/>
       <c r="G556" s="8"/>
       <c r="H556" s="8"/>
@@ -33846,7 +33842,7 @@
       <c r="J556" s="7"/>
       <c r="L556" s="7"/>
     </row>
-    <row r="557" spans="4:12" ht="12.5">
+    <row r="557" spans="4:12">
       <c r="D557" s="7"/>
       <c r="G557" s="8"/>
       <c r="H557" s="8"/>
@@ -33854,7 +33850,7 @@
       <c r="J557" s="7"/>
       <c r="L557" s="7"/>
     </row>
-    <row r="558" spans="4:12" ht="12.5">
+    <row r="558" spans="4:12">
       <c r="D558" s="7"/>
       <c r="G558" s="8"/>
       <c r="H558" s="8"/>
@@ -33862,7 +33858,7 @@
       <c r="J558" s="7"/>
       <c r="L558" s="7"/>
     </row>
-    <row r="559" spans="4:12" ht="12.5">
+    <row r="559" spans="4:12">
       <c r="D559" s="7"/>
       <c r="G559" s="8"/>
       <c r="H559" s="8"/>
@@ -33870,7 +33866,7 @@
       <c r="J559" s="7"/>
       <c r="L559" s="7"/>
     </row>
-    <row r="560" spans="4:12" ht="12.5">
+    <row r="560" spans="4:12">
       <c r="D560" s="7"/>
       <c r="G560" s="8"/>
       <c r="H560" s="8"/>
@@ -33878,7 +33874,7 @@
       <c r="J560" s="7"/>
       <c r="L560" s="7"/>
     </row>
-    <row r="561" spans="4:12" ht="12.5">
+    <row r="561" spans="4:12">
       <c r="D561" s="7"/>
       <c r="G561" s="8"/>
       <c r="H561" s="8"/>
@@ -33886,7 +33882,7 @@
       <c r="J561" s="7"/>
       <c r="L561" s="7"/>
     </row>
-    <row r="562" spans="4:12" ht="12.5">
+    <row r="562" spans="4:12">
       <c r="D562" s="7"/>
       <c r="G562" s="8"/>
       <c r="H562" s="8"/>
@@ -33894,7 +33890,7 @@
       <c r="J562" s="7"/>
       <c r="L562" s="7"/>
     </row>
-    <row r="563" spans="4:12" ht="12.5">
+    <row r="563" spans="4:12">
       <c r="D563" s="7"/>
       <c r="G563" s="8"/>
       <c r="H563" s="8"/>
@@ -33902,7 +33898,7 @@
       <c r="J563" s="7"/>
       <c r="L563" s="7"/>
     </row>
-    <row r="564" spans="4:12" ht="12.5">
+    <row r="564" spans="4:12">
       <c r="D564" s="7"/>
       <c r="G564" s="8"/>
       <c r="H564" s="8"/>
@@ -33910,7 +33906,7 @@
       <c r="J564" s="7"/>
       <c r="L564" s="7"/>
     </row>
-    <row r="565" spans="4:12" ht="12.5">
+    <row r="565" spans="4:12">
       <c r="D565" s="7"/>
       <c r="G565" s="8"/>
       <c r="H565" s="8"/>
@@ -33918,7 +33914,7 @@
       <c r="J565" s="7"/>
       <c r="L565" s="7"/>
     </row>
-    <row r="566" spans="4:12" ht="12.5">
+    <row r="566" spans="4:12">
       <c r="D566" s="7"/>
       <c r="G566" s="8"/>
       <c r="H566" s="8"/>
@@ -33926,7 +33922,7 @@
       <c r="J566" s="7"/>
       <c r="L566" s="7"/>
     </row>
-    <row r="567" spans="4:12" ht="12.5">
+    <row r="567" spans="4:12">
       <c r="D567" s="7"/>
       <c r="G567" s="8"/>
       <c r="H567" s="8"/>
@@ -33934,7 +33930,7 @@
       <c r="J567" s="7"/>
       <c r="L567" s="7"/>
     </row>
-    <row r="568" spans="4:12" ht="12.5">
+    <row r="568" spans="4:12">
       <c r="D568" s="7"/>
       <c r="G568" s="8"/>
       <c r="H568" s="8"/>
@@ -33942,7 +33938,7 @@
       <c r="J568" s="7"/>
       <c r="L568" s="7"/>
     </row>
-    <row r="569" spans="4:12" ht="12.5">
+    <row r="569" spans="4:12">
       <c r="D569" s="7"/>
       <c r="G569" s="8"/>
       <c r="H569" s="8"/>
@@ -33950,7 +33946,7 @@
       <c r="J569" s="7"/>
       <c r="L569" s="7"/>
     </row>
-    <row r="570" spans="4:12" ht="12.5">
+    <row r="570" spans="4:12">
       <c r="D570" s="7"/>
       <c r="G570" s="8"/>
       <c r="H570" s="8"/>
@@ -33958,7 +33954,7 @@
       <c r="J570" s="7"/>
       <c r="L570" s="7"/>
     </row>
-    <row r="571" spans="4:12" ht="12.5">
+    <row r="571" spans="4:12">
       <c r="D571" s="7"/>
       <c r="G571" s="8"/>
       <c r="H571" s="8"/>
@@ -33966,7 +33962,7 @@
       <c r="J571" s="7"/>
       <c r="L571" s="7"/>
     </row>
-    <row r="572" spans="4:12" ht="12.5">
+    <row r="572" spans="4:12">
       <c r="D572" s="7"/>
       <c r="G572" s="8"/>
       <c r="H572" s="8"/>
@@ -33974,7 +33970,7 @@
       <c r="J572" s="7"/>
       <c r="L572" s="7"/>
     </row>
-    <row r="573" spans="4:12" ht="12.5">
+    <row r="573" spans="4:12">
       <c r="D573" s="7"/>
       <c r="G573" s="8"/>
       <c r="H573" s="8"/>
@@ -33982,7 +33978,7 @@
       <c r="J573" s="7"/>
       <c r="L573" s="7"/>
     </row>
-    <row r="574" spans="4:12" ht="12.5">
+    <row r="574" spans="4:12">
       <c r="D574" s="7"/>
       <c r="G574" s="8"/>
       <c r="H574" s="8"/>
@@ -33990,7 +33986,7 @@
       <c r="J574" s="7"/>
       <c r="L574" s="7"/>
     </row>
-    <row r="575" spans="4:12" ht="12.5">
+    <row r="575" spans="4:12">
       <c r="D575" s="7"/>
       <c r="G575" s="8"/>
       <c r="H575" s="8"/>
@@ -33998,7 +33994,7 @@
       <c r="J575" s="7"/>
       <c r="L575" s="7"/>
     </row>
-    <row r="576" spans="4:12" ht="12.5">
+    <row r="576" spans="4:12">
       <c r="D576" s="7"/>
       <c r="G576" s="8"/>
       <c r="H576" s="8"/>
@@ -34006,7 +34002,7 @@
       <c r="J576" s="7"/>
       <c r="L576" s="7"/>
     </row>
-    <row r="577" spans="4:12" ht="12.5">
+    <row r="577" spans="4:12">
       <c r="D577" s="7"/>
       <c r="G577" s="8"/>
       <c r="H577" s="8"/>
@@ -34014,7 +34010,7 @@
       <c r="J577" s="7"/>
       <c r="L577" s="7"/>
     </row>
-    <row r="578" spans="4:12" ht="12.5">
+    <row r="578" spans="4:12">
       <c r="D578" s="7"/>
       <c r="G578" s="8"/>
       <c r="H578" s="8"/>
@@ -34022,7 +34018,7 @@
       <c r="J578" s="7"/>
       <c r="L578" s="7"/>
     </row>
-    <row r="579" spans="4:12" ht="12.5">
+    <row r="579" spans="4:12">
       <c r="D579" s="7"/>
       <c r="G579" s="8"/>
       <c r="H579" s="8"/>
@@ -34030,7 +34026,7 @@
       <c r="J579" s="7"/>
       <c r="L579" s="7"/>
     </row>
-    <row r="580" spans="4:12" ht="12.5">
+    <row r="580" spans="4:12">
       <c r="D580" s="7"/>
       <c r="G580" s="8"/>
       <c r="H580" s="8"/>
@@ -34038,7 +34034,7 @@
       <c r="J580" s="7"/>
       <c r="L580" s="7"/>
     </row>
-    <row r="581" spans="4:12" ht="12.5">
+    <row r="581" spans="4:12">
       <c r="D581" s="7"/>
       <c r="G581" s="8"/>
       <c r="H581" s="8"/>
@@ -34046,7 +34042,7 @@
       <c r="J581" s="7"/>
       <c r="L581" s="7"/>
     </row>
-    <row r="582" spans="4:12" ht="12.5">
+    <row r="582" spans="4:12">
       <c r="D582" s="7"/>
       <c r="G582" s="8"/>
       <c r="H582" s="8"/>
@@ -34054,7 +34050,7 @@
       <c r="J582" s="7"/>
       <c r="L582" s="7"/>
     </row>
-    <row r="583" spans="4:12" ht="12.5">
+    <row r="583" spans="4:12">
       <c r="D583" s="7"/>
       <c r="G583" s="8"/>
       <c r="H583" s="8"/>
@@ -34062,7 +34058,7 @@
       <c r="J583" s="7"/>
       <c r="L583" s="7"/>
     </row>
-    <row r="584" spans="4:12" ht="12.5">
+    <row r="584" spans="4:12">
       <c r="D584" s="7"/>
       <c r="G584" s="8"/>
       <c r="H584" s="8"/>
@@ -34070,7 +34066,7 @@
       <c r="J584" s="7"/>
       <c r="L584" s="7"/>
     </row>
-    <row r="585" spans="4:12" ht="12.5">
+    <row r="585" spans="4:12">
       <c r="D585" s="7"/>
       <c r="G585" s="8"/>
       <c r="H585" s="8"/>
@@ -34078,7 +34074,7 @@
       <c r="J585" s="7"/>
       <c r="L585" s="7"/>
     </row>
-    <row r="586" spans="4:12" ht="12.5">
+    <row r="586" spans="4:12">
       <c r="D586" s="7"/>
       <c r="G586" s="8"/>
       <c r="H586" s="8"/>
@@ -34086,7 +34082,7 @@
       <c r="J586" s="7"/>
       <c r="L586" s="7"/>
     </row>
-    <row r="587" spans="4:12" ht="12.5">
+    <row r="587" spans="4:12">
       <c r="D587" s="7"/>
       <c r="G587" s="8"/>
       <c r="H587" s="8"/>
@@ -34094,7 +34090,7 @@
       <c r="J587" s="7"/>
       <c r="L587" s="7"/>
     </row>
-    <row r="588" spans="4:12" ht="12.5">
+    <row r="588" spans="4:12">
       <c r="D588" s="7"/>
       <c r="G588" s="8"/>
       <c r="H588" s="8"/>
@@ -34102,7 +34098,7 @@
       <c r="J588" s="7"/>
       <c r="L588" s="7"/>
     </row>
-    <row r="589" spans="4:12" ht="12.5">
+    <row r="589" spans="4:12">
       <c r="D589" s="7"/>
       <c r="G589" s="8"/>
       <c r="H589" s="8"/>
@@ -34110,7 +34106,7 @@
       <c r="J589" s="7"/>
       <c r="L589" s="7"/>
     </row>
-    <row r="590" spans="4:12" ht="12.5">
+    <row r="590" spans="4:12">
       <c r="D590" s="7"/>
       <c r="G590" s="8"/>
       <c r="H590" s="8"/>
@@ -34118,7 +34114,7 @@
       <c r="J590" s="7"/>
       <c r="L590" s="7"/>
     </row>
-    <row r="591" spans="4:12" ht="12.5">
+    <row r="591" spans="4:12">
       <c r="D591" s="7"/>
       <c r="G591" s="8"/>
       <c r="H591" s="8"/>
@@ -34126,7 +34122,7 @@
       <c r="J591" s="7"/>
       <c r="L591" s="7"/>
     </row>
-    <row r="592" spans="4:12" ht="12.5">
+    <row r="592" spans="4:12">
       <c r="D592" s="7"/>
       <c r="G592" s="8"/>
       <c r="H592" s="8"/>
@@ -34134,7 +34130,7 @@
       <c r="J592" s="7"/>
       <c r="L592" s="7"/>
     </row>
-    <row r="593" spans="4:12" ht="12.5">
+    <row r="593" spans="4:12">
       <c r="D593" s="7"/>
       <c r="G593" s="8"/>
       <c r="H593" s="8"/>
@@ -34142,7 +34138,7 @@
       <c r="J593" s="7"/>
       <c r="L593" s="7"/>
     </row>
-    <row r="594" spans="4:12" ht="12.5">
+    <row r="594" spans="4:12">
       <c r="D594" s="7"/>
       <c r="G594" s="8"/>
       <c r="H594" s="8"/>
@@ -34150,7 +34146,7 @@
       <c r="J594" s="7"/>
       <c r="L594" s="7"/>
     </row>
-    <row r="595" spans="4:12" ht="12.5">
+    <row r="595" spans="4:12">
       <c r="D595" s="7"/>
       <c r="G595" s="8"/>
       <c r="H595" s="8"/>
@@ -34158,7 +34154,7 @@
       <c r="J595" s="7"/>
       <c r="L595" s="7"/>
     </row>
-    <row r="596" spans="4:12" ht="12.5">
+    <row r="596" spans="4:12">
       <c r="D596" s="7"/>
       <c r="G596" s="8"/>
       <c r="H596" s="8"/>
@@ -34166,7 +34162,7 @@
       <c r="J596" s="7"/>
       <c r="L596" s="7"/>
     </row>
-    <row r="597" spans="4:12" ht="12.5">
+    <row r="597" spans="4:12">
       <c r="D597" s="7"/>
       <c r="G597" s="8"/>
       <c r="H597" s="8"/>
@@ -34174,7 +34170,7 @@
       <c r="J597" s="7"/>
       <c r="L597" s="7"/>
     </row>
-    <row r="598" spans="4:12" ht="12.5">
+    <row r="598" spans="4:12">
       <c r="D598" s="7"/>
       <c r="G598" s="8"/>
       <c r="H598" s="8"/>
@@ -34182,7 +34178,7 @@
       <c r="J598" s="7"/>
       <c r="L598" s="7"/>
     </row>
-    <row r="599" spans="4:12" ht="12.5">
+    <row r="599" spans="4:12">
       <c r="D599" s="7"/>
       <c r="G599" s="8"/>
       <c r="H599" s="8"/>
@@ -34190,7 +34186,7 @@
       <c r="J599" s="7"/>
       <c r="L599" s="7"/>
     </row>
-    <row r="600" spans="4:12" ht="12.5">
+    <row r="600" spans="4:12">
       <c r="D600" s="7"/>
       <c r="G600" s="8"/>
       <c r="H600" s="8"/>
@@ -34198,7 +34194,7 @@
       <c r="J600" s="7"/>
       <c r="L600" s="7"/>
     </row>
-    <row r="601" spans="4:12" ht="12.5">
+    <row r="601" spans="4:12">
       <c r="D601" s="7"/>
       <c r="G601" s="8"/>
       <c r="H601" s="8"/>
@@ -34206,7 +34202,7 @@
       <c r="J601" s="7"/>
       <c r="L601" s="7"/>
     </row>
-    <row r="602" spans="4:12" ht="12.5">
+    <row r="602" spans="4:12">
       <c r="D602" s="7"/>
       <c r="G602" s="8"/>
       <c r="H602" s="8"/>
@@ -34214,7 +34210,7 @@
       <c r="J602" s="7"/>
       <c r="L602" s="7"/>
     </row>
-    <row r="603" spans="4:12" ht="12.5">
+    <row r="603" spans="4:12">
       <c r="D603" s="7"/>
       <c r="G603" s="8"/>
       <c r="H603" s="8"/>
@@ -34222,7 +34218,7 @@
       <c r="J603" s="7"/>
       <c r="L603" s="7"/>
     </row>
-    <row r="604" spans="4:12" ht="12.5">
+    <row r="604" spans="4:12">
       <c r="D604" s="7"/>
       <c r="G604" s="8"/>
       <c r="H604" s="8"/>
@@ -34230,7 +34226,7 @@
       <c r="J604" s="7"/>
       <c r="L604" s="7"/>
     </row>
-    <row r="605" spans="4:12" ht="12.5">
+    <row r="605" spans="4:12">
       <c r="D605" s="7"/>
       <c r="G605" s="8"/>
       <c r="H605" s="8"/>
@@ -34238,7 +34234,7 @@
       <c r="J605" s="7"/>
       <c r="L605" s="7"/>
     </row>
-    <row r="606" spans="4:12" ht="12.5">
+    <row r="606" spans="4:12">
       <c r="D606" s="7"/>
       <c r="G606" s="8"/>
       <c r="H606" s="8"/>
@@ -34246,7 +34242,7 @@
       <c r="J606" s="7"/>
       <c r="L606" s="7"/>
     </row>
-    <row r="607" spans="4:12" ht="12.5">
+    <row r="607" spans="4:12">
       <c r="D607" s="7"/>
       <c r="G607" s="8"/>
       <c r="H607" s="8"/>
@@ -34254,7 +34250,7 @@
       <c r="J607" s="7"/>
       <c r="L607" s="7"/>
     </row>
-    <row r="608" spans="4:12" ht="12.5">
+    <row r="608" spans="4:12">
       <c r="D608" s="7"/>
       <c r="G608" s="8"/>
       <c r="H608" s="8"/>
@@ -34262,7 +34258,7 @@
       <c r="J608" s="7"/>
       <c r="L608" s="7"/>
     </row>
-    <row r="609" spans="4:12" ht="12.5">
+    <row r="609" spans="4:12">
       <c r="D609" s="7"/>
       <c r="G609" s="8"/>
       <c r="H609" s="8"/>
@@ -34270,7 +34266,7 @@
       <c r="J609" s="7"/>
       <c r="L609" s="7"/>
     </row>
-    <row r="610" spans="4:12" ht="12.5">
+    <row r="610" spans="4:12">
       <c r="D610" s="7"/>
       <c r="G610" s="8"/>
       <c r="H610" s="8"/>
@@ -34278,7 +34274,7 @@
       <c r="J610" s="7"/>
       <c r="L610" s="7"/>
     </row>
-    <row r="611" spans="4:12" ht="12.5">
+    <row r="611" spans="4:12">
       <c r="D611" s="7"/>
       <c r="G611" s="8"/>
       <c r="H611" s="8"/>
@@ -34286,7 +34282,7 @@
       <c r="J611" s="7"/>
       <c r="L611" s="7"/>
     </row>
-    <row r="612" spans="4:12" ht="12.5">
+    <row r="612" spans="4:12">
       <c r="D612" s="7"/>
       <c r="G612" s="8"/>
       <c r="H612" s="8"/>
@@ -34294,7 +34290,7 @@
       <c r="J612" s="7"/>
       <c r="L612" s="7"/>
     </row>
-    <row r="613" spans="4:12" ht="12.5">
+    <row r="613" spans="4:12">
       <c r="D613" s="7"/>
       <c r="G613" s="8"/>
       <c r="H613" s="8"/>
@@ -34302,7 +34298,7 @@
       <c r="J613" s="7"/>
       <c r="L613" s="7"/>
     </row>
-    <row r="614" spans="4:12" ht="12.5">
+    <row r="614" spans="4:12">
       <c r="D614" s="7"/>
       <c r="G614" s="8"/>
       <c r="H614" s="8"/>
@@ -34310,7 +34306,7 @@
       <c r="J614" s="7"/>
       <c r="L614" s="7"/>
     </row>
-    <row r="615" spans="4:12" ht="12.5">
+    <row r="615" spans="4:12">
       <c r="D615" s="7"/>
       <c r="G615" s="8"/>
       <c r="H615" s="8"/>
@@ -34318,7 +34314,7 @@
       <c r="J615" s="7"/>
       <c r="L615" s="7"/>
     </row>
-    <row r="616" spans="4:12" ht="12.5">
+    <row r="616" spans="4:12">
       <c r="D616" s="7"/>
       <c r="G616" s="8"/>
       <c r="H616" s="8"/>
@@ -34326,7 +34322,7 @@
       <c r="J616" s="7"/>
       <c r="L616" s="7"/>
     </row>
-    <row r="617" spans="4:12" ht="12.5">
+    <row r="617" spans="4:12">
       <c r="D617" s="7"/>
       <c r="G617" s="8"/>
       <c r="H617" s="8"/>
@@ -34334,7 +34330,7 @@
       <c r="J617" s="7"/>
       <c r="L617" s="7"/>
     </row>
-    <row r="618" spans="4:12" ht="12.5">
+    <row r="618" spans="4:12">
       <c r="D618" s="7"/>
       <c r="G618" s="8"/>
       <c r="H618" s="8"/>
@@ -34342,7 +34338,7 @@
       <c r="J618" s="7"/>
       <c r="L618" s="7"/>
     </row>
-    <row r="619" spans="4:12" ht="12.5">
+    <row r="619" spans="4:12">
       <c r="D619" s="7"/>
       <c r="G619" s="8"/>
       <c r="H619" s="8"/>
@@ -34350,7 +34346,7 @@
       <c r="J619" s="7"/>
       <c r="L619" s="7"/>
     </row>
-    <row r="620" spans="4:12" ht="12.5">
+    <row r="620" spans="4:12">
       <c r="D620" s="7"/>
       <c r="G620" s="8"/>
       <c r="H620" s="8"/>
@@ -34358,7 +34354,7 @@
       <c r="J620" s="7"/>
       <c r="L620" s="7"/>
     </row>
-    <row r="621" spans="4:12" ht="12.5">
+    <row r="621" spans="4:12">
       <c r="D621" s="7"/>
       <c r="G621" s="8"/>
       <c r="H621" s="8"/>
@@ -34366,7 +34362,7 @@
       <c r="J621" s="7"/>
       <c r="L621" s="7"/>
     </row>
-    <row r="622" spans="4:12" ht="12.5">
+    <row r="622" spans="4:12">
       <c r="D622" s="7"/>
       <c r="G622" s="8"/>
       <c r="H622" s="8"/>
@@ -34374,7 +34370,7 @@
       <c r="J622" s="7"/>
       <c r="L622" s="7"/>
     </row>
-    <row r="623" spans="4:12" ht="12.5">
+    <row r="623" spans="4:12">
       <c r="D623" s="7"/>
       <c r="G623" s="8"/>
       <c r="H623" s="8"/>
@@ -34382,7 +34378,7 @@
       <c r="J623" s="7"/>
       <c r="L623" s="7"/>
     </row>
-    <row r="624" spans="4:12" ht="12.5">
+    <row r="624" spans="4:12">
       <c r="D624" s="7"/>
       <c r="G624" s="8"/>
       <c r="H624" s="8"/>
@@ -34390,7 +34386,7 @@
       <c r="J624" s="7"/>
       <c r="L624" s="7"/>
     </row>
-    <row r="625" spans="4:12" ht="12.5">
+    <row r="625" spans="4:12">
       <c r="D625" s="7"/>
       <c r="G625" s="8"/>
       <c r="H625" s="8"/>
@@ -34398,7 +34394,7 @@
       <c r="J625" s="7"/>
       <c r="L625" s="7"/>
     </row>
-    <row r="626" spans="4:12" ht="12.5">
+    <row r="626" spans="4:12">
       <c r="D626" s="7"/>
       <c r="G626" s="8"/>
       <c r="H626" s="8"/>
@@ -34406,7 +34402,7 @@
       <c r="J626" s="7"/>
       <c r="L626" s="7"/>
     </row>
-    <row r="627" spans="4:12" ht="12.5">
+    <row r="627" spans="4:12">
       <c r="D627" s="7"/>
       <c r="G627" s="8"/>
       <c r="H627" s="8"/>
@@ -34414,7 +34410,7 @@
       <c r="J627" s="7"/>
       <c r="L627" s="7"/>
     </row>
-    <row r="628" spans="4:12" ht="12.5">
+    <row r="628" spans="4:12">
       <c r="D628" s="7"/>
       <c r="G628" s="8"/>
       <c r="H628" s="8"/>
@@ -34422,7 +34418,7 @@
       <c r="J628" s="7"/>
       <c r="L628" s="7"/>
     </row>
-    <row r="629" spans="4:12" ht="12.5">
+    <row r="629" spans="4:12">
       <c r="D629" s="7"/>
       <c r="G629" s="8"/>
       <c r="H629" s="8"/>
@@ -34430,7 +34426,7 @@
       <c r="J629" s="7"/>
       <c r="L629" s="7"/>
     </row>
-    <row r="630" spans="4:12" ht="12.5">
+    <row r="630" spans="4:12">
       <c r="D630" s="7"/>
       <c r="G630" s="8"/>
       <c r="H630" s="8"/>
@@ -34438,7 +34434,7 @@
       <c r="J630" s="7"/>
       <c r="L630" s="7"/>
     </row>
-    <row r="631" spans="4:12" ht="12.5">
+    <row r="631" spans="4:12">
       <c r="D631" s="7"/>
       <c r="G631" s="8"/>
       <c r="H631" s="8"/>
@@ -34446,7 +34442,7 @@
       <c r="J631" s="7"/>
       <c r="L631" s="7"/>
     </row>
-    <row r="632" spans="4:12" ht="12.5">
+    <row r="632" spans="4:12">
       <c r="D632" s="7"/>
       <c r="G632" s="8"/>
       <c r="H632" s="8"/>
@@ -34454,7 +34450,7 @@
       <c r="J632" s="7"/>
       <c r="L632" s="7"/>
     </row>
-    <row r="633" spans="4:12" ht="12.5">
+    <row r="633" spans="4:12">
       <c r="D633" s="7"/>
       <c r="G633" s="8"/>
       <c r="H633" s="8"/>
@@ -34462,7 +34458,7 @@
       <c r="J633" s="7"/>
       <c r="L633" s="7"/>
     </row>
-    <row r="634" spans="4:12" ht="12.5">
+    <row r="634" spans="4:12">
       <c r="D634" s="7"/>
       <c r="G634" s="8"/>
       <c r="H634" s="8"/>
@@ -34470,7 +34466,7 @@
       <c r="J634" s="7"/>
       <c r="L634" s="7"/>
     </row>
-    <row r="635" spans="4:12" ht="12.5">
+    <row r="635" spans="4:12">
       <c r="D635" s="7"/>
       <c r="G635" s="8"/>
       <c r="H635" s="8"/>
@@ -34478,7 +34474,7 @@
       <c r="J635" s="7"/>
       <c r="L635" s="7"/>
     </row>
-    <row r="636" spans="4:12" ht="12.5">
+    <row r="636" spans="4:12">
       <c r="D636" s="7"/>
       <c r="G636" s="8"/>
       <c r="H636" s="8"/>
@@ -34486,7 +34482,7 @@
       <c r="J636" s="7"/>
       <c r="L636" s="7"/>
     </row>
-    <row r="637" spans="4:12" ht="12.5">
+    <row r="637" spans="4:12">
       <c r="D637" s="7"/>
       <c r="G637" s="8"/>
       <c r="H637" s="8"/>
@@ -34494,7 +34490,7 @@
       <c r="J637" s="7"/>
       <c r="L637" s="7"/>
     </row>
-    <row r="638" spans="4:12" ht="12.5">
+    <row r="638" spans="4:12">
       <c r="D638" s="7"/>
       <c r="G638" s="8"/>
       <c r="H638" s="8"/>
@@ -34502,7 +34498,7 @@
       <c r="J638" s="7"/>
       <c r="L638" s="7"/>
     </row>
-    <row r="639" spans="4:12" ht="12.5">
+    <row r="639" spans="4:12">
       <c r="D639" s="7"/>
       <c r="G639" s="8"/>
       <c r="H639" s="8"/>
@@ -34510,7 +34506,7 @@
       <c r="J639" s="7"/>
       <c r="L639" s="7"/>
     </row>
-    <row r="640" spans="4:12" ht="12.5">
+    <row r="640" spans="4:12">
       <c r="D640" s="7"/>
       <c r="G640" s="8"/>
       <c r="H640" s="8"/>
@@ -34518,7 +34514,7 @@
       <c r="J640" s="7"/>
       <c r="L640" s="7"/>
     </row>
-    <row r="641" spans="4:12" ht="12.5">
+    <row r="641" spans="4:12">
       <c r="D641" s="7"/>
       <c r="G641" s="8"/>
       <c r="H641" s="8"/>
@@ -34526,7 +34522,7 @@
       <c r="J641" s="7"/>
       <c r="L641" s="7"/>
     </row>
-    <row r="642" spans="4:12" ht="12.5">
+    <row r="642" spans="4:12">
       <c r="D642" s="7"/>
       <c r="G642" s="8"/>
       <c r="H642" s="8"/>
@@ -34534,7 +34530,7 @@
       <c r="J642" s="7"/>
       <c r="L642" s="7"/>
     </row>
-    <row r="643" spans="4:12" ht="12.5">
+    <row r="643" spans="4:12">
       <c r="D643" s="7"/>
       <c r="G643" s="8"/>
       <c r="H643" s="8"/>
@@ -34542,7 +34538,7 @@
       <c r="J643" s="7"/>
       <c r="L643" s="7"/>
     </row>
-    <row r="644" spans="4:12" ht="12.5">
+    <row r="644" spans="4:12">
       <c r="D644" s="7"/>
       <c r="G644" s="8"/>
       <c r="H644" s="8"/>
@@ -34550,7 +34546,7 @@
       <c r="J644" s="7"/>
       <c r="L644" s="7"/>
     </row>
-    <row r="645" spans="4:12" ht="12.5">
+    <row r="645" spans="4:12">
       <c r="D645" s="7"/>
       <c r="G645" s="8"/>
       <c r="H645" s="8"/>
@@ -34558,7 +34554,7 @@
       <c r="J645" s="7"/>
       <c r="L645" s="7"/>
     </row>
-    <row r="646" spans="4:12" ht="12.5">
+    <row r="646" spans="4:12">
       <c r="D646" s="7"/>
       <c r="G646" s="8"/>
       <c r="H646" s="8"/>
@@ -34566,7 +34562,7 @@
       <c r="J646" s="7"/>
       <c r="L646" s="7"/>
     </row>
-    <row r="647" spans="4:12" ht="12.5">
+    <row r="647" spans="4:12">
       <c r="D647" s="7"/>
       <c r="G647" s="8"/>
       <c r="H647" s="8"/>
@@ -34574,7 +34570,7 @@
       <c r="J647" s="7"/>
       <c r="L647" s="7"/>
     </row>
-    <row r="648" spans="4:12" ht="12.5">
+    <row r="648" spans="4:12">
       <c r="D648" s="7"/>
       <c r="G648" s="8"/>
       <c r="H648" s="8"/>
@@ -34582,7 +34578,7 @@
       <c r="J648" s="7"/>
       <c r="L648" s="7"/>
     </row>
-    <row r="649" spans="4:12" ht="12.5">
+    <row r="649" spans="4:12">
       <c r="D649" s="7"/>
       <c r="G649" s="8"/>
       <c r="H649" s="8"/>
@@ -34590,7 +34586,7 @@
       <c r="J649" s="7"/>
       <c r="L649" s="7"/>
     </row>
-    <row r="650" spans="4:12" ht="12.5">
+    <row r="650" spans="4:12">
       <c r="D650" s="7"/>
       <c r="G650" s="8"/>
       <c r="H650" s="8"/>
@@ -34598,7 +34594,7 @@
       <c r="J650" s="7"/>
       <c r="L650" s="7"/>
     </row>
-    <row r="651" spans="4:12" ht="12.5">
+    <row r="651" spans="4:12">
       <c r="D651" s="7"/>
       <c r="G651" s="8"/>
       <c r="H651" s="8"/>
@@ -34606,7 +34602,7 @@
       <c r="J651" s="7"/>
       <c r="L651" s="7"/>
     </row>
-    <row r="652" spans="4:12" ht="12.5">
+    <row r="652" spans="4:12">
       <c r="D652" s="7"/>
       <c r="G652" s="8"/>
       <c r="H652" s="8"/>
@@ -34614,7 +34610,7 @@
       <c r="J652" s="7"/>
       <c r="L652" s="7"/>
     </row>
-    <row r="653" spans="4:12" ht="12.5">
+    <row r="653" spans="4:12">
       <c r="D653" s="7"/>
       <c r="G653" s="8"/>
       <c r="H653" s="8"/>
@@ -34622,7 +34618,7 @@
       <c r="J653" s="7"/>
       <c r="L653" s="7"/>
     </row>
-    <row r="654" spans="4:12" ht="12.5">
+    <row r="654" spans="4:12">
       <c r="D654" s="7"/>
       <c r="G654" s="8"/>
       <c r="H654" s="8"/>
@@ -34630,7 +34626,7 @@
       <c r="J654" s="7"/>
       <c r="L654" s="7"/>
     </row>
-    <row r="655" spans="4:12" ht="12.5">
+    <row r="655" spans="4:12">
       <c r="D655" s="7"/>
       <c r="G655" s="8"/>
       <c r="H655" s="8"/>
@@ -34638,7 +34634,7 @@
       <c r="J655" s="7"/>
       <c r="L655" s="7"/>
     </row>
-    <row r="656" spans="4:12" ht="12.5">
+    <row r="656" spans="4:12">
       <c r="D656" s="7"/>
       <c r="G656" s="8"/>
       <c r="H656" s="8"/>
@@ -34646,7 +34642,7 @@
       <c r="J656" s="7"/>
       <c r="L656" s="7"/>
     </row>
-    <row r="657" spans="4:12" ht="12.5">
+    <row r="657" spans="4:12">
       <c r="D657" s="7"/>
       <c r="G657" s="8"/>
       <c r="H657" s="8"/>
@@ -34654,7 +34650,7 @@
       <c r="J657" s="7"/>
       <c r="L657" s="7"/>
     </row>
-    <row r="658" spans="4:12" ht="12.5">
+    <row r="658" spans="4:12">
       <c r="D658" s="7"/>
       <c r="G658" s="8"/>
       <c r="H658" s="8"/>
@@ -34662,7 +34658,7 @@
       <c r="J658" s="7"/>
       <c r="L658" s="7"/>
     </row>
-    <row r="659" spans="4:12" ht="12.5">
+    <row r="659" spans="4:12">
       <c r="D659" s="7"/>
       <c r="G659" s="8"/>
       <c r="H659" s="8"/>
@@ -34670,7 +34666,7 @@
       <c r="J659" s="7"/>
       <c r="L659" s="7"/>
     </row>
-    <row r="660" spans="4:12" ht="12.5">
+    <row r="660" spans="4:12">
       <c r="D660" s="7"/>
       <c r="G660" s="8"/>
       <c r="H660" s="8"/>
@@ -34678,7 +34674,7 @@
       <c r="J660" s="7"/>
       <c r="L660" s="7"/>
     </row>
-    <row r="661" spans="4:12" ht="12.5">
+    <row r="661" spans="4:12">
       <c r="D661" s="7"/>
       <c r="G661" s="8"/>
       <c r="H661" s="8"/>
@@ -34686,7 +34682,7 @@
       <c r="J661" s="7"/>
       <c r="L661" s="7"/>
     </row>
-    <row r="662" spans="4:12" ht="12.5">
+    <row r="662" spans="4:12">
       <c r="D662" s="7"/>
       <c r="G662" s="8"/>
       <c r="H662" s="8"/>
@@ -34694,7 +34690,7 @@
       <c r="J662" s="7"/>
       <c r="L662" s="7"/>
     </row>
-    <row r="663" spans="4:12" ht="12.5">
+    <row r="663" spans="4:12">
       <c r="D663" s="7"/>
       <c r="G663" s="8"/>
       <c r="H663" s="8"/>
@@ -34702,7 +34698,7 @@
       <c r="J663" s="7"/>
       <c r="L663" s="7"/>
     </row>
-    <row r="664" spans="4:12" ht="12.5">
+    <row r="664" spans="4:12">
       <c r="D664" s="7"/>
       <c r="G664" s="8"/>
       <c r="H664" s="8"/>
@@ -34710,7 +34706,7 @@
       <c r="J664" s="7"/>
       <c r="L664" s="7"/>
     </row>
-    <row r="665" spans="4:12" ht="12.5">
+    <row r="665" spans="4:12">
       <c r="D665" s="7"/>
       <c r="G665" s="8"/>
       <c r="H665" s="8"/>
@@ -34718,7 +34714,7 @@
       <c r="J665" s="7"/>
       <c r="L665" s="7"/>
     </row>
-    <row r="666" spans="4:12" ht="12.5">
+    <row r="666" spans="4:12">
       <c r="D666" s="7"/>
       <c r="G666" s="8"/>
       <c r="H666" s="8"/>
@@ -34726,7 +34722,7 @@
       <c r="J666" s="7"/>
       <c r="L666" s="7"/>
     </row>
-    <row r="667" spans="4:12" ht="12.5">
+    <row r="667" spans="4:12">
       <c r="D667" s="7"/>
       <c r="G667" s="8"/>
       <c r="H667" s="8"/>
@@ -34734,7 +34730,7 @@
       <c r="J667" s="7"/>
       <c r="L667" s="7"/>
     </row>
-    <row r="668" spans="4:12" ht="12.5">
+    <row r="668" spans="4:12">
       <c r="D668" s="7"/>
       <c r="G668" s="8"/>
       <c r="H668" s="8"/>
@@ -34742,7 +34738,7 @@
       <c r="J668" s="7"/>
       <c r="L668" s="7"/>
     </row>
-    <row r="669" spans="4:12" ht="12.5">
+    <row r="669" spans="4:12">
       <c r="D669" s="7"/>
       <c r="G669" s="8"/>
       <c r="H669" s="8"/>
@@ -34750,7 +34746,7 @@
       <c r="J669" s="7"/>
       <c r="L669" s="7"/>
     </row>
-    <row r="670" spans="4:12" ht="12.5">
+    <row r="670" spans="4:12">
       <c r="D670" s="7"/>
       <c r="G670" s="8"/>
       <c r="H670" s="8"/>
@@ -34758,7 +34754,7 @@
       <c r="J670" s="7"/>
       <c r="L670" s="7"/>
     </row>
-    <row r="671" spans="4:12" ht="12.5">
+    <row r="671" spans="4:12">
       <c r="D671" s="7"/>
       <c r="G671" s="8"/>
       <c r="H671" s="8"/>
@@ -34766,7 +34762,7 @@
       <c r="J671" s="7"/>
       <c r="L671" s="7"/>
     </row>
-    <row r="672" spans="4:12" ht="12.5">
+    <row r="672" spans="4:12">
       <c r="D672" s="7"/>
       <c r="G672" s="8"/>
       <c r="H672" s="8"/>
@@ -34774,7 +34770,7 @@
       <c r="J672" s="7"/>
       <c r="L672" s="7"/>
     </row>
-    <row r="673" spans="4:12" ht="12.5">
+    <row r="673" spans="4:12">
       <c r="D673" s="7"/>
       <c r="G673" s="8"/>
       <c r="H673" s="8"/>
@@ -34782,7 +34778,7 @@
       <c r="J673" s="7"/>
       <c r="L673" s="7"/>
     </row>
-    <row r="674" spans="4:12" ht="12.5">
+    <row r="674" spans="4:12">
       <c r="D674" s="7"/>
       <c r="G674" s="8"/>
       <c r="H674" s="8"/>
@@ -34790,7 +34786,7 @@
       <c r="J674" s="7"/>
       <c r="L674" s="7"/>
     </row>
-    <row r="675" spans="4:12" ht="12.5">
+    <row r="675" spans="4:12">
       <c r="D675" s="7"/>
       <c r="G675" s="8"/>
       <c r="H675" s="8"/>
@@ -34798,7 +34794,7 @@
       <c r="J675" s="7"/>
       <c r="L675" s="7"/>
     </row>
-    <row r="676" spans="4:12" ht="12.5">
+    <row r="676" spans="4:12">
       <c r="D676" s="7"/>
       <c r="G676" s="8"/>
       <c r="H676" s="8"/>
@@ -34806,7 +34802,7 @@
       <c r="J676" s="7"/>
       <c r="L676" s="7"/>
     </row>
-    <row r="677" spans="4:12" ht="12.5">
+    <row r="677" spans="4:12">
       <c r="D677" s="7"/>
       <c r="G677" s="8"/>
       <c r="H677" s="8"/>
@@ -34814,7 +34810,7 @@
       <c r="J677" s="7"/>
       <c r="L677" s="7"/>
     </row>
-    <row r="678" spans="4:12" ht="12.5">
+    <row r="678" spans="4:12">
       <c r="D678" s="7"/>
       <c r="G678" s="8"/>
       <c r="H678" s="8"/>
@@ -34822,7 +34818,7 @@
       <c r="J678" s="7"/>
       <c r="L678" s="7"/>
     </row>
-    <row r="679" spans="4:12" ht="12.5">
+    <row r="679" spans="4:12">
       <c r="D679" s="7"/>
       <c r="G679" s="8"/>
       <c r="H679" s="8"/>
@@ -34830,7 +34826,7 @@
       <c r="J679" s="7"/>
       <c r="L679" s="7"/>
     </row>
-    <row r="680" spans="4:12" ht="12.5">
+    <row r="680" spans="4:12">
       <c r="D680" s="7"/>
       <c r="G680" s="8"/>
       <c r="H680" s="8"/>
@@ -34838,7 +34834,7 @@
       <c r="J680" s="7"/>
       <c r="L680" s="7"/>
     </row>
-    <row r="681" spans="4:12" ht="12.5">
+    <row r="681" spans="4:12">
       <c r="D681" s="7"/>
       <c r="G681" s="8"/>
       <c r="H681" s="8"/>
@@ -34846,7 +34842,7 @@
       <c r="J681" s="7"/>
       <c r="L681" s="7"/>
     </row>
-    <row r="682" spans="4:12" ht="12.5">
+    <row r="682" spans="4:12">
       <c r="D682" s="7"/>
       <c r="G682" s="8"/>
       <c r="H682" s="8"/>
@@ -34854,7 +34850,7 @@
       <c r="J682" s="7"/>
       <c r="L682" s="7"/>
     </row>
-    <row r="683" spans="4:12" ht="12.5">
+    <row r="683" spans="4:12">
       <c r="D683" s="7"/>
       <c r="G683" s="8"/>
       <c r="H683" s="8"/>
@@ -34862,7 +34858,7 @@
       <c r="J683" s="7"/>
       <c r="L683" s="7"/>
     </row>
-    <row r="684" spans="4:12" ht="12.5">
+    <row r="684" spans="4:12">
       <c r="D684" s="7"/>
       <c r="G684" s="8"/>
       <c r="H684" s="8"/>
@@ -34870,7 +34866,7 @@
       <c r="J684" s="7"/>
       <c r="L684" s="7"/>
     </row>
-    <row r="685" spans="4:12" ht="12.5">
+    <row r="685" spans="4:12">
       <c r="D685" s="7"/>
       <c r="G685" s="8"/>
       <c r="H685" s="8"/>
@@ -34878,7 +34874,7 @@
       <c r="J685" s="7"/>
       <c r="L685" s="7"/>
     </row>
-    <row r="686" spans="4:12" ht="12.5">
+    <row r="686" spans="4:12">
       <c r="D686" s="7"/>
       <c r="G686" s="8"/>
       <c r="H686" s="8"/>
@@ -34886,7 +34882,7 @@
       <c r="J686" s="7"/>
       <c r="L686" s="7"/>
     </row>
-    <row r="687" spans="4:12" ht="12.5">
+    <row r="687" spans="4:12">
       <c r="D687" s="7"/>
       <c r="G687" s="8"/>
       <c r="H687" s="8"/>
@@ -34894,7 +34890,7 @@
       <c r="J687" s="7"/>
       <c r="L687" s="7"/>
     </row>
-    <row r="688" spans="4:12" ht="12.5">
+    <row r="688" spans="4:12">
       <c r="D688" s="7"/>
       <c r="G688" s="8"/>
       <c r="H688" s="8"/>
@@ -34902,7 +34898,7 @@
       <c r="J688" s="7"/>
       <c r="L688" s="7"/>
     </row>
-    <row r="689" spans="4:12" ht="12.5">
+    <row r="689" spans="4:12">
       <c r="D689" s="7"/>
       <c r="G689" s="8"/>
       <c r="H689" s="8"/>
@@ -34910,7 +34906,7 @@
       <c r="J689" s="7"/>
       <c r="L689" s="7"/>
     </row>
-    <row r="690" spans="4:12" ht="12.5">
+    <row r="690" spans="4:12">
       <c r="D690" s="7"/>
       <c r="G690" s="8"/>
       <c r="H690" s="8"/>
@@ -34918,7 +34914,7 @@
       <c r="J690" s="7"/>
       <c r="L690" s="7"/>
     </row>
-    <row r="691" spans="4:12" ht="12.5">
+    <row r="691" spans="4:12">
       <c r="D691" s="7"/>
       <c r="G691" s="8"/>
       <c r="H691" s="8"/>
@@ -34926,7 +34922,7 @@
       <c r="J691" s="7"/>
       <c r="L691" s="7"/>
     </row>
-    <row r="692" spans="4:12" ht="12.5">
+    <row r="692" spans="4:12">
       <c r="D692" s="7"/>
       <c r="G692" s="8"/>
       <c r="H692" s="8"/>
@@ -34934,7 +34930,7 @@
       <c r="J692" s="7"/>
       <c r="L692" s="7"/>
     </row>
-    <row r="693" spans="4:12" ht="12.5">
+    <row r="693" spans="4:12">
       <c r="D693" s="7"/>
       <c r="G693" s="8"/>
       <c r="H693" s="8"/>
@@ -34942,7 +34938,7 @@
       <c r="J693" s="7"/>
       <c r="L693" s="7"/>
     </row>
-    <row r="694" spans="4:12" ht="12.5">
+    <row r="694" spans="4:12">
       <c r="D694" s="7"/>
       <c r="G694" s="8"/>
       <c r="H694" s="8"/>
@@ -34950,7 +34946,7 @@
       <c r="J694" s="7"/>
       <c r="L694" s="7"/>
     </row>
-    <row r="695" spans="4:12" ht="12.5">
+    <row r="695" spans="4:12">
       <c r="D695" s="7"/>
       <c r="G695" s="8"/>
       <c r="H695" s="8"/>
@@ -34958,7 +34954,7 @@
       <c r="J695" s="7"/>
       <c r="L695" s="7"/>
     </row>
-    <row r="696" spans="4:12" ht="12.5">
+    <row r="696" spans="4:12">
       <c r="D696" s="7"/>
       <c r="G696" s="8"/>
       <c r="H696" s="8"/>
@@ -34966,7 +34962,7 @@
       <c r="J696" s="7"/>
       <c r="L696" s="7"/>
     </row>
-    <row r="697" spans="4:12" ht="12.5">
+    <row r="697" spans="4:12">
       <c r="D697" s="7"/>
       <c r="G697" s="8"/>
       <c r="H697" s="8"/>
@@ -34974,7 +34970,7 @@
       <c r="J697" s="7"/>
       <c r="L697" s="7"/>
     </row>
-    <row r="698" spans="4:12" ht="12.5">
+    <row r="698" spans="4:12">
       <c r="D698" s="7"/>
       <c r="G698" s="8"/>
       <c r="H698" s="8"/>
@@ -34982,7 +34978,7 @@
       <c r="J698" s="7"/>
       <c r="L698" s="7"/>
     </row>
-    <row r="699" spans="4:12" ht="12.5">
+    <row r="699" spans="4:12">
       <c r="D699" s="7"/>
       <c r="G699" s="8"/>
       <c r="H699" s="8"/>
@@ -34990,7 +34986,7 @@
       <c r="J699" s="7"/>
       <c r="L699" s="7"/>
     </row>
-    <row r="700" spans="4:12" ht="12.5">
+    <row r="700" spans="4:12">
       <c r="D700" s="7"/>
       <c r="G700" s="8"/>
       <c r="H700" s="8"/>
@@ -34998,7 +34994,7 @@
       <c r="J700" s="7"/>
       <c r="L700" s="7"/>
     </row>
-    <row r="701" spans="4:12" ht="12.5">
+    <row r="701" spans="4:12">
       <c r="D701" s="7"/>
       <c r="G701" s="8"/>
       <c r="H701" s="8"/>
@@ -35006,7 +35002,7 @@
       <c r="J701" s="7"/>
       <c r="L701" s="7"/>
     </row>
-    <row r="702" spans="4:12" ht="12.5">
+    <row r="702" spans="4:12">
       <c r="D702" s="7"/>
       <c r="G702" s="8"/>
       <c r="H702" s="8"/>
@@ -35014,7 +35010,7 @@
       <c r="J702" s="7"/>
       <c r="L702" s="7"/>
     </row>
-    <row r="703" spans="4:12" ht="12.5">
+    <row r="703" spans="4:12">
       <c r="D703" s="7"/>
       <c r="G703" s="8"/>
       <c r="H703" s="8"/>
@@ -35022,7 +35018,7 @@
       <c r="J703" s="7"/>
       <c r="L703" s="7"/>
     </row>
-    <row r="704" spans="4:12" ht="12.5">
+    <row r="704" spans="4:12">
       <c r="D704" s="7"/>
       <c r="G704" s="8"/>
       <c r="H704" s="8"/>
@@ -35030,7 +35026,7 @@
       <c r="J704" s="7"/>
       <c r="L704" s="7"/>
     </row>
-    <row r="705" spans="4:12" ht="12.5">
+    <row r="705" spans="4:12">
       <c r="D705" s="7"/>
       <c r="G705" s="8"/>
       <c r="H705" s="8"/>
@@ -35038,7 +35034,7 @@
       <c r="J705" s="7"/>
       <c r="L705" s="7"/>
     </row>
-    <row r="706" spans="4:12" ht="12.5">
+    <row r="706" spans="4:12">
       <c r="D706" s="7"/>
       <c r="G706" s="8"/>
       <c r="H706" s="8"/>
@@ -35046,7 +35042,7 @@
       <c r="J706" s="7"/>
       <c r="L706" s="7"/>
     </row>
-    <row r="707" spans="4:12" ht="12.5">
+    <row r="707" spans="4:12">
       <c r="D707" s="7"/>
       <c r="G707" s="8"/>
       <c r="H707" s="8"/>
@@ -35054,7 +35050,7 @@
       <c r="J707" s="7"/>
       <c r="L707" s="7"/>
     </row>
-    <row r="708" spans="4:12" ht="12.5">
+    <row r="708" spans="4:12">
       <c r="D708" s="7"/>
       <c r="G708" s="8"/>
       <c r="H708" s="8"/>
@@ -35062,7 +35058,7 @@
       <c r="J708" s="7"/>
       <c r="L708" s="7"/>
     </row>
-    <row r="709" spans="4:12" ht="12.5">
+    <row r="709" spans="4:12">
       <c r="D709" s="7"/>
       <c r="G709" s="8"/>
       <c r="H709" s="8"/>
@@ -35070,7 +35066,7 @@
       <c r="J709" s="7"/>
       <c r="L709" s="7"/>
     </row>
-    <row r="710" spans="4:12" ht="12.5">
+    <row r="710" spans="4:12">
       <c r="D710" s="7"/>
       <c r="G710" s="8"/>
       <c r="H710" s="8"/>
@@ -35078,7 +35074,7 @@
       <c r="J710" s="7"/>
       <c r="L710" s="7"/>
     </row>
-    <row r="711" spans="4:12" ht="12.5">
+    <row r="711" spans="4:12">
       <c r="D711" s="7"/>
       <c r="G711" s="8"/>
       <c r="H711" s="8"/>
@@ -35086,7 +35082,7 @@
       <c r="J711" s="7"/>
       <c r="L711" s="7"/>
     </row>
-    <row r="712" spans="4:12" ht="12.5">
+    <row r="712" spans="4:12">
       <c r="D712" s="7"/>
       <c r="G712" s="8"/>
       <c r="H712" s="8"/>
@@ -35094,7 +35090,7 @@
       <c r="J712" s="7"/>
       <c r="L712" s="7"/>
     </row>
-    <row r="713" spans="4:12" ht="12.5">
+    <row r="713" spans="4:12">
       <c r="D713" s="7"/>
       <c r="G713" s="8"/>
       <c r="H713" s="8"/>
@@ -35102,7 +35098,7 @@
       <c r="J713" s="7"/>
       <c r="L713" s="7"/>
     </row>
-    <row r="714" spans="4:12" ht="12.5">
+    <row r="714" spans="4:12">
       <c r="D714" s="7"/>
       <c r="G714" s="8"/>
       <c r="H714" s="8"/>
@@ -35110,7 +35106,7 @@
       <c r="J714" s="7"/>
       <c r="L714" s="7"/>
     </row>
-    <row r="715" spans="4:12" ht="12.5">
+    <row r="715" spans="4:12">
       <c r="D715" s="7"/>
       <c r="G715" s="8"/>
       <c r="H715" s="8"/>
@@ -35118,7 +35114,7 @@
       <c r="J715" s="7"/>
       <c r="L715" s="7"/>
     </row>
-    <row r="716" spans="4:12" ht="12.5">
+    <row r="716" spans="4:12">
       <c r="D716" s="7"/>
       <c r="G716" s="8"/>
       <c r="H716" s="8"/>
@@ -35126,7 +35122,7 @@
       <c r="J716" s="7"/>
       <c r="L716" s="7"/>
     </row>
-    <row r="717" spans="4:12" ht="12.5">
+    <row r="717" spans="4:12">
       <c r="D717" s="7"/>
       <c r="G717" s="8"/>
       <c r="H717" s="8"/>
@@ -35134,7 +35130,7 @@
       <c r="J717" s="7"/>
       <c r="L717" s="7"/>
     </row>
-    <row r="718" spans="4:12" ht="12.5">
+    <row r="718" spans="4:12">
       <c r="D718" s="7"/>
       <c r="G718" s="8"/>
       <c r="H718" s="8"/>
@@ -35142,7 +35138,7 @@
       <c r="J718" s="7"/>
       <c r="L718" s="7"/>
     </row>
-    <row r="719" spans="4:12" ht="12.5">
+    <row r="719" spans="4:12">
       <c r="D719" s="7"/>
       <c r="G719" s="8"/>
       <c r="H719" s="8"/>
@@ -35150,7 +35146,7 @@
       <c r="J719" s="7"/>
       <c r="L719" s="7"/>
     </row>
-    <row r="720" spans="4:12" ht="12.5">
+    <row r="720" spans="4:12">
       <c r="D720" s="7"/>
       <c r="G720" s="8"/>
       <c r="H720" s="8"/>
@@ -35158,7 +35154,7 @@
       <c r="J720" s="7"/>
       <c r="L720" s="7"/>
     </row>
-    <row r="721" spans="4:12" ht="12.5">
+    <row r="721" spans="4:12">
       <c r="D721" s="7"/>
       <c r="G721" s="8"/>
       <c r="H721" s="8"/>
@@ -35166,7 +35162,7 @@
       <c r="J721" s="7"/>
       <c r="L721" s="7"/>
     </row>
-    <row r="722" spans="4:12" ht="12.5">
+    <row r="722" spans="4:12">
       <c r="D722" s="7"/>
       <c r="G722" s="8"/>
       <c r="H722" s="8"/>
@@ -35174,7 +35170,7 @@
       <c r="J722" s="7"/>
       <c r="L722" s="7"/>
     </row>
-    <row r="723" spans="4:12" ht="12.5">
+    <row r="723" spans="4:12">
       <c r="D723" s="7"/>
       <c r="G723" s="8"/>
       <c r="H723" s="8"/>
@@ -35182,7 +35178,7 @@
       <c r="J723" s="7"/>
       <c r="L723" s="7"/>
     </row>
-    <row r="724" spans="4:12" ht="12.5">
+    <row r="724" spans="4:12">
       <c r="D724" s="7"/>
       <c r="G724" s="8"/>
       <c r="H724" s="8"/>
@@ -35190,7 +35186,7 @@
       <c r="J724" s="7"/>
       <c r="L724" s="7"/>
     </row>
-    <row r="725" spans="4:12" ht="12.5">
+    <row r="725" spans="4:12">
       <c r="D725" s="7"/>
       <c r="G725" s="8"/>
       <c r="H725" s="8"/>
@@ -35198,7 +35194,7 @@
       <c r="J725" s="7"/>
       <c r="L725" s="7"/>
     </row>
-    <row r="726" spans="4:12" ht="12.5">
+    <row r="726" spans="4:12">
       <c r="D726" s="7"/>
       <c r="G726" s="8"/>
       <c r="H726" s="8"/>
@@ -35206,7 +35202,7 @@
       <c r="J726" s="7"/>
       <c r="L726" s="7"/>
     </row>
-    <row r="727" spans="4:12" ht="12.5">
+    <row r="727" spans="4:12">
       <c r="D727" s="7"/>
       <c r="G727" s="8"/>
       <c r="H727" s="8"/>
@@ -35214,7 +35210,7 @@
       <c r="J727" s="7"/>
       <c r="L727" s="7"/>
     </row>
-    <row r="728" spans="4:12" ht="12.5">
+    <row r="728" spans="4:12">
       <c r="D728" s="7"/>
       <c r="G728" s="8"/>
       <c r="H728" s="8"/>
@@ -35222,7 +35218,7 @@
       <c r="J728" s="7"/>
       <c r="L728" s="7"/>
     </row>
-    <row r="729" spans="4:12" ht="12.5">
+    <row r="729" spans="4:12">
       <c r="D729" s="7"/>
       <c r="G729" s="8"/>
       <c r="H729" s="8"/>
@@ -35230,7 +35226,7 @@
       <c r="J729" s="7"/>
       <c r="L729" s="7"/>
     </row>
-    <row r="730" spans="4:12" ht="12.5">
+    <row r="730" spans="4:12">
       <c r="D730" s="7"/>
       <c r="G730" s="8"/>
       <c r="H730" s="8"/>
@@ -35238,7 +35234,7 @@
       <c r="J730" s="7"/>
       <c r="L730" s="7"/>
     </row>
-    <row r="731" spans="4:12" ht="12.5">
+    <row r="731" spans="4:12">
       <c r="D731" s="7"/>
       <c r="G731" s="8"/>
       <c r="H731" s="8"/>
@@ -35246,7 +35242,7 @@
       <c r="J731" s="7"/>
       <c r="L731" s="7"/>
     </row>
-    <row r="732" spans="4:12" ht="12.5">
+    <row r="732" spans="4:12">
       <c r="D732" s="7"/>
       <c r="G732" s="8"/>
       <c r="H732" s="8"/>
@@ -35254,7 +35250,7 @@
       <c r="J732" s="7"/>
       <c r="L732" s="7"/>
     </row>
-    <row r="733" spans="4:12" ht="12.5">
+    <row r="733" spans="4:12">
       <c r="D733" s="7"/>
       <c r="G733" s="8"/>
       <c r="H733" s="8"/>
@@ -35262,7 +35258,7 @@
       <c r="J733" s="7"/>
       <c r="L733" s="7"/>
     </row>
-    <row r="734" spans="4:12" ht="12.5">
+    <row r="734" spans="4:12">
       <c r="D734" s="7"/>
       <c r="G734" s="8"/>
       <c r="H734" s="8"/>
@@ -35270,7 +35266,7 @@
       <c r="J734" s="7"/>
       <c r="L734" s="7"/>
     </row>
-    <row r="735" spans="4:12" ht="12.5">
+    <row r="735" spans="4:12">
       <c r="D735" s="7"/>
       <c r="G735" s="8"/>
       <c r="H735" s="8"/>
@@ -35278,7 +35274,7 @@
       <c r="J735" s="7"/>
       <c r="L735" s="7"/>
     </row>
-    <row r="736" spans="4:12" ht="12.5">
+    <row r="736" spans="4:12">
       <c r="D736" s="7"/>
       <c r="G736" s="8"/>
       <c r="H736" s="8"/>
@@ -35286,7 +35282,7 @@
       <c r="J736" s="7"/>
       <c r="L736" s="7"/>
     </row>
-    <row r="737" spans="4:12" ht="12.5">
+    <row r="737" spans="4:12">
       <c r="D737" s="7"/>
       <c r="G737" s="8"/>
       <c r="H737" s="8"/>
@@ -35294,7 +35290,7 @@
       <c r="J737" s="7"/>
       <c r="L737" s="7"/>
     </row>
-    <row r="738" spans="4:12" ht="12.5">
+    <row r="738" spans="4:12">
       <c r="D738" s="7"/>
       <c r="G738" s="8"/>
       <c r="H738" s="8"/>
@@ -35302,7 +35298,7 @@
       <c r="J738" s="7"/>
       <c r="L738" s="7"/>
     </row>
-    <row r="739" spans="4:12" ht="12.5">
+    <row r="739" spans="4:12">
       <c r="D739" s="7"/>
       <c r="G739" s="8"/>
       <c r="H739" s="8"/>
@@ -35310,7 +35306,7 @@
       <c r="J739" s="7"/>
       <c r="L739" s="7"/>
     </row>
-    <row r="740" spans="4:12" ht="12.5">
+    <row r="740" spans="4:12">
       <c r="D740" s="7"/>
       <c r="G740" s="8"/>
       <c r="H740" s="8"/>
@@ -35318,7 +35314,7 @@
       <c r="J740" s="7"/>
       <c r="L740" s="7"/>
     </row>
-    <row r="741" spans="4:12" ht="12.5">
+    <row r="741" spans="4:12">
       <c r="D741" s="7"/>
       <c r="G741" s="8"/>
       <c r="H741" s="8"/>
@@ -35326,7 +35322,7 @@
       <c r="J741" s="7"/>
       <c r="L741" s="7"/>
     </row>
-    <row r="742" spans="4:12" ht="12.5">
+    <row r="742" spans="4:12">
       <c r="D742" s="7"/>
       <c r="G742" s="8"/>
       <c r="H742" s="8"/>
@@ -35334,7 +35330,7 @@
       <c r="J742" s="7"/>
       <c r="L742" s="7"/>
     </row>
-    <row r="743" spans="4:12" ht="12.5">
+    <row r="743" spans="4:12">
       <c r="D743" s="7"/>
       <c r="G743" s="8"/>
       <c r="H743" s="8"/>
@@ -35342,7 +35338,7 @@
       <c r="J743" s="7"/>
       <c r="L743" s="7"/>
     </row>
-    <row r="744" spans="4:12" ht="12.5">
+    <row r="744" spans="4:12">
       <c r="D744" s="7"/>
       <c r="G744" s="8"/>
       <c r="H744" s="8"/>
@@ -35350,7 +35346,7 @@
       <c r="J744" s="7"/>
       <c r="L744" s="7"/>
     </row>
-    <row r="745" spans="4:12" ht="12.5">
+    <row r="745" spans="4:12">
       <c r="D745" s="7"/>
       <c r="G745" s="8"/>
       <c r="H745" s="8"/>
@@ -35358,7 +35354,7 @@
       <c r="J745" s="7"/>
       <c r="L745" s="7"/>
     </row>
-    <row r="746" spans="4:12" ht="12.5">
+    <row r="746" spans="4:12">
       <c r="D746" s="7"/>
       <c r="G746" s="8"/>
       <c r="H746" s="8"/>
@@ -35366,7 +35362,7 @@
       <c r="J746" s="7"/>
       <c r="L746" s="7"/>
     </row>
-    <row r="747" spans="4:12" ht="12.5">
+    <row r="747" spans="4:12">
       <c r="D747" s="7"/>
       <c r="G747" s="8"/>
       <c r="H747" s="8"/>
@@ -35374,7 +35370,7 @@
       <c r="J747" s="7"/>
       <c r="L747" s="7"/>
     </row>
-    <row r="748" spans="4:12" ht="12.5">
+    <row r="748" spans="4:12">
       <c r="D748" s="7"/>
       <c r="G748" s="8"/>
       <c r="H748" s="8"/>
@@ -35382,7 +35378,7 @@
       <c r="J748" s="7"/>
       <c r="L748" s="7"/>
     </row>
-    <row r="749" spans="4:12" ht="12.5">
+    <row r="749" spans="4:12">
       <c r="D749" s="7"/>
       <c r="G749" s="8"/>
       <c r="H749" s="8"/>
@@ -35390,7 +35386,7 @@
       <c r="J749" s="7"/>
       <c r="L749" s="7"/>
     </row>
-    <row r="750" spans="4:12" ht="12.5">
+    <row r="750" spans="4:12">
       <c r="D750" s="7"/>
       <c r="G750" s="8"/>
       <c r="H750" s="8"/>
@@ -35398,7 +35394,7 @@
       <c r="J750" s="7"/>
       <c r="L750" s="7"/>
     </row>
-    <row r="751" spans="4:12" ht="12.5">
+    <row r="751" spans="4:12">
       <c r="D751" s="7"/>
       <c r="G751" s="8"/>
       <c r="H751" s="8"/>
@@ -35406,7 +35402,7 @@
       <c r="J751" s="7"/>
       <c r="L751" s="7"/>
     </row>
-    <row r="752" spans="4:12" ht="12.5">
+    <row r="752" spans="4:12">
       <c r="D752" s="7"/>
       <c r="G752" s="8"/>
       <c r="H752" s="8"/>
@@ -35414,7 +35410,7 @@
       <c r="J752" s="7"/>
       <c r="L752" s="7"/>
     </row>
-    <row r="753" spans="4:12" ht="12.5">
+    <row r="753" spans="4:12">
       <c r="D753" s="7"/>
       <c r="G753" s="8"/>
       <c r="H753" s="8"/>
@@ -35422,7 +35418,7 @@
       <c r="J753" s="7"/>
       <c r="L753" s="7"/>
     </row>
-    <row r="754" spans="4:12" ht="12.5">
+    <row r="754" spans="4:12">
       <c r="D754" s="7"/>
       <c r="G754" s="8"/>
       <c r="H754" s="8"/>
@@ -35430,7 +35426,7 @@
       <c r="J754" s="7"/>
       <c r="L754" s="7"/>
     </row>
-    <row r="755" spans="4:12" ht="12.5">
+    <row r="755" spans="4:12">
       <c r="D755" s="7"/>
       <c r="G755" s="8"/>
       <c r="H755" s="8"/>
@@ -35438,7 +35434,7 @@
       <c r="J755" s="7"/>
       <c r="L755" s="7"/>
     </row>
-    <row r="756" spans="4:12" ht="12.5">
+    <row r="756" spans="4:12">
       <c r="D756" s="7"/>
       <c r="G756" s="8"/>
       <c r="H756" s="8"/>
@@ -35446,7 +35442,7 @@
       <c r="J756" s="7"/>
       <c r="L756" s="7"/>
     </row>
-    <row r="757" spans="4:12" ht="12.5">
+    <row r="757" spans="4:12">
       <c r="D757" s="7"/>
       <c r="G757" s="8"/>
       <c r="H757" s="8"/>
@@ -35454,7 +35450,7 @@
       <c r="J757" s="7"/>
       <c r="L757" s="7"/>
     </row>
-    <row r="758" spans="4:12" ht="12.5">
+    <row r="758" spans="4:12">
       <c r="D758" s="7"/>
       <c r="G758" s="8"/>
       <c r="H758" s="8"/>
@@ -35462,7 +35458,7 @@
       <c r="J758" s="7"/>
       <c r="L758" s="7"/>
     </row>
-    <row r="759" spans="4:12" ht="12.5">
+    <row r="759" spans="4:12">
       <c r="D759" s="7"/>
       <c r="G759" s="8"/>
       <c r="H759" s="8"/>
@@ -35470,7 +35466,7 @@
       <c r="J759" s="7"/>
       <c r="L759" s="7"/>
     </row>
-    <row r="760" spans="4:12" ht="12.5">
+    <row r="760" spans="4:12">
       <c r="D760" s="7"/>
       <c r="G760" s="8"/>
       <c r="H760" s="8"/>
@@ -35478,7 +35474,7 @@
       <c r="J760" s="7"/>
       <c r="L760" s="7"/>
     </row>
-    <row r="761" spans="4:12" ht="12.5">
+    <row r="761" spans="4:12">
       <c r="D761" s="7"/>
       <c r="G761" s="8"/>
       <c r="H761" s="8"/>
@@ -35486,7 +35482,7 @@
       <c r="J761" s="7"/>
       <c r="L761" s="7"/>
     </row>
-    <row r="762" spans="4:12" ht="12.5">
+    <row r="762" spans="4:12">
       <c r="D762" s="7"/>
       <c r="G762" s="8"/>
       <c r="H762" s="8"/>
@@ -35494,7 +35490,7 @@
       <c r="J762" s="7"/>
       <c r="L762" s="7"/>
     </row>
-    <row r="763" spans="4:12" ht="12.5">
+    <row r="763" spans="4:12">
       <c r="D763" s="7"/>
       <c r="G763" s="8"/>
       <c r="H763" s="8"/>
@@ -35502,7 +35498,7 @@
       <c r="J763" s="7"/>
       <c r="L763" s="7"/>
     </row>
-    <row r="764" spans="4:12" ht="12.5">
+    <row r="764" spans="4:12">
       <c r="D764" s="7"/>
       <c r="G764" s="8"/>
       <c r="H764" s="8"/>
@@ -35510,7 +35506,7 @@
       <c r="J764" s="7"/>
       <c r="L764" s="7"/>
     </row>
-    <row r="765" spans="4:12" ht="12.5">
+    <row r="765" spans="4:12">
       <c r="D765" s="7"/>
       <c r="G765" s="8"/>
       <c r="H765" s="8"/>
@@ -35518,7 +35514,7 @@
       <c r="J765" s="7"/>
       <c r="L765" s="7"/>
     </row>
-    <row r="766" spans="4:12" ht="12.5">
+    <row r="766" spans="4:12">
       <c r="D766" s="7"/>
       <c r="G766" s="8"/>
       <c r="H766" s="8"/>
@@ -35526,7 +35522,7 @@
       <c r="J766" s="7"/>
       <c r="L766" s="7"/>
     </row>
-    <row r="767" spans="4:12" ht="12.5">
+    <row r="767" spans="4:12">
       <c r="D767" s="7"/>
       <c r="G767" s="8"/>
       <c r="H767" s="8"/>
@@ -35534,7 +35530,7 @@
       <c r="J767" s="7"/>
       <c r="L767" s="7"/>
     </row>
-    <row r="768" spans="4:12" ht="12.5">
+    <row r="768" spans="4:12">
       <c r="D768" s="7"/>
       <c r="G768" s="8"/>
       <c r="H768" s="8"/>
@@ -35542,7 +35538,7 @@
       <c r="J768" s="7"/>
       <c r="L768" s="7"/>
     </row>
-    <row r="769" spans="4:12" ht="12.5">
+    <row r="769" spans="4:12">
       <c r="D769" s="7"/>
       <c r="G769" s="8"/>
       <c r="H769" s="8"/>
@@ -35550,7 +35546,7 @@
       <c r="J769" s="7"/>
       <c r="L769" s="7"/>
     </row>
-    <row r="770" spans="4:12" ht="12.5">
+    <row r="770" spans="4:12">
       <c r="D770" s="7"/>
       <c r="G770" s="8"/>
       <c r="H770" s="8"/>
@@ -35558,7 +35554,7 @@
       <c r="J770" s="7"/>
       <c r="L770" s="7"/>
     </row>
-    <row r="771" spans="4:12" ht="12.5">
+    <row r="771" spans="4:12">
       <c r="D771" s="7"/>
       <c r="G771" s="8"/>
       <c r="H771" s="8"/>
@@ -35566,7 +35562,7 @@
       <c r="J771" s="7"/>
       <c r="L771" s="7"/>
     </row>
-    <row r="772" spans="4:12" ht="12.5">
+    <row r="772" spans="4:12">
       <c r="D772" s="7"/>
       <c r="G772" s="8"/>
       <c r="H772" s="8"/>
@@ -35574,7 +35570,7 @@
       <c r="J772" s="7"/>
       <c r="L772" s="7"/>
     </row>
-    <row r="773" spans="4:12" ht="12.5">
+    <row r="773" spans="4:12">
       <c r="D773" s="7"/>
       <c r="G773" s="8"/>
       <c r="H773" s="8"/>
@@ -35582,7 +35578,7 @@
       <c r="J773" s="7"/>
       <c r="L773" s="7"/>
     </row>
-    <row r="774" spans="4:12" ht="12.5">
+    <row r="774" spans="4:12">
       <c r="D774" s="7"/>
       <c r="G774" s="8"/>
       <c r="H774" s="8"/>
@@ -35590,7 +35586,7 @@
       <c r="J774" s="7"/>
       <c r="L774" s="7"/>
     </row>
-    <row r="775" spans="4:12" ht="12.5">
+    <row r="775" spans="4:12">
       <c r="D775" s="7"/>
       <c r="G775" s="8"/>
       <c r="H775" s="8"/>
@@ -35598,7 +35594,7 @@
       <c r="J775" s="7"/>
       <c r="L775" s="7"/>
     </row>
-    <row r="776" spans="4:12" ht="12.5">
+    <row r="776" spans="4:12">
       <c r="D776" s="7"/>
       <c r="G776" s="8"/>
       <c r="H776" s="8"/>
@@ -35606,7 +35602,7 @@
       <c r="J776" s="7"/>
       <c r="L776" s="7"/>
     </row>
-    <row r="777" spans="4:12" ht="12.5">
+    <row r="777" spans="4:12">
       <c r="D777" s="7"/>
       <c r="G777" s="8"/>
       <c r="H777" s="8"/>
@@ -35614,7 +35610,7 @@
       <c r="J777" s="7"/>
       <c r="L777" s="7"/>
     </row>
-    <row r="778" spans="4:12" ht="12.5">
+    <row r="778" spans="4:12">
       <c r="D778" s="7"/>
       <c r="G778" s="8"/>
       <c r="H778" s="8"/>
@@ -35622,7 +35618,7 @@
       <c r="J778" s="7"/>
       <c r="L778" s="7"/>
     </row>
-    <row r="779" spans="4:12" ht="12.5">
+    <row r="779" spans="4:12">
       <c r="D779" s="7"/>
       <c r="G779" s="8"/>
       <c r="H779" s="8"/>
@@ -35630,7 +35626,7 @@
       <c r="J779" s="7"/>
       <c r="L779" s="7"/>
     </row>
-    <row r="780" spans="4:12" ht="12.5">
+    <row r="780" spans="4:12">
       <c r="D780" s="7"/>
       <c r="G780" s="8"/>
       <c r="H780" s="8"/>
@@ -35638,7 +35634,7 @@
       <c r="J780" s="7"/>
       <c r="L780" s="7"/>
     </row>
-    <row r="781" spans="4:12" ht="12.5">
+    <row r="781" spans="4:12">
       <c r="D781" s="7"/>
       <c r="G781" s="8"/>
       <c r="H781" s="8"/>
@@ -35646,7 +35642,7 @@
       <c r="J781" s="7"/>
       <c r="L781" s="7"/>
     </row>
-    <row r="782" spans="4:12" ht="12.5">
+    <row r="782" spans="4:12">
       <c r="D782" s="7"/>
       <c r="G782" s="8"/>
       <c r="H782" s="8"/>
@@ -35654,7 +35650,7 @@
       <c r="J782" s="7"/>
       <c r="L782" s="7"/>
     </row>
-    <row r="783" spans="4:12" ht="12.5">
+    <row r="783" spans="4:12">
       <c r="D783" s="7"/>
       <c r="G783" s="8"/>
       <c r="H783" s="8"/>
@@ -35662,7 +35658,7 @@
       <c r="J783" s="7"/>
       <c r="L783" s="7"/>
     </row>
-    <row r="784" spans="4:12" ht="12.5">
+    <row r="784" spans="4:12">
       <c r="D784" s="7"/>
       <c r="G784" s="8"/>
       <c r="H784" s="8"/>
@@ -35670,7 +35666,7 @@
       <c r="J784" s="7"/>
       <c r="L784" s="7"/>
     </row>
-    <row r="785" spans="4:12" ht="12.5">
+    <row r="785" spans="4:12">
       <c r="D785" s="7"/>
       <c r="G785" s="8"/>
       <c r="H785" s="8"/>
@@ -35678,7 +35674,7 @@
       <c r="J785" s="7"/>
       <c r="L785" s="7"/>
     </row>
-    <row r="786" spans="4:12" ht="12.5">
+    <row r="786" spans="4:12">
       <c r="D786" s="7"/>
       <c r="G786" s="8"/>
       <c r="H786" s="8"/>
@@ -35686,7 +35682,7 @@
       <c r="J786" s="7"/>
       <c r="L786" s="7"/>
     </row>
-    <row r="787" spans="4:12" ht="12.5">
+    <row r="787" spans="4:12">
       <c r="D787" s="7"/>
       <c r="G787" s="8"/>
       <c r="H787" s="8"/>
@@ -35694,7 +35690,7 @@
       <c r="J787" s="7"/>
       <c r="L787" s="7"/>
     </row>
-    <row r="788" spans="4:12" ht="12.5">
+    <row r="788" spans="4:12">
       <c r="D788" s="7"/>
       <c r="G788" s="8"/>
       <c r="H788" s="8"/>
@@ -35702,7 +35698,7 @@
       <c r="J788" s="7"/>
       <c r="L788" s="7"/>
     </row>
-    <row r="789" spans="4:12" ht="12.5">
+    <row r="789" spans="4:12">
       <c r="D789" s="7"/>
       <c r="G789" s="8"/>
       <c r="H789" s="8"/>
@@ -35710,7 +35706,7 @@
       <c r="J789" s="7"/>
       <c r="L789" s="7"/>
     </row>
-    <row r="790" spans="4:12" ht="12.5">
+    <row r="790" spans="4:12">
       <c r="D790" s="7"/>
       <c r="G790" s="8"/>
       <c r="H790" s="8"/>
@@ -35718,7 +35714,7 @@
       <c r="J790" s="7"/>
       <c r="L790" s="7"/>
     </row>
-    <row r="791" spans="4:12" ht="12.5">
+    <row r="791" spans="4:12">
       <c r="D791" s="7"/>
       <c r="G791" s="8"/>
       <c r="H791" s="8"/>
@@ -35726,7 +35722,7 @@
       <c r="J791" s="7"/>
       <c r="L791" s="7"/>
     </row>
-    <row r="792" spans="4:12" ht="12.5">
+    <row r="792" spans="4:12">
       <c r="D792" s="7"/>
       <c r="G792" s="8"/>
       <c r="H792" s="8"/>
@@ -35734,7 +35730,7 @@
       <c r="J792" s="7"/>
       <c r="L792" s="7"/>
     </row>
-    <row r="793" spans="4:12" ht="12.5">
+    <row r="793" spans="4:12">
       <c r="D793" s="7"/>
       <c r="G793" s="8"/>
       <c r="H793" s="8"/>
@@ -35742,7 +35738,7 @@
       <c r="J793" s="7"/>
       <c r="L793" s="7"/>
     </row>
-    <row r="794" spans="4:12" ht="12.5">
+    <row r="794" spans="4:12">
       <c r="D794" s="7"/>
       <c r="G794" s="8"/>
       <c r="H794" s="8"/>
@@ -35750,7 +35746,7 @@
       <c r="J794" s="7"/>
       <c r="L794" s="7"/>
     </row>
-    <row r="795" spans="4:12" ht="12.5">
+    <row r="795" spans="4:12">
       <c r="D795" s="7"/>
       <c r="G795" s="8"/>
       <c r="H795" s="8"/>
@@ -35758,7 +35754,7 @@
       <c r="J795" s="7"/>
       <c r="L795" s="7"/>
     </row>
-    <row r="796" spans="4:12" ht="12.5">
+    <row r="796" spans="4:12">
       <c r="D796" s="7"/>
       <c r="G796" s="8"/>
       <c r="H796" s="8"/>
@@ -35766,7 +35762,7 @@
       <c r="J796" s="7"/>
       <c r="L796" s="7"/>
     </row>
-    <row r="797" spans="4:12" ht="12.5">
+    <row r="797" spans="4:12">
       <c r="D797" s="7"/>
       <c r="G797" s="8"/>
       <c r="H797" s="8"/>
@@ -35774,7 +35770,7 @@
       <c r="J797" s="7"/>
       <c r="L797" s="7"/>
     </row>
-    <row r="798" spans="4:12" ht="12.5">
+    <row r="798" spans="4:12">
       <c r="D798" s="7"/>
       <c r="G798" s="8"/>
       <c r="H798" s="8"/>
@@ -35782,7 +35778,7 @@
       <c r="J798" s="7"/>
       <c r="L798" s="7"/>
     </row>
-    <row r="799" spans="4:12" ht="12.5">
+    <row r="799" spans="4:12">
       <c r="D799" s="7"/>
       <c r="G799" s="8"/>
       <c r="H799" s="8"/>
@@ -35790,7 +35786,7 @@
       <c r="J799" s="7"/>
       <c r="L799" s="7"/>
     </row>
-    <row r="800" spans="4:12" ht="12.5">
+    <row r="800" spans="4:12">
       <c r="D800" s="7"/>
       <c r="G800" s="8"/>
       <c r="H800" s="8"/>
@@ -35798,7 +35794,7 @@
       <c r="J800" s="7"/>
       <c r="L800" s="7"/>
     </row>
-    <row r="801" spans="4:12" ht="12.5">
+    <row r="801" spans="4:12">
       <c r="D801" s="7"/>
       <c r="G801" s="8"/>
       <c r="H801" s="8"/>
@@ -35806,7 +35802,7 @@
       <c r="J801" s="7"/>
       <c r="L801" s="7"/>
     </row>
-    <row r="802" spans="4:12" ht="12.5">
+    <row r="802" spans="4:12">
       <c r="D802" s="7"/>
       <c r="G802" s="8"/>
       <c r="H802" s="8"/>
@@ -35814,7 +35810,7 @@
       <c r="J802" s="7"/>
       <c r="L802" s="7"/>
     </row>
-    <row r="803" spans="4:12" ht="12.5">
+    <row r="803" spans="4:12">
       <c r="D803" s="7"/>
       <c r="G803" s="8"/>
       <c r="H803" s="8"/>
@@ -35822,7 +35818,7 @@
       <c r="J803" s="7"/>
       <c r="L803" s="7"/>
     </row>
-    <row r="804" spans="4:12" ht="12.5">
+    <row r="804" spans="4:12">
       <c r="D804" s="7"/>
       <c r="G804" s="8"/>
       <c r="H804" s="8"/>
@@ -35830,7 +35826,7 @@
       <c r="J804" s="7"/>
       <c r="L804" s="7"/>
     </row>
-    <row r="805" spans="4:12" ht="12.5">
+    <row r="805" spans="4:12">
       <c r="D805" s="7"/>
       <c r="G805" s="8"/>
       <c r="H805" s="8"/>
@@ -35838,7 +35834,7 @@
       <c r="J805" s="7"/>
       <c r="L805" s="7"/>
     </row>
-    <row r="806" spans="4:12" ht="12.5">
+    <row r="806" spans="4:12">
       <c r="D806" s="7"/>
       <c r="G806" s="8"/>
       <c r="H806" s="8"/>
@@ -35846,7 +35842,7 @@
       <c r="J806" s="7"/>
       <c r="L806" s="7"/>
     </row>
-    <row r="807" spans="4:12" ht="12.5">
+    <row r="807" spans="4:12">
       <c r="D807" s="7"/>
       <c r="G807" s="8"/>
       <c r="H807" s="8"/>
@@ -35854,7 +35850,7 @@
       <c r="J807" s="7"/>
       <c r="L807" s="7"/>
     </row>
-    <row r="808" spans="4:12" ht="12.5">
+    <row r="808" spans="4:12">
       <c r="D808" s="7"/>
       <c r="G808" s="8"/>
       <c r="H808" s="8"/>
@@ -35862,7 +35858,7 @@
       <c r="J808" s="7"/>
       <c r="L808" s="7"/>
     </row>
-    <row r="809" spans="4:12" ht="12.5">
+    <row r="809" spans="4:12">
       <c r="D809" s="7"/>
       <c r="G809" s="8"/>
       <c r="H809" s="8"/>
@@ -35870,7 +35866,7 @@
       <c r="J809" s="7"/>
       <c r="L809" s="7"/>
     </row>
-    <row r="810" spans="4:12" ht="12.5">
+    <row r="810" spans="4:12">
       <c r="D810" s="7"/>
       <c r="G810" s="8"/>
       <c r="H810" s="8"/>
@@ -35878,7 +35874,7 @@
       <c r="J810" s="7"/>
       <c r="L810" s="7"/>
     </row>
-    <row r="811" spans="4:12" ht="12.5">
+    <row r="811" spans="4:12">
       <c r="D811" s="7"/>
       <c r="G811" s="8"/>
       <c r="H811" s="8"/>
@@ -35886,7 +35882,7 @@
       <c r="J811" s="7"/>
       <c r="L811" s="7"/>
     </row>
-    <row r="812" spans="4:12" ht="12.5">
+    <row r="812" spans="4:12">
       <c r="D812" s="7"/>
       <c r="G812" s="8"/>
       <c r="H812" s="8"/>
@@ -35894,7 +35890,7 @@
       <c r="J812" s="7"/>
       <c r="L812" s="7"/>
     </row>
-    <row r="813" spans="4:12" ht="12.5">
+    <row r="813" spans="4:12">
       <c r="D813" s="7"/>
       <c r="G813" s="8"/>
       <c r="H813" s="8"/>
@@ -35902,7 +35898,7 @@
       <c r="J813" s="7"/>
       <c r="L813" s="7"/>
     </row>
-    <row r="814" spans="4:12" ht="12.5">
+    <row r="814" spans="4:12">
       <c r="D814" s="7"/>
       <c r="G814" s="8"/>
       <c r="H814" s="8"/>
@@ -35910,7 +35906,7 @@
       <c r="J814" s="7"/>
       <c r="L814" s="7"/>
     </row>
-    <row r="815" spans="4:12" ht="12.5">
+    <row r="815" spans="4:12">
       <c r="D815" s="7"/>
       <c r="G815" s="8"/>
       <c r="H815" s="8"/>
@@ -35918,7 +35914,7 @@
       <c r="J815" s="7"/>
       <c r="L815" s="7"/>
     </row>
-    <row r="816" spans="4:12" ht="12.5">
+    <row r="816" spans="4:12">
       <c r="D816" s="7"/>
       <c r="G816" s="8"/>
       <c r="H816" s="8"/>
@@ -35926,7 +35922,7 @@
       <c r="J816" s="7"/>
       <c r="L816" s="7"/>
     </row>
-    <row r="817" spans="4:12" ht="12.5">
+    <row r="817" spans="4:12">
       <c r="D817" s="7"/>
       <c r="G817" s="8"/>
       <c r="H817" s="8"/>
@@ -35934,7 +35930,7 @@
       <c r="J817" s="7"/>
       <c r="L817" s="7"/>
     </row>
-    <row r="818" spans="4:12" ht="12.5">
+    <row r="818" spans="4:12">
       <c r="D818" s="7"/>
       <c r="G818" s="8"/>
       <c r="H818" s="8"/>
@@ -35942,7 +35938,7 @@
       <c r="J818" s="7"/>
       <c r="L818" s="7"/>
     </row>
-    <row r="819" spans="4:12" ht="12.5">
+    <row r="819" spans="4:12">
       <c r="D819" s="7"/>
       <c r="G819" s="8"/>
       <c r="H819" s="8"/>
@@ -35950,7 +35946,7 @@
       <c r="J819" s="7"/>
       <c r="L819" s="7"/>
     </row>
-    <row r="820" spans="4:12" ht="12.5">
+    <row r="820" spans="4:12">
       <c r="D820" s="7"/>
       <c r="G820" s="8"/>
       <c r="H820" s="8"/>
@@ -35958,7 +35954,7 @@
       <c r="J820" s="7"/>
       <c r="L820" s="7"/>
     </row>
-    <row r="821" spans="4:12" ht="12.5">
+    <row r="821" spans="4:12">
       <c r="D821" s="7"/>
       <c r="G821" s="8"/>
       <c r="H821" s="8"/>
@@ -35966,7 +35962,7 @@
       <c r="J821" s="7"/>
       <c r="L821" s="7"/>
     </row>
-    <row r="822" spans="4:12" ht="12.5">
+    <row r="822" spans="4:12">
       <c r="D822" s="7"/>
       <c r="G822" s="8"/>
       <c r="H822" s="8"/>
@@ -35974,7 +35970,7 @@
       <c r="J822" s="7"/>
       <c r="L822" s="7"/>
     </row>
-    <row r="823" spans="4:12" ht="12.5">
+    <row r="823" spans="4:12">
       <c r="D823" s="7"/>
       <c r="G823" s="8"/>
       <c r="H823" s="8"/>
@@ -35982,7 +35978,7 @@
       <c r="J823" s="7"/>
       <c r="L823" s="7"/>
     </row>
-    <row r="824" spans="4:12" ht="12.5">
+    <row r="824" spans="4:12">
       <c r="D824" s="7"/>
       <c r="G824" s="8"/>
       <c r="H824" s="8"/>
@@ -35990,7 +35986,7 @@
       <c r="J824" s="7"/>
       <c r="L824" s="7"/>
     </row>
-    <row r="825" spans="4:12" ht="12.5">
+    <row r="825" spans="4:12">
       <c r="D825" s="7"/>
       <c r="G825" s="8"/>
       <c r="H825" s="8"/>
@@ -35998,7 +35994,7 @@
       <c r="J825" s="7"/>
       <c r="L825" s="7"/>
     </row>
-    <row r="826" spans="4:12" ht="12.5">
+    <row r="826" spans="4:12">
       <c r="D826" s="7"/>
       <c r="G826" s="8"/>
       <c r="H826" s="8"/>
@@ -36006,7 +36002,7 @@
       <c r="J826" s="7"/>
       <c r="L826" s="7"/>
     </row>
-    <row r="827" spans="4:12" ht="12.5">
+    <row r="827" spans="4:12">
       <c r="D827" s="7"/>
       <c r="G827" s="8"/>
       <c r="H827" s="8"/>
@@ -36014,7 +36010,7 @@
       <c r="J827" s="7"/>
       <c r="L827" s="7"/>
     </row>
-    <row r="828" spans="4:12" ht="12.5">
+    <row r="828" spans="4:12">
       <c r="D828" s="7"/>
       <c r="G828" s="8"/>
       <c r="H828" s="8"/>
@@ -36022,7 +36018,7 @@
       <c r="J828" s="7"/>
       <c r="L828" s="7"/>
     </row>
-    <row r="829" spans="4:12" ht="12.5">
+    <row r="829" spans="4:12">
       <c r="D829" s="7"/>
       <c r="G829" s="8"/>
       <c r="H829" s="8"/>
@@ -36030,7 +36026,7 @@
       <c r="J829" s="7"/>
       <c r="L829" s="7"/>
     </row>
-    <row r="830" spans="4:12" ht="12.5">
+    <row r="830" spans="4:12">
       <c r="D830" s="7"/>
       <c r="G830" s="8"/>
       <c r="H830" s="8"/>
@@ -36038,7 +36034,7 @@
       <c r="J830" s="7"/>
       <c r="L830" s="7"/>
     </row>
-    <row r="831" spans="4:12" ht="12.5">
+    <row r="831" spans="4:12">
       <c r="D831" s="7"/>
       <c r="G831" s="8"/>
       <c r="H831" s="8"/>
@@ -36046,7 +36042,7 @@
       <c r="J831" s="7"/>
       <c r="L831" s="7"/>
     </row>
-    <row r="832" spans="4:12" ht="12.5">
+    <row r="832" spans="4:12">
       <c r="D832" s="7"/>
       <c r="G832" s="8"/>
       <c r="H832" s="8"/>
@@ -36054,7 +36050,7 @@
       <c r="J832" s="7"/>
       <c r="L832" s="7"/>
     </row>
-    <row r="833" spans="4:12" ht="12.5">
+    <row r="833" spans="4:12">
       <c r="D833" s="7"/>
       <c r="G833" s="8"/>
       <c r="H833" s="8"/>
@@ -36062,7 +36058,7 @@
       <c r="J833" s="7"/>
       <c r="L833" s="7"/>
     </row>
-    <row r="834" spans="4:12" ht="12.5">
+    <row r="834" spans="4:12">
       <c r="D834" s="7"/>
       <c r="G834" s="8"/>
       <c r="H834" s="8"/>
@@ -36070,7 +36066,7 @@
       <c r="J834" s="7"/>
       <c r="L834" s="7"/>
     </row>
-    <row r="835" spans="4:12" ht="12.5">
+    <row r="835" spans="4:12">
       <c r="D835" s="7"/>
       <c r="G835" s="8"/>
       <c r="H835" s="8"/>
@@ -36078,7 +36074,7 @@
       <c r="J835" s="7"/>
       <c r="L835" s="7"/>
     </row>
-    <row r="836" spans="4:12" ht="12.5">
+    <row r="836" spans="4:12">
       <c r="D836" s="7"/>
       <c r="G836" s="8"/>
       <c r="H836" s="8"/>
@@ -36086,7 +36082,7 @@
       <c r="J836" s="7"/>
       <c r="L836" s="7"/>
     </row>
-    <row r="837" spans="4:12" ht="12.5">
+    <row r="837" spans="4:12">
       <c r="D837" s="7"/>
       <c r="G837" s="8"/>
       <c r="H837" s="8"/>
@@ -36094,7 +36090,7 @@
       <c r="J837" s="7"/>
       <c r="L837" s="7"/>
     </row>
-    <row r="838" spans="4:12" ht="12.5">
+    <row r="838" spans="4:12">
       <c r="D838" s="7"/>
       <c r="G838" s="8"/>
       <c r="H838" s="8"/>
@@ -36102,7 +36098,7 @@
       <c r="J838" s="7"/>
       <c r="L838" s="7"/>
     </row>
-    <row r="839" spans="4:12" ht="12.5">
+    <row r="839" spans="4:12">
       <c r="D839" s="7"/>
       <c r="G839" s="8"/>
       <c r="H839" s="8"/>
@@ -36110,7 +36106,7 @@
       <c r="J839" s="7"/>
       <c r="L839" s="7"/>
     </row>
-    <row r="840" spans="4:12" ht="12.5">
+    <row r="840" spans="4:12">
       <c r="D840" s="7"/>
       <c r="G840" s="8"/>
       <c r="H840" s="8"/>
@@ -36118,7 +36114,7 @@
       <c r="J840" s="7"/>
       <c r="L840" s="7"/>
     </row>
-    <row r="841" spans="4:12" ht="12.5">
+    <row r="841" spans="4:12">
       <c r="D841" s="7"/>
       <c r="G841" s="8"/>
       <c r="H841" s="8"/>
@@ -36126,7 +36122,7 @@
       <c r="J841" s="7"/>
       <c r="L841" s="7"/>
     </row>
-    <row r="842" spans="4:12" ht="12.5">
+    <row r="842" spans="4:12">
       <c r="D842" s="7"/>
       <c r="G842" s="8"/>
       <c r="H842" s="8"/>
@@ -36134,7 +36130,7 @@
       <c r="J842" s="7"/>
       <c r="L842" s="7"/>
     </row>
-    <row r="843" spans="4:12" ht="12.5">
+    <row r="843" spans="4:12">
       <c r="D843" s="7"/>
       <c r="G843" s="8"/>
       <c r="H843" s="8"/>
@@ -36142,7 +36138,7 @@
       <c r="J843" s="7"/>
       <c r="L843" s="7"/>
     </row>
-    <row r="844" spans="4:12" ht="12.5">
+    <row r="844" spans="4:12">
       <c r="D844" s="7"/>
       <c r="G844" s="8"/>
       <c r="H844" s="8"/>
@@ -36150,7 +36146,7 @@
       <c r="J844" s="7"/>
       <c r="L844" s="7"/>
     </row>
-    <row r="845" spans="4:12" ht="12.5">
+    <row r="845" spans="4:12">
       <c r="D845" s="7"/>
       <c r="G845" s="8"/>
       <c r="H845" s="8"/>
@@ -36158,7 +36154,7 @@
       <c r="J845" s="7"/>
       <c r="L845" s="7"/>
     </row>
-    <row r="846" spans="4:12" ht="12.5">
+    <row r="846" spans="4:12">
       <c r="D846" s="7"/>
       <c r="G846" s="8"/>
       <c r="H846" s="8"/>
@@ -36166,7 +36162,7 @@
       <c r="J846" s="7"/>
       <c r="L846" s="7"/>
     </row>
-    <row r="847" spans="4:12" ht="12.5">
+    <row r="847" spans="4:12">
       <c r="D847" s="7"/>
       <c r="G847" s="8"/>
       <c r="H847" s="8"/>
@@ -36174,7 +36170,7 @@
       <c r="J847" s="7"/>
       <c r="L847" s="7"/>
     </row>
-    <row r="848" spans="4:12" ht="12.5">
+    <row r="848" spans="4:12">
       <c r="D848" s="7"/>
       <c r="G848" s="8"/>
       <c r="H848" s="8"/>
@@ -36182,7 +36178,7 @@
       <c r="J848" s="7"/>
       <c r="L848" s="7"/>
     </row>
-    <row r="849" spans="4:12" ht="12.5">
+    <row r="849" spans="4:12">
       <c r="D849" s="7"/>
       <c r="G849" s="8"/>
       <c r="H849" s="8"/>
@@ -36190,7 +36186,7 @@
       <c r="J849" s="7"/>
       <c r="L849" s="7"/>
     </row>
-    <row r="850" spans="4:12" ht="12.5">
+    <row r="850" spans="4:12">
       <c r="D850" s="7"/>
       <c r="G850" s="8"/>
       <c r="H850" s="8"/>
@@ -36198,7 +36194,7 @@
       <c r="J850" s="7"/>
       <c r="L850" s="7"/>
     </row>
-    <row r="851" spans="4:12" ht="12.5">
+    <row r="851" spans="4:12">
       <c r="D851" s="7"/>
       <c r="G851" s="8"/>
       <c r="H851" s="8"/>
@@ -36206,7 +36202,7 @@
       <c r="J851" s="7"/>
       <c r="L851" s="7"/>
     </row>
-    <row r="852" spans="4:12" ht="12.5">
+    <row r="852" spans="4:12">
       <c r="D852" s="7"/>
       <c r="G852" s="8"/>
       <c r="H852" s="8"/>
@@ -36214,7 +36210,7 @@
       <c r="J852" s="7"/>
       <c r="L852" s="7"/>
     </row>
-    <row r="853" spans="4:12" ht="12.5">
+    <row r="853" spans="4:12">
       <c r="D853" s="7"/>
       <c r="G853" s="8"/>
       <c r="H853" s="8"/>
@@ -36222,7 +36218,7 @@
       <c r="J853" s="7"/>
       <c r="L853" s="7"/>
     </row>
-    <row r="854" spans="4:12" ht="12.5">
+    <row r="854" spans="4:12">
       <c r="D854" s="7"/>
       <c r="G854" s="8"/>
       <c r="H854" s="8"/>
@@ -36230,7 +36226,7 @@
       <c r="J854" s="7"/>
       <c r="L854" s="7"/>
     </row>
-    <row r="855" spans="4:12" ht="12.5">
+    <row r="855" spans="4:12">
       <c r="D855" s="7"/>
       <c r="G855" s="8"/>
       <c r="H855" s="8"/>
@@ -36238,7 +36234,7 @@
       <c r="J855" s="7"/>
       <c r="L855" s="7"/>
     </row>
-    <row r="856" spans="4:12" ht="12.5">
+    <row r="856" spans="4:12">
       <c r="D856" s="7"/>
       <c r="G856" s="8"/>
       <c r="H856" s="8"/>
@@ -36246,7 +36242,7 @@
       <c r="J856" s="7"/>
       <c r="L856" s="7"/>
     </row>
-    <row r="857" spans="4:12" ht="12.5">
+    <row r="857" spans="4:12">
       <c r="D857" s="7"/>
       <c r="G857" s="8"/>
       <c r="H857" s="8"/>
@@ -36254,7 +36250,7 @@
       <c r="J857" s="7"/>
       <c r="L857" s="7"/>
     </row>
-    <row r="858" spans="4:12" ht="12.5">
+    <row r="858" spans="4:12">
       <c r="D858" s="7"/>
       <c r="G858" s="8"/>
       <c r="H858" s="8"/>
@@ -36262,7 +36258,7 @@
       <c r="J858" s="7"/>
       <c r="L858" s="7"/>
     </row>
-    <row r="859" spans="4:12" ht="12.5">
+    <row r="859" spans="4:12">
       <c r="D859" s="7"/>
       <c r="G859" s="8"/>
       <c r="H859" s="8"/>
@@ -36270,7 +36266,7 @@
       <c r="J859" s="7"/>
       <c r="L859" s="7"/>
     </row>
-    <row r="860" spans="4:12" ht="12.5">
+    <row r="860" spans="4:12">
       <c r="D860" s="7"/>
       <c r="G860" s="8"/>
       <c r="H860" s="8"/>
@@ -36278,7 +36274,7 @@
       <c r="J860" s="7"/>
       <c r="L860" s="7"/>
     </row>
-    <row r="861" spans="4:12" ht="12.5">
+    <row r="861" spans="4:12">
       <c r="D861" s="7"/>
       <c r="G861" s="8"/>
       <c r="H861" s="8"/>
@@ -36286,7 +36282,7 @@
       <c r="J861" s="7"/>
       <c r="L861" s="7"/>
     </row>
-    <row r="862" spans="4:12" ht="12.5">
+    <row r="862" spans="4:12">
       <c r="D862" s="7"/>
       <c r="G862" s="8"/>
       <c r="H862" s="8"/>
@@ -36294,7 +36290,7 @@
       <c r="J862" s="7"/>
       <c r="L862" s="7"/>
     </row>
-    <row r="863" spans="4:12" ht="12.5">
+    <row r="863" spans="4:12">
       <c r="D863" s="7"/>
       <c r="G863" s="8"/>
       <c r="H863" s="8"/>
@@ -36302,7 +36298,7 @@
       <c r="J863" s="7"/>
       <c r="L863" s="7"/>
     </row>
-    <row r="864" spans="4:12" ht="12.5">
+    <row r="864" spans="4:12">
       <c r="D864" s="7"/>
       <c r="G864" s="8"/>
       <c r="H864" s="8"/>
@@ -36310,7 +36306,7 @@
       <c r="J864" s="7"/>
       <c r="L864" s="7"/>
     </row>
-    <row r="865" spans="4:12" ht="12.5">
+    <row r="865" spans="4:12">
       <c r="D865" s="7"/>
       <c r="G865" s="8"/>
       <c r="H865" s="8"/>
@@ -36318,7 +36314,7 @@
       <c r="J865" s="7"/>
       <c r="L865" s="7"/>
     </row>
-    <row r="866" spans="4:12" ht="12.5">
+    <row r="866" spans="4:12">
       <c r="D866" s="7"/>
       <c r="G866" s="8"/>
       <c r="H866" s="8"/>
@@ -36326,7 +36322,7 @@
       <c r="J866" s="7"/>
       <c r="L866" s="7"/>
     </row>
-    <row r="867" spans="4:12" ht="12.5">
+    <row r="867" spans="4:12">
       <c r="D867" s="7"/>
       <c r="G867" s="8"/>
       <c r="H867" s="8"/>
@@ -36334,7 +36330,7 @@
       <c r="J867" s="7"/>
       <c r="L867" s="7"/>
     </row>
-    <row r="868" spans="4:12" ht="12.5">
+    <row r="868" spans="4:12">
       <c r="D868" s="7"/>
       <c r="G868" s="8"/>
       <c r="H868" s="8"/>
@@ -36342,7 +36338,7 @@
       <c r="J868" s="7"/>
       <c r="L868" s="7"/>
     </row>
-    <row r="869" spans="4:12" ht="12.5">
+    <row r="869" spans="4:12">
       <c r="D869" s="7"/>
       <c r="G869" s="8"/>
       <c r="H869" s="8"/>
@@ -36350,7 +36346,7 @@
       <c r="J869" s="7"/>
       <c r="L869" s="7"/>
     </row>
-    <row r="870" spans="4:12" ht="12.5">
+    <row r="870" spans="4:12">
       <c r="D870" s="7"/>
       <c r="G870" s="8"/>
       <c r="H870" s="8"/>
@@ -36358,7 +36354,7 @@
       <c r="J870" s="7"/>
       <c r="L870" s="7"/>
     </row>
-    <row r="871" spans="4:12" ht="12.5">
+    <row r="871" spans="4:12">
       <c r="D871" s="7"/>
       <c r="G871" s="8"/>
       <c r="H871" s="8"/>
@@ -36366,7 +36362,7 @@
       <c r="J871" s="7"/>
       <c r="L871" s="7"/>
     </row>
-    <row r="872" spans="4:12" ht="12.5">
+    <row r="872" spans="4:12">
       <c r="D872" s="7"/>
       <c r="G872" s="8"/>
       <c r="H872" s="8"/>
@@ -36374,7 +36370,7 @@
       <c r="J872" s="7"/>
       <c r="L872" s="7"/>
     </row>
-    <row r="873" spans="4:12" ht="12.5">
+    <row r="873" spans="4:12">
       <c r="D873" s="7"/>
       <c r="G873" s="8"/>
       <c r="H873" s="8"/>
@@ -36382,7 +36378,7 @@
       <c r="J873" s="7"/>
       <c r="L873" s="7"/>
     </row>
-    <row r="874" spans="4:12" ht="12.5">
+    <row r="874" spans="4:12">
       <c r="D874" s="7"/>
       <c r="G874" s="8"/>
       <c r="H874" s="8"/>
@@ -36390,7 +36386,7 @@
       <c r="J874" s="7"/>
       <c r="L874" s="7"/>
     </row>
-    <row r="875" spans="4:12" ht="12.5">
+    <row r="875" spans="4:12">
       <c r="D875" s="7"/>
       <c r="G875" s="8"/>
       <c r="H875" s="8"/>
@@ -36398,7 +36394,7 @@
       <c r="J875" s="7"/>
       <c r="L875" s="7"/>
     </row>
-    <row r="876" spans="4:12" ht="12.5">
+    <row r="876" spans="4:12">
       <c r="D876" s="7"/>
       <c r="G876" s="8"/>
       <c r="H876" s="8"/>
@@ -36406,7 +36402,7 @@
       <c r="J876" s="7"/>
       <c r="L876" s="7"/>
     </row>
-    <row r="877" spans="4:12" ht="12.5">
+    <row r="877" spans="4:12">
       <c r="D877" s="7"/>
       <c r="G877" s="8"/>
       <c r="H877" s="8"/>
@@ -36414,7 +36410,7 @@
       <c r="J877" s="7"/>
       <c r="L877" s="7"/>
     </row>
-    <row r="878" spans="4:12" ht="12.5">
+    <row r="878" spans="4:12">
       <c r="D878" s="7"/>
       <c r="G878" s="8"/>
       <c r="H878" s="8"/>
@@ -36422,7 +36418,7 @@
       <c r="J878" s="7"/>
       <c r="L878" s="7"/>
     </row>
-    <row r="879" spans="4:12" ht="12.5">
+    <row r="879" spans="4:12">
       <c r="D879" s="7"/>
       <c r="G879" s="8"/>
       <c r="H879" s="8"/>
@@ -36430,7 +36426,7 @@
       <c r="J879" s="7"/>
       <c r="L879" s="7"/>
     </row>
-    <row r="880" spans="4:12" ht="12.5">
+    <row r="880" spans="4:12">
       <c r="D880" s="7"/>
       <c r="G880" s="8"/>
       <c r="H880" s="8"/>
@@ -36438,7 +36434,7 @@
       <c r="J880" s="7"/>
       <c r="L880" s="7"/>
     </row>
-    <row r="881" spans="4:12" ht="12.5">
+    <row r="881" spans="4:12">
       <c r="D881" s="7"/>
       <c r="G881" s="8"/>
       <c r="H881" s="8"/>
@@ -36446,7 +36442,7 @@
       <c r="J881" s="7"/>
       <c r="L881" s="7"/>
     </row>
-    <row r="882" spans="4:12" ht="12.5">
+    <row r="882" spans="4:12">
       <c r="D882" s="7"/>
       <c r="G882" s="8"/>
       <c r="H882" s="8"/>
@@ -36454,7 +36450,7 @@
       <c r="J882" s="7"/>
       <c r="L882" s="7"/>
     </row>
-    <row r="883" spans="4:12" ht="12.5">
+    <row r="883" spans="4:12">
       <c r="D883" s="7"/>
       <c r="G883" s="8"/>
       <c r="H883" s="8"/>
@@ -36462,7 +36458,7 @@
       <c r="J883" s="7"/>
       <c r="L883" s="7"/>
     </row>
-    <row r="884" spans="4:12" ht="12.5">
+    <row r="884" spans="4:12">
       <c r="D884" s="7"/>
       <c r="G884" s="8"/>
       <c r="H884" s="8"/>
@@ -36470,7 +36466,7 @@
       <c r="J884" s="7"/>
       <c r="L884" s="7"/>
     </row>
-    <row r="885" spans="4:12" ht="12.5">
+    <row r="885" spans="4:12">
       <c r="D885" s="7"/>
       <c r="G885" s="8"/>
       <c r="H885" s="8"/>
@@ -36478,7 +36474,7 @@
       <c r="J885" s="7"/>
       <c r="L885" s="7"/>
     </row>
-    <row r="886" spans="4:12" ht="12.5">
+    <row r="886" spans="4:12">
       <c r="D886" s="7"/>
       <c r="G886" s="8"/>
       <c r="H886" s="8"/>
@@ -36486,7 +36482,7 @@
       <c r="J886" s="7"/>
       <c r="L886" s="7"/>
     </row>
-    <row r="887" spans="4:12" ht="12.5">
+    <row r="887" spans="4:12">
       <c r="D887" s="7"/>
       <c r="G887" s="8"/>
       <c r="H887" s="8"/>
@@ -36494,7 +36490,7 @@
       <c r="J887" s="7"/>
       <c r="L887" s="7"/>
     </row>
-    <row r="888" spans="4:12" ht="12.5">
+    <row r="888" spans="4:12">
       <c r="D888" s="7"/>
       <c r="G888" s="8"/>
       <c r="H888" s="8"/>
@@ -36502,7 +36498,7 @@
       <c r="J888" s="7"/>
       <c r="L888" s="7"/>
     </row>
-    <row r="889" spans="4:12" ht="12.5">
+    <row r="889" spans="4:12">
       <c r="D889" s="7"/>
       <c r="G889" s="8"/>
       <c r="H889" s="8"/>
@@ -36510,7 +36506,7 @@
       <c r="J889" s="7"/>
       <c r="L889" s="7"/>
     </row>
-    <row r="890" spans="4:12" ht="12.5">
+    <row r="890" spans="4:12">
       <c r="D890" s="7"/>
       <c r="G890" s="8"/>
       <c r="H890" s="8"/>
@@ -36518,7 +36514,7 @@
       <c r="J890" s="7"/>
       <c r="L890" s="7"/>
     </row>
-    <row r="891" spans="4:12" ht="12.5">
+    <row r="891" spans="4:12">
       <c r="D891" s="7"/>
       <c r="G891" s="8"/>
       <c r="H891" s="8"/>
@@ -36526,7 +36522,7 @@
       <c r="J891" s="7"/>
       <c r="L891" s="7"/>
     </row>
-    <row r="892" spans="4:12" ht="12.5">
+    <row r="892" spans="4:12">
       <c r="D892" s="7"/>
       <c r="G892" s="8"/>
       <c r="H892" s="8"/>
@@ -36534,7 +36530,7 @@
       <c r="J892" s="7"/>
       <c r="L892" s="7"/>
     </row>
-    <row r="893" spans="4:12" ht="12.5">
+    <row r="893" spans="4:12">
       <c r="D893" s="7"/>
       <c r="G893" s="8"/>
       <c r="H893" s="8"/>
@@ -36542,7 +36538,7 @@
       <c r="J893" s="7"/>
       <c r="L893" s="7"/>
     </row>
-    <row r="894" spans="4:12" ht="12.5">
+    <row r="894" spans="4:12">
       <c r="D894" s="7"/>
       <c r="G894" s="8"/>
       <c r="H894" s="8"/>
@@ -36550,7 +36546,7 @@
       <c r="J894" s="7"/>
       <c r="L894" s="7"/>
     </row>
-    <row r="895" spans="4:12" ht="12.5">
+    <row r="895" spans="4:12">
       <c r="D895" s="7"/>
       <c r="G895" s="8"/>
       <c r="H895" s="8"/>
@@ -36558,7 +36554,7 @@
       <c r="J895" s="7"/>
       <c r="L895" s="7"/>
     </row>
-    <row r="896" spans="4:12" ht="12.5">
+    <row r="896" spans="4:12">
       <c r="D896" s="7"/>
       <c r="G896" s="8"/>
       <c r="H896" s="8"/>
@@ -36566,7 +36562,7 @@
       <c r="J896" s="7"/>
       <c r="L896" s="7"/>
     </row>
-    <row r="897" spans="4:12" ht="12.5">
+    <row r="897" spans="4:12">
       <c r="D897" s="7"/>
       <c r="G897" s="8"/>
       <c r="H897" s="8"/>
@@ -36574,7 +36570,7 @@
       <c r="J897" s="7"/>
       <c r="L897" s="7"/>
     </row>
-    <row r="898" spans="4:12" ht="12.5">
+    <row r="898" spans="4:12">
       <c r="D898" s="7"/>
       <c r="G898" s="8"/>
       <c r="H898" s="8"/>
@@ -36582,7 +36578,7 @@
       <c r="J898" s="7"/>
       <c r="L898" s="7"/>
     </row>
-    <row r="899" spans="4:12" ht="12.5">
+    <row r="899" spans="4:12">
       <c r="D899" s="7"/>
       <c r="G899" s="8"/>
       <c r="H899" s="8"/>
@@ -36590,7 +36586,7 @@
       <c r="J899" s="7"/>
       <c r="L899" s="7"/>
     </row>
-    <row r="900" spans="4:12" ht="12.5">
+    <row r="900" spans="4:12">
       <c r="D900" s="7"/>
       <c r="G900" s="8"/>
       <c r="H900" s="8"/>
@@ -36598,7 +36594,7 @@
       <c r="J900" s="7"/>
       <c r="L900" s="7"/>
     </row>
-    <row r="901" spans="4:12" ht="12.5">
+    <row r="901" spans="4:12">
       <c r="D901" s="7"/>
       <c r="G901" s="8"/>
       <c r="H901" s="8"/>
@@ -36606,7 +36602,7 @@
       <c r="J901" s="7"/>
       <c r="L901" s="7"/>
     </row>
-    <row r="902" spans="4:12" ht="12.5">
+    <row r="902" spans="4:12">
       <c r="D902" s="7"/>
       <c r="G902" s="8"/>
       <c r="H902" s="8"/>
@@ -36614,7 +36610,7 @@
       <c r="J902" s="7"/>
       <c r="L902" s="7"/>
     </row>
-    <row r="903" spans="4:12" ht="12.5">
+    <row r="903" spans="4:12">
       <c r="D903" s="7"/>
       <c r="G903" s="8"/>
       <c r="H903" s="8"/>
@@ -36622,7 +36618,7 @@
       <c r="J903" s="7"/>
       <c r="L903" s="7"/>
     </row>
-    <row r="904" spans="4:12" ht="12.5">
+    <row r="904" spans="4:12">
       <c r="D904" s="7"/>
       <c r="G904" s="8"/>
       <c r="H904" s="8"/>
@@ -36630,7 +36626,7 @@
       <c r="J904" s="7"/>
       <c r="L904" s="7"/>
     </row>
-    <row r="905" spans="4:12" ht="12.5">
+    <row r="905" spans="4:12">
       <c r="D905" s="7"/>
       <c r="G905" s="8"/>
       <c r="H905" s="8"/>
@@ -36638,7 +36634,7 @@
       <c r="J905" s="7"/>
       <c r="L905" s="7"/>
     </row>
-    <row r="906" spans="4:12" ht="12.5">
+    <row r="906" spans="4:12">
       <c r="D906" s="7"/>
       <c r="G906" s="8"/>
       <c r="H906" s="8"/>
@@ -36646,7 +36642,7 @@
       <c r="J906" s="7"/>
       <c r="L906" s="7"/>
     </row>
-    <row r="907" spans="4:12" ht="12.5">
+    <row r="907" spans="4:12">
       <c r="D907" s="7"/>
       <c r="G907" s="8"/>
       <c r="H907" s="8"/>
@@ -36654,7 +36650,7 @@
       <c r="J907" s="7"/>
       <c r="L907" s="7"/>
     </row>
-    <row r="908" spans="4:12" ht="12.5">
+    <row r="908" spans="4:12">
       <c r="D908" s="7"/>
       <c r="G908" s="8"/>
       <c r="H908" s="8"/>
@@ -36662,7 +36658,7 @@
       <c r="J908" s="7"/>
       <c r="L908" s="7"/>
     </row>
-    <row r="909" spans="4:12" ht="12.5">
+    <row r="909" spans="4:12">
       <c r="D909" s="7"/>
       <c r="G909" s="8"/>
       <c r="H909" s="8"/>
@@ -36670,7 +36666,7 @@
       <c r="J909" s="7"/>
       <c r="L909" s="7"/>
     </row>
-    <row r="910" spans="4:12" ht="12.5">
+    <row r="910" spans="4:12">
       <c r="D910" s="7"/>
       <c r="G910" s="8"/>
       <c r="H910" s="8"/>
@@ -36678,7 +36674,7 @@
       <c r="J910" s="7"/>
       <c r="L910" s="7"/>
     </row>
-    <row r="911" spans="4:12" ht="12.5">
+    <row r="911" spans="4:12">
       <c r="D911" s="7"/>
       <c r="G911" s="8"/>
       <c r="H911" s="8"/>
@@ -36686,7 +36682,7 @@
       <c r="J911" s="7"/>
       <c r="L911" s="7"/>
     </row>
-    <row r="912" spans="4:12" ht="12.5">
+    <row r="912" spans="4:12">
       <c r="D912" s="7"/>
       <c r="G912" s="8"/>
       <c r="H912" s="8"/>
@@ -36694,7 +36690,7 @@
       <c r="J912" s="7"/>
       <c r="L912" s="7"/>
     </row>
-    <row r="913" spans="4:12" ht="12.5">
+    <row r="913" spans="4:12">
       <c r="D913" s="7"/>
       <c r="G913" s="8"/>
       <c r="H913" s="8"/>
@@ -36702,7 +36698,7 @@
       <c r="J913" s="7"/>
       <c r="L913" s="7"/>
     </row>
-    <row r="914" spans="4:12" ht="12.5">
+    <row r="914" spans="4:12">
       <c r="D914" s="7"/>
       <c r="G914" s="8"/>
       <c r="H914" s="8"/>
@@ -36710,7 +36706,7 @@
       <c r="J914" s="7"/>
       <c r="L914" s="7"/>
     </row>
-    <row r="915" spans="4:12" ht="12.5">
+    <row r="915" spans="4:12">
       <c r="D915" s="7"/>
       <c r="G915" s="8"/>
       <c r="H915" s="8"/>
@@ -36718,7 +36714,7 @@
       <c r="J915" s="7"/>
       <c r="L915" s="7"/>
     </row>
-    <row r="916" spans="4:12" ht="12.5">
+    <row r="916" spans="4:12">
       <c r="D916" s="7"/>
       <c r="G916" s="8"/>
       <c r="H916" s="8"/>
@@ -36726,7 +36722,7 @@
       <c r="J916" s="7"/>
       <c r="L916" s="7"/>
     </row>
-    <row r="917" spans="4:12" ht="12.5">
+    <row r="917" spans="4:12">
       <c r="D917" s="7"/>
       <c r="G917" s="8"/>
       <c r="H917" s="8"/>
@@ -36734,7 +36730,7 @@
       <c r="J917" s="7"/>
       <c r="L917" s="7"/>
     </row>
-    <row r="918" spans="4:12" ht="12.5">
+    <row r="918" spans="4:12">
       <c r="D918" s="7"/>
       <c r="G918" s="8"/>
       <c r="H918" s="8"/>
@@ -36742,7 +36738,7 @@
       <c r="J918" s="7"/>
       <c r="L918" s="7"/>
     </row>
-    <row r="919" spans="4:12" ht="12.5">
+    <row r="919" spans="4:12">
       <c r="D919" s="7"/>
       <c r="G919" s="8"/>
       <c r="H919" s="8"/>
@@ -36750,7 +36746,7 @@
       <c r="J919" s="7"/>
       <c r="L919" s="7"/>
     </row>
-    <row r="920" spans="4:12" ht="12.5">
+    <row r="920" spans="4:12">
       <c r="D920" s="7"/>
       <c r="G920" s="8"/>
       <c r="H920" s="8"/>
@@ -36758,7 +36754,7 @@
       <c r="J920" s="7"/>
       <c r="L920" s="7"/>
     </row>
-    <row r="921" spans="4:12" ht="12.5">
+    <row r="921" spans="4:12">
       <c r="D921" s="7"/>
       <c r="G921" s="8"/>
       <c r="H921" s="8"/>
@@ -36766,7 +36762,7 @@
       <c r="J921" s="7"/>
       <c r="L921" s="7"/>
     </row>
-    <row r="922" spans="4:12" ht="12.5">
+    <row r="922" spans="4:12">
       <c r="D922" s="7"/>
       <c r="G922" s="8"/>
       <c r="H922" s="8"/>
@@ -36774,7 +36770,7 @@
       <c r="J922" s="7"/>
       <c r="L922" s="7"/>
     </row>
-    <row r="923" spans="4:12" ht="12.5">
+    <row r="923" spans="4:12">
       <c r="D923" s="7"/>
       <c r="G923" s="8"/>
       <c r="H923" s="8"/>
@@ -36782,7 +36778,7 @@
       <c r="J923" s="7"/>
       <c r="L923" s="7"/>
     </row>
-    <row r="924" spans="4:12" ht="12.5">
+    <row r="924" spans="4:12">
       <c r="D924" s="7"/>
       <c r="G924" s="8"/>
       <c r="H924" s="8"/>
@@ -36790,7 +36786,7 @@
       <c r="J924" s="7"/>
       <c r="L924" s="7"/>
     </row>
-    <row r="925" spans="4:12" ht="12.5">
+    <row r="925" spans="4:12">
       <c r="D925" s="7"/>
       <c r="G925" s="8"/>
       <c r="H925" s="8"/>
@@ -36798,7 +36794,7 @@
       <c r="J925" s="7"/>
       <c r="L925" s="7"/>
     </row>
-    <row r="926" spans="4:12" ht="12.5">
+    <row r="926" spans="4:12">
       <c r="D926" s="7"/>
       <c r="G926" s="8"/>
       <c r="H926" s="8"/>
@@ -36806,7 +36802,7 @@
       <c r="J926" s="7"/>
       <c r="L926" s="7"/>
     </row>
-    <row r="927" spans="4:12" ht="12.5">
+    <row r="927" spans="4:12">
       <c r="D927" s="7"/>
       <c r="G927" s="8"/>
       <c r="H927" s="8"/>
@@ -36814,7 +36810,7 @@
       <c r="J927" s="7"/>
       <c r="L927" s="7"/>
     </row>
-    <row r="928" spans="4:12" ht="12.5">
+    <row r="928" spans="4:12">
       <c r="D928" s="7"/>
       <c r="G928" s="8"/>
       <c r="H928" s="8"/>
@@ -36822,7 +36818,7 @@
       <c r="J928" s="7"/>
       <c r="L928" s="7"/>
     </row>
-    <row r="929" spans="4:12" ht="12.5">
+    <row r="929" spans="4:12">
       <c r="D929" s="7"/>
       <c r="G929" s="8"/>
       <c r="H929" s="8"/>
@@ -36830,7 +36826,7 @@
       <c r="J929" s="7"/>
       <c r="L929" s="7"/>
     </row>
-    <row r="930" spans="4:12" ht="12.5">
+    <row r="930" spans="4:12">
       <c r="D930" s="7"/>
       <c r="G930" s="8"/>
       <c r="H930" s="8"/>
@@ -36838,7 +36834,7 @@
       <c r="J930" s="7"/>
       <c r="L930" s="7"/>
     </row>
-    <row r="931" spans="4:12" ht="12.5">
+    <row r="931" spans="4:12">
       <c r="D931" s="7"/>
       <c r="G931" s="8"/>
       <c r="H931" s="8"/>
@@ -36846,7 +36842,7 @@
       <c r="J931" s="7"/>
       <c r="L931" s="7"/>
     </row>
-    <row r="932" spans="4:12" ht="12.5">
+    <row r="932" spans="4:12">
       <c r="D932" s="7"/>
       <c r="G932" s="8"/>
       <c r="H932" s="8"/>
@@ -36854,7 +36850,7 @@
       <c r="J932" s="7"/>
       <c r="L932" s="7"/>
     </row>
-    <row r="933" spans="4:12" ht="12.5">
+    <row r="933" spans="4:12">
       <c r="D933" s="7"/>
       <c r="G933" s="8"/>
       <c r="H933" s="8"/>
@@ -36862,7 +36858,7 @@
       <c r="J933" s="7"/>
       <c r="L933" s="7"/>
     </row>
-    <row r="934" spans="4:12" ht="12.5">
+    <row r="934" spans="4:12">
       <c r="D934" s="7"/>
       <c r="G934" s="8"/>
       <c r="H934" s="8"/>
@@ -36870,7 +36866,7 @@
       <c r="J934" s="7"/>
       <c r="L934" s="7"/>
     </row>
-    <row r="935" spans="4:12" ht="12.5">
+    <row r="935" spans="4:12">
       <c r="D935" s="7"/>
       <c r="G935" s="8"/>
       <c r="H935" s="8"/>
@@ -36878,7 +36874,7 @@
       <c r="J935" s="7"/>
       <c r="L935" s="7"/>
     </row>
-    <row r="936" spans="4:12" ht="12.5">
+    <row r="936" spans="4:12">
       <c r="D936" s="7"/>
       <c r="G936" s="8"/>
       <c r="H936" s="8"/>
@@ -36886,7 +36882,7 @@
       <c r="J936" s="7"/>
       <c r="L936" s="7"/>
     </row>
-    <row r="937" spans="4:12" ht="12.5">
+    <row r="937" spans="4:12">
       <c r="D937" s="7"/>
       <c r="G937" s="8"/>
       <c r="H937" s="8"/>
@@ -36894,7 +36890,7 @@
       <c r="J937" s="7"/>
       <c r="L937" s="7"/>
     </row>
-    <row r="938" spans="4:12" ht="12.5">
+    <row r="938" spans="4:12">
       <c r="D938" s="7"/>
       <c r="G938" s="8"/>
       <c r="H938" s="8"/>
@@ -36902,7 +36898,7 @@
       <c r="J938" s="7"/>
       <c r="L938" s="7"/>
     </row>
-    <row r="939" spans="4:12" ht="12.5">
+    <row r="939" spans="4:12">
       <c r="D939" s="7"/>
       <c r="G939" s="8"/>
       <c r="H939" s="8"/>
@@ -36910,7 +36906,7 @@
       <c r="J939" s="7"/>
       <c r="L939" s="7"/>
     </row>
-    <row r="940" spans="4:12" ht="12.5">
+    <row r="940" spans="4:12">
       <c r="D940" s="7"/>
       <c r="G940" s="8"/>
       <c r="H940" s="8"/>
@@ -36918,7 +36914,7 @@
       <c r="J940" s="7"/>
       <c r="L940" s="7"/>
     </row>
-    <row r="941" spans="4:12" ht="12.5">
+    <row r="941" spans="4:12">
       <c r="D941" s="7"/>
       <c r="G941" s="8"/>
       <c r="H941" s="8"/>
@@ -36926,7 +36922,7 @@
       <c r="J941" s="7"/>
       <c r="L941" s="7"/>
     </row>
-    <row r="942" spans="4:12" ht="12.5">
+    <row r="942" spans="4:12">
       <c r="D942" s="7"/>
       <c r="G942" s="8"/>
       <c r="H942" s="8"/>
@@ -36934,7 +36930,7 @@
       <c r="J942" s="7"/>
       <c r="L942" s="7"/>
     </row>
-    <row r="943" spans="4:12" ht="12.5">
+    <row r="943" spans="4:12">
       <c r="D943" s="7"/>
       <c r="G943" s="8"/>
       <c r="H943" s="8"/>
@@ -36942,7 +36938,7 @@
       <c r="J943" s="7"/>
       <c r="L943" s="7"/>
     </row>
-    <row r="944" spans="4:12" ht="12.5">
+    <row r="944" spans="4:12">
       <c r="D944" s="7"/>
       <c r="G944" s="8"/>
       <c r="H944" s="8"/>
@@ -36950,7 +36946,7 @@
       <c r="J944" s="7"/>
       <c r="L944" s="7"/>
     </row>
-    <row r="945" spans="4:12" ht="12.5">
+    <row r="945" spans="4:12">
       <c r="D945" s="7"/>
       <c r="G945" s="8"/>
       <c r="H945" s="8"/>
@@ -36958,7 +36954,7 @@
       <c r="J945" s="7"/>
       <c r="L945" s="7"/>
     </row>
-    <row r="946" spans="4:12" ht="12.5">
+    <row r="946" spans="4:12">
       <c r="D946" s="7"/>
       <c r="G946" s="8"/>
       <c r="H946" s="8"/>
@@ -36966,7 +36962,7 @@
       <c r="J946" s="7"/>
       <c r="L946" s="7"/>
     </row>
-    <row r="947" spans="4:12" ht="12.5">
+    <row r="947" spans="4:12">
       <c r="D947" s="7"/>
       <c r="G947" s="8"/>
       <c r="H947" s="8"/>
@@ -36974,7 +36970,7 @@
       <c r="J947" s="7"/>
       <c r="L947" s="7"/>
     </row>
-    <row r="948" spans="4:12" ht="12.5">
+    <row r="948" spans="4:12">
       <c r="D948" s="7"/>
       <c r="G948" s="8"/>
       <c r="H948" s="8"/>
@@ -36982,7 +36978,7 @@
       <c r="J948" s="7"/>
       <c r="L948" s="7"/>
     </row>
-    <row r="949" spans="4:12" ht="12.5">
+    <row r="949" spans="4:12">
       <c r="D949" s="7"/>
       <c r="G949" s="8"/>
       <c r="H949" s="8"/>
@@ -36990,7 +36986,7 @@
       <c r="J949" s="7"/>
       <c r="L949" s="7"/>
     </row>
-    <row r="950" spans="4:12" ht="12.5">
+    <row r="950" spans="4:12">
       <c r="D950" s="7"/>
       <c r="G950" s="8"/>
       <c r="H950" s="8"/>
@@ -36998,7 +36994,7 @@
       <c r="J950" s="7"/>
       <c r="L950" s="7"/>
     </row>
-    <row r="951" spans="4:12" ht="12.5">
+    <row r="951" spans="4:12">
       <c r="D951" s="7"/>
       <c r="G951" s="8"/>
       <c r="H951" s="8"/>
@@ -37006,7 +37002,7 @@
       <c r="J951" s="7"/>
       <c r="L951" s="7"/>
     </row>
-    <row r="952" spans="4:12" ht="12.5">
+    <row r="952" spans="4:12">
       <c r="D952" s="7"/>
       <c r="G952" s="8"/>
       <c r="H952" s="8"/>
@@ -37014,7 +37010,7 @@
       <c r="J952" s="7"/>
       <c r="L952" s="7"/>
     </row>
-    <row r="953" spans="4:12" ht="12.5">
+    <row r="953" spans="4:12">
       <c r="D953" s="7"/>
       <c r="G953" s="8"/>
       <c r="H953" s="8"/>
@@ -37022,7 +37018,7 @@
       <c r="J953" s="7"/>
       <c r="L953" s="7"/>
     </row>
-    <row r="954" spans="4:12" ht="12.5">
+    <row r="954" spans="4:12">
       <c r="D954" s="7"/>
       <c r="G954" s="8"/>
       <c r="H954" s="8"/>
@@ -37030,7 +37026,7 @@
       <c r="J954" s="7"/>
       <c r="L954" s="7"/>
     </row>
-    <row r="955" spans="4:12" ht="12.5">
+    <row r="955" spans="4:12">
       <c r="D955" s="7"/>
       <c r="G955" s="8"/>
       <c r="H955" s="8"/>
@@ -37038,7 +37034,7 @@
       <c r="J955" s="7"/>
       <c r="L955" s="7"/>
     </row>
-    <row r="956" spans="4:12" ht="12.5">
+    <row r="956" spans="4:12">
       <c r="D956" s="7"/>
       <c r="G956" s="8"/>
       <c r="H956" s="8"/>
@@ -37046,7 +37042,7 @@
       <c r="J956" s="7"/>
       <c r="L956" s="7"/>
     </row>
-    <row r="957" spans="4:12" ht="12.5">
+    <row r="957" spans="4:12">
       <c r="D957" s="7"/>
       <c r="G957" s="8"/>
       <c r="H957" s="8"/>
@@ -37054,7 +37050,7 @@
       <c r="J957" s="7"/>
       <c r="L957" s="7"/>
     </row>
-    <row r="958" spans="4:12" ht="12.5">
+    <row r="958" spans="4:12">
       <c r="D958" s="7"/>
       <c r="G958" s="8"/>
       <c r="H958" s="8"/>
@@ -37062,7 +37058,7 @@
       <c r="J958" s="7"/>
       <c r="L958" s="7"/>
     </row>
-    <row r="959" spans="4:12" ht="12.5">
+    <row r="959" spans="4:12">
       <c r="D959" s="7"/>
       <c r="G959" s="8"/>
       <c r="H959" s="8"/>
@@ -37070,7 +37066,7 @@
       <c r="J959" s="7"/>
       <c r="L959" s="7"/>
     </row>
-    <row r="960" spans="4:12" ht="12.5">
+    <row r="960" spans="4:12">
       <c r="D960" s="7"/>
       <c r="G960" s="8"/>
       <c r="H960" s="8"/>
@@ -37078,7 +37074,7 @@
       <c r="J960" s="7"/>
       <c r="L960" s="7"/>
     </row>
-    <row r="961" spans="4:12" ht="12.5">
+    <row r="961" spans="4:12">
       <c r="D961" s="7"/>
       <c r="G961" s="8"/>
       <c r="H961" s="8"/>
@@ -37086,7 +37082,7 @@
       <c r="J961" s="7"/>
       <c r="L961" s="7"/>
     </row>
-    <row r="962" spans="4:12" ht="12.5">
+    <row r="962" spans="4:12">
       <c r="D962" s="7"/>
       <c r="G962" s="8"/>
       <c r="H962" s="8"/>
@@ -37094,7 +37090,7 @@
       <c r="J962" s="7"/>
       <c r="L962" s="7"/>
     </row>
-    <row r="963" spans="4:12" ht="12.5">
+    <row r="963" spans="4:12">
       <c r="D963" s="7"/>
       <c r="G963" s="8"/>
       <c r="H963" s="8"/>
@@ -37102,7 +37098,7 @@
       <c r="J963" s="7"/>
       <c r="L963" s="7"/>
     </row>
-    <row r="964" spans="4:12" ht="12.5">
+    <row r="964" spans="4:12">
       <c r="D964" s="7"/>
       <c r="G964" s="8"/>
       <c r="H964" s="8"/>
@@ -37110,7 +37106,7 @@
       <c r="J964" s="7"/>
       <c r="L964" s="7"/>
     </row>
-    <row r="965" spans="4:12" ht="12.5">
+    <row r="965" spans="4:12">
       <c r="D965" s="7"/>
       <c r="G965" s="8"/>
       <c r="H965" s="8"/>
@@ -37118,7 +37114,7 @@
       <c r="J965" s="7"/>
       <c r="L965" s="7"/>
     </row>
-    <row r="966" spans="4:12" ht="12.5">
+    <row r="966" spans="4:12">
       <c r="D966" s="7"/>
       <c r="G966" s="8"/>
       <c r="H966" s="8"/>
@@ -37126,7 +37122,7 @@
       <c r="J966" s="7"/>
       <c r="L966" s="7"/>
     </row>
-    <row r="967" spans="4:12" ht="12.5">
+    <row r="967" spans="4:12">
       <c r="D967" s="7"/>
       <c r="G967" s="8"/>
       <c r="H967" s="8"/>
@@ -37134,7 +37130,7 @@
       <c r="J967" s="7"/>
       <c r="L967" s="7"/>
     </row>
-    <row r="968" spans="4:12" ht="12.5">
+    <row r="968" spans="4:12">
       <c r="D968" s="7"/>
       <c r="G968" s="8"/>
       <c r="H968" s="8"/>
@@ -37142,7 +37138,7 @@
       <c r="J968" s="7"/>
       <c r="L968" s="7"/>
     </row>
-    <row r="969" spans="4:12" ht="12.5">
+    <row r="969" spans="4:12">
       <c r="D969" s="7"/>
       <c r="G969" s="8"/>
       <c r="H969" s="8"/>
@@ -37150,7 +37146,7 @@
       <c r="J969" s="7"/>
       <c r="L969" s="7"/>
     </row>
-    <row r="970" spans="4:12" ht="12.5">
+    <row r="970" spans="4:12">
       <c r="D970" s="7"/>
       <c r="G970" s="8"/>
       <c r="H970" s="8"/>
@@ -37158,7 +37154,7 @@
       <c r="J970" s="7"/>
       <c r="L970" s="7"/>
     </row>
-    <row r="971" spans="4:12" ht="12.5">
+    <row r="971" spans="4:12">
       <c r="D971" s="7"/>
       <c r="G971" s="8"/>
       <c r="H971" s="8"/>
@@ -37166,7 +37162,7 @@
       <c r="J971" s="7"/>
       <c r="L971" s="7"/>
     </row>
-    <row r="972" spans="4:12" ht="12.5">
+    <row r="972" spans="4:12">
       <c r="D972" s="7"/>
       <c r="G972" s="8"/>
       <c r="H972" s="8"/>
@@ -37174,7 +37170,7 @@
       <c r="J972" s="7"/>
       <c r="L972" s="7"/>
     </row>
-    <row r="973" spans="4:12" ht="12.5">
+    <row r="973" spans="4:12">
       <c r="D973" s="7"/>
       <c r="G973" s="8"/>
       <c r="H973" s="8"/>
@@ -37182,7 +37178,7 @@
       <c r="J973" s="7"/>
       <c r="L973" s="7"/>
     </row>
-    <row r="974" spans="4:12" ht="12.5">
+    <row r="974" spans="4:12">
       <c r="D974" s="7"/>
       <c r="G974" s="8"/>
       <c r="H974" s="8"/>
@@ -37190,7 +37186,7 @@
       <c r="J974" s="7"/>
       <c r="L974" s="7"/>
     </row>
-    <row r="975" spans="4:12" ht="12.5">
+    <row r="975" spans="4:12">
       <c r="D975" s="7"/>
       <c r="G975" s="8"/>
       <c r="H975" s="8"/>
@@ -37198,7 +37194,7 @@
       <c r="J975" s="7"/>
       <c r="L975" s="7"/>
     </row>
-    <row r="976" spans="4:12" ht="12.5">
+    <row r="976" spans="4:12">
       <c r="D976" s="7"/>
       <c r="G976" s="8"/>
       <c r="H976" s="8"/>
@@ -37206,7 +37202,7 @@
       <c r="J976" s="7"/>
       <c r="L976" s="7"/>
     </row>
-    <row r="977" spans="4:12" ht="12.5">
+    <row r="977" spans="4:12">
       <c r="D977" s="7"/>
       <c r="G977" s="8"/>
       <c r="H977" s="8"/>
@@ -37214,7 +37210,7 @@
       <c r="J977" s="7"/>
       <c r="L977" s="7"/>
     </row>
-    <row r="978" spans="4:12" ht="12.5">
+    <row r="978" spans="4:12">
       <c r="D978" s="7"/>
       <c r="G978" s="8"/>
       <c r="H978" s="8"/>
@@ -37222,7 +37218,7 @@
       <c r="J978" s="7"/>
       <c r="L978" s="7"/>
     </row>
-    <row r="979" spans="4:12" ht="12.5">
+    <row r="979" spans="4:12">
       <c r="D979" s="7"/>
       <c r="G979" s="8"/>
       <c r="H979" s="8"/>
@@ -37230,7 +37226,7 @@
       <c r="J979" s="7"/>
       <c r="L979" s="7"/>
     </row>
-    <row r="980" spans="4:12" ht="12.5">
+    <row r="980" spans="4:12">
       <c r="D980" s="7"/>
       <c r="G980" s="8"/>
       <c r="H980" s="8"/>
@@ -37238,7 +37234,7 @@
       <c r="J980" s="7"/>
       <c r="L980" s="7"/>
     </row>
-    <row r="981" spans="4:12" ht="12.5">
+    <row r="981" spans="4:12">
       <c r="D981" s="7"/>
       <c r="G981" s="8"/>
       <c r="H981" s="8"/>
@@ -37246,7 +37242,7 @@
       <c r="J981" s="7"/>
       <c r="L981" s="7"/>
     </row>
-    <row r="982" spans="4:12" ht="12.5">
+    <row r="982" spans="4:12">
       <c r="D982" s="7"/>
       <c r="G982" s="8"/>
       <c r="H982" s="8"/>
@@ -37254,7 +37250,7 @@
       <c r="J982" s="7"/>
       <c r="L982" s="7"/>
     </row>
-    <row r="983" spans="4:12" ht="12.5">
+    <row r="983" spans="4:12">
       <c r="D983" s="7"/>
       <c r="G983" s="8"/>
       <c r="H983" s="8"/>
@@ -37262,7 +37258,7 @@
       <c r="J983" s="7"/>
       <c r="L983" s="7"/>
     </row>
-    <row r="984" spans="4:12" ht="12.5">
+    <row r="984" spans="4:12">
       <c r="D984" s="7"/>
       <c r="G984" s="8"/>
       <c r="H984" s="8"/>
@@ -37270,7 +37266,7 @@
       <c r="J984" s="7"/>
       <c r="L984" s="7"/>
     </row>
-    <row r="985" spans="4:12" ht="12.5">
+    <row r="985" spans="4:12">
       <c r="D985" s="7"/>
       <c r="G985" s="8"/>
       <c r="H985" s="8"/>
@@ -37278,7 +37274,7 @@
       <c r="J985" s="7"/>
       <c r="L985" s="7"/>
     </row>
-    <row r="986" spans="4:12" ht="12.5">
+    <row r="986" spans="4:12">
       <c r="D986" s="7"/>
       <c r="G986" s="8"/>
       <c r="H986" s="8"/>
@@ -37286,7 +37282,7 @@
       <c r="J986" s="7"/>
       <c r="L986" s="7"/>
     </row>
-    <row r="987" spans="4:12" ht="12.5">
+    <row r="987" spans="4:12">
       <c r="D987" s="7"/>
       <c r="G987" s="8"/>
       <c r="H987" s="8"/>
@@ -37294,7 +37290,7 @@
       <c r="J987" s="7"/>
       <c r="L987" s="7"/>
     </row>
-    <row r="988" spans="4:12" ht="12.5">
+    <row r="988" spans="4:12">
       <c r="D988" s="7"/>
       <c r="G988" s="8"/>
       <c r="H988" s="8"/>
@@ -37302,7 +37298,7 @@
       <c r="J988" s="7"/>
       <c r="L988" s="7"/>
     </row>
-    <row r="989" spans="4:12" ht="12.5">
+    <row r="989" spans="4:12">
       <c r="D989" s="7"/>
       <c r="G989" s="8"/>
       <c r="H989" s="8"/>
@@ -37310,7 +37306,7 @@
       <c r="J989" s="7"/>
       <c r="L989" s="7"/>
     </row>
-    <row r="990" spans="4:12" ht="12.5">
+    <row r="990" spans="4:12">
       <c r="D990" s="7"/>
       <c r="G990" s="8"/>
       <c r="H990" s="8"/>
@@ -37318,7 +37314,7 @@
       <c r="J990" s="7"/>
       <c r="L990" s="7"/>
     </row>
-    <row r="991" spans="4:12" ht="12.5">
+    <row r="991" spans="4:12">
       <c r="D991" s="7"/>
       <c r="G991" s="8"/>
       <c r="H991" s="8"/>
@@ -37326,7 +37322,7 @@
       <c r="J991" s="7"/>
       <c r="L991" s="7"/>
     </row>
-    <row r="992" spans="4:12" ht="12.5">
+    <row r="992" spans="4:12">
       <c r="D992" s="7"/>
       <c r="G992" s="8"/>
       <c r="H992" s="8"/>
@@ -46930,7 +46926,7 @@
       <c r="AG7" s="65"/>
       <c r="AH7" s="65"/>
     </row>
-    <row r="8" spans="1:39" ht="50">
+    <row r="8" spans="1:39" ht="37.5">
       <c r="A8" s="15"/>
       <c r="B8" s="66" t="s">
         <v>498</v>

--- a/Archivos/Archivos_origen/Planeación contenido blog Aciertala 2025.xlsx
+++ b/Archivos/Archivos_origen/Planeación contenido blog Aciertala 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/jhor_caro_virtualsoft_tech/Documents/Documentos/GitHub/Planeaci-n_SEO/Archivos/Archivos_origen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="11_D2D46AE609F6779E136FF9258C46CEF0CFAB49D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99BAF1B8-C05C-4804-A656-554FF2413095}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="11_D2D46AE609F6779E136FF9258C46CEF0CFAB49D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08BC1D8F-85A0-4CC1-94F5-2E4D9AF3C4A5}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Abril" sheetId="1" r:id="rId1"/>
@@ -4127,7 +4127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4399,13 +4399,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4639,11 +4645,13 @@
     <col min="9" max="9" width="26.7265625" style="102" customWidth="1"/>
     <col min="10" max="10" width="26.6328125" style="102" customWidth="1"/>
     <col min="11" max="11" width="17.26953125" style="102" customWidth="1"/>
-    <col min="12" max="13" width="12.90625" customWidth="1"/>
+    <col min="12" max="12" width="12.90625" customWidth="1"/>
+    <col min="13" max="13" width="12.90625" style="111" customWidth="1"/>
     <col min="14" max="14" width="25.08984375" style="102" customWidth="1"/>
     <col min="15" max="16" width="27.7265625" style="102" customWidth="1"/>
     <col min="17" max="17" width="14.453125" style="102" customWidth="1"/>
-    <col min="18" max="19" width="14.453125" customWidth="1"/>
+    <col min="18" max="18" width="14.453125" customWidth="1"/>
+    <col min="19" max="19" width="14.453125" style="111" customWidth="1"/>
     <col min="20" max="20" width="23.90625" style="102" customWidth="1"/>
     <col min="21" max="21" width="31.90625" style="102" customWidth="1"/>
     <col min="22" max="16384" width="12.6328125" style="102"/>
@@ -4686,7 +4694,7 @@
       <c r="L1" s="106" t="s">
         <v>798</v>
       </c>
-      <c r="M1" s="106" t="s">
+      <c r="M1" s="109" t="s">
         <v>800</v>
       </c>
       <c r="N1" s="3" t="s">
@@ -4704,7 +4712,7 @@
       <c r="R1" s="106" t="s">
         <v>801</v>
       </c>
-      <c r="S1" s="106" t="s">
+      <c r="S1" s="109" t="s">
         <v>802</v>
       </c>
       <c r="T1" s="3" t="s">
@@ -4767,7 +4775,7 @@
       <c r="L2" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M2" s="108">
+      <c r="M2" s="110">
         <v>120</v>
       </c>
       <c r="N2" s="11" t="s">
@@ -4779,7 +4787,7 @@
       <c r="R2" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S2" s="108">
+      <c r="S2" s="110">
         <v>60</v>
       </c>
       <c r="T2" s="13" t="s">
@@ -4823,7 +4831,7 @@
       <c r="L3" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M3" s="108">
+      <c r="M3" s="110">
         <v>30</v>
       </c>
       <c r="N3" s="16" t="s">
@@ -4839,7 +4847,7 @@
       <c r="R3" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S3" s="108">
+      <c r="S3" s="110">
         <v>15</v>
       </c>
       <c r="T3" s="17" t="s">
@@ -4884,7 +4892,7 @@
       <c r="L4" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M4" s="108">
+      <c r="M4" s="110">
         <v>60</v>
       </c>
       <c r="N4" s="11" t="s">
@@ -4900,7 +4908,7 @@
       <c r="R4" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S4" s="108">
+      <c r="S4" s="110">
         <v>60</v>
       </c>
       <c r="T4" s="17" t="s">
@@ -4945,7 +4953,7 @@
       <c r="L5" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M5" s="108">
+      <c r="M5" s="110">
         <v>30</v>
       </c>
       <c r="N5" s="16" t="s">
@@ -4961,7 +4969,7 @@
       <c r="R5" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S5" s="108">
+      <c r="S5" s="110">
         <v>30</v>
       </c>
       <c r="T5" s="13" t="s">
@@ -5006,7 +5014,7 @@
       <c r="L6" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M6" s="108">
+      <c r="M6" s="110">
         <v>15</v>
       </c>
       <c r="N6" s="13" t="s">
@@ -5022,7 +5030,7 @@
       <c r="R6" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S6" s="108">
+      <c r="S6" s="110">
         <v>15</v>
       </c>
       <c r="T6" s="13" t="s">
@@ -5067,7 +5075,7 @@
       <c r="L7" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M7" s="108">
+      <c r="M7" s="110">
         <v>120</v>
       </c>
       <c r="N7" s="11" t="s">
@@ -5082,7 +5090,7 @@
       <c r="R7" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S7" s="108">
+      <c r="S7" s="110">
         <v>120</v>
       </c>
       <c r="T7" s="13" t="s">
@@ -5126,7 +5134,7 @@
       <c r="L8" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M8" s="108">
+      <c r="M8" s="110">
         <v>30</v>
       </c>
       <c r="N8" s="11" t="s">
@@ -5141,7 +5149,7 @@
       <c r="R8" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S8" s="108">
+      <c r="S8" s="110">
         <v>30</v>
       </c>
       <c r="T8" s="13" t="s">
@@ -5185,7 +5193,7 @@
       <c r="L9" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M9" s="108">
+      <c r="M9" s="110">
         <v>45</v>
       </c>
       <c r="N9" s="11" t="s">
@@ -5200,7 +5208,7 @@
       <c r="R9" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S9" s="108">
+      <c r="S9" s="110">
         <v>45</v>
       </c>
       <c r="T9" s="13" t="s">
@@ -5244,7 +5252,7 @@
       <c r="L10" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M10" s="108">
+      <c r="M10" s="110">
         <v>60</v>
       </c>
       <c r="N10" s="11" t="s">
@@ -5260,7 +5268,7 @@
       <c r="R10" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S10" s="108">
+      <c r="S10" s="110">
         <v>60</v>
       </c>
       <c r="T10" s="13" t="s">
@@ -5305,7 +5313,7 @@
       <c r="L11" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M11" s="108">
+      <c r="M11" s="110">
         <v>60</v>
       </c>
       <c r="N11" s="11" t="s">
@@ -5321,7 +5329,7 @@
       <c r="R11" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S11" s="108">
+      <c r="S11" s="110">
         <v>60</v>
       </c>
       <c r="T11" s="21" t="s">
@@ -5365,7 +5373,7 @@
       <c r="L12" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M12" s="108">
+      <c r="M12" s="110">
         <v>30</v>
       </c>
       <c r="N12" s="11" t="s">
@@ -5381,7 +5389,7 @@
       <c r="R12" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S12" s="108">
+      <c r="S12" s="110">
         <v>30</v>
       </c>
       <c r="T12" s="13" t="s">
@@ -5426,7 +5434,7 @@
       <c r="L13" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M13" s="108">
+      <c r="M13" s="110">
         <v>60</v>
       </c>
       <c r="N13" s="11" t="s">
@@ -5442,7 +5450,7 @@
       <c r="R13" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S13" s="108">
+      <c r="S13" s="110">
         <v>60</v>
       </c>
       <c r="T13" s="21" t="s">
@@ -5487,7 +5495,7 @@
       <c r="L14" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M14" s="108">
+      <c r="M14" s="110">
         <v>90</v>
       </c>
       <c r="N14" s="11" t="s">
@@ -5503,7 +5511,7 @@
       <c r="R14" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S14" s="108">
+      <c r="S14" s="110">
         <v>90</v>
       </c>
       <c r="T14" s="21" t="s">
@@ -5548,7 +5556,7 @@
       <c r="L15" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M15" s="108">
+      <c r="M15" s="110">
         <v>30</v>
       </c>
       <c r="N15" s="11" t="s">
@@ -5564,7 +5572,7 @@
       <c r="R15" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S15" s="108">
+      <c r="S15" s="110">
         <v>30</v>
       </c>
       <c r="T15" s="26" t="s">
@@ -5578,10 +5586,10 @@
       <c r="I16" s="9"/>
       <c r="J16" s="7"/>
       <c r="L16" s="107"/>
-      <c r="M16" s="108"/>
+      <c r="M16" s="110"/>
       <c r="N16" s="7"/>
       <c r="R16" s="107"/>
-      <c r="S16" s="108"/>
+      <c r="S16" s="110"/>
     </row>
     <row r="17" spans="7:19" ht="15.75" customHeight="1">
       <c r="G17" s="8"/>
@@ -5589,10 +5597,10 @@
       <c r="I17" s="9"/>
       <c r="J17" s="7"/>
       <c r="L17" s="107"/>
-      <c r="M17" s="108"/>
+      <c r="M17" s="110"/>
       <c r="N17" s="7"/>
       <c r="R17" s="107"/>
-      <c r="S17" s="108"/>
+      <c r="S17" s="110"/>
     </row>
     <row r="18" spans="7:19" ht="15.75" customHeight="1">
       <c r="G18" s="8"/>
@@ -5601,7 +5609,7 @@
       <c r="J18" s="7"/>
       <c r="N18" s="7"/>
       <c r="R18" s="107"/>
-      <c r="S18" s="108"/>
+      <c r="S18" s="110"/>
     </row>
     <row r="19" spans="7:19" ht="15.75" customHeight="1">
       <c r="G19" s="8"/>
@@ -5609,10 +5617,10 @@
       <c r="I19" s="9"/>
       <c r="J19" s="7"/>
       <c r="L19" s="18"/>
-      <c r="M19" s="63"/>
+      <c r="M19" s="112"/>
       <c r="N19" s="7"/>
       <c r="R19" s="18"/>
-      <c r="S19" s="63"/>
+      <c r="S19" s="112"/>
     </row>
     <row r="20" spans="7:19" ht="15.75" customHeight="1">
       <c r="G20" s="8"/>
@@ -5620,10 +5628,10 @@
       <c r="I20" s="9"/>
       <c r="J20" s="7"/>
       <c r="L20" s="63"/>
-      <c r="M20" s="63"/>
+      <c r="M20" s="112"/>
       <c r="N20" s="7"/>
       <c r="R20" s="63"/>
-      <c r="S20" s="63"/>
+      <c r="S20" s="112"/>
     </row>
     <row r="21" spans="7:19" ht="15.75" customHeight="1">
       <c r="G21" s="8"/>
@@ -12489,10 +12497,12 @@
     <col min="9" max="9" width="26.7265625" customWidth="1"/>
     <col min="10" max="10" width="26.6328125" customWidth="1"/>
     <col min="11" max="11" width="12.6328125" customWidth="1"/>
-    <col min="12" max="13" width="12.90625" customWidth="1"/>
+    <col min="12" max="12" width="12.90625" customWidth="1"/>
+    <col min="13" max="13" width="12.90625" style="111" customWidth="1"/>
     <col min="14" max="14" width="25.08984375" customWidth="1"/>
     <col min="15" max="16" width="27.7265625" customWidth="1"/>
-    <col min="17" max="19" width="14.453125" customWidth="1"/>
+    <col min="17" max="18" width="14.453125" customWidth="1"/>
+    <col min="19" max="19" width="14.453125" style="111" customWidth="1"/>
     <col min="20" max="20" width="23.90625" customWidth="1"/>
     <col min="21" max="21" width="31.90625" customWidth="1"/>
   </cols>
@@ -12534,7 +12544,7 @@
       <c r="L1" s="106" t="s">
         <v>798</v>
       </c>
-      <c r="M1" s="106" t="s">
+      <c r="M1" s="109" t="s">
         <v>800</v>
       </c>
       <c r="N1" s="3" t="s">
@@ -12552,7 +12562,7 @@
       <c r="R1" s="106" t="s">
         <v>801</v>
       </c>
-      <c r="S1" s="106" t="s">
+      <c r="S1" s="109" t="s">
         <v>802</v>
       </c>
       <c r="T1" s="3" t="s">
@@ -12615,7 +12625,7 @@
       <c r="L2" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M2" s="108">
+      <c r="M2" s="110">
         <v>120</v>
       </c>
       <c r="N2" s="11" t="s">
@@ -12630,7 +12640,7 @@
       <c r="R2" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S2" s="108">
+      <c r="S2" s="110">
         <v>60</v>
       </c>
       <c r="T2" s="13" t="s">
@@ -12674,7 +12684,7 @@
       <c r="L3" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M3" s="108">
+      <c r="M3" s="110">
         <v>30</v>
       </c>
       <c r="N3" s="11" t="s">
@@ -12690,7 +12700,7 @@
       <c r="R3" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S3" s="108">
+      <c r="S3" s="110">
         <v>15</v>
       </c>
       <c r="T3" s="17" t="s">
@@ -12735,7 +12745,7 @@
       <c r="L4" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M4" s="108">
+      <c r="M4" s="110">
         <v>60</v>
       </c>
       <c r="N4" s="16" t="s">
@@ -12751,7 +12761,7 @@
       <c r="R4" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S4" s="108">
+      <c r="S4" s="110">
         <v>60</v>
       </c>
       <c r="T4" s="17" t="s">
@@ -12796,7 +12806,7 @@
       <c r="L5" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M5" s="108">
+      <c r="M5" s="110">
         <v>30</v>
       </c>
       <c r="N5" s="16" t="s">
@@ -12812,7 +12822,7 @@
       <c r="R5" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S5" s="108">
+      <c r="S5" s="110">
         <v>30</v>
       </c>
       <c r="T5" s="13" t="s">
@@ -12857,7 +12867,7 @@
       <c r="L6" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M6" s="108">
+      <c r="M6" s="110">
         <v>15</v>
       </c>
       <c r="N6" s="11" t="s">
@@ -12873,7 +12883,7 @@
       <c r="R6" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S6" s="108">
+      <c r="S6" s="110">
         <v>15</v>
       </c>
       <c r="T6" s="21" t="s">
@@ -12918,7 +12928,7 @@
       <c r="L7" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M7" s="108">
+      <c r="M7" s="110">
         <v>120</v>
       </c>
       <c r="N7" s="11" t="s">
@@ -12934,7 +12944,7 @@
       <c r="R7" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S7" s="108">
+      <c r="S7" s="110">
         <v>120</v>
       </c>
       <c r="T7" s="13" t="s">
@@ -12979,7 +12989,7 @@
       <c r="L8" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M8" s="108">
+      <c r="M8" s="110">
         <v>30</v>
       </c>
       <c r="N8" s="11" t="s">
@@ -12994,7 +13004,7 @@
       <c r="R8" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S8" s="108">
+      <c r="S8" s="110">
         <v>30</v>
       </c>
       <c r="T8" s="13" t="s">
@@ -13038,7 +13048,7 @@
       <c r="L9" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M9" s="108">
+      <c r="M9" s="110">
         <v>45</v>
       </c>
       <c r="N9" s="11" t="s">
@@ -13056,7 +13066,7 @@
       <c r="R9" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S9" s="108">
+      <c r="S9" s="110">
         <v>45</v>
       </c>
       <c r="T9" s="21" t="s">
@@ -13100,7 +13110,7 @@
       <c r="L10" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M10" s="108">
+      <c r="M10" s="110">
         <v>60</v>
       </c>
       <c r="N10" s="7"/>
@@ -13111,7 +13121,7 @@
       <c r="R10" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S10" s="108">
+      <c r="S10" s="110">
         <v>60</v>
       </c>
       <c r="T10" s="7"/>
@@ -13153,7 +13163,7 @@
       <c r="L11" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M11" s="108">
+      <c r="M11" s="110">
         <v>60</v>
       </c>
       <c r="N11" s="11" t="s">
@@ -13169,7 +13179,7 @@
       <c r="R11" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S11" s="108">
+      <c r="S11" s="110">
         <v>60</v>
       </c>
       <c r="T11" s="13" t="s">
@@ -13214,7 +13224,7 @@
       <c r="L12" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M12" s="108">
+      <c r="M12" s="110">
         <v>30</v>
       </c>
       <c r="N12" s="11" t="s">
@@ -13230,7 +13240,7 @@
       <c r="R12" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S12" s="108">
+      <c r="S12" s="110">
         <v>30</v>
       </c>
       <c r="T12" s="21" t="s">
@@ -13274,7 +13284,7 @@
       <c r="L13" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M13" s="108">
+      <c r="M13" s="110">
         <v>60</v>
       </c>
       <c r="N13" s="11" t="s">
@@ -13290,7 +13300,7 @@
       <c r="R13" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S13" s="108">
+      <c r="S13" s="110">
         <v>60</v>
       </c>
       <c r="T13" s="13" t="s">
@@ -13335,7 +13345,7 @@
       <c r="L14" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M14" s="108">
+      <c r="M14" s="110">
         <v>90</v>
       </c>
       <c r="N14" s="11" t="s">
@@ -13351,7 +13361,7 @@
       <c r="R14" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S14" s="108">
+      <c r="S14" s="110">
         <v>90</v>
       </c>
       <c r="T14" s="13" t="s">
@@ -13396,7 +13406,7 @@
       <c r="L15" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M15" s="108">
+      <c r="M15" s="110">
         <v>30</v>
       </c>
       <c r="N15" s="11" t="s">
@@ -13414,7 +13424,7 @@
       <c r="R15" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S15" s="108">
+      <c r="S15" s="110">
         <v>30</v>
       </c>
       <c r="T15" s="17" t="s">
@@ -13428,10 +13438,10 @@
       <c r="I16" s="9"/>
       <c r="J16" s="7"/>
       <c r="L16" s="107"/>
-      <c r="M16" s="108"/>
+      <c r="M16" s="110"/>
       <c r="N16" s="7"/>
       <c r="R16" s="107"/>
-      <c r="S16" s="108"/>
+      <c r="S16" s="110"/>
     </row>
     <row r="17" spans="7:19" ht="15.75" customHeight="1">
       <c r="G17" s="8"/>
@@ -13439,10 +13449,10 @@
       <c r="I17" s="9"/>
       <c r="J17" s="7"/>
       <c r="L17" s="107"/>
-      <c r="M17" s="108"/>
+      <c r="M17" s="110"/>
       <c r="N17" s="7"/>
       <c r="R17" s="107"/>
-      <c r="S17" s="108"/>
+      <c r="S17" s="110"/>
     </row>
     <row r="18" spans="7:19" ht="15.75" customHeight="1">
       <c r="G18" s="8"/>
@@ -13457,10 +13467,10 @@
       <c r="I19" s="9"/>
       <c r="J19" s="7"/>
       <c r="L19" s="18"/>
-      <c r="M19" s="63"/>
+      <c r="M19" s="112"/>
       <c r="N19" s="7"/>
       <c r="R19" s="18"/>
-      <c r="S19" s="63"/>
+      <c r="S19" s="112"/>
     </row>
     <row r="20" spans="7:19" ht="15.75" customHeight="1">
       <c r="G20" s="8"/>
@@ -13468,10 +13478,10 @@
       <c r="I20" s="9"/>
       <c r="J20" s="7"/>
       <c r="L20" s="63"/>
-      <c r="M20" s="63"/>
+      <c r="M20" s="112"/>
       <c r="N20" s="7"/>
       <c r="R20" s="63"/>
-      <c r="S20" s="63"/>
+      <c r="S20" s="112"/>
     </row>
     <row r="21" spans="7:19" ht="15.75" customHeight="1">
       <c r="G21" s="8"/>
@@ -20384,7 +20394,7 @@
       <c r="L1" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="M1" s="109" t="s">
+      <c r="M1" s="113" t="s">
         <v>800</v>
       </c>
       <c r="N1" s="3" t="s">
@@ -20402,7 +20412,7 @@
       <c r="R1" s="3" t="s">
         <v>801</v>
       </c>
-      <c r="S1" s="109" t="s">
+      <c r="S1" s="113" t="s">
         <v>802</v>
       </c>
       <c r="T1" s="3" t="s">
@@ -29158,10 +29168,12 @@
     <col min="5" max="8" width="26.6328125" customWidth="1"/>
     <col min="9" max="9" width="26.7265625" customWidth="1"/>
     <col min="10" max="10" width="26.6328125" customWidth="1"/>
-    <col min="11" max="13" width="12.6328125" customWidth="1"/>
+    <col min="11" max="12" width="12.6328125" customWidth="1"/>
+    <col min="13" max="13" width="12.6328125" style="111" customWidth="1"/>
     <col min="14" max="14" width="25.08984375" customWidth="1"/>
     <col min="15" max="16" width="27.7265625" customWidth="1"/>
-    <col min="17" max="19" width="14.453125" customWidth="1"/>
+    <col min="17" max="18" width="14.453125" customWidth="1"/>
+    <col min="19" max="19" width="14.453125" style="111" customWidth="1"/>
     <col min="20" max="20" width="23.90625" customWidth="1"/>
     <col min="21" max="21" width="31.90625" customWidth="1"/>
   </cols>
@@ -29203,7 +29215,7 @@
       <c r="L1" s="106" t="s">
         <v>798</v>
       </c>
-      <c r="M1" s="106" t="s">
+      <c r="M1" s="109" t="s">
         <v>800</v>
       </c>
       <c r="N1" s="3" t="s">
@@ -29221,7 +29233,7 @@
       <c r="R1" s="106" t="s">
         <v>801</v>
       </c>
-      <c r="S1" s="106" t="s">
+      <c r="S1" s="109" t="s">
         <v>802</v>
       </c>
       <c r="T1" s="3" t="s">
@@ -29284,7 +29296,7 @@
       <c r="L2" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M2" s="108">
+      <c r="M2" s="110">
         <v>30</v>
       </c>
       <c r="N2" s="11" t="s">
@@ -29300,7 +29312,7 @@
       <c r="R2" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S2" s="108">
+      <c r="S2" s="110">
         <v>15</v>
       </c>
       <c r="T2" s="17" t="s">
@@ -29345,7 +29357,7 @@
       <c r="L3" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M3" s="108">
+      <c r="M3" s="110">
         <v>60</v>
       </c>
       <c r="N3" s="7"/>
@@ -29356,7 +29368,7 @@
       <c r="R3" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S3" s="108">
+      <c r="S3" s="110">
         <v>15</v>
       </c>
       <c r="T3" s="7"/>
@@ -29398,7 +29410,7 @@
       <c r="L4" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M4" s="108">
+      <c r="M4" s="110">
         <v>30</v>
       </c>
       <c r="N4" s="11" t="s">
@@ -29414,7 +29426,7 @@
       <c r="R4" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S4" s="108">
+      <c r="S4" s="110">
         <v>60</v>
       </c>
       <c r="T4" s="13" t="s">
@@ -29459,7 +29471,7 @@
       <c r="L5" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M5" s="108">
+      <c r="M5" s="110">
         <v>15</v>
       </c>
       <c r="N5" s="16" t="s">
@@ -29475,7 +29487,7 @@
       <c r="R5" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S5" s="108">
+      <c r="S5" s="110">
         <v>30</v>
       </c>
       <c r="T5" s="17" t="s">
@@ -29520,7 +29532,7 @@
       <c r="L6" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M6" s="108">
+      <c r="M6" s="110">
         <v>30</v>
       </c>
       <c r="N6" s="16" t="s">
@@ -29536,7 +29548,7 @@
       <c r="R6" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S6" s="108">
+      <c r="S6" s="110">
         <v>15</v>
       </c>
       <c r="T6" s="21" t="s">
@@ -29581,7 +29593,7 @@
       <c r="L7" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M7" s="108">
+      <c r="M7" s="110">
         <v>45</v>
       </c>
       <c r="N7" s="16" t="s">
@@ -29597,7 +29609,7 @@
       <c r="R7" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S7" s="108">
+      <c r="S7" s="110">
         <v>120</v>
       </c>
       <c r="T7" s="13" t="s">
@@ -29642,7 +29654,7 @@
       <c r="L8" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M8" s="108">
+      <c r="M8" s="110">
         <v>60</v>
       </c>
       <c r="N8" s="11" t="s">
@@ -29657,7 +29669,7 @@
       <c r="R8" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S8" s="108">
+      <c r="S8" s="110">
         <v>30</v>
       </c>
       <c r="T8" s="13" t="s">
@@ -29701,7 +29713,7 @@
       <c r="L9" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M9" s="108">
+      <c r="M9" s="110">
         <v>60</v>
       </c>
       <c r="N9" s="30" t="s">
@@ -29717,7 +29729,7 @@
       <c r="R9" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S9" s="108">
+      <c r="S9" s="110">
         <v>45</v>
       </c>
       <c r="T9" s="21" t="s">
@@ -29761,7 +29773,7 @@
       <c r="L10" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M10" s="108">
+      <c r="M10" s="110">
         <v>30</v>
       </c>
       <c r="N10" s="11" t="s">
@@ -29776,7 +29788,7 @@
       <c r="R10" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S10" s="108">
+      <c r="S10" s="110">
         <v>60</v>
       </c>
       <c r="T10" s="13" t="s">
@@ -29820,7 +29832,7 @@
       <c r="L11" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M11" s="108">
+      <c r="M11" s="110">
         <v>60</v>
       </c>
       <c r="N11" s="11" t="s">
@@ -29836,7 +29848,7 @@
       <c r="R11" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S11" s="108">
+      <c r="S11" s="110">
         <v>60</v>
       </c>
       <c r="T11" s="13" t="s">
@@ -29881,7 +29893,7 @@
       <c r="L12" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M12" s="108">
+      <c r="M12" s="110">
         <v>90</v>
       </c>
       <c r="N12" s="19" t="s">
@@ -29897,7 +29909,7 @@
       <c r="R12" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S12" s="108">
+      <c r="S12" s="110">
         <v>30</v>
       </c>
       <c r="T12" s="13" t="s">
@@ -29942,7 +29954,7 @@
       <c r="L13" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M13" s="108">
+      <c r="M13" s="110">
         <v>30</v>
       </c>
       <c r="N13" s="31" t="s">
@@ -29958,7 +29970,7 @@
       <c r="R13" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S13" s="108">
+      <c r="S13" s="110">
         <v>60</v>
       </c>
       <c r="T13" s="17" t="s">
@@ -30003,7 +30015,7 @@
       <c r="L14" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M14" s="108">
+      <c r="M14" s="110">
         <v>15</v>
       </c>
       <c r="N14" s="21" t="s">
@@ -30017,7 +30029,7 @@
       <c r="R14" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S14" s="108">
+      <c r="S14" s="110">
         <v>90</v>
       </c>
       <c r="T14" s="13" t="s">
@@ -30062,7 +30074,7 @@
       <c r="L15" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="M15" s="108">
+      <c r="M15" s="110">
         <v>120</v>
       </c>
       <c r="N15" s="11" t="s">
@@ -30078,7 +30090,7 @@
       <c r="R15" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="S15" s="108">
+      <c r="S15" s="110">
         <v>30</v>
       </c>
       <c r="T15" s="21" t="s">
@@ -30093,10 +30105,10 @@
       <c r="J16" s="7"/>
       <c r="K16" s="18"/>
       <c r="L16" s="63"/>
-      <c r="M16" s="63"/>
+      <c r="M16" s="112"/>
       <c r="N16" s="7"/>
       <c r="R16" s="107"/>
-      <c r="S16" s="108"/>
+      <c r="S16" s="110"/>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" s="7"/>
@@ -30106,7 +30118,7 @@
       <c r="J17" s="7"/>
       <c r="N17" s="7"/>
       <c r="R17" s="107"/>
-      <c r="S17" s="108"/>
+      <c r="S17" s="110"/>
     </row>
     <row r="18" spans="4:19">
       <c r="D18" s="7"/>
@@ -30116,7 +30128,7 @@
       <c r="J18" s="7"/>
       <c r="N18" s="7"/>
       <c r="R18" s="107"/>
-      <c r="S18" s="108"/>
+      <c r="S18" s="110"/>
     </row>
     <row r="19" spans="4:19">
       <c r="D19" s="7"/>
@@ -30126,7 +30138,7 @@
       <c r="J19" s="7"/>
       <c r="N19" s="7"/>
       <c r="R19" s="18"/>
-      <c r="S19" s="63"/>
+      <c r="S19" s="112"/>
     </row>
     <row r="20" spans="4:19">
       <c r="D20" s="7"/>
@@ -30136,7 +30148,7 @@
       <c r="J20" s="7"/>
       <c r="N20" s="7"/>
       <c r="R20" s="63"/>
-      <c r="S20" s="63"/>
+      <c r="S20" s="112"/>
     </row>
     <row r="21" spans="4:19">
       <c r="D21" s="7"/>
@@ -37980,10 +37992,12 @@
     <col min="11" max="11" width="26.7265625" customWidth="1"/>
     <col min="12" max="12" width="26.6328125" customWidth="1"/>
     <col min="13" max="13" width="12.6328125" customWidth="1"/>
-    <col min="14" max="15" width="12.90625" customWidth="1"/>
+    <col min="14" max="14" width="12.90625" customWidth="1"/>
+    <col min="15" max="15" width="12.90625" style="111" customWidth="1"/>
     <col min="16" max="16" width="25.08984375" customWidth="1"/>
     <col min="17" max="18" width="27.7265625" customWidth="1"/>
-    <col min="19" max="21" width="14.453125" customWidth="1"/>
+    <col min="19" max="20" width="14.453125" customWidth="1"/>
+    <col min="21" max="21" width="14.453125" style="111" customWidth="1"/>
     <col min="22" max="22" width="23.90625" customWidth="1"/>
     <col min="23" max="23" width="31.90625" customWidth="1"/>
   </cols>
@@ -38029,7 +38043,7 @@
       <c r="N1" s="106" t="s">
         <v>798</v>
       </c>
-      <c r="O1" s="106" t="s">
+      <c r="O1" s="109" t="s">
         <v>800</v>
       </c>
       <c r="P1" s="34" t="s">
@@ -38047,7 +38061,7 @@
       <c r="T1" s="106" t="s">
         <v>801</v>
       </c>
-      <c r="U1" s="106" t="s">
+      <c r="U1" s="109" t="s">
         <v>802</v>
       </c>
       <c r="V1" s="34" t="s">
@@ -38094,6 +38108,7 @@
         <v>45869</v>
       </c>
       <c r="N2" s="107"/>
+      <c r="O2"/>
       <c r="P2" s="43"/>
       <c r="Q2" s="43"/>
       <c r="R2" s="43"/>
@@ -38101,6 +38116,7 @@
         <v>45870</v>
       </c>
       <c r="T2" s="107"/>
+      <c r="U2"/>
       <c r="V2" s="37"/>
       <c r="W2" s="37"/>
       <c r="X2" s="37"/>
@@ -38161,7 +38177,7 @@
       <c r="N3" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O3" s="108">
+      <c r="O3" s="110">
         <v>30</v>
       </c>
       <c r="P3" s="45" t="s">
@@ -38177,7 +38193,7 @@
       <c r="T3" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U3" s="108">
+      <c r="U3" s="110">
         <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
@@ -38242,7 +38258,7 @@
       <c r="N4" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O4" s="108">
+      <c r="O4" s="110">
         <v>60</v>
       </c>
       <c r="P4" s="45" t="s">
@@ -38258,7 +38274,7 @@
       <c r="T4" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U4" s="108">
+      <c r="U4" s="110">
         <v>60</v>
       </c>
       <c r="V4" s="47" t="s">
@@ -38323,7 +38339,7 @@
       <c r="N5" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O5" s="108">
+      <c r="O5" s="110">
         <v>30</v>
       </c>
       <c r="P5" s="45" t="s">
@@ -38339,7 +38355,7 @@
       <c r="T5" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U5" s="108">
+      <c r="U5" s="110">
         <v>30</v>
       </c>
       <c r="V5" s="50" t="s">
@@ -38404,7 +38420,7 @@
       <c r="N6" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O6" s="108">
+      <c r="O6" s="110">
         <v>15</v>
       </c>
       <c r="P6" s="45" t="s">
@@ -38420,7 +38436,7 @@
       <c r="T6" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U6" s="108">
+      <c r="U6" s="110">
         <v>15</v>
       </c>
       <c r="V6" s="53" t="s">
@@ -38542,7 +38558,7 @@
       <c r="N8" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O8" s="108">
+      <c r="O8" s="110">
         <v>30</v>
       </c>
       <c r="P8" s="45" t="s">
@@ -38558,7 +38574,7 @@
       <c r="T8" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U8" s="108">
+      <c r="U8" s="110">
         <v>30</v>
       </c>
       <c r="V8" s="53" t="s">
@@ -38623,7 +38639,7 @@
       <c r="N9" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O9" s="108">
+      <c r="O9" s="110">
         <v>45</v>
       </c>
       <c r="P9" s="54" t="s">
@@ -38639,7 +38655,7 @@
       <c r="T9" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U9" s="108">
+      <c r="U9" s="110">
         <v>45</v>
       </c>
       <c r="V9" s="50" t="s">
@@ -38704,7 +38720,7 @@
       <c r="N10" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="110">
         <v>60</v>
       </c>
       <c r="P10" s="56" t="s">
@@ -38720,7 +38736,7 @@
       <c r="T10" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U10" s="108">
+      <c r="U10" s="110">
         <v>60</v>
       </c>
       <c r="V10" s="53" t="s">
@@ -38785,7 +38801,7 @@
       <c r="N11" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O11" s="108">
+      <c r="O11" s="110">
         <v>60</v>
       </c>
       <c r="P11" s="54" t="s">
@@ -38801,7 +38817,7 @@
       <c r="T11" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U11" s="108">
+      <c r="U11" s="110">
         <v>60</v>
       </c>
       <c r="V11" s="59" t="s">
@@ -38866,7 +38882,7 @@
       <c r="N12" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O12" s="108">
+      <c r="O12" s="110">
         <v>30</v>
       </c>
       <c r="P12" s="60" t="s">
@@ -38882,7 +38898,7 @@
       <c r="T12" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U12" s="108">
+      <c r="U12" s="110">
         <v>30</v>
       </c>
       <c r="V12" s="53" t="s">
@@ -38947,7 +38963,7 @@
       <c r="N13" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O13" s="108">
+      <c r="O13" s="110">
         <v>60</v>
       </c>
       <c r="P13" s="54" t="s">
@@ -38963,7 +38979,7 @@
       <c r="T13" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U13" s="108">
+      <c r="U13" s="110">
         <v>60</v>
       </c>
       <c r="V13" s="53" t="s">
@@ -39028,7 +39044,7 @@
       <c r="N14" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O14" s="108">
+      <c r="O14" s="110">
         <v>90</v>
       </c>
       <c r="P14" s="45" t="s">
@@ -39044,7 +39060,7 @@
       <c r="T14" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U14" s="108">
+      <c r="U14" s="110">
         <v>90</v>
       </c>
       <c r="V14" s="53" t="s">
@@ -39166,7 +39182,7 @@
       <c r="N16" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O16" s="108">
+      <c r="O16" s="110">
         <v>30</v>
       </c>
       <c r="P16" s="45" t="s">
@@ -39182,7 +39198,7 @@
       <c r="T16" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U16" s="108">
+      <c r="U16" s="110">
         <v>30</v>
       </c>
       <c r="V16" s="53" t="s">
@@ -39247,7 +39263,7 @@
       <c r="N17" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O17" s="108">
+      <c r="O17" s="110">
         <v>15</v>
       </c>
       <c r="P17" s="54" t="s">
@@ -39263,7 +39279,7 @@
       <c r="T17" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U17" s="108">
+      <c r="U17" s="110">
         <v>15</v>
       </c>
       <c r="V17" s="53" t="s">
@@ -39328,7 +39344,7 @@
       <c r="N18" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O18" s="108">
+      <c r="O18" s="110">
         <v>120</v>
       </c>
       <c r="P18" s="54" t="s">
@@ -39344,7 +39360,7 @@
       <c r="T18" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U18" s="108">
+      <c r="U18" s="110">
         <v>60</v>
       </c>
       <c r="V18" s="47" t="s">
@@ -39402,13 +39418,13 @@
       <c r="L20" s="7"/>
       <c r="M20" s="63"/>
       <c r="N20" s="63"/>
-      <c r="O20" s="63"/>
+      <c r="O20" s="112"/>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="8"/>
       <c r="S20" s="63"/>
       <c r="T20" s="63"/>
-      <c r="U20" s="63"/>
+      <c r="U20" s="112"/>
     </row>
     <row r="21" spans="1:39" ht="12.5">
       <c r="F21" s="7"/>
@@ -47241,11 +47257,13 @@
     <col min="9" max="10" width="26.6328125" customWidth="1"/>
     <col min="11" max="11" width="26.7265625" customWidth="1"/>
     <col min="12" max="12" width="24.7265625" customWidth="1"/>
-    <col min="13" max="15" width="12.90625" customWidth="1"/>
+    <col min="13" max="14" width="12.90625" customWidth="1"/>
+    <col min="15" max="15" width="12.90625" style="111" customWidth="1"/>
     <col min="16" max="16" width="16.26953125" customWidth="1"/>
     <col min="17" max="17" width="13.08984375" customWidth="1"/>
     <col min="18" max="18" width="14.90625" customWidth="1"/>
-    <col min="19" max="21" width="14.453125" customWidth="1"/>
+    <col min="19" max="20" width="14.453125" customWidth="1"/>
+    <col min="21" max="21" width="14.453125" style="111" customWidth="1"/>
     <col min="22" max="22" width="23.90625" customWidth="1"/>
     <col min="23" max="23" width="31.90625" customWidth="1"/>
   </cols>
@@ -47291,7 +47309,7 @@
       <c r="N1" s="106" t="s">
         <v>798</v>
       </c>
-      <c r="O1" s="106" t="s">
+      <c r="O1" s="109" t="s">
         <v>800</v>
       </c>
       <c r="P1" s="3" t="s">
@@ -47309,7 +47327,7 @@
       <c r="T1" s="106" t="s">
         <v>801</v>
       </c>
-      <c r="U1" s="106" t="s">
+      <c r="U1" s="109" t="s">
         <v>802</v>
       </c>
       <c r="V1" s="3" t="s">
@@ -47414,7 +47432,7 @@
       <c r="N3" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O3" s="108">
+      <c r="O3" s="110">
         <v>30</v>
       </c>
       <c r="P3" s="73" t="s">
@@ -47430,7 +47448,7 @@
       <c r="T3" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U3" s="108">
+      <c r="U3" s="110">
         <v>15</v>
       </c>
       <c r="V3" s="39"/>
@@ -47493,7 +47511,7 @@
       <c r="N4" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O4" s="108">
+      <c r="O4" s="110">
         <v>60</v>
       </c>
       <c r="P4" s="67"/>
@@ -47505,7 +47523,7 @@
       <c r="T4" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U4" s="108">
+      <c r="U4" s="110">
         <v>60</v>
       </c>
       <c r="V4" s="67"/>
@@ -47568,7 +47586,7 @@
       <c r="N5" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O5" s="108">
+      <c r="O5" s="110">
         <v>30</v>
       </c>
       <c r="P5" s="66"/>
@@ -47580,7 +47598,7 @@
       <c r="T5" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U5" s="108">
+      <c r="U5" s="110">
         <v>30</v>
       </c>
       <c r="V5" s="67"/>
@@ -47643,7 +47661,7 @@
       <c r="N6" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O6" s="108">
+      <c r="O6" s="110">
         <v>15</v>
       </c>
       <c r="P6" s="66"/>
@@ -47655,7 +47673,7 @@
       <c r="T6" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U6" s="108">
+      <c r="U6" s="110">
         <v>15</v>
       </c>
       <c r="V6" s="68"/>
@@ -47698,7 +47716,7 @@
       <c r="N7" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O7" s="108">
+      <c r="O7" s="110">
         <v>120</v>
       </c>
       <c r="P7" s="71"/>
@@ -47708,7 +47726,7 @@
       <c r="T7" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U7" s="108">
+      <c r="U7" s="110">
         <v>120</v>
       </c>
       <c r="V7" s="65"/>
@@ -47725,7 +47743,7 @@
       <c r="AG7" s="65"/>
       <c r="AH7" s="65"/>
     </row>
-    <row r="8" spans="1:39" ht="50">
+    <row r="8" spans="1:39" ht="37.5">
       <c r="A8" s="15"/>
       <c r="B8" s="66" t="s">
         <v>498</v>
@@ -47766,7 +47784,7 @@
       <c r="N8" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O8" s="108">
+      <c r="O8" s="110">
         <v>30</v>
       </c>
       <c r="P8" s="66"/>
@@ -47778,7 +47796,7 @@
       <c r="T8" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U8" s="108">
+      <c r="U8" s="110">
         <v>30</v>
       </c>
       <c r="V8" s="67"/>
@@ -47841,7 +47859,7 @@
       <c r="N9" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O9" s="108">
+      <c r="O9" s="110">
         <v>45</v>
       </c>
       <c r="P9" s="66"/>
@@ -47853,7 +47871,7 @@
       <c r="T9" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U9" s="108">
+      <c r="U9" s="110">
         <v>45</v>
       </c>
       <c r="V9" s="68"/>
@@ -47916,7 +47934,7 @@
       <c r="N10" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="110">
         <v>60</v>
       </c>
       <c r="P10" s="66"/>
@@ -47928,7 +47946,7 @@
       <c r="T10" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U10" s="108">
+      <c r="U10" s="110">
         <v>60</v>
       </c>
       <c r="V10" s="67"/>
@@ -47991,7 +48009,7 @@
       <c r="N11" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O11" s="108">
+      <c r="O11" s="110">
         <v>60</v>
       </c>
       <c r="P11" s="66"/>
@@ -48003,7 +48021,7 @@
       <c r="T11" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U11" s="108">
+      <c r="U11" s="110">
         <v>60</v>
       </c>
       <c r="V11" s="68"/>
@@ -48066,7 +48084,7 @@
       <c r="N12" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O12" s="108">
+      <c r="O12" s="110">
         <v>30</v>
       </c>
       <c r="P12" s="79"/>
@@ -48078,7 +48096,7 @@
       <c r="T12" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U12" s="108">
+      <c r="U12" s="110">
         <v>30</v>
       </c>
       <c r="V12" s="67"/>
@@ -48141,7 +48159,7 @@
       <c r="N13" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O13" s="108">
+      <c r="O13" s="110">
         <v>60</v>
       </c>
       <c r="P13" s="15"/>
@@ -48153,7 +48171,7 @@
       <c r="T13" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U13" s="108">
+      <c r="U13" s="110">
         <v>60</v>
       </c>
       <c r="V13" s="7"/>
@@ -48216,7 +48234,7 @@
       <c r="N14" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O14" s="108">
+      <c r="O14" s="110">
         <v>90</v>
       </c>
       <c r="P14" s="15"/>
@@ -48228,7 +48246,7 @@
       <c r="T14" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U14" s="108">
+      <c r="U14" s="110">
         <v>90</v>
       </c>
       <c r="V14" s="7"/>
@@ -48267,7 +48285,7 @@
       <c r="N15" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O15" s="108">
+      <c r="O15" s="110">
         <v>30</v>
       </c>
       <c r="P15" s="14"/>
@@ -48277,7 +48295,7 @@
       <c r="T15" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U15" s="108">
+      <c r="U15" s="110">
         <v>30</v>
       </c>
     </row>
@@ -48322,7 +48340,7 @@
       <c r="N16" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O16" s="108">
+      <c r="O16" s="110">
         <v>30</v>
       </c>
       <c r="P16" s="66"/>
@@ -48334,7 +48352,7 @@
       <c r="T16" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U16" s="108">
+      <c r="U16" s="110">
         <v>30</v>
       </c>
       <c r="V16" s="67"/>
@@ -48397,7 +48415,7 @@
       <c r="N17" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O17" s="108">
+      <c r="O17" s="110">
         <v>15</v>
       </c>
       <c r="P17" s="15"/>
@@ -48409,7 +48427,7 @@
       <c r="T17" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U17" s="108">
+      <c r="U17" s="110">
         <v>15</v>
       </c>
       <c r="V17" s="7"/>
@@ -48472,7 +48490,7 @@
       <c r="N18" s="107" t="s">
         <v>799</v>
       </c>
-      <c r="O18" s="108">
+      <c r="O18" s="110">
         <v>120</v>
       </c>
       <c r="P18" s="15"/>
@@ -48484,7 +48502,7 @@
       <c r="T18" s="107" t="s">
         <v>803</v>
       </c>
-      <c r="U18" s="108">
+      <c r="U18" s="110">
         <v>60</v>
       </c>
       <c r="V18" s="8"/>
@@ -48521,13 +48539,13 @@
       <c r="L19" s="7"/>
       <c r="M19" s="18"/>
       <c r="N19" s="18"/>
-      <c r="O19" s="63"/>
+      <c r="O19" s="112"/>
       <c r="P19" s="14"/>
       <c r="Q19" s="14"/>
       <c r="R19" s="14"/>
       <c r="S19" s="18"/>
       <c r="T19" s="18"/>
-      <c r="U19" s="63"/>
+      <c r="U19" s="112"/>
     </row>
     <row r="20" spans="1:39">
       <c r="I20" s="8"/>
@@ -48536,13 +48554,13 @@
       <c r="L20" s="7"/>
       <c r="M20" s="63"/>
       <c r="N20" s="63"/>
-      <c r="O20" s="63"/>
+      <c r="O20" s="112"/>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="8"/>
       <c r="S20" s="63"/>
       <c r="T20" s="63"/>
-      <c r="U20" s="63"/>
+      <c r="U20" s="112"/>
     </row>
     <row r="21" spans="1:39">
       <c r="F21" s="7"/>

--- a/Archivos/Archivos_origen/Planeación contenido blog Aciertala 2025.xlsx
+++ b/Archivos/Archivos_origen/Planeación contenido blog Aciertala 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/jhor_caro_virtualsoft_tech/Documents/Documentos/Proyectos QuotaMedia/SEO/Planeacion SEO/Archivos enviados para octubre (con columnas)/Planeacion SEO Octubre/Planeacion SEO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QuotaMedia\Downloads\planeacion octubre editada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="11_17192862E27F48489F65EED23D257B8F7EB66E3C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95711980-90AC-4817-9C77-A91DDE52C5C3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FDA7E3-7A82-4F1E-BA5C-A7A728AE648D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Octubre" sheetId="7" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="44">
   <si>
     <t>Tema pilar</t>
   </si>
@@ -152,9 +152,6 @@
   </si>
   <si>
     <t>Tiempo estimado publicacion</t>
-  </si>
-  <si>
-    <t>Santiago</t>
   </si>
   <si>
     <t>Manuela</t>
@@ -301,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -416,7 +413,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,10 +437,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -636,35 +637,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AM990"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="0.7265625" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" customWidth="1"/>
-    <col min="4" max="4" width="17.26953125" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" customWidth="1"/>
-    <col min="6" max="6" width="24.54296875" customWidth="1"/>
+    <col min="1" max="1" width="0.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" customWidth="1"/>
+    <col min="6" max="6" width="24.5546875" customWidth="1"/>
     <col min="7" max="7" width="25" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="10" width="26.54296875" customWidth="1"/>
-    <col min="11" max="11" width="26.7265625" customWidth="1"/>
-    <col min="12" max="12" width="24.7265625" customWidth="1"/>
-    <col min="13" max="13" width="12.81640625" customWidth="1"/>
-    <col min="14" max="15" width="17.26953125" style="39" customWidth="1"/>
-    <col min="16" max="16" width="16.26953125" customWidth="1"/>
-    <col min="17" max="17" width="13.1796875" customWidth="1"/>
-    <col min="18" max="18" width="14.81640625" customWidth="1"/>
-    <col min="19" max="19" width="14.453125" customWidth="1"/>
-    <col min="20" max="21" width="14.453125" style="39" customWidth="1"/>
-    <col min="22" max="22" width="23.81640625" customWidth="1"/>
-    <col min="23" max="23" width="31.81640625" customWidth="1"/>
+    <col min="9" max="10" width="26.5546875" customWidth="1"/>
+    <col min="11" max="11" width="26.77734375" customWidth="1"/>
+    <col min="12" max="12" width="24.77734375" customWidth="1"/>
+    <col min="13" max="13" width="12.77734375" customWidth="1"/>
+    <col min="14" max="15" width="17.21875" style="39" customWidth="1"/>
+    <col min="16" max="16" width="16.21875" customWidth="1"/>
+    <col min="17" max="17" width="13.21875" customWidth="1"/>
+    <col min="18" max="18" width="14.77734375" customWidth="1"/>
+    <col min="19" max="19" width="14.44140625" customWidth="1"/>
+    <col min="20" max="21" width="14.44140625" style="39" customWidth="1"/>
+    <col min="22" max="22" width="23.77734375" customWidth="1"/>
+    <col min="23" max="23" width="31.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="39">
+    <row r="1" spans="1:39" ht="39.6">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>22</v>
@@ -749,7 +750,7 @@
       <c r="AL1" s="5"/>
       <c r="AM1" s="5"/>
     </row>
-    <row r="2" spans="1:39" ht="25">
+    <row r="2" spans="1:39" ht="26.4">
       <c r="A2" s="15"/>
       <c r="B2" s="9" t="s">
         <v>23</v>
@@ -776,10 +777,10 @@
         <v>45926</v>
       </c>
       <c r="N2" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O2" s="38">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P2" s="9"/>
       <c r="Q2" s="9"/>
@@ -812,7 +813,7 @@
       <c r="AL2" s="10"/>
       <c r="AM2" s="10"/>
     </row>
-    <row r="3" spans="1:39" ht="29">
+    <row r="3" spans="1:39" ht="28.8">
       <c r="A3" s="9"/>
       <c r="B3" s="9" t="s">
         <v>23</v>
@@ -839,10 +840,10 @@
         <v>45931</v>
       </c>
       <c r="N3" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O3" s="38">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="P3" s="9"/>
       <c r="Q3" s="19"/>
@@ -854,7 +855,7 @@
         <v>43</v>
       </c>
       <c r="U3" s="38">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="V3" s="10"/>
       <c r="W3" s="10"/>
@@ -875,7 +876,7 @@
       <c r="AL3" s="10"/>
       <c r="AM3" s="10"/>
     </row>
-    <row r="4" spans="1:39" ht="29">
+    <row r="4" spans="1:39" ht="28.8">
       <c r="A4" s="9"/>
       <c r="B4" s="9" t="s">
         <v>23</v>
@@ -902,10 +903,10 @@
         <v>45931</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O4" s="38">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
@@ -917,7 +918,7 @@
         <v>43</v>
       </c>
       <c r="U4" s="38">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="V4" s="11"/>
       <c r="W4" s="10"/>
@@ -938,7 +939,7 @@
       <c r="AL4" s="10"/>
       <c r="AM4" s="10"/>
     </row>
-    <row r="5" spans="1:39" ht="29">
+    <row r="5" spans="1:39" ht="28.8">
       <c r="A5" s="9"/>
       <c r="B5" s="9" t="s">
         <v>23</v>
@@ -965,10 +966,10 @@
         <v>45932</v>
       </c>
       <c r="N5" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O5" s="38">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P5" s="19"/>
       <c r="Q5" s="20"/>
@@ -1001,7 +1002,7 @@
       <c r="AL5" s="10"/>
       <c r="AM5" s="10"/>
     </row>
-    <row r="6" spans="1:39" ht="58">
+    <row r="6" spans="1:39" ht="43.2">
       <c r="A6" s="9"/>
       <c r="B6" s="9" t="s">
         <v>23</v>
@@ -1028,10 +1029,10 @@
         <v>45932</v>
       </c>
       <c r="N6" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O6" s="38">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
@@ -1043,7 +1044,7 @@
         <v>43</v>
       </c>
       <c r="U6" s="38">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -1064,7 +1065,7 @@
       <c r="AL6" s="10"/>
       <c r="AM6" s="10"/>
     </row>
-    <row r="7" spans="1:39" ht="25">
+    <row r="7" spans="1:39" ht="26.4">
       <c r="A7" s="15"/>
       <c r="B7" s="9" t="s">
         <v>23</v>
@@ -1091,10 +1092,10 @@
         <v>45936</v>
       </c>
       <c r="N7" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O7" s="38">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
@@ -1127,7 +1128,7 @@
       <c r="AL7" s="10"/>
       <c r="AM7" s="10"/>
     </row>
-    <row r="8" spans="1:39" ht="25.5">
+    <row r="8" spans="1:39" ht="26.4">
       <c r="A8" s="9"/>
       <c r="B8" s="9" t="s">
         <v>23</v>
@@ -1154,10 +1155,10 @@
         <v>45958</v>
       </c>
       <c r="N8" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O8" s="38">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
@@ -1169,7 +1170,7 @@
         <v>43</v>
       </c>
       <c r="U8" s="38">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="V8" s="11"/>
       <c r="W8" s="10"/>
@@ -1190,7 +1191,7 @@
       <c r="AL8" s="10"/>
       <c r="AM8" s="10"/>
     </row>
-    <row r="9" spans="1:39" ht="25">
+    <row r="9" spans="1:39" ht="26.4">
       <c r="A9" s="9"/>
       <c r="B9" s="9" t="s">
         <v>23</v>
@@ -1217,7 +1218,7 @@
         <v>45945</v>
       </c>
       <c r="N9" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O9" s="38">
         <v>60</v>
@@ -1232,7 +1233,7 @@
         <v>43</v>
       </c>
       <c r="U9" s="38">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="V9" s="10"/>
       <c r="W9" s="10"/>
@@ -1253,7 +1254,7 @@
       <c r="AL9" s="10"/>
       <c r="AM9" s="10"/>
     </row>
-    <row r="10" spans="1:39" ht="25">
+    <row r="10" spans="1:39" ht="26.4">
       <c r="A10" s="9"/>
       <c r="B10" s="9" t="s">
         <v>23</v>
@@ -1280,10 +1281,10 @@
         <v>45946</v>
       </c>
       <c r="N10" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O10" s="38">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="P10" s="14"/>
       <c r="Q10" s="14"/>
@@ -1295,7 +1296,7 @@
         <v>43</v>
       </c>
       <c r="U10" s="38">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="V10" s="10"/>
       <c r="W10" s="10"/>
@@ -1316,7 +1317,7 @@
       <c r="AL10" s="10"/>
       <c r="AM10" s="10"/>
     </row>
-    <row r="11" spans="1:39" ht="14.5">
+    <row r="11" spans="1:39" ht="14.4">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
         <v>23</v>
@@ -1343,10 +1344,10 @@
         <v>45951</v>
       </c>
       <c r="N11" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O11" s="38">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="P11" s="10"/>
       <c r="Q11" s="10"/>
@@ -1358,7 +1359,7 @@
         <v>43</v>
       </c>
       <c r="U11" s="38">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="V11" s="10"/>
       <c r="W11" s="10"/>
@@ -1379,7 +1380,7 @@
       <c r="AL11" s="10"/>
       <c r="AM11" s="10"/>
     </row>
-    <row r="12" spans="1:39" ht="43.5">
+    <row r="12" spans="1:39" ht="43.2">
       <c r="A12" s="9"/>
       <c r="B12" s="9" t="s">
         <v>23</v>
@@ -1406,7 +1407,7 @@
         <v>45952</v>
       </c>
       <c r="N12" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O12" s="38">
         <v>60</v>
@@ -1417,11 +1418,11 @@
       <c r="S12" s="13">
         <v>45953</v>
       </c>
-      <c r="T12" s="37" t="s">
+      <c r="T12" s="41" t="s">
         <v>43</v>
       </c>
       <c r="U12" s="38">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="V12" s="10"/>
       <c r="W12" s="10"/>
@@ -1442,7 +1443,7 @@
       <c r="AL12" s="10"/>
       <c r="AM12" s="10"/>
     </row>
-    <row r="13" spans="1:39" ht="29">
+    <row r="13" spans="1:39" ht="28.8">
       <c r="A13" s="9"/>
       <c r="B13" s="9" t="s">
         <v>23</v>
@@ -1467,10 +1468,10 @@
         <v>45953</v>
       </c>
       <c r="N13" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="38">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
@@ -1482,7 +1483,7 @@
         <v>43</v>
       </c>
       <c r="U13" s="38">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="V13" s="10"/>
       <c r="W13" s="10"/>
@@ -1503,7 +1504,7 @@
       <c r="AL13" s="10"/>
       <c r="AM13" s="10"/>
     </row>
-    <row r="14" spans="1:39" ht="12.5" hidden="1">
+    <row r="14" spans="1:39" ht="13.2">
       <c r="A14" s="9"/>
       <c r="B14" s="15" t="s">
         <v>19</v>
@@ -1521,10 +1522,10 @@
       <c r="K14" s="31"/>
       <c r="L14" s="15"/>
       <c r="M14" s="32"/>
-      <c r="N14" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="O14" s="40">
+      <c r="N14" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="O14" s="35">
         <v>60</v>
       </c>
       <c r="P14" s="33"/>
@@ -1535,7 +1536,7 @@
         <v>43</v>
       </c>
       <c r="U14" s="35">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="V14" s="15"/>
       <c r="W14" s="15"/>
@@ -1556,7 +1557,7 @@
       <c r="AL14" s="15"/>
       <c r="AM14" s="15"/>
     </row>
-    <row r="15" spans="1:39" ht="12.5" hidden="1">
+    <row r="15" spans="1:39" ht="13.2">
       <c r="A15" s="15"/>
       <c r="B15" s="15" t="s">
         <v>19</v>
@@ -1574,10 +1575,10 @@
       <c r="K15" s="31"/>
       <c r="L15" s="15"/>
       <c r="M15" s="32"/>
-      <c r="N15" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="O15" s="39">
+      <c r="N15" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="O15" s="35">
         <v>60</v>
       </c>
       <c r="P15" s="33"/>
@@ -1588,7 +1589,7 @@
         <v>43</v>
       </c>
       <c r="U15" s="35">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="V15" s="15"/>
       <c r="W15" s="15"/>
@@ -1609,7 +1610,7 @@
       <c r="AL15" s="15"/>
       <c r="AM15" s="15"/>
     </row>
-    <row r="16" spans="1:39" ht="12.5" hidden="1">
+    <row r="16" spans="1:39" ht="13.2">
       <c r="A16" s="9"/>
       <c r="B16" s="15" t="s">
         <v>19</v>
@@ -1627,14 +1628,22 @@
       <c r="K16" s="31"/>
       <c r="L16" s="15"/>
       <c r="M16" s="32"/>
-      <c r="N16"/>
-      <c r="O16"/>
+      <c r="N16" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="O16" s="40">
+        <v>60</v>
+      </c>
       <c r="P16" s="33"/>
       <c r="Q16" s="33"/>
       <c r="R16" s="33"/>
       <c r="S16" s="32"/>
-      <c r="T16"/>
-      <c r="U16"/>
+      <c r="T16" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="U16" s="38">
+        <v>15</v>
+      </c>
       <c r="V16" s="15"/>
       <c r="W16" s="15"/>
       <c r="X16" s="15"/>
@@ -1654,7 +1663,7 @@
       <c r="AL16" s="15"/>
       <c r="AM16" s="15"/>
     </row>
-    <row r="17" spans="1:39" ht="29">
+    <row r="17" spans="1:39" ht="28.8">
       <c r="A17" s="9"/>
       <c r="B17" s="9" t="s">
         <v>23</v>
@@ -1678,15 +1687,21 @@
       <c r="K17" s="12"/>
       <c r="L17" s="12"/>
       <c r="M17" s="13"/>
+      <c r="N17" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="O17" s="41">
+        <v>60</v>
+      </c>
       <c r="P17" s="9"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="9"/>
       <c r="S17" s="13"/>
-      <c r="T17" s="37" t="s">
+      <c r="T17" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="U17" s="40">
-        <v>60</v>
+      <c r="U17" s="42">
+        <v>30</v>
       </c>
       <c r="V17" s="10"/>
       <c r="W17" s="10"/>
@@ -1707,7 +1722,7 @@
       <c r="AL17" s="10"/>
       <c r="AM17" s="10"/>
     </row>
-    <row r="18" spans="1:39" ht="43.5">
+    <row r="18" spans="1:39" ht="43.2">
       <c r="A18" s="9"/>
       <c r="B18" s="9" t="s">
         <v>23</v>
@@ -1731,15 +1746,21 @@
       <c r="K18" s="12"/>
       <c r="L18" s="12"/>
       <c r="M18" s="13"/>
+      <c r="N18" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="O18" s="41">
+        <v>60</v>
+      </c>
       <c r="P18" s="9"/>
       <c r="Q18" s="10"/>
       <c r="R18" s="9"/>
       <c r="S18" s="13"/>
-      <c r="T18" s="37" t="s">
+      <c r="T18" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="U18" s="39">
-        <v>60</v>
+      <c r="U18" s="41">
+        <v>30</v>
       </c>
       <c r="V18" s="11"/>
       <c r="W18" s="10"/>
@@ -1760,7 +1781,7 @@
       <c r="AL18" s="10"/>
       <c r="AM18" s="10"/>
     </row>
-    <row r="19" spans="1:39" ht="12.5" hidden="1">
+    <row r="19" spans="1:39" ht="13.2">
       <c r="A19" s="33"/>
       <c r="B19" s="15" t="s">
         <v>19</v>
@@ -1778,14 +1799,22 @@
       <c r="K19" s="31"/>
       <c r="L19" s="15"/>
       <c r="M19" s="32"/>
-      <c r="N19"/>
-      <c r="O19"/>
+      <c r="N19" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="O19" s="40">
+        <v>60</v>
+      </c>
       <c r="P19" s="33"/>
       <c r="Q19" s="33"/>
       <c r="R19" s="33"/>
       <c r="S19" s="32"/>
-      <c r="T19"/>
-      <c r="U19"/>
+      <c r="T19" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="U19" s="40">
+        <v>15</v>
+      </c>
       <c r="V19" s="15"/>
       <c r="W19" s="15"/>
       <c r="X19" s="15"/>
@@ -1805,7 +1834,7 @@
       <c r="AL19" s="15"/>
       <c r="AM19" s="15"/>
     </row>
-    <row r="20" spans="1:39" ht="12.5">
+    <row r="20" spans="1:39" ht="13.2">
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="5"/>
@@ -1816,7 +1845,7 @@
       <c r="R20" s="4"/>
       <c r="S20" s="7"/>
     </row>
-    <row r="21" spans="1:39" ht="12.5">
+    <row r="21" spans="1:39" ht="13.2">
       <c r="F21" s="3"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
@@ -1824,7 +1853,7 @@
       <c r="L21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:39" ht="12.5">
+    <row r="22" spans="1:39" ht="13.2">
       <c r="F22" s="3"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -1832,7 +1861,7 @@
       <c r="L22" s="3"/>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:39" ht="12.5">
+    <row r="23" spans="1:39" ht="13.2">
       <c r="F23" s="3"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
@@ -1840,7 +1869,7 @@
       <c r="L23" s="3"/>
       <c r="P23" s="3"/>
     </row>
-    <row r="24" spans="1:39" ht="12.5">
+    <row r="24" spans="1:39" ht="13.2">
       <c r="F24" s="3"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
@@ -1848,7 +1877,7 @@
       <c r="L24" s="3"/>
       <c r="P24" s="3"/>
     </row>
-    <row r="25" spans="1:39" ht="12.5">
+    <row r="25" spans="1:39" ht="13.2">
       <c r="F25" s="3"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
@@ -1856,7 +1885,7 @@
       <c r="L25" s="3"/>
       <c r="P25" s="3"/>
     </row>
-    <row r="26" spans="1:39" ht="12.5">
+    <row r="26" spans="1:39" ht="13.2">
       <c r="F26" s="3"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
@@ -1864,7 +1893,7 @@
       <c r="L26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:39" ht="12.5">
+    <row r="27" spans="1:39" ht="13.2">
       <c r="F27" s="3"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -1872,7 +1901,7 @@
       <c r="L27" s="3"/>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:39" ht="12.5">
+    <row r="28" spans="1:39" ht="13.2">
       <c r="F28" s="3"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -1880,7 +1909,7 @@
       <c r="L28" s="3"/>
       <c r="P28" s="3"/>
     </row>
-    <row r="29" spans="1:39" ht="12.5">
+    <row r="29" spans="1:39" ht="13.2">
       <c r="F29" s="3"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
@@ -1888,7 +1917,7 @@
       <c r="L29" s="3"/>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:39" ht="12.5">
+    <row r="30" spans="1:39" ht="13.2">
       <c r="F30" s="3"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -1896,7 +1925,7 @@
       <c r="L30" s="3"/>
       <c r="P30" s="3"/>
     </row>
-    <row r="31" spans="1:39" ht="12.5">
+    <row r="31" spans="1:39" ht="13.2">
       <c r="F31" s="3"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
@@ -1904,7 +1933,7 @@
       <c r="L31" s="3"/>
       <c r="P31" s="3"/>
     </row>
-    <row r="32" spans="1:39" ht="12.5">
+    <row r="32" spans="1:39" ht="13.2">
       <c r="F32" s="3"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -1912,7 +1941,7 @@
       <c r="L32" s="3"/>
       <c r="P32" s="3"/>
     </row>
-    <row r="33" spans="6:16" ht="12.5">
+    <row r="33" spans="6:16" ht="13.2">
       <c r="F33" s="3"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
@@ -1920,7 +1949,7 @@
       <c r="L33" s="3"/>
       <c r="P33" s="3"/>
     </row>
-    <row r="34" spans="6:16" ht="12.5">
+    <row r="34" spans="6:16" ht="13.2">
       <c r="F34" s="3"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
@@ -1928,7 +1957,7 @@
       <c r="L34" s="3"/>
       <c r="P34" s="3"/>
     </row>
-    <row r="35" spans="6:16" ht="12.5">
+    <row r="35" spans="6:16" ht="13.2">
       <c r="F35" s="3"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -1936,7 +1965,7 @@
       <c r="L35" s="3"/>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="6:16" ht="12.5">
+    <row r="36" spans="6:16" ht="13.2">
       <c r="F36" s="3"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
@@ -1944,7 +1973,7 @@
       <c r="L36" s="3"/>
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="6:16" ht="12.5">
+    <row r="37" spans="6:16" ht="13.2">
       <c r="F37" s="3"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
@@ -1952,7 +1981,7 @@
       <c r="L37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="6:16" ht="12.5">
+    <row r="38" spans="6:16" ht="13.2">
       <c r="F38" s="3"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
@@ -1960,7 +1989,7 @@
       <c r="L38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="6:16" ht="12.5">
+    <row r="39" spans="6:16" ht="13.2">
       <c r="F39" s="3"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
@@ -1968,7 +1997,7 @@
       <c r="L39" s="3"/>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="6:16" ht="12.5">
+    <row r="40" spans="6:16" ht="13.2">
       <c r="F40" s="3"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -1976,7 +2005,7 @@
       <c r="L40" s="3"/>
       <c r="P40" s="3"/>
     </row>
-    <row r="41" spans="6:16" ht="12.5">
+    <row r="41" spans="6:16" ht="13.2">
       <c r="F41" s="3"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
@@ -1984,7 +2013,7 @@
       <c r="L41" s="3"/>
       <c r="P41" s="3"/>
     </row>
-    <row r="42" spans="6:16" ht="12.5">
+    <row r="42" spans="6:16" ht="13.2">
       <c r="F42" s="3"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -1992,7 +2021,7 @@
       <c r="L42" s="3"/>
       <c r="P42" s="3"/>
     </row>
-    <row r="43" spans="6:16" ht="12.5">
+    <row r="43" spans="6:16" ht="13.2">
       <c r="F43" s="3"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
@@ -2000,7 +2029,7 @@
       <c r="L43" s="3"/>
       <c r="P43" s="3"/>
     </row>
-    <row r="44" spans="6:16" ht="12.5">
+    <row r="44" spans="6:16" ht="13.2">
       <c r="F44" s="3"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -2008,7 +2037,7 @@
       <c r="L44" s="3"/>
       <c r="P44" s="3"/>
     </row>
-    <row r="45" spans="6:16" ht="12.5">
+    <row r="45" spans="6:16" ht="13.2">
       <c r="F45" s="3"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
@@ -2016,7 +2045,7 @@
       <c r="L45" s="3"/>
       <c r="P45" s="3"/>
     </row>
-    <row r="46" spans="6:16" ht="12.5">
+    <row r="46" spans="6:16" ht="13.2">
       <c r="F46" s="3"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
@@ -2024,7 +2053,7 @@
       <c r="L46" s="3"/>
       <c r="P46" s="3"/>
     </row>
-    <row r="47" spans="6:16" ht="12.5">
+    <row r="47" spans="6:16" ht="13.2">
       <c r="F47" s="3"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
@@ -2032,7 +2061,7 @@
       <c r="L47" s="3"/>
       <c r="P47" s="3"/>
     </row>
-    <row r="48" spans="6:16" ht="12.5">
+    <row r="48" spans="6:16" ht="13.2">
       <c r="F48" s="3"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
@@ -2040,7 +2069,7 @@
       <c r="L48" s="3"/>
       <c r="P48" s="3"/>
     </row>
-    <row r="49" spans="6:16" ht="12.5">
+    <row r="49" spans="6:16" ht="13.2">
       <c r="F49" s="3"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
@@ -2048,7 +2077,7 @@
       <c r="L49" s="3"/>
       <c r="P49" s="3"/>
     </row>
-    <row r="50" spans="6:16" ht="12.5">
+    <row r="50" spans="6:16" ht="13.2">
       <c r="F50" s="3"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
@@ -2056,7 +2085,7 @@
       <c r="L50" s="3"/>
       <c r="P50" s="3"/>
     </row>
-    <row r="51" spans="6:16" ht="12.5">
+    <row r="51" spans="6:16" ht="13.2">
       <c r="F51" s="3"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
@@ -2064,7 +2093,7 @@
       <c r="L51" s="3"/>
       <c r="P51" s="3"/>
     </row>
-    <row r="52" spans="6:16" ht="12.5">
+    <row r="52" spans="6:16" ht="13.2">
       <c r="F52" s="3"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
@@ -2072,7 +2101,7 @@
       <c r="L52" s="3"/>
       <c r="P52" s="3"/>
     </row>
-    <row r="53" spans="6:16" ht="12.5">
+    <row r="53" spans="6:16" ht="13.2">
       <c r="F53" s="3"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -2080,7 +2109,7 @@
       <c r="L53" s="3"/>
       <c r="P53" s="3"/>
     </row>
-    <row r="54" spans="6:16" ht="12.5">
+    <row r="54" spans="6:16" ht="13.2">
       <c r="F54" s="3"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
@@ -2088,7 +2117,7 @@
       <c r="L54" s="3"/>
       <c r="P54" s="3"/>
     </row>
-    <row r="55" spans="6:16" ht="12.5">
+    <row r="55" spans="6:16" ht="13.2">
       <c r="F55" s="3"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
@@ -2096,7 +2125,7 @@
       <c r="L55" s="3"/>
       <c r="P55" s="3"/>
     </row>
-    <row r="56" spans="6:16" ht="12.5">
+    <row r="56" spans="6:16" ht="13.2">
       <c r="F56" s="3"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
@@ -2104,7 +2133,7 @@
       <c r="L56" s="3"/>
       <c r="P56" s="3"/>
     </row>
-    <row r="57" spans="6:16" ht="12.5">
+    <row r="57" spans="6:16" ht="13.2">
       <c r="F57" s="3"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
@@ -2112,7 +2141,7 @@
       <c r="L57" s="3"/>
       <c r="P57" s="3"/>
     </row>
-    <row r="58" spans="6:16" ht="12.5">
+    <row r="58" spans="6:16" ht="13.2">
       <c r="F58" s="3"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
@@ -2120,7 +2149,7 @@
       <c r="L58" s="3"/>
       <c r="P58" s="3"/>
     </row>
-    <row r="59" spans="6:16" ht="12.5">
+    <row r="59" spans="6:16" ht="13.2">
       <c r="F59" s="3"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
@@ -2128,7 +2157,7 @@
       <c r="L59" s="3"/>
       <c r="P59" s="3"/>
     </row>
-    <row r="60" spans="6:16" ht="12.5">
+    <row r="60" spans="6:16" ht="13.2">
       <c r="F60" s="3"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
@@ -2136,7 +2165,7 @@
       <c r="L60" s="3"/>
       <c r="P60" s="3"/>
     </row>
-    <row r="61" spans="6:16" ht="12.5">
+    <row r="61" spans="6:16" ht="13.2">
       <c r="F61" s="3"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
@@ -2144,7 +2173,7 @@
       <c r="L61" s="3"/>
       <c r="P61" s="3"/>
     </row>
-    <row r="62" spans="6:16" ht="12.5">
+    <row r="62" spans="6:16" ht="13.2">
       <c r="F62" s="3"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
@@ -2152,7 +2181,7 @@
       <c r="L62" s="3"/>
       <c r="P62" s="3"/>
     </row>
-    <row r="63" spans="6:16" ht="12.5">
+    <row r="63" spans="6:16" ht="13.2">
       <c r="F63" s="3"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
@@ -2160,7 +2189,7 @@
       <c r="L63" s="3"/>
       <c r="P63" s="3"/>
     </row>
-    <row r="64" spans="6:16" ht="12.5">
+    <row r="64" spans="6:16" ht="13.2">
       <c r="F64" s="3"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
@@ -2168,7 +2197,7 @@
       <c r="L64" s="3"/>
       <c r="P64" s="3"/>
     </row>
-    <row r="65" spans="6:16" ht="12.5">
+    <row r="65" spans="6:16" ht="13.2">
       <c r="F65" s="3"/>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
@@ -2176,7 +2205,7 @@
       <c r="L65" s="3"/>
       <c r="P65" s="3"/>
     </row>
-    <row r="66" spans="6:16" ht="12.5">
+    <row r="66" spans="6:16" ht="13.2">
       <c r="F66" s="3"/>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
@@ -2184,7 +2213,7 @@
       <c r="L66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="6:16" ht="12.5">
+    <row r="67" spans="6:16" ht="13.2">
       <c r="F67" s="3"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
@@ -2192,7 +2221,7 @@
       <c r="L67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="6:16" ht="12.5">
+    <row r="68" spans="6:16" ht="13.2">
       <c r="F68" s="3"/>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
@@ -2200,7 +2229,7 @@
       <c r="L68" s="3"/>
       <c r="P68" s="3"/>
     </row>
-    <row r="69" spans="6:16" ht="12.5">
+    <row r="69" spans="6:16" ht="13.2">
       <c r="F69" s="3"/>
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
@@ -2208,7 +2237,7 @@
       <c r="L69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="6:16" ht="12.5">
+    <row r="70" spans="6:16" ht="13.2">
       <c r="F70" s="3"/>
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
@@ -2216,7 +2245,7 @@
       <c r="L70" s="3"/>
       <c r="P70" s="3"/>
     </row>
-    <row r="71" spans="6:16" ht="12.5">
+    <row r="71" spans="6:16" ht="13.2">
       <c r="F71" s="3"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
@@ -2224,7 +2253,7 @@
       <c r="L71" s="3"/>
       <c r="P71" s="3"/>
     </row>
-    <row r="72" spans="6:16" ht="12.5">
+    <row r="72" spans="6:16" ht="13.2">
       <c r="F72" s="3"/>
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
@@ -2232,7 +2261,7 @@
       <c r="L72" s="3"/>
       <c r="P72" s="3"/>
     </row>
-    <row r="73" spans="6:16" ht="12.5">
+    <row r="73" spans="6:16" ht="13.2">
       <c r="F73" s="3"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
@@ -2240,7 +2269,7 @@
       <c r="L73" s="3"/>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="6:16" ht="12.5">
+    <row r="74" spans="6:16" ht="13.2">
       <c r="F74" s="3"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
@@ -2248,7 +2277,7 @@
       <c r="L74" s="3"/>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="6:16" ht="12.5">
+    <row r="75" spans="6:16" ht="13.2">
       <c r="F75" s="3"/>
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
@@ -2256,7 +2285,7 @@
       <c r="L75" s="3"/>
       <c r="P75" s="3"/>
     </row>
-    <row r="76" spans="6:16" ht="12.5">
+    <row r="76" spans="6:16" ht="13.2">
       <c r="F76" s="3"/>
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
@@ -2264,7 +2293,7 @@
       <c r="L76" s="3"/>
       <c r="P76" s="3"/>
     </row>
-    <row r="77" spans="6:16" ht="12.5">
+    <row r="77" spans="6:16" ht="13.2">
       <c r="F77" s="3"/>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
@@ -2272,7 +2301,7 @@
       <c r="L77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="6:16" ht="12.5">
+    <row r="78" spans="6:16" ht="13.2">
       <c r="F78" s="3"/>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
@@ -2280,7 +2309,7 @@
       <c r="L78" s="3"/>
       <c r="P78" s="3"/>
     </row>
-    <row r="79" spans="6:16" ht="12.5">
+    <row r="79" spans="6:16" ht="13.2">
       <c r="F79" s="3"/>
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
@@ -2288,7 +2317,7 @@
       <c r="L79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="6:16" ht="12.5">
+    <row r="80" spans="6:16" ht="13.2">
       <c r="F80" s="3"/>
       <c r="I80" s="4"/>
       <c r="J80" s="4"/>
@@ -2296,7 +2325,7 @@
       <c r="L80" s="3"/>
       <c r="P80" s="3"/>
     </row>
-    <row r="81" spans="6:16" ht="12.5">
+    <row r="81" spans="6:16" ht="13.2">
       <c r="F81" s="3"/>
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
@@ -2304,7 +2333,7 @@
       <c r="L81" s="3"/>
       <c r="P81" s="3"/>
     </row>
-    <row r="82" spans="6:16" ht="12.5">
+    <row r="82" spans="6:16" ht="13.2">
       <c r="F82" s="3"/>
       <c r="I82" s="4"/>
       <c r="J82" s="4"/>
@@ -2312,7 +2341,7 @@
       <c r="L82" s="3"/>
       <c r="P82" s="3"/>
     </row>
-    <row r="83" spans="6:16" ht="12.5">
+    <row r="83" spans="6:16" ht="13.2">
       <c r="F83" s="3"/>
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
@@ -2320,7 +2349,7 @@
       <c r="L83" s="3"/>
       <c r="P83" s="3"/>
     </row>
-    <row r="84" spans="6:16" ht="12.5">
+    <row r="84" spans="6:16" ht="13.2">
       <c r="F84" s="3"/>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
@@ -2328,7 +2357,7 @@
       <c r="L84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="6:16" ht="12.5">
+    <row r="85" spans="6:16" ht="13.2">
       <c r="F85" s="3"/>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
@@ -2336,7 +2365,7 @@
       <c r="L85" s="3"/>
       <c r="P85" s="3"/>
     </row>
-    <row r="86" spans="6:16" ht="12.5">
+    <row r="86" spans="6:16" ht="13.2">
       <c r="F86" s="3"/>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
@@ -2344,7 +2373,7 @@
       <c r="L86" s="3"/>
       <c r="P86" s="3"/>
     </row>
-    <row r="87" spans="6:16" ht="12.5">
+    <row r="87" spans="6:16" ht="13.2">
       <c r="F87" s="3"/>
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
@@ -2352,7 +2381,7 @@
       <c r="L87" s="3"/>
       <c r="P87" s="3"/>
     </row>
-    <row r="88" spans="6:16" ht="12.5">
+    <row r="88" spans="6:16" ht="13.2">
       <c r="F88" s="3"/>
       <c r="I88" s="4"/>
       <c r="J88" s="4"/>
@@ -2360,7 +2389,7 @@
       <c r="L88" s="3"/>
       <c r="P88" s="3"/>
     </row>
-    <row r="89" spans="6:16" ht="12.5">
+    <row r="89" spans="6:16" ht="13.2">
       <c r="F89" s="3"/>
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
@@ -2368,7 +2397,7 @@
       <c r="L89" s="3"/>
       <c r="P89" s="3"/>
     </row>
-    <row r="90" spans="6:16" ht="12.5">
+    <row r="90" spans="6:16" ht="13.2">
       <c r="F90" s="3"/>
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
@@ -2376,7 +2405,7 @@
       <c r="L90" s="3"/>
       <c r="P90" s="3"/>
     </row>
-    <row r="91" spans="6:16" ht="12.5">
+    <row r="91" spans="6:16" ht="13.2">
       <c r="F91" s="3"/>
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
@@ -2384,7 +2413,7 @@
       <c r="L91" s="3"/>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="6:16" ht="12.5">
+    <row r="92" spans="6:16" ht="13.2">
       <c r="F92" s="3"/>
       <c r="I92" s="4"/>
       <c r="J92" s="4"/>
@@ -2392,7 +2421,7 @@
       <c r="L92" s="3"/>
       <c r="P92" s="3"/>
     </row>
-    <row r="93" spans="6:16" ht="12.5">
+    <row r="93" spans="6:16" ht="13.2">
       <c r="F93" s="3"/>
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
@@ -2400,7 +2429,7 @@
       <c r="L93" s="3"/>
       <c r="P93" s="3"/>
     </row>
-    <row r="94" spans="6:16" ht="12.5">
+    <row r="94" spans="6:16" ht="13.2">
       <c r="F94" s="3"/>
       <c r="I94" s="4"/>
       <c r="J94" s="4"/>
@@ -2408,7 +2437,7 @@
       <c r="L94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="6:16" ht="12.5">
+    <row r="95" spans="6:16" ht="13.2">
       <c r="F95" s="3"/>
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
@@ -2416,7 +2445,7 @@
       <c r="L95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="6:16" ht="12.5">
+    <row r="96" spans="6:16" ht="13.2">
       <c r="F96" s="3"/>
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
@@ -2424,7 +2453,7 @@
       <c r="L96" s="3"/>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="6:16" ht="12.5">
+    <row r="97" spans="6:16" ht="13.2">
       <c r="F97" s="3"/>
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
@@ -2432,7 +2461,7 @@
       <c r="L97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="6:16" ht="12.5">
+    <row r="98" spans="6:16" ht="13.2">
       <c r="F98" s="3"/>
       <c r="I98" s="4"/>
       <c r="J98" s="4"/>
@@ -2440,7 +2469,7 @@
       <c r="L98" s="3"/>
       <c r="P98" s="3"/>
     </row>
-    <row r="99" spans="6:16" ht="12.5">
+    <row r="99" spans="6:16" ht="13.2">
       <c r="F99" s="3"/>
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
@@ -2448,7 +2477,7 @@
       <c r="L99" s="3"/>
       <c r="P99" s="3"/>
     </row>
-    <row r="100" spans="6:16" ht="12.5">
+    <row r="100" spans="6:16" ht="13.2">
       <c r="F100" s="3"/>
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
@@ -2456,7 +2485,7 @@
       <c r="L100" s="3"/>
       <c r="P100" s="3"/>
     </row>
-    <row r="101" spans="6:16" ht="12.5">
+    <row r="101" spans="6:16" ht="13.2">
       <c r="F101" s="3"/>
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
@@ -2464,7 +2493,7 @@
       <c r="L101" s="3"/>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="6:16" ht="12.5">
+    <row r="102" spans="6:16" ht="13.2">
       <c r="F102" s="3"/>
       <c r="I102" s="4"/>
       <c r="J102" s="4"/>
@@ -2472,7 +2501,7 @@
       <c r="L102" s="3"/>
       <c r="P102" s="3"/>
     </row>
-    <row r="103" spans="6:16" ht="12.5">
+    <row r="103" spans="6:16" ht="13.2">
       <c r="F103" s="3"/>
       <c r="I103" s="4"/>
       <c r="J103" s="4"/>
@@ -2480,7 +2509,7 @@
       <c r="L103" s="3"/>
       <c r="P103" s="3"/>
     </row>
-    <row r="104" spans="6:16" ht="12.5">
+    <row r="104" spans="6:16" ht="13.2">
       <c r="F104" s="3"/>
       <c r="I104" s="4"/>
       <c r="J104" s="4"/>
@@ -2488,7 +2517,7 @@
       <c r="L104" s="3"/>
       <c r="P104" s="3"/>
     </row>
-    <row r="105" spans="6:16" ht="12.5">
+    <row r="105" spans="6:16" ht="13.2">
       <c r="F105" s="3"/>
       <c r="I105" s="4"/>
       <c r="J105" s="4"/>
@@ -2496,7 +2525,7 @@
       <c r="L105" s="3"/>
       <c r="P105" s="3"/>
     </row>
-    <row r="106" spans="6:16" ht="12.5">
+    <row r="106" spans="6:16" ht="13.2">
       <c r="F106" s="3"/>
       <c r="I106" s="4"/>
       <c r="J106" s="4"/>
@@ -2504,7 +2533,7 @@
       <c r="L106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="6:16" ht="12.5">
+    <row r="107" spans="6:16" ht="13.2">
       <c r="F107" s="3"/>
       <c r="I107" s="4"/>
       <c r="J107" s="4"/>
@@ -2512,7 +2541,7 @@
       <c r="L107" s="3"/>
       <c r="P107" s="3"/>
     </row>
-    <row r="108" spans="6:16" ht="12.5">
+    <row r="108" spans="6:16" ht="13.2">
       <c r="F108" s="3"/>
       <c r="I108" s="4"/>
       <c r="J108" s="4"/>
@@ -2520,7 +2549,7 @@
       <c r="L108" s="3"/>
       <c r="P108" s="3"/>
     </row>
-    <row r="109" spans="6:16" ht="12.5">
+    <row r="109" spans="6:16" ht="13.2">
       <c r="F109" s="3"/>
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
@@ -2528,7 +2557,7 @@
       <c r="L109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="6:16" ht="12.5">
+    <row r="110" spans="6:16" ht="13.2">
       <c r="F110" s="3"/>
       <c r="I110" s="4"/>
       <c r="J110" s="4"/>
@@ -2536,7 +2565,7 @@
       <c r="L110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="6:16" ht="12.5">
+    <row r="111" spans="6:16" ht="13.2">
       <c r="F111" s="3"/>
       <c r="I111" s="4"/>
       <c r="J111" s="4"/>
@@ -2544,7 +2573,7 @@
       <c r="L111" s="3"/>
       <c r="P111" s="3"/>
     </row>
-    <row r="112" spans="6:16" ht="12.5">
+    <row r="112" spans="6:16" ht="13.2">
       <c r="F112" s="3"/>
       <c r="I112" s="4"/>
       <c r="J112" s="4"/>
@@ -2552,7 +2581,7 @@
       <c r="L112" s="3"/>
       <c r="P112" s="3"/>
     </row>
-    <row r="113" spans="6:16" ht="12.5">
+    <row r="113" spans="6:16" ht="13.2">
       <c r="F113" s="3"/>
       <c r="I113" s="4"/>
       <c r="J113" s="4"/>
@@ -2560,7 +2589,7 @@
       <c r="L113" s="3"/>
       <c r="P113" s="3"/>
     </row>
-    <row r="114" spans="6:16" ht="12.5">
+    <row r="114" spans="6:16" ht="13.2">
       <c r="F114" s="3"/>
       <c r="I114" s="4"/>
       <c r="J114" s="4"/>
@@ -2568,7 +2597,7 @@
       <c r="L114" s="3"/>
       <c r="P114" s="3"/>
     </row>
-    <row r="115" spans="6:16" ht="12.5">
+    <row r="115" spans="6:16" ht="13.2">
       <c r="F115" s="3"/>
       <c r="I115" s="4"/>
       <c r="J115" s="4"/>
@@ -2576,7 +2605,7 @@
       <c r="L115" s="3"/>
       <c r="P115" s="3"/>
     </row>
-    <row r="116" spans="6:16" ht="12.5">
+    <row r="116" spans="6:16" ht="13.2">
       <c r="F116" s="3"/>
       <c r="I116" s="4"/>
       <c r="J116" s="4"/>
@@ -2584,7 +2613,7 @@
       <c r="L116" s="3"/>
       <c r="P116" s="3"/>
     </row>
-    <row r="117" spans="6:16" ht="12.5">
+    <row r="117" spans="6:16" ht="13.2">
       <c r="F117" s="3"/>
       <c r="I117" s="4"/>
       <c r="J117" s="4"/>
@@ -2592,7 +2621,7 @@
       <c r="L117" s="3"/>
       <c r="P117" s="3"/>
     </row>
-    <row r="118" spans="6:16" ht="12.5">
+    <row r="118" spans="6:16" ht="13.2">
       <c r="F118" s="3"/>
       <c r="I118" s="4"/>
       <c r="J118" s="4"/>
@@ -2600,7 +2629,7 @@
       <c r="L118" s="3"/>
       <c r="P118" s="3"/>
     </row>
-    <row r="119" spans="6:16" ht="12.5">
+    <row r="119" spans="6:16" ht="13.2">
       <c r="F119" s="3"/>
       <c r="I119" s="4"/>
       <c r="J119" s="4"/>
@@ -2608,7 +2637,7 @@
       <c r="L119" s="3"/>
       <c r="P119" s="3"/>
     </row>
-    <row r="120" spans="6:16" ht="12.5">
+    <row r="120" spans="6:16" ht="13.2">
       <c r="F120" s="3"/>
       <c r="I120" s="4"/>
       <c r="J120" s="4"/>
@@ -2616,7 +2645,7 @@
       <c r="L120" s="3"/>
       <c r="P120" s="3"/>
     </row>
-    <row r="121" spans="6:16" ht="12.5">
+    <row r="121" spans="6:16" ht="13.2">
       <c r="F121" s="3"/>
       <c r="I121" s="4"/>
       <c r="J121" s="4"/>
@@ -2624,7 +2653,7 @@
       <c r="L121" s="3"/>
       <c r="P121" s="3"/>
     </row>
-    <row r="122" spans="6:16" ht="12.5">
+    <row r="122" spans="6:16" ht="13.2">
       <c r="F122" s="3"/>
       <c r="I122" s="4"/>
       <c r="J122" s="4"/>
@@ -2632,7 +2661,7 @@
       <c r="L122" s="3"/>
       <c r="P122" s="3"/>
     </row>
-    <row r="123" spans="6:16" ht="12.5">
+    <row r="123" spans="6:16" ht="13.2">
       <c r="F123" s="3"/>
       <c r="I123" s="4"/>
       <c r="J123" s="4"/>
@@ -2640,7 +2669,7 @@
       <c r="L123" s="3"/>
       <c r="P123" s="3"/>
     </row>
-    <row r="124" spans="6:16" ht="12.5">
+    <row r="124" spans="6:16" ht="13.2">
       <c r="F124" s="3"/>
       <c r="I124" s="4"/>
       <c r="J124" s="4"/>
@@ -2648,7 +2677,7 @@
       <c r="L124" s="3"/>
       <c r="P124" s="3"/>
     </row>
-    <row r="125" spans="6:16" ht="12.5">
+    <row r="125" spans="6:16" ht="13.2">
       <c r="F125" s="3"/>
       <c r="I125" s="4"/>
       <c r="J125" s="4"/>
@@ -2656,7 +2685,7 @@
       <c r="L125" s="3"/>
       <c r="P125" s="3"/>
     </row>
-    <row r="126" spans="6:16" ht="12.5">
+    <row r="126" spans="6:16" ht="13.2">
       <c r="F126" s="3"/>
       <c r="I126" s="4"/>
       <c r="J126" s="4"/>
@@ -2664,7 +2693,7 @@
       <c r="L126" s="3"/>
       <c r="P126" s="3"/>
     </row>
-    <row r="127" spans="6:16" ht="12.5">
+    <row r="127" spans="6:16" ht="13.2">
       <c r="F127" s="3"/>
       <c r="I127" s="4"/>
       <c r="J127" s="4"/>
@@ -2672,7 +2701,7 @@
       <c r="L127" s="3"/>
       <c r="P127" s="3"/>
     </row>
-    <row r="128" spans="6:16" ht="12.5">
+    <row r="128" spans="6:16" ht="13.2">
       <c r="F128" s="3"/>
       <c r="I128" s="4"/>
       <c r="J128" s="4"/>
@@ -2680,7 +2709,7 @@
       <c r="L128" s="3"/>
       <c r="P128" s="3"/>
     </row>
-    <row r="129" spans="6:16" ht="12.5">
+    <row r="129" spans="6:16" ht="13.2">
       <c r="F129" s="3"/>
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
@@ -2688,7 +2717,7 @@
       <c r="L129" s="3"/>
       <c r="P129" s="3"/>
     </row>
-    <row r="130" spans="6:16" ht="12.5">
+    <row r="130" spans="6:16" ht="13.2">
       <c r="F130" s="3"/>
       <c r="I130" s="4"/>
       <c r="J130" s="4"/>
@@ -2696,7 +2725,7 @@
       <c r="L130" s="3"/>
       <c r="P130" s="3"/>
     </row>
-    <row r="131" spans="6:16" ht="12.5">
+    <row r="131" spans="6:16" ht="13.2">
       <c r="F131" s="3"/>
       <c r="I131" s="4"/>
       <c r="J131" s="4"/>
@@ -2704,7 +2733,7 @@
       <c r="L131" s="3"/>
       <c r="P131" s="3"/>
     </row>
-    <row r="132" spans="6:16" ht="12.5">
+    <row r="132" spans="6:16" ht="13.2">
       <c r="F132" s="3"/>
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
@@ -2712,7 +2741,7 @@
       <c r="L132" s="3"/>
       <c r="P132" s="3"/>
     </row>
-    <row r="133" spans="6:16" ht="12.5">
+    <row r="133" spans="6:16" ht="13.2">
       <c r="F133" s="3"/>
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
@@ -2720,7 +2749,7 @@
       <c r="L133" s="3"/>
       <c r="P133" s="3"/>
     </row>
-    <row r="134" spans="6:16" ht="12.5">
+    <row r="134" spans="6:16" ht="13.2">
       <c r="F134" s="3"/>
       <c r="I134" s="4"/>
       <c r="J134" s="4"/>
@@ -2728,7 +2757,7 @@
       <c r="L134" s="3"/>
       <c r="P134" s="3"/>
     </row>
-    <row r="135" spans="6:16" ht="12.5">
+    <row r="135" spans="6:16" ht="13.2">
       <c r="F135" s="3"/>
       <c r="I135" s="4"/>
       <c r="J135" s="4"/>
@@ -2736,7 +2765,7 @@
       <c r="L135" s="3"/>
       <c r="P135" s="3"/>
     </row>
-    <row r="136" spans="6:16" ht="12.5">
+    <row r="136" spans="6:16" ht="13.2">
       <c r="F136" s="3"/>
       <c r="I136" s="4"/>
       <c r="J136" s="4"/>
@@ -2744,7 +2773,7 @@
       <c r="L136" s="3"/>
       <c r="P136" s="3"/>
     </row>
-    <row r="137" spans="6:16" ht="12.5">
+    <row r="137" spans="6:16" ht="13.2">
       <c r="F137" s="3"/>
       <c r="I137" s="4"/>
       <c r="J137" s="4"/>
@@ -2752,7 +2781,7 @@
       <c r="L137" s="3"/>
       <c r="P137" s="3"/>
     </row>
-    <row r="138" spans="6:16" ht="12.5">
+    <row r="138" spans="6:16" ht="13.2">
       <c r="F138" s="3"/>
       <c r="I138" s="4"/>
       <c r="J138" s="4"/>
@@ -2760,7 +2789,7 @@
       <c r="L138" s="3"/>
       <c r="P138" s="3"/>
     </row>
-    <row r="139" spans="6:16" ht="12.5">
+    <row r="139" spans="6:16" ht="13.2">
       <c r="F139" s="3"/>
       <c r="I139" s="4"/>
       <c r="J139" s="4"/>
@@ -2768,7 +2797,7 @@
       <c r="L139" s="3"/>
       <c r="P139" s="3"/>
     </row>
-    <row r="140" spans="6:16" ht="12.5">
+    <row r="140" spans="6:16" ht="13.2">
       <c r="F140" s="3"/>
       <c r="I140" s="4"/>
       <c r="J140" s="4"/>
@@ -2776,7 +2805,7 @@
       <c r="L140" s="3"/>
       <c r="P140" s="3"/>
     </row>
-    <row r="141" spans="6:16" ht="12.5">
+    <row r="141" spans="6:16" ht="13.2">
       <c r="F141" s="3"/>
       <c r="I141" s="4"/>
       <c r="J141" s="4"/>
@@ -2784,7 +2813,7 @@
       <c r="L141" s="3"/>
       <c r="P141" s="3"/>
     </row>
-    <row r="142" spans="6:16" ht="12.5">
+    <row r="142" spans="6:16" ht="13.2">
       <c r="F142" s="3"/>
       <c r="I142" s="4"/>
       <c r="J142" s="4"/>
@@ -2792,7 +2821,7 @@
       <c r="L142" s="3"/>
       <c r="P142" s="3"/>
     </row>
-    <row r="143" spans="6:16" ht="12.5">
+    <row r="143" spans="6:16" ht="13.2">
       <c r="F143" s="3"/>
       <c r="I143" s="4"/>
       <c r="J143" s="4"/>
@@ -2800,7 +2829,7 @@
       <c r="L143" s="3"/>
       <c r="P143" s="3"/>
     </row>
-    <row r="144" spans="6:16" ht="12.5">
+    <row r="144" spans="6:16" ht="13.2">
       <c r="F144" s="3"/>
       <c r="I144" s="4"/>
       <c r="J144" s="4"/>
@@ -2808,7 +2837,7 @@
       <c r="L144" s="3"/>
       <c r="P144" s="3"/>
     </row>
-    <row r="145" spans="6:16" ht="12.5">
+    <row r="145" spans="6:16" ht="13.2">
       <c r="F145" s="3"/>
       <c r="I145" s="4"/>
       <c r="J145" s="4"/>
@@ -2816,7 +2845,7 @@
       <c r="L145" s="3"/>
       <c r="P145" s="3"/>
     </row>
-    <row r="146" spans="6:16" ht="12.5">
+    <row r="146" spans="6:16" ht="13.2">
       <c r="F146" s="3"/>
       <c r="I146" s="4"/>
       <c r="J146" s="4"/>
@@ -2824,7 +2853,7 @@
       <c r="L146" s="3"/>
       <c r="P146" s="3"/>
     </row>
-    <row r="147" spans="6:16" ht="12.5">
+    <row r="147" spans="6:16" ht="13.2">
       <c r="F147" s="3"/>
       <c r="I147" s="4"/>
       <c r="J147" s="4"/>
@@ -2832,7 +2861,7 @@
       <c r="L147" s="3"/>
       <c r="P147" s="3"/>
     </row>
-    <row r="148" spans="6:16" ht="12.5">
+    <row r="148" spans="6:16" ht="13.2">
       <c r="F148" s="3"/>
       <c r="I148" s="4"/>
       <c r="J148" s="4"/>
@@ -2840,7 +2869,7 @@
       <c r="L148" s="3"/>
       <c r="P148" s="3"/>
     </row>
-    <row r="149" spans="6:16" ht="12.5">
+    <row r="149" spans="6:16" ht="13.2">
       <c r="F149" s="3"/>
       <c r="I149" s="4"/>
       <c r="J149" s="4"/>
@@ -2848,7 +2877,7 @@
       <c r="L149" s="3"/>
       <c r="P149" s="3"/>
     </row>
-    <row r="150" spans="6:16" ht="12.5">
+    <row r="150" spans="6:16" ht="13.2">
       <c r="F150" s="3"/>
       <c r="I150" s="4"/>
       <c r="J150" s="4"/>
@@ -2856,7 +2885,7 @@
       <c r="L150" s="3"/>
       <c r="P150" s="3"/>
     </row>
-    <row r="151" spans="6:16" ht="12.5">
+    <row r="151" spans="6:16" ht="13.2">
       <c r="F151" s="3"/>
       <c r="I151" s="4"/>
       <c r="J151" s="4"/>
@@ -2864,7 +2893,7 @@
       <c r="L151" s="3"/>
       <c r="P151" s="3"/>
     </row>
-    <row r="152" spans="6:16" ht="12.5">
+    <row r="152" spans="6:16" ht="13.2">
       <c r="F152" s="3"/>
       <c r="I152" s="4"/>
       <c r="J152" s="4"/>
@@ -2872,7 +2901,7 @@
       <c r="L152" s="3"/>
       <c r="P152" s="3"/>
     </row>
-    <row r="153" spans="6:16" ht="12.5">
+    <row r="153" spans="6:16" ht="13.2">
       <c r="F153" s="3"/>
       <c r="I153" s="4"/>
       <c r="J153" s="4"/>
@@ -2880,7 +2909,7 @@
       <c r="L153" s="3"/>
       <c r="P153" s="3"/>
     </row>
-    <row r="154" spans="6:16" ht="12.5">
+    <row r="154" spans="6:16" ht="13.2">
       <c r="F154" s="3"/>
       <c r="I154" s="4"/>
       <c r="J154" s="4"/>
@@ -2888,7 +2917,7 @@
       <c r="L154" s="3"/>
       <c r="P154" s="3"/>
     </row>
-    <row r="155" spans="6:16" ht="12.5">
+    <row r="155" spans="6:16" ht="13.2">
       <c r="F155" s="3"/>
       <c r="I155" s="4"/>
       <c r="J155" s="4"/>
@@ -2896,7 +2925,7 @@
       <c r="L155" s="3"/>
       <c r="P155" s="3"/>
     </row>
-    <row r="156" spans="6:16" ht="12.5">
+    <row r="156" spans="6:16" ht="13.2">
       <c r="F156" s="3"/>
       <c r="I156" s="4"/>
       <c r="J156" s="4"/>
@@ -2904,7 +2933,7 @@
       <c r="L156" s="3"/>
       <c r="P156" s="3"/>
     </row>
-    <row r="157" spans="6:16" ht="12.5">
+    <row r="157" spans="6:16" ht="13.2">
       <c r="F157" s="3"/>
       <c r="I157" s="4"/>
       <c r="J157" s="4"/>
@@ -2912,7 +2941,7 @@
       <c r="L157" s="3"/>
       <c r="P157" s="3"/>
     </row>
-    <row r="158" spans="6:16" ht="12.5">
+    <row r="158" spans="6:16" ht="13.2">
       <c r="F158" s="3"/>
       <c r="I158" s="4"/>
       <c r="J158" s="4"/>
@@ -2920,7 +2949,7 @@
       <c r="L158" s="3"/>
       <c r="P158" s="3"/>
     </row>
-    <row r="159" spans="6:16" ht="12.5">
+    <row r="159" spans="6:16" ht="13.2">
       <c r="F159" s="3"/>
       <c r="I159" s="4"/>
       <c r="J159" s="4"/>
@@ -2928,7 +2957,7 @@
       <c r="L159" s="3"/>
       <c r="P159" s="3"/>
     </row>
-    <row r="160" spans="6:16" ht="12.5">
+    <row r="160" spans="6:16" ht="13.2">
       <c r="F160" s="3"/>
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
@@ -2936,7 +2965,7 @@
       <c r="L160" s="3"/>
       <c r="P160" s="3"/>
     </row>
-    <row r="161" spans="6:16" ht="12.5">
+    <row r="161" spans="6:16" ht="13.2">
       <c r="F161" s="3"/>
       <c r="I161" s="4"/>
       <c r="J161" s="4"/>
@@ -2944,7 +2973,7 @@
       <c r="L161" s="3"/>
       <c r="P161" s="3"/>
     </row>
-    <row r="162" spans="6:16" ht="12.5">
+    <row r="162" spans="6:16" ht="13.2">
       <c r="F162" s="3"/>
       <c r="I162" s="4"/>
       <c r="J162" s="4"/>
@@ -2952,7 +2981,7 @@
       <c r="L162" s="3"/>
       <c r="P162" s="3"/>
     </row>
-    <row r="163" spans="6:16" ht="12.5">
+    <row r="163" spans="6:16" ht="13.2">
       <c r="F163" s="3"/>
       <c r="I163" s="4"/>
       <c r="J163" s="4"/>
@@ -2960,7 +2989,7 @@
       <c r="L163" s="3"/>
       <c r="P163" s="3"/>
     </row>
-    <row r="164" spans="6:16" ht="12.5">
+    <row r="164" spans="6:16" ht="13.2">
       <c r="F164" s="3"/>
       <c r="I164" s="4"/>
       <c r="J164" s="4"/>
@@ -2968,7 +2997,7 @@
       <c r="L164" s="3"/>
       <c r="P164" s="3"/>
     </row>
-    <row r="165" spans="6:16" ht="12.5">
+    <row r="165" spans="6:16" ht="13.2">
       <c r="F165" s="3"/>
       <c r="I165" s="4"/>
       <c r="J165" s="4"/>
@@ -2976,7 +3005,7 @@
       <c r="L165" s="3"/>
       <c r="P165" s="3"/>
     </row>
-    <row r="166" spans="6:16" ht="12.5">
+    <row r="166" spans="6:16" ht="13.2">
       <c r="F166" s="3"/>
       <c r="I166" s="4"/>
       <c r="J166" s="4"/>
@@ -2984,7 +3013,7 @@
       <c r="L166" s="3"/>
       <c r="P166" s="3"/>
     </row>
-    <row r="167" spans="6:16" ht="12.5">
+    <row r="167" spans="6:16" ht="13.2">
       <c r="F167" s="3"/>
       <c r="I167" s="4"/>
       <c r="J167" s="4"/>
@@ -2992,7 +3021,7 @@
       <c r="L167" s="3"/>
       <c r="P167" s="3"/>
     </row>
-    <row r="168" spans="6:16" ht="12.5">
+    <row r="168" spans="6:16" ht="13.2">
       <c r="F168" s="3"/>
       <c r="I168" s="4"/>
       <c r="J168" s="4"/>
@@ -3000,7 +3029,7 @@
       <c r="L168" s="3"/>
       <c r="P168" s="3"/>
     </row>
-    <row r="169" spans="6:16" ht="12.5">
+    <row r="169" spans="6:16" ht="13.2">
       <c r="F169" s="3"/>
       <c r="I169" s="4"/>
       <c r="J169" s="4"/>
@@ -3008,7 +3037,7 @@
       <c r="L169" s="3"/>
       <c r="P169" s="3"/>
     </row>
-    <row r="170" spans="6:16" ht="12.5">
+    <row r="170" spans="6:16" ht="13.2">
       <c r="F170" s="3"/>
       <c r="I170" s="4"/>
       <c r="J170" s="4"/>
@@ -3016,7 +3045,7 @@
       <c r="L170" s="3"/>
       <c r="P170" s="3"/>
     </row>
-    <row r="171" spans="6:16" ht="12.5">
+    <row r="171" spans="6:16" ht="13.2">
       <c r="F171" s="3"/>
       <c r="I171" s="4"/>
       <c r="J171" s="4"/>
@@ -3024,7 +3053,7 @@
       <c r="L171" s="3"/>
       <c r="P171" s="3"/>
     </row>
-    <row r="172" spans="6:16" ht="12.5">
+    <row r="172" spans="6:16" ht="13.2">
       <c r="F172" s="3"/>
       <c r="I172" s="4"/>
       <c r="J172" s="4"/>
@@ -3032,7 +3061,7 @@
       <c r="L172" s="3"/>
       <c r="P172" s="3"/>
     </row>
-    <row r="173" spans="6:16" ht="12.5">
+    <row r="173" spans="6:16" ht="13.2">
       <c r="F173" s="3"/>
       <c r="I173" s="4"/>
       <c r="J173" s="4"/>
@@ -3040,7 +3069,7 @@
       <c r="L173" s="3"/>
       <c r="P173" s="3"/>
     </row>
-    <row r="174" spans="6:16" ht="12.5">
+    <row r="174" spans="6:16" ht="13.2">
       <c r="F174" s="3"/>
       <c r="I174" s="4"/>
       <c r="J174" s="4"/>
@@ -3048,7 +3077,7 @@
       <c r="L174" s="3"/>
       <c r="P174" s="3"/>
     </row>
-    <row r="175" spans="6:16" ht="12.5">
+    <row r="175" spans="6:16" ht="13.2">
       <c r="F175" s="3"/>
       <c r="I175" s="4"/>
       <c r="J175" s="4"/>
@@ -3056,7 +3085,7 @@
       <c r="L175" s="3"/>
       <c r="P175" s="3"/>
     </row>
-    <row r="176" spans="6:16" ht="12.5">
+    <row r="176" spans="6:16" ht="13.2">
       <c r="F176" s="3"/>
       <c r="I176" s="4"/>
       <c r="J176" s="4"/>
@@ -3064,7 +3093,7 @@
       <c r="L176" s="3"/>
       <c r="P176" s="3"/>
     </row>
-    <row r="177" spans="6:16" ht="12.5">
+    <row r="177" spans="6:16" ht="13.2">
       <c r="F177" s="3"/>
       <c r="I177" s="4"/>
       <c r="J177" s="4"/>
@@ -3072,7 +3101,7 @@
       <c r="L177" s="3"/>
       <c r="P177" s="3"/>
     </row>
-    <row r="178" spans="6:16" ht="12.5">
+    <row r="178" spans="6:16" ht="13.2">
       <c r="F178" s="3"/>
       <c r="I178" s="4"/>
       <c r="J178" s="4"/>
@@ -3080,7 +3109,7 @@
       <c r="L178" s="3"/>
       <c r="P178" s="3"/>
     </row>
-    <row r="179" spans="6:16" ht="12.5">
+    <row r="179" spans="6:16" ht="13.2">
       <c r="F179" s="3"/>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
@@ -3088,7 +3117,7 @@
       <c r="L179" s="3"/>
       <c r="P179" s="3"/>
     </row>
-    <row r="180" spans="6:16" ht="12.5">
+    <row r="180" spans="6:16" ht="13.2">
       <c r="F180" s="3"/>
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
@@ -3096,7 +3125,7 @@
       <c r="L180" s="3"/>
       <c r="P180" s="3"/>
     </row>
-    <row r="181" spans="6:16" ht="12.5">
+    <row r="181" spans="6:16" ht="13.2">
       <c r="F181" s="3"/>
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
@@ -3104,7 +3133,7 @@
       <c r="L181" s="3"/>
       <c r="P181" s="3"/>
     </row>
-    <row r="182" spans="6:16" ht="12.5">
+    <row r="182" spans="6:16" ht="13.2">
       <c r="F182" s="3"/>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
@@ -3112,7 +3141,7 @@
       <c r="L182" s="3"/>
       <c r="P182" s="3"/>
     </row>
-    <row r="183" spans="6:16" ht="12.5">
+    <row r="183" spans="6:16" ht="13.2">
       <c r="F183" s="3"/>
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
@@ -3120,7 +3149,7 @@
       <c r="L183" s="3"/>
       <c r="P183" s="3"/>
     </row>
-    <row r="184" spans="6:16" ht="12.5">
+    <row r="184" spans="6:16" ht="13.2">
       <c r="F184" s="3"/>
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
@@ -3128,7 +3157,7 @@
       <c r="L184" s="3"/>
       <c r="P184" s="3"/>
     </row>
-    <row r="185" spans="6:16" ht="12.5">
+    <row r="185" spans="6:16" ht="13.2">
       <c r="F185" s="3"/>
       <c r="I185" s="4"/>
       <c r="J185" s="4"/>
@@ -3136,7 +3165,7 @@
       <c r="L185" s="3"/>
       <c r="P185" s="3"/>
     </row>
-    <row r="186" spans="6:16" ht="12.5">
+    <row r="186" spans="6:16" ht="13.2">
       <c r="F186" s="3"/>
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
@@ -3144,7 +3173,7 @@
       <c r="L186" s="3"/>
       <c r="P186" s="3"/>
     </row>
-    <row r="187" spans="6:16" ht="12.5">
+    <row r="187" spans="6:16" ht="13.2">
       <c r="F187" s="3"/>
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
@@ -3152,7 +3181,7 @@
       <c r="L187" s="3"/>
       <c r="P187" s="3"/>
     </row>
-    <row r="188" spans="6:16" ht="12.5">
+    <row r="188" spans="6:16" ht="13.2">
       <c r="F188" s="3"/>
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
@@ -3160,7 +3189,7 @@
       <c r="L188" s="3"/>
       <c r="P188" s="3"/>
     </row>
-    <row r="189" spans="6:16" ht="12.5">
+    <row r="189" spans="6:16" ht="13.2">
       <c r="F189" s="3"/>
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
@@ -3168,7 +3197,7 @@
       <c r="L189" s="3"/>
       <c r="P189" s="3"/>
     </row>
-    <row r="190" spans="6:16" ht="12.5">
+    <row r="190" spans="6:16" ht="13.2">
       <c r="F190" s="3"/>
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
@@ -3176,7 +3205,7 @@
       <c r="L190" s="3"/>
       <c r="P190" s="3"/>
     </row>
-    <row r="191" spans="6:16" ht="12.5">
+    <row r="191" spans="6:16" ht="13.2">
       <c r="F191" s="3"/>
       <c r="I191" s="4"/>
       <c r="J191" s="4"/>
@@ -3184,7 +3213,7 @@
       <c r="L191" s="3"/>
       <c r="P191" s="3"/>
     </row>
-    <row r="192" spans="6:16" ht="12.5">
+    <row r="192" spans="6:16" ht="13.2">
       <c r="F192" s="3"/>
       <c r="I192" s="4"/>
       <c r="J192" s="4"/>
@@ -3192,7 +3221,7 @@
       <c r="L192" s="3"/>
       <c r="P192" s="3"/>
     </row>
-    <row r="193" spans="6:16" ht="12.5">
+    <row r="193" spans="6:16" ht="13.2">
       <c r="F193" s="3"/>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
@@ -3200,7 +3229,7 @@
       <c r="L193" s="3"/>
       <c r="P193" s="3"/>
     </row>
-    <row r="194" spans="6:16" ht="12.5">
+    <row r="194" spans="6:16" ht="13.2">
       <c r="F194" s="3"/>
       <c r="I194" s="4"/>
       <c r="J194" s="4"/>
@@ -3208,7 +3237,7 @@
       <c r="L194" s="3"/>
       <c r="P194" s="3"/>
     </row>
-    <row r="195" spans="6:16" ht="12.5">
+    <row r="195" spans="6:16" ht="13.2">
       <c r="F195" s="3"/>
       <c r="I195" s="4"/>
       <c r="J195" s="4"/>
@@ -3216,7 +3245,7 @@
       <c r="L195" s="3"/>
       <c r="P195" s="3"/>
     </row>
-    <row r="196" spans="6:16" ht="12.5">
+    <row r="196" spans="6:16" ht="13.2">
       <c r="F196" s="3"/>
       <c r="I196" s="4"/>
       <c r="J196" s="4"/>
@@ -3224,7 +3253,7 @@
       <c r="L196" s="3"/>
       <c r="P196" s="3"/>
     </row>
-    <row r="197" spans="6:16" ht="12.5">
+    <row r="197" spans="6:16" ht="13.2">
       <c r="F197" s="3"/>
       <c r="I197" s="4"/>
       <c r="J197" s="4"/>
@@ -3232,7 +3261,7 @@
       <c r="L197" s="3"/>
       <c r="P197" s="3"/>
     </row>
-    <row r="198" spans="6:16" ht="12.5">
+    <row r="198" spans="6:16" ht="13.2">
       <c r="F198" s="3"/>
       <c r="I198" s="4"/>
       <c r="J198" s="4"/>
@@ -3240,7 +3269,7 @@
       <c r="L198" s="3"/>
       <c r="P198" s="3"/>
     </row>
-    <row r="199" spans="6:16" ht="12.5">
+    <row r="199" spans="6:16" ht="13.2">
       <c r="F199" s="3"/>
       <c r="I199" s="4"/>
       <c r="J199" s="4"/>
@@ -3248,7 +3277,7 @@
       <c r="L199" s="3"/>
       <c r="P199" s="3"/>
     </row>
-    <row r="200" spans="6:16" ht="12.5">
+    <row r="200" spans="6:16" ht="13.2">
       <c r="F200" s="3"/>
       <c r="I200" s="4"/>
       <c r="J200" s="4"/>
@@ -3256,7 +3285,7 @@
       <c r="L200" s="3"/>
       <c r="P200" s="3"/>
     </row>
-    <row r="201" spans="6:16" ht="12.5">
+    <row r="201" spans="6:16" ht="13.2">
       <c r="F201" s="3"/>
       <c r="I201" s="4"/>
       <c r="J201" s="4"/>
@@ -3264,7 +3293,7 @@
       <c r="L201" s="3"/>
       <c r="P201" s="3"/>
     </row>
-    <row r="202" spans="6:16" ht="12.5">
+    <row r="202" spans="6:16" ht="13.2">
       <c r="F202" s="3"/>
       <c r="I202" s="4"/>
       <c r="J202" s="4"/>
@@ -3272,7 +3301,7 @@
       <c r="L202" s="3"/>
       <c r="P202" s="3"/>
     </row>
-    <row r="203" spans="6:16" ht="12.5">
+    <row r="203" spans="6:16" ht="13.2">
       <c r="F203" s="3"/>
       <c r="I203" s="4"/>
       <c r="J203" s="4"/>
@@ -3280,7 +3309,7 @@
       <c r="L203" s="3"/>
       <c r="P203" s="3"/>
     </row>
-    <row r="204" spans="6:16" ht="12.5">
+    <row r="204" spans="6:16" ht="13.2">
       <c r="F204" s="3"/>
       <c r="I204" s="4"/>
       <c r="J204" s="4"/>
@@ -3288,7 +3317,7 @@
       <c r="L204" s="3"/>
       <c r="P204" s="3"/>
     </row>
-    <row r="205" spans="6:16" ht="12.5">
+    <row r="205" spans="6:16" ht="13.2">
       <c r="F205" s="3"/>
       <c r="I205" s="4"/>
       <c r="J205" s="4"/>
@@ -3296,7 +3325,7 @@
       <c r="L205" s="3"/>
       <c r="P205" s="3"/>
     </row>
-    <row r="206" spans="6:16" ht="12.5">
+    <row r="206" spans="6:16" ht="13.2">
       <c r="F206" s="3"/>
       <c r="I206" s="4"/>
       <c r="J206" s="4"/>
@@ -3304,7 +3333,7 @@
       <c r="L206" s="3"/>
       <c r="P206" s="3"/>
     </row>
-    <row r="207" spans="6:16" ht="12.5">
+    <row r="207" spans="6:16" ht="13.2">
       <c r="F207" s="3"/>
       <c r="I207" s="4"/>
       <c r="J207" s="4"/>
@@ -3312,7 +3341,7 @@
       <c r="L207" s="3"/>
       <c r="P207" s="3"/>
     </row>
-    <row r="208" spans="6:16" ht="12.5">
+    <row r="208" spans="6:16" ht="13.2">
       <c r="F208" s="3"/>
       <c r="I208" s="4"/>
       <c r="J208" s="4"/>
@@ -3320,7 +3349,7 @@
       <c r="L208" s="3"/>
       <c r="P208" s="3"/>
     </row>
-    <row r="209" spans="6:16" ht="12.5">
+    <row r="209" spans="6:16" ht="13.2">
       <c r="F209" s="3"/>
       <c r="I209" s="4"/>
       <c r="J209" s="4"/>
@@ -3328,7 +3357,7 @@
       <c r="L209" s="3"/>
       <c r="P209" s="3"/>
     </row>
-    <row r="210" spans="6:16" ht="12.5">
+    <row r="210" spans="6:16" ht="13.2">
       <c r="F210" s="3"/>
       <c r="I210" s="4"/>
       <c r="J210" s="4"/>
@@ -3336,7 +3365,7 @@
       <c r="L210" s="3"/>
       <c r="P210" s="3"/>
     </row>
-    <row r="211" spans="6:16" ht="12.5">
+    <row r="211" spans="6:16" ht="13.2">
       <c r="F211" s="3"/>
       <c r="I211" s="4"/>
       <c r="J211" s="4"/>
@@ -3344,7 +3373,7 @@
       <c r="L211" s="3"/>
       <c r="P211" s="3"/>
     </row>
-    <row r="212" spans="6:16" ht="12.5">
+    <row r="212" spans="6:16" ht="13.2">
       <c r="F212" s="3"/>
       <c r="I212" s="4"/>
       <c r="J212" s="4"/>
@@ -3352,7 +3381,7 @@
       <c r="L212" s="3"/>
       <c r="P212" s="3"/>
     </row>
-    <row r="213" spans="6:16" ht="12.5">
+    <row r="213" spans="6:16" ht="13.2">
       <c r="F213" s="3"/>
       <c r="I213" s="4"/>
       <c r="J213" s="4"/>
@@ -3360,7 +3389,7 @@
       <c r="L213" s="3"/>
       <c r="P213" s="3"/>
     </row>
-    <row r="214" spans="6:16" ht="12.5">
+    <row r="214" spans="6:16" ht="13.2">
       <c r="F214" s="3"/>
       <c r="I214" s="4"/>
       <c r="J214" s="4"/>
@@ -3368,7 +3397,7 @@
       <c r="L214" s="3"/>
       <c r="P214" s="3"/>
     </row>
-    <row r="215" spans="6:16" ht="12.5">
+    <row r="215" spans="6:16" ht="13.2">
       <c r="F215" s="3"/>
       <c r="I215" s="4"/>
       <c r="J215" s="4"/>
@@ -3376,7 +3405,7 @@
       <c r="L215" s="3"/>
       <c r="P215" s="3"/>
     </row>
-    <row r="216" spans="6:16" ht="12.5">
+    <row r="216" spans="6:16" ht="13.2">
       <c r="F216" s="3"/>
       <c r="I216" s="4"/>
       <c r="J216" s="4"/>
@@ -3384,7 +3413,7 @@
       <c r="L216" s="3"/>
       <c r="P216" s="3"/>
     </row>
-    <row r="217" spans="6:16" ht="12.5">
+    <row r="217" spans="6:16" ht="13.2">
       <c r="F217" s="3"/>
       <c r="I217" s="4"/>
       <c r="J217" s="4"/>
@@ -3392,7 +3421,7 @@
       <c r="L217" s="3"/>
       <c r="P217" s="3"/>
     </row>
-    <row r="218" spans="6:16" ht="12.5">
+    <row r="218" spans="6:16" ht="13.2">
       <c r="F218" s="3"/>
       <c r="I218" s="4"/>
       <c r="J218" s="4"/>
@@ -3400,7 +3429,7 @@
       <c r="L218" s="3"/>
       <c r="P218" s="3"/>
     </row>
-    <row r="219" spans="6:16" ht="12.5">
+    <row r="219" spans="6:16" ht="13.2">
       <c r="F219" s="3"/>
       <c r="I219" s="4"/>
       <c r="J219" s="4"/>
@@ -3408,7 +3437,7 @@
       <c r="L219" s="3"/>
       <c r="P219" s="3"/>
     </row>
-    <row r="220" spans="6:16" ht="12.5">
+    <row r="220" spans="6:16" ht="13.2">
       <c r="F220" s="3"/>
       <c r="I220" s="4"/>
       <c r="J220" s="4"/>
@@ -3416,7 +3445,7 @@
       <c r="L220" s="3"/>
       <c r="P220" s="3"/>
     </row>
-    <row r="221" spans="6:16" ht="12.5">
+    <row r="221" spans="6:16" ht="13.2">
       <c r="F221" s="3"/>
       <c r="I221" s="4"/>
       <c r="J221" s="4"/>
@@ -3424,7 +3453,7 @@
       <c r="L221" s="3"/>
       <c r="P221" s="3"/>
     </row>
-    <row r="222" spans="6:16" ht="12.5">
+    <row r="222" spans="6:16" ht="13.2">
       <c r="F222" s="3"/>
       <c r="I222" s="4"/>
       <c r="J222" s="4"/>
@@ -3432,7 +3461,7 @@
       <c r="L222" s="3"/>
       <c r="P222" s="3"/>
     </row>
-    <row r="223" spans="6:16" ht="12.5">
+    <row r="223" spans="6:16" ht="13.2">
       <c r="F223" s="3"/>
       <c r="I223" s="4"/>
       <c r="J223" s="4"/>
@@ -3440,7 +3469,7 @@
       <c r="L223" s="3"/>
       <c r="P223" s="3"/>
     </row>
-    <row r="224" spans="6:16" ht="12.5">
+    <row r="224" spans="6:16" ht="13.2">
       <c r="F224" s="3"/>
       <c r="I224" s="4"/>
       <c r="J224" s="4"/>
@@ -3448,7 +3477,7 @@
       <c r="L224" s="3"/>
       <c r="P224" s="3"/>
     </row>
-    <row r="225" spans="6:16" ht="12.5">
+    <row r="225" spans="6:16" ht="13.2">
       <c r="F225" s="3"/>
       <c r="I225" s="4"/>
       <c r="J225" s="4"/>
@@ -3456,7 +3485,7 @@
       <c r="L225" s="3"/>
       <c r="P225" s="3"/>
     </row>
-    <row r="226" spans="6:16" ht="12.5">
+    <row r="226" spans="6:16" ht="13.2">
       <c r="F226" s="3"/>
       <c r="I226" s="4"/>
       <c r="J226" s="4"/>
@@ -3464,7 +3493,7 @@
       <c r="L226" s="3"/>
       <c r="P226" s="3"/>
     </row>
-    <row r="227" spans="6:16" ht="12.5">
+    <row r="227" spans="6:16" ht="13.2">
       <c r="F227" s="3"/>
       <c r="I227" s="4"/>
       <c r="J227" s="4"/>
@@ -3472,7 +3501,7 @@
       <c r="L227" s="3"/>
       <c r="P227" s="3"/>
     </row>
-    <row r="228" spans="6:16" ht="12.5">
+    <row r="228" spans="6:16" ht="13.2">
       <c r="F228" s="3"/>
       <c r="I228" s="4"/>
       <c r="J228" s="4"/>
@@ -3480,7 +3509,7 @@
       <c r="L228" s="3"/>
       <c r="P228" s="3"/>
     </row>
-    <row r="229" spans="6:16" ht="12.5">
+    <row r="229" spans="6:16" ht="13.2">
       <c r="F229" s="3"/>
       <c r="I229" s="4"/>
       <c r="J229" s="4"/>
@@ -3488,7 +3517,7 @@
       <c r="L229" s="3"/>
       <c r="P229" s="3"/>
     </row>
-    <row r="230" spans="6:16" ht="12.5">
+    <row r="230" spans="6:16" ht="13.2">
       <c r="F230" s="3"/>
       <c r="I230" s="4"/>
       <c r="J230" s="4"/>
@@ -3496,7 +3525,7 @@
       <c r="L230" s="3"/>
       <c r="P230" s="3"/>
     </row>
-    <row r="231" spans="6:16" ht="12.5">
+    <row r="231" spans="6:16" ht="13.2">
       <c r="F231" s="3"/>
       <c r="I231" s="4"/>
       <c r="J231" s="4"/>
@@ -3504,7 +3533,7 @@
       <c r="L231" s="3"/>
       <c r="P231" s="3"/>
     </row>
-    <row r="232" spans="6:16" ht="12.5">
+    <row r="232" spans="6:16" ht="13.2">
       <c r="F232" s="3"/>
       <c r="I232" s="4"/>
       <c r="J232" s="4"/>
@@ -3512,7 +3541,7 @@
       <c r="L232" s="3"/>
       <c r="P232" s="3"/>
     </row>
-    <row r="233" spans="6:16" ht="12.5">
+    <row r="233" spans="6:16" ht="13.2">
       <c r="F233" s="3"/>
       <c r="I233" s="4"/>
       <c r="J233" s="4"/>
@@ -3520,7 +3549,7 @@
       <c r="L233" s="3"/>
       <c r="P233" s="3"/>
     </row>
-    <row r="234" spans="6:16" ht="12.5">
+    <row r="234" spans="6:16" ht="13.2">
       <c r="F234" s="3"/>
       <c r="I234" s="4"/>
       <c r="J234" s="4"/>
@@ -3528,7 +3557,7 @@
       <c r="L234" s="3"/>
       <c r="P234" s="3"/>
     </row>
-    <row r="235" spans="6:16" ht="12.5">
+    <row r="235" spans="6:16" ht="13.2">
       <c r="F235" s="3"/>
       <c r="I235" s="4"/>
       <c r="J235" s="4"/>
@@ -3536,7 +3565,7 @@
       <c r="L235" s="3"/>
       <c r="P235" s="3"/>
     </row>
-    <row r="236" spans="6:16" ht="12.5">
+    <row r="236" spans="6:16" ht="13.2">
       <c r="F236" s="3"/>
       <c r="I236" s="4"/>
       <c r="J236" s="4"/>
@@ -3544,7 +3573,7 @@
       <c r="L236" s="3"/>
       <c r="P236" s="3"/>
     </row>
-    <row r="237" spans="6:16" ht="12.5">
+    <row r="237" spans="6:16" ht="13.2">
       <c r="F237" s="3"/>
       <c r="I237" s="4"/>
       <c r="J237" s="4"/>
@@ -3552,7 +3581,7 @@
       <c r="L237" s="3"/>
       <c r="P237" s="3"/>
     </row>
-    <row r="238" spans="6:16" ht="12.5">
+    <row r="238" spans="6:16" ht="13.2">
       <c r="F238" s="3"/>
       <c r="I238" s="4"/>
       <c r="J238" s="4"/>
@@ -3560,7 +3589,7 @@
       <c r="L238" s="3"/>
       <c r="P238" s="3"/>
     </row>
-    <row r="239" spans="6:16" ht="12.5">
+    <row r="239" spans="6:16" ht="13.2">
       <c r="F239" s="3"/>
       <c r="I239" s="4"/>
       <c r="J239" s="4"/>
@@ -3568,7 +3597,7 @@
       <c r="L239" s="3"/>
       <c r="P239" s="3"/>
     </row>
-    <row r="240" spans="6:16" ht="12.5">
+    <row r="240" spans="6:16" ht="13.2">
       <c r="F240" s="3"/>
       <c r="I240" s="4"/>
       <c r="J240" s="4"/>
@@ -3576,7 +3605,7 @@
       <c r="L240" s="3"/>
       <c r="P240" s="3"/>
     </row>
-    <row r="241" spans="6:16" ht="12.5">
+    <row r="241" spans="6:16" ht="13.2">
       <c r="F241" s="3"/>
       <c r="I241" s="4"/>
       <c r="J241" s="4"/>
@@ -3584,7 +3613,7 @@
       <c r="L241" s="3"/>
       <c r="P241" s="3"/>
     </row>
-    <row r="242" spans="6:16" ht="12.5">
+    <row r="242" spans="6:16" ht="13.2">
       <c r="F242" s="3"/>
       <c r="I242" s="4"/>
       <c r="J242" s="4"/>
@@ -3592,7 +3621,7 @@
       <c r="L242" s="3"/>
       <c r="P242" s="3"/>
     </row>
-    <row r="243" spans="6:16" ht="12.5">
+    <row r="243" spans="6:16" ht="13.2">
       <c r="F243" s="3"/>
       <c r="I243" s="4"/>
       <c r="J243" s="4"/>
@@ -3600,7 +3629,7 @@
       <c r="L243" s="3"/>
       <c r="P243" s="3"/>
     </row>
-    <row r="244" spans="6:16" ht="12.5">
+    <row r="244" spans="6:16" ht="13.2">
       <c r="F244" s="3"/>
       <c r="I244" s="4"/>
       <c r="J244" s="4"/>
@@ -3608,7 +3637,7 @@
       <c r="L244" s="3"/>
       <c r="P244" s="3"/>
     </row>
-    <row r="245" spans="6:16" ht="12.5">
+    <row r="245" spans="6:16" ht="13.2">
       <c r="F245" s="3"/>
       <c r="I245" s="4"/>
       <c r="J245" s="4"/>
@@ -3616,7 +3645,7 @@
       <c r="L245" s="3"/>
       <c r="P245" s="3"/>
     </row>
-    <row r="246" spans="6:16" ht="12.5">
+    <row r="246" spans="6:16" ht="13.2">
       <c r="F246" s="3"/>
       <c r="I246" s="4"/>
       <c r="J246" s="4"/>
@@ -3624,7 +3653,7 @@
       <c r="L246" s="3"/>
       <c r="P246" s="3"/>
     </row>
-    <row r="247" spans="6:16" ht="12.5">
+    <row r="247" spans="6:16" ht="13.2">
       <c r="F247" s="3"/>
       <c r="I247" s="4"/>
       <c r="J247" s="4"/>
@@ -3632,7 +3661,7 @@
       <c r="L247" s="3"/>
       <c r="P247" s="3"/>
     </row>
-    <row r="248" spans="6:16" ht="12.5">
+    <row r="248" spans="6:16" ht="13.2">
       <c r="F248" s="3"/>
       <c r="I248" s="4"/>
       <c r="J248" s="4"/>
@@ -3640,7 +3669,7 @@
       <c r="L248" s="3"/>
       <c r="P248" s="3"/>
     </row>
-    <row r="249" spans="6:16" ht="12.5">
+    <row r="249" spans="6:16" ht="13.2">
       <c r="F249" s="3"/>
       <c r="I249" s="4"/>
       <c r="J249" s="4"/>
@@ -3648,7 +3677,7 @@
       <c r="L249" s="3"/>
       <c r="P249" s="3"/>
     </row>
-    <row r="250" spans="6:16" ht="12.5">
+    <row r="250" spans="6:16" ht="13.2">
       <c r="F250" s="3"/>
       <c r="I250" s="4"/>
       <c r="J250" s="4"/>
@@ -3656,7 +3685,7 @@
       <c r="L250" s="3"/>
       <c r="P250" s="3"/>
     </row>
-    <row r="251" spans="6:16" ht="12.5">
+    <row r="251" spans="6:16" ht="13.2">
       <c r="F251" s="3"/>
       <c r="I251" s="4"/>
       <c r="J251" s="4"/>
@@ -3664,7 +3693,7 @@
       <c r="L251" s="3"/>
       <c r="P251" s="3"/>
     </row>
-    <row r="252" spans="6:16" ht="12.5">
+    <row r="252" spans="6:16" ht="13.2">
       <c r="F252" s="3"/>
       <c r="I252" s="4"/>
       <c r="J252" s="4"/>
@@ -3672,7 +3701,7 @@
       <c r="L252" s="3"/>
       <c r="P252" s="3"/>
     </row>
-    <row r="253" spans="6:16" ht="12.5">
+    <row r="253" spans="6:16" ht="13.2">
       <c r="F253" s="3"/>
       <c r="I253" s="4"/>
       <c r="J253" s="4"/>
@@ -3680,7 +3709,7 @@
       <c r="L253" s="3"/>
       <c r="P253" s="3"/>
     </row>
-    <row r="254" spans="6:16" ht="12.5">
+    <row r="254" spans="6:16" ht="13.2">
       <c r="F254" s="3"/>
       <c r="I254" s="4"/>
       <c r="J254" s="4"/>
@@ -3688,7 +3717,7 @@
       <c r="L254" s="3"/>
       <c r="P254" s="3"/>
     </row>
-    <row r="255" spans="6:16" ht="12.5">
+    <row r="255" spans="6:16" ht="13.2">
       <c r="F255" s="3"/>
       <c r="I255" s="4"/>
       <c r="J255" s="4"/>
@@ -3696,7 +3725,7 @@
       <c r="L255" s="3"/>
       <c r="P255" s="3"/>
     </row>
-    <row r="256" spans="6:16" ht="12.5">
+    <row r="256" spans="6:16" ht="13.2">
       <c r="F256" s="3"/>
       <c r="I256" s="4"/>
       <c r="J256" s="4"/>
@@ -3704,7 +3733,7 @@
       <c r="L256" s="3"/>
       <c r="P256" s="3"/>
     </row>
-    <row r="257" spans="6:16" ht="12.5">
+    <row r="257" spans="6:16" ht="13.2">
       <c r="F257" s="3"/>
       <c r="I257" s="4"/>
       <c r="J257" s="4"/>
@@ -3712,7 +3741,7 @@
       <c r="L257" s="3"/>
       <c r="P257" s="3"/>
     </row>
-    <row r="258" spans="6:16" ht="12.5">
+    <row r="258" spans="6:16" ht="13.2">
       <c r="F258" s="3"/>
       <c r="I258" s="4"/>
       <c r="J258" s="4"/>
@@ -3720,7 +3749,7 @@
       <c r="L258" s="3"/>
       <c r="P258" s="3"/>
     </row>
-    <row r="259" spans="6:16" ht="12.5">
+    <row r="259" spans="6:16" ht="13.2">
       <c r="F259" s="3"/>
       <c r="I259" s="4"/>
       <c r="J259" s="4"/>
@@ -3728,7 +3757,7 @@
       <c r="L259" s="3"/>
       <c r="P259" s="3"/>
     </row>
-    <row r="260" spans="6:16" ht="12.5">
+    <row r="260" spans="6:16" ht="13.2">
       <c r="F260" s="3"/>
       <c r="I260" s="4"/>
       <c r="J260" s="4"/>
@@ -3736,7 +3765,7 @@
       <c r="L260" s="3"/>
       <c r="P260" s="3"/>
     </row>
-    <row r="261" spans="6:16" ht="12.5">
+    <row r="261" spans="6:16" ht="13.2">
       <c r="F261" s="3"/>
       <c r="I261" s="4"/>
       <c r="J261" s="4"/>
@@ -3744,7 +3773,7 @@
       <c r="L261" s="3"/>
       <c r="P261" s="3"/>
     </row>
-    <row r="262" spans="6:16" ht="12.5">
+    <row r="262" spans="6:16" ht="13.2">
       <c r="F262" s="3"/>
       <c r="I262" s="4"/>
       <c r="J262" s="4"/>
@@ -3752,7 +3781,7 @@
       <c r="L262" s="3"/>
       <c r="P262" s="3"/>
     </row>
-    <row r="263" spans="6:16" ht="12.5">
+    <row r="263" spans="6:16" ht="13.2">
       <c r="F263" s="3"/>
       <c r="I263" s="4"/>
       <c r="J263" s="4"/>
@@ -3760,7 +3789,7 @@
       <c r="L263" s="3"/>
       <c r="P263" s="3"/>
     </row>
-    <row r="264" spans="6:16" ht="12.5">
+    <row r="264" spans="6:16" ht="13.2">
       <c r="F264" s="3"/>
       <c r="I264" s="4"/>
       <c r="J264" s="4"/>
@@ -3768,7 +3797,7 @@
       <c r="L264" s="3"/>
       <c r="P264" s="3"/>
     </row>
-    <row r="265" spans="6:16" ht="12.5">
+    <row r="265" spans="6:16" ht="13.2">
       <c r="F265" s="3"/>
       <c r="I265" s="4"/>
       <c r="J265" s="4"/>
@@ -3776,7 +3805,7 @@
       <c r="L265" s="3"/>
       <c r="P265" s="3"/>
     </row>
-    <row r="266" spans="6:16" ht="12.5">
+    <row r="266" spans="6:16" ht="13.2">
       <c r="F266" s="3"/>
       <c r="I266" s="4"/>
       <c r="J266" s="4"/>
@@ -3784,7 +3813,7 @@
       <c r="L266" s="3"/>
       <c r="P266" s="3"/>
     </row>
-    <row r="267" spans="6:16" ht="12.5">
+    <row r="267" spans="6:16" ht="13.2">
       <c r="F267" s="3"/>
       <c r="I267" s="4"/>
       <c r="J267" s="4"/>
@@ -3792,7 +3821,7 @@
       <c r="L267" s="3"/>
       <c r="P267" s="3"/>
     </row>
-    <row r="268" spans="6:16" ht="12.5">
+    <row r="268" spans="6:16" ht="13.2">
       <c r="F268" s="3"/>
       <c r="I268" s="4"/>
       <c r="J268" s="4"/>
@@ -3800,7 +3829,7 @@
       <c r="L268" s="3"/>
       <c r="P268" s="3"/>
     </row>
-    <row r="269" spans="6:16" ht="12.5">
+    <row r="269" spans="6:16" ht="13.2">
       <c r="F269" s="3"/>
       <c r="I269" s="4"/>
       <c r="J269" s="4"/>
@@ -3808,7 +3837,7 @@
       <c r="L269" s="3"/>
       <c r="P269" s="3"/>
     </row>
-    <row r="270" spans="6:16" ht="12.5">
+    <row r="270" spans="6:16" ht="13.2">
       <c r="F270" s="3"/>
       <c r="I270" s="4"/>
       <c r="J270" s="4"/>
@@ -3816,7 +3845,7 @@
       <c r="L270" s="3"/>
       <c r="P270" s="3"/>
     </row>
-    <row r="271" spans="6:16" ht="12.5">
+    <row r="271" spans="6:16" ht="13.2">
       <c r="F271" s="3"/>
       <c r="I271" s="4"/>
       <c r="J271" s="4"/>
@@ -3824,7 +3853,7 @@
       <c r="L271" s="3"/>
       <c r="P271" s="3"/>
     </row>
-    <row r="272" spans="6:16" ht="12.5">
+    <row r="272" spans="6:16" ht="13.2">
       <c r="F272" s="3"/>
       <c r="I272" s="4"/>
       <c r="J272" s="4"/>
@@ -3832,7 +3861,7 @@
       <c r="L272" s="3"/>
       <c r="P272" s="3"/>
     </row>
-    <row r="273" spans="6:16" ht="12.5">
+    <row r="273" spans="6:16" ht="13.2">
       <c r="F273" s="3"/>
       <c r="I273" s="4"/>
       <c r="J273" s="4"/>
@@ -3840,7 +3869,7 @@
       <c r="L273" s="3"/>
       <c r="P273" s="3"/>
     </row>
-    <row r="274" spans="6:16" ht="12.5">
+    <row r="274" spans="6:16" ht="13.2">
       <c r="F274" s="3"/>
       <c r="I274" s="4"/>
       <c r="J274" s="4"/>
@@ -3848,7 +3877,7 @@
       <c r="L274" s="3"/>
       <c r="P274" s="3"/>
     </row>
-    <row r="275" spans="6:16" ht="12.5">
+    <row r="275" spans="6:16" ht="13.2">
       <c r="F275" s="3"/>
       <c r="I275" s="4"/>
       <c r="J275" s="4"/>
@@ -3856,7 +3885,7 @@
       <c r="L275" s="3"/>
       <c r="P275" s="3"/>
     </row>
-    <row r="276" spans="6:16" ht="12.5">
+    <row r="276" spans="6:16" ht="13.2">
       <c r="F276" s="3"/>
       <c r="I276" s="4"/>
       <c r="J276" s="4"/>
@@ -3864,7 +3893,7 @@
       <c r="L276" s="3"/>
       <c r="P276" s="3"/>
     </row>
-    <row r="277" spans="6:16" ht="12.5">
+    <row r="277" spans="6:16" ht="13.2">
       <c r="F277" s="3"/>
       <c r="I277" s="4"/>
       <c r="J277" s="4"/>
@@ -3872,7 +3901,7 @@
       <c r="L277" s="3"/>
       <c r="P277" s="3"/>
     </row>
-    <row r="278" spans="6:16" ht="12.5">
+    <row r="278" spans="6:16" ht="13.2">
       <c r="F278" s="3"/>
       <c r="I278" s="4"/>
       <c r="J278" s="4"/>
@@ -3880,7 +3909,7 @@
       <c r="L278" s="3"/>
       <c r="P278" s="3"/>
     </row>
-    <row r="279" spans="6:16" ht="12.5">
+    <row r="279" spans="6:16" ht="13.2">
       <c r="F279" s="3"/>
       <c r="I279" s="4"/>
       <c r="J279" s="4"/>
@@ -3888,7 +3917,7 @@
       <c r="L279" s="3"/>
       <c r="P279" s="3"/>
     </row>
-    <row r="280" spans="6:16" ht="12.5">
+    <row r="280" spans="6:16" ht="13.2">
       <c r="F280" s="3"/>
       <c r="I280" s="4"/>
       <c r="J280" s="4"/>
@@ -3896,7 +3925,7 @@
       <c r="L280" s="3"/>
       <c r="P280" s="3"/>
     </row>
-    <row r="281" spans="6:16" ht="12.5">
+    <row r="281" spans="6:16" ht="13.2">
       <c r="F281" s="3"/>
       <c r="I281" s="4"/>
       <c r="J281" s="4"/>
@@ -3904,7 +3933,7 @@
       <c r="L281" s="3"/>
       <c r="P281" s="3"/>
     </row>
-    <row r="282" spans="6:16" ht="12.5">
+    <row r="282" spans="6:16" ht="13.2">
       <c r="F282" s="3"/>
       <c r="I282" s="4"/>
       <c r="J282" s="4"/>
@@ -3912,7 +3941,7 @@
       <c r="L282" s="3"/>
       <c r="P282" s="3"/>
     </row>
-    <row r="283" spans="6:16" ht="12.5">
+    <row r="283" spans="6:16" ht="13.2">
       <c r="F283" s="3"/>
       <c r="I283" s="4"/>
       <c r="J283" s="4"/>
@@ -3920,7 +3949,7 @@
       <c r="L283" s="3"/>
       <c r="P283" s="3"/>
     </row>
-    <row r="284" spans="6:16" ht="12.5">
+    <row r="284" spans="6:16" ht="13.2">
       <c r="F284" s="3"/>
       <c r="I284" s="4"/>
       <c r="J284" s="4"/>
@@ -3928,7 +3957,7 @@
       <c r="L284" s="3"/>
       <c r="P284" s="3"/>
     </row>
-    <row r="285" spans="6:16" ht="12.5">
+    <row r="285" spans="6:16" ht="13.2">
       <c r="F285" s="3"/>
       <c r="I285" s="4"/>
       <c r="J285" s="4"/>
@@ -3936,7 +3965,7 @@
       <c r="L285" s="3"/>
       <c r="P285" s="3"/>
     </row>
-    <row r="286" spans="6:16" ht="12.5">
+    <row r="286" spans="6:16" ht="13.2">
       <c r="F286" s="3"/>
       <c r="I286" s="4"/>
       <c r="J286" s="4"/>
@@ -3944,7 +3973,7 @@
       <c r="L286" s="3"/>
       <c r="P286" s="3"/>
     </row>
-    <row r="287" spans="6:16" ht="12.5">
+    <row r="287" spans="6:16" ht="13.2">
       <c r="F287" s="3"/>
       <c r="I287" s="4"/>
       <c r="J287" s="4"/>
@@ -3952,7 +3981,7 @@
       <c r="L287" s="3"/>
       <c r="P287" s="3"/>
     </row>
-    <row r="288" spans="6:16" ht="12.5">
+    <row r="288" spans="6:16" ht="13.2">
       <c r="F288" s="3"/>
       <c r="I288" s="4"/>
       <c r="J288" s="4"/>
@@ -3960,7 +3989,7 @@
       <c r="L288" s="3"/>
       <c r="P288" s="3"/>
     </row>
-    <row r="289" spans="6:16" ht="12.5">
+    <row r="289" spans="6:16" ht="13.2">
       <c r="F289" s="3"/>
       <c r="I289" s="4"/>
       <c r="J289" s="4"/>
@@ -3968,7 +3997,7 @@
       <c r="L289" s="3"/>
       <c r="P289" s="3"/>
     </row>
-    <row r="290" spans="6:16" ht="12.5">
+    <row r="290" spans="6:16" ht="13.2">
       <c r="F290" s="3"/>
       <c r="I290" s="4"/>
       <c r="J290" s="4"/>
@@ -3976,7 +4005,7 @@
       <c r="L290" s="3"/>
       <c r="P290" s="3"/>
     </row>
-    <row r="291" spans="6:16" ht="12.5">
+    <row r="291" spans="6:16" ht="13.2">
       <c r="F291" s="3"/>
       <c r="I291" s="4"/>
       <c r="J291" s="4"/>
@@ -3984,7 +4013,7 @@
       <c r="L291" s="3"/>
       <c r="P291" s="3"/>
     </row>
-    <row r="292" spans="6:16" ht="12.5">
+    <row r="292" spans="6:16" ht="13.2">
       <c r="F292" s="3"/>
       <c r="I292" s="4"/>
       <c r="J292" s="4"/>
@@ -3992,7 +4021,7 @@
       <c r="L292" s="3"/>
       <c r="P292" s="3"/>
     </row>
-    <row r="293" spans="6:16" ht="12.5">
+    <row r="293" spans="6:16" ht="13.2">
       <c r="F293" s="3"/>
       <c r="I293" s="4"/>
       <c r="J293" s="4"/>
@@ -4000,7 +4029,7 @@
       <c r="L293" s="3"/>
       <c r="P293" s="3"/>
     </row>
-    <row r="294" spans="6:16" ht="12.5">
+    <row r="294" spans="6:16" ht="13.2">
       <c r="F294" s="3"/>
       <c r="I294" s="4"/>
       <c r="J294" s="4"/>
@@ -4008,7 +4037,7 @@
       <c r="L294" s="3"/>
       <c r="P294" s="3"/>
     </row>
-    <row r="295" spans="6:16" ht="12.5">
+    <row r="295" spans="6:16" ht="13.2">
       <c r="F295" s="3"/>
       <c r="I295" s="4"/>
       <c r="J295" s="4"/>
@@ -4016,7 +4045,7 @@
       <c r="L295" s="3"/>
       <c r="P295" s="3"/>
     </row>
-    <row r="296" spans="6:16" ht="12.5">
+    <row r="296" spans="6:16" ht="13.2">
       <c r="F296" s="3"/>
       <c r="I296" s="4"/>
       <c r="J296" s="4"/>
@@ -4024,7 +4053,7 @@
       <c r="L296" s="3"/>
       <c r="P296" s="3"/>
     </row>
-    <row r="297" spans="6:16" ht="12.5">
+    <row r="297" spans="6:16" ht="13.2">
       <c r="F297" s="3"/>
       <c r="I297" s="4"/>
       <c r="J297" s="4"/>
@@ -4032,7 +4061,7 @@
       <c r="L297" s="3"/>
       <c r="P297" s="3"/>
     </row>
-    <row r="298" spans="6:16" ht="12.5">
+    <row r="298" spans="6:16" ht="13.2">
       <c r="F298" s="3"/>
       <c r="I298" s="4"/>
       <c r="J298" s="4"/>
@@ -4040,7 +4069,7 @@
       <c r="L298" s="3"/>
       <c r="P298" s="3"/>
     </row>
-    <row r="299" spans="6:16" ht="12.5">
+    <row r="299" spans="6:16" ht="13.2">
       <c r="F299" s="3"/>
       <c r="I299" s="4"/>
       <c r="J299" s="4"/>
@@ -4048,7 +4077,7 @@
       <c r="L299" s="3"/>
       <c r="P299" s="3"/>
     </row>
-    <row r="300" spans="6:16" ht="12.5">
+    <row r="300" spans="6:16" ht="13.2">
       <c r="F300" s="3"/>
       <c r="I300" s="4"/>
       <c r="J300" s="4"/>
@@ -4056,7 +4085,7 @@
       <c r="L300" s="3"/>
       <c r="P300" s="3"/>
     </row>
-    <row r="301" spans="6:16" ht="12.5">
+    <row r="301" spans="6:16" ht="13.2">
       <c r="F301" s="3"/>
       <c r="I301" s="4"/>
       <c r="J301" s="4"/>
@@ -4064,7 +4093,7 @@
       <c r="L301" s="3"/>
       <c r="P301" s="3"/>
     </row>
-    <row r="302" spans="6:16" ht="12.5">
+    <row r="302" spans="6:16" ht="13.2">
       <c r="F302" s="3"/>
       <c r="I302" s="4"/>
       <c r="J302" s="4"/>
@@ -4072,7 +4101,7 @@
       <c r="L302" s="3"/>
       <c r="P302" s="3"/>
     </row>
-    <row r="303" spans="6:16" ht="12.5">
+    <row r="303" spans="6:16" ht="13.2">
       <c r="F303" s="3"/>
       <c r="I303" s="4"/>
       <c r="J303" s="4"/>
@@ -4080,7 +4109,7 @@
       <c r="L303" s="3"/>
       <c r="P303" s="3"/>
     </row>
-    <row r="304" spans="6:16" ht="12.5">
+    <row r="304" spans="6:16" ht="13.2">
       <c r="F304" s="3"/>
       <c r="I304" s="4"/>
       <c r="J304" s="4"/>
@@ -4088,7 +4117,7 @@
       <c r="L304" s="3"/>
       <c r="P304" s="3"/>
     </row>
-    <row r="305" spans="6:16" ht="12.5">
+    <row r="305" spans="6:16" ht="13.2">
       <c r="F305" s="3"/>
       <c r="I305" s="4"/>
       <c r="J305" s="4"/>
@@ -4096,7 +4125,7 @@
       <c r="L305" s="3"/>
       <c r="P305" s="3"/>
     </row>
-    <row r="306" spans="6:16" ht="12.5">
+    <row r="306" spans="6:16" ht="13.2">
       <c r="F306" s="3"/>
       <c r="I306" s="4"/>
       <c r="J306" s="4"/>
@@ -4104,7 +4133,7 @@
       <c r="L306" s="3"/>
       <c r="P306" s="3"/>
     </row>
-    <row r="307" spans="6:16" ht="12.5">
+    <row r="307" spans="6:16" ht="13.2">
       <c r="F307" s="3"/>
       <c r="I307" s="4"/>
       <c r="J307" s="4"/>
@@ -4112,7 +4141,7 @@
       <c r="L307" s="3"/>
       <c r="P307" s="3"/>
     </row>
-    <row r="308" spans="6:16" ht="12.5">
+    <row r="308" spans="6:16" ht="13.2">
       <c r="F308" s="3"/>
       <c r="I308" s="4"/>
       <c r="J308" s="4"/>
@@ -4120,7 +4149,7 @@
       <c r="L308" s="3"/>
       <c r="P308" s="3"/>
     </row>
-    <row r="309" spans="6:16" ht="12.5">
+    <row r="309" spans="6:16" ht="13.2">
       <c r="F309" s="3"/>
       <c r="I309" s="4"/>
       <c r="J309" s="4"/>
@@ -4128,7 +4157,7 @@
       <c r="L309" s="3"/>
       <c r="P309" s="3"/>
     </row>
-    <row r="310" spans="6:16" ht="12.5">
+    <row r="310" spans="6:16" ht="13.2">
       <c r="F310" s="3"/>
       <c r="I310" s="4"/>
       <c r="J310" s="4"/>
@@ -4136,7 +4165,7 @@
       <c r="L310" s="3"/>
       <c r="P310" s="3"/>
     </row>
-    <row r="311" spans="6:16" ht="12.5">
+    <row r="311" spans="6:16" ht="13.2">
       <c r="F311" s="3"/>
       <c r="I311" s="4"/>
       <c r="J311" s="4"/>
@@ -4144,7 +4173,7 @@
       <c r="L311" s="3"/>
       <c r="P311" s="3"/>
     </row>
-    <row r="312" spans="6:16" ht="12.5">
+    <row r="312" spans="6:16" ht="13.2">
       <c r="F312" s="3"/>
       <c r="I312" s="4"/>
       <c r="J312" s="4"/>
@@ -4152,7 +4181,7 @@
       <c r="L312" s="3"/>
       <c r="P312" s="3"/>
     </row>
-    <row r="313" spans="6:16" ht="12.5">
+    <row r="313" spans="6:16" ht="13.2">
       <c r="F313" s="3"/>
       <c r="I313" s="4"/>
       <c r="J313" s="4"/>
@@ -4160,7 +4189,7 @@
       <c r="L313" s="3"/>
       <c r="P313" s="3"/>
     </row>
-    <row r="314" spans="6:16" ht="12.5">
+    <row r="314" spans="6:16" ht="13.2">
       <c r="F314" s="3"/>
       <c r="I314" s="4"/>
       <c r="J314" s="4"/>
@@ -4168,7 +4197,7 @@
       <c r="L314" s="3"/>
       <c r="P314" s="3"/>
     </row>
-    <row r="315" spans="6:16" ht="12.5">
+    <row r="315" spans="6:16" ht="13.2">
       <c r="F315" s="3"/>
       <c r="I315" s="4"/>
       <c r="J315" s="4"/>
@@ -4176,7 +4205,7 @@
       <c r="L315" s="3"/>
       <c r="P315" s="3"/>
     </row>
-    <row r="316" spans="6:16" ht="12.5">
+    <row r="316" spans="6:16" ht="13.2">
       <c r="F316" s="3"/>
       <c r="I316" s="4"/>
       <c r="J316" s="4"/>
@@ -4184,7 +4213,7 @@
       <c r="L316" s="3"/>
       <c r="P316" s="3"/>
     </row>
-    <row r="317" spans="6:16" ht="12.5">
+    <row r="317" spans="6:16" ht="13.2">
       <c r="F317" s="3"/>
       <c r="I317" s="4"/>
       <c r="J317" s="4"/>
@@ -4192,7 +4221,7 @@
       <c r="L317" s="3"/>
       <c r="P317" s="3"/>
     </row>
-    <row r="318" spans="6:16" ht="12.5">
+    <row r="318" spans="6:16" ht="13.2">
       <c r="F318" s="3"/>
       <c r="I318" s="4"/>
       <c r="J318" s="4"/>
@@ -4200,7 +4229,7 @@
       <c r="L318" s="3"/>
       <c r="P318" s="3"/>
     </row>
-    <row r="319" spans="6:16" ht="12.5">
+    <row r="319" spans="6:16" ht="13.2">
       <c r="F319" s="3"/>
       <c r="I319" s="4"/>
       <c r="J319" s="4"/>
@@ -4208,7 +4237,7 @@
       <c r="L319" s="3"/>
       <c r="P319" s="3"/>
     </row>
-    <row r="320" spans="6:16" ht="12.5">
+    <row r="320" spans="6:16" ht="13.2">
       <c r="F320" s="3"/>
       <c r="I320" s="4"/>
       <c r="J320" s="4"/>
@@ -4216,7 +4245,7 @@
       <c r="L320" s="3"/>
       <c r="P320" s="3"/>
     </row>
-    <row r="321" spans="6:16" ht="12.5">
+    <row r="321" spans="6:16" ht="13.2">
       <c r="F321" s="3"/>
       <c r="I321" s="4"/>
       <c r="J321" s="4"/>
@@ -4224,7 +4253,7 @@
       <c r="L321" s="3"/>
       <c r="P321" s="3"/>
     </row>
-    <row r="322" spans="6:16" ht="12.5">
+    <row r="322" spans="6:16" ht="13.2">
       <c r="F322" s="3"/>
       <c r="I322" s="4"/>
       <c r="J322" s="4"/>
@@ -4232,7 +4261,7 @@
       <c r="L322" s="3"/>
       <c r="P322" s="3"/>
     </row>
-    <row r="323" spans="6:16" ht="12.5">
+    <row r="323" spans="6:16" ht="13.2">
       <c r="F323" s="3"/>
       <c r="I323" s="4"/>
       <c r="J323" s="4"/>
@@ -4240,7 +4269,7 @@
       <c r="L323" s="3"/>
       <c r="P323" s="3"/>
     </row>
-    <row r="324" spans="6:16" ht="12.5">
+    <row r="324" spans="6:16" ht="13.2">
       <c r="F324" s="3"/>
       <c r="I324" s="4"/>
       <c r="J324" s="4"/>
@@ -4248,7 +4277,7 @@
       <c r="L324" s="3"/>
       <c r="P324" s="3"/>
     </row>
-    <row r="325" spans="6:16" ht="12.5">
+    <row r="325" spans="6:16" ht="13.2">
       <c r="F325" s="3"/>
       <c r="I325" s="4"/>
       <c r="J325" s="4"/>
@@ -4256,7 +4285,7 @@
       <c r="L325" s="3"/>
       <c r="P325" s="3"/>
     </row>
-    <row r="326" spans="6:16" ht="12.5">
+    <row r="326" spans="6:16" ht="13.2">
       <c r="F326" s="3"/>
       <c r="I326" s="4"/>
       <c r="J326" s="4"/>
@@ -4264,7 +4293,7 @@
       <c r="L326" s="3"/>
       <c r="P326" s="3"/>
     </row>
-    <row r="327" spans="6:16" ht="12.5">
+    <row r="327" spans="6:16" ht="13.2">
       <c r="F327" s="3"/>
       <c r="I327" s="4"/>
       <c r="J327" s="4"/>
@@ -4272,7 +4301,7 @@
       <c r="L327" s="3"/>
       <c r="P327" s="3"/>
     </row>
-    <row r="328" spans="6:16" ht="12.5">
+    <row r="328" spans="6:16" ht="13.2">
       <c r="F328" s="3"/>
       <c r="I328" s="4"/>
       <c r="J328" s="4"/>
@@ -4280,7 +4309,7 @@
       <c r="L328" s="3"/>
       <c r="P328" s="3"/>
     </row>
-    <row r="329" spans="6:16" ht="12.5">
+    <row r="329" spans="6:16" ht="13.2">
       <c r="F329" s="3"/>
       <c r="I329" s="4"/>
       <c r="J329" s="4"/>
@@ -4288,7 +4317,7 @@
       <c r="L329" s="3"/>
       <c r="P329" s="3"/>
     </row>
-    <row r="330" spans="6:16" ht="12.5">
+    <row r="330" spans="6:16" ht="13.2">
       <c r="F330" s="3"/>
       <c r="I330" s="4"/>
       <c r="J330" s="4"/>
@@ -4296,7 +4325,7 @@
       <c r="L330" s="3"/>
       <c r="P330" s="3"/>
     </row>
-    <row r="331" spans="6:16" ht="12.5">
+    <row r="331" spans="6:16" ht="13.2">
       <c r="F331" s="3"/>
       <c r="I331" s="4"/>
       <c r="J331" s="4"/>
@@ -4304,7 +4333,7 @@
       <c r="L331" s="3"/>
       <c r="P331" s="3"/>
     </row>
-    <row r="332" spans="6:16" ht="12.5">
+    <row r="332" spans="6:16" ht="13.2">
       <c r="F332" s="3"/>
       <c r="I332" s="4"/>
       <c r="J332" s="4"/>
@@ -4312,7 +4341,7 @@
       <c r="L332" s="3"/>
       <c r="P332" s="3"/>
     </row>
-    <row r="333" spans="6:16" ht="12.5">
+    <row r="333" spans="6:16" ht="13.2">
       <c r="F333" s="3"/>
       <c r="I333" s="4"/>
       <c r="J333" s="4"/>
@@ -4320,7 +4349,7 @@
       <c r="L333" s="3"/>
       <c r="P333" s="3"/>
     </row>
-    <row r="334" spans="6:16" ht="12.5">
+    <row r="334" spans="6:16" ht="13.2">
       <c r="F334" s="3"/>
       <c r="I334" s="4"/>
       <c r="J334" s="4"/>
@@ -4328,7 +4357,7 @@
       <c r="L334" s="3"/>
       <c r="P334" s="3"/>
     </row>
-    <row r="335" spans="6:16" ht="12.5">
+    <row r="335" spans="6:16" ht="13.2">
       <c r="F335" s="3"/>
       <c r="I335" s="4"/>
       <c r="J335" s="4"/>
@@ -4336,7 +4365,7 @@
       <c r="L335" s="3"/>
       <c r="P335" s="3"/>
     </row>
-    <row r="336" spans="6:16" ht="12.5">
+    <row r="336" spans="6:16" ht="13.2">
       <c r="F336" s="3"/>
       <c r="I336" s="4"/>
       <c r="J336" s="4"/>
@@ -4344,7 +4373,7 @@
       <c r="L336" s="3"/>
       <c r="P336" s="3"/>
     </row>
-    <row r="337" spans="6:16" ht="12.5">
+    <row r="337" spans="6:16" ht="13.2">
       <c r="F337" s="3"/>
       <c r="I337" s="4"/>
       <c r="J337" s="4"/>
@@ -4352,7 +4381,7 @@
       <c r="L337" s="3"/>
       <c r="P337" s="3"/>
     </row>
-    <row r="338" spans="6:16" ht="12.5">
+    <row r="338" spans="6:16" ht="13.2">
       <c r="F338" s="3"/>
       <c r="I338" s="4"/>
       <c r="J338" s="4"/>
@@ -4360,7 +4389,7 @@
       <c r="L338" s="3"/>
       <c r="P338" s="3"/>
     </row>
-    <row r="339" spans="6:16" ht="12.5">
+    <row r="339" spans="6:16" ht="13.2">
       <c r="F339" s="3"/>
       <c r="I339" s="4"/>
       <c r="J339" s="4"/>
@@ -4368,7 +4397,7 @@
       <c r="L339" s="3"/>
       <c r="P339" s="3"/>
     </row>
-    <row r="340" spans="6:16" ht="12.5">
+    <row r="340" spans="6:16" ht="13.2">
       <c r="F340" s="3"/>
       <c r="I340" s="4"/>
       <c r="J340" s="4"/>
@@ -4376,7 +4405,7 @@
       <c r="L340" s="3"/>
       <c r="P340" s="3"/>
     </row>
-    <row r="341" spans="6:16" ht="12.5">
+    <row r="341" spans="6:16" ht="13.2">
       <c r="F341" s="3"/>
       <c r="I341" s="4"/>
       <c r="J341" s="4"/>
@@ -4384,7 +4413,7 @@
       <c r="L341" s="3"/>
       <c r="P341" s="3"/>
     </row>
-    <row r="342" spans="6:16" ht="12.5">
+    <row r="342" spans="6:16" ht="13.2">
       <c r="F342" s="3"/>
       <c r="I342" s="4"/>
       <c r="J342" s="4"/>
@@ -4392,7 +4421,7 @@
       <c r="L342" s="3"/>
       <c r="P342" s="3"/>
     </row>
-    <row r="343" spans="6:16" ht="12.5">
+    <row r="343" spans="6:16" ht="13.2">
       <c r="F343" s="3"/>
       <c r="I343" s="4"/>
       <c r="J343" s="4"/>
@@ -4400,7 +4429,7 @@
       <c r="L343" s="3"/>
       <c r="P343" s="3"/>
     </row>
-    <row r="344" spans="6:16" ht="12.5">
+    <row r="344" spans="6:16" ht="13.2">
       <c r="F344" s="3"/>
       <c r="I344" s="4"/>
       <c r="J344" s="4"/>
@@ -4408,7 +4437,7 @@
       <c r="L344" s="3"/>
       <c r="P344" s="3"/>
     </row>
-    <row r="345" spans="6:16" ht="12.5">
+    <row r="345" spans="6:16" ht="13.2">
       <c r="F345" s="3"/>
       <c r="I345" s="4"/>
       <c r="J345" s="4"/>
@@ -4416,7 +4445,7 @@
       <c r="L345" s="3"/>
       <c r="P345" s="3"/>
     </row>
-    <row r="346" spans="6:16" ht="12.5">
+    <row r="346" spans="6:16" ht="13.2">
       <c r="F346" s="3"/>
       <c r="I346" s="4"/>
       <c r="J346" s="4"/>
@@ -4424,7 +4453,7 @@
       <c r="L346" s="3"/>
       <c r="P346" s="3"/>
     </row>
-    <row r="347" spans="6:16" ht="12.5">
+    <row r="347" spans="6:16" ht="13.2">
       <c r="F347" s="3"/>
       <c r="I347" s="4"/>
       <c r="J347" s="4"/>
@@ -4432,7 +4461,7 @@
       <c r="L347" s="3"/>
       <c r="P347" s="3"/>
     </row>
-    <row r="348" spans="6:16" ht="12.5">
+    <row r="348" spans="6:16" ht="13.2">
       <c r="F348" s="3"/>
       <c r="I348" s="4"/>
       <c r="J348" s="4"/>
@@ -4440,7 +4469,7 @@
       <c r="L348" s="3"/>
       <c r="P348" s="3"/>
     </row>
-    <row r="349" spans="6:16" ht="12.5">
+    <row r="349" spans="6:16" ht="13.2">
       <c r="F349" s="3"/>
       <c r="I349" s="4"/>
       <c r="J349" s="4"/>
@@ -4448,7 +4477,7 @@
       <c r="L349" s="3"/>
       <c r="P349" s="3"/>
     </row>
-    <row r="350" spans="6:16" ht="12.5">
+    <row r="350" spans="6:16" ht="13.2">
       <c r="F350" s="3"/>
       <c r="I350" s="4"/>
       <c r="J350" s="4"/>
@@ -4456,7 +4485,7 @@
       <c r="L350" s="3"/>
       <c r="P350" s="3"/>
     </row>
-    <row r="351" spans="6:16" ht="12.5">
+    <row r="351" spans="6:16" ht="13.2">
       <c r="F351" s="3"/>
       <c r="I351" s="4"/>
       <c r="J351" s="4"/>
@@ -4464,7 +4493,7 @@
       <c r="L351" s="3"/>
       <c r="P351" s="3"/>
     </row>
-    <row r="352" spans="6:16" ht="12.5">
+    <row r="352" spans="6:16" ht="13.2">
       <c r="F352" s="3"/>
       <c r="I352" s="4"/>
       <c r="J352" s="4"/>
@@ -4472,7 +4501,7 @@
       <c r="L352" s="3"/>
       <c r="P352" s="3"/>
     </row>
-    <row r="353" spans="6:16" ht="12.5">
+    <row r="353" spans="6:16" ht="13.2">
       <c r="F353" s="3"/>
       <c r="I353" s="4"/>
       <c r="J353" s="4"/>
@@ -4480,7 +4509,7 @@
       <c r="L353" s="3"/>
       <c r="P353" s="3"/>
     </row>
-    <row r="354" spans="6:16" ht="12.5">
+    <row r="354" spans="6:16" ht="13.2">
       <c r="F354" s="3"/>
       <c r="I354" s="4"/>
       <c r="J354" s="4"/>
@@ -4488,7 +4517,7 @@
       <c r="L354" s="3"/>
       <c r="P354" s="3"/>
     </row>
-    <row r="355" spans="6:16" ht="12.5">
+    <row r="355" spans="6:16" ht="13.2">
       <c r="F355" s="3"/>
       <c r="I355" s="4"/>
       <c r="J355" s="4"/>
@@ -4496,7 +4525,7 @@
       <c r="L355" s="3"/>
       <c r="P355" s="3"/>
     </row>
-    <row r="356" spans="6:16" ht="12.5">
+    <row r="356" spans="6:16" ht="13.2">
       <c r="F356" s="3"/>
       <c r="I356" s="4"/>
       <c r="J356" s="4"/>
@@ -4504,7 +4533,7 @@
       <c r="L356" s="3"/>
       <c r="P356" s="3"/>
     </row>
-    <row r="357" spans="6:16" ht="12.5">
+    <row r="357" spans="6:16" ht="13.2">
       <c r="F357" s="3"/>
       <c r="I357" s="4"/>
       <c r="J357" s="4"/>
@@ -4512,7 +4541,7 @@
       <c r="L357" s="3"/>
       <c r="P357" s="3"/>
     </row>
-    <row r="358" spans="6:16" ht="12.5">
+    <row r="358" spans="6:16" ht="13.2">
       <c r="F358" s="3"/>
       <c r="I358" s="4"/>
       <c r="J358" s="4"/>
@@ -4520,7 +4549,7 @@
       <c r="L358" s="3"/>
       <c r="P358" s="3"/>
     </row>
-    <row r="359" spans="6:16" ht="12.5">
+    <row r="359" spans="6:16" ht="13.2">
       <c r="F359" s="3"/>
       <c r="I359" s="4"/>
       <c r="J359" s="4"/>
@@ -4528,7 +4557,7 @@
       <c r="L359" s="3"/>
       <c r="P359" s="3"/>
     </row>
-    <row r="360" spans="6:16" ht="12.5">
+    <row r="360" spans="6:16" ht="13.2">
       <c r="F360" s="3"/>
       <c r="I360" s="4"/>
       <c r="J360" s="4"/>
@@ -4536,7 +4565,7 @@
       <c r="L360" s="3"/>
       <c r="P360" s="3"/>
     </row>
-    <row r="361" spans="6:16" ht="12.5">
+    <row r="361" spans="6:16" ht="13.2">
       <c r="F361" s="3"/>
       <c r="I361" s="4"/>
       <c r="J361" s="4"/>
@@ -4544,7 +4573,7 @@
       <c r="L361" s="3"/>
       <c r="P361" s="3"/>
     </row>
-    <row r="362" spans="6:16" ht="12.5">
+    <row r="362" spans="6:16" ht="13.2">
       <c r="F362" s="3"/>
       <c r="I362" s="4"/>
       <c r="J362" s="4"/>
@@ -4552,7 +4581,7 @@
       <c r="L362" s="3"/>
       <c r="P362" s="3"/>
     </row>
-    <row r="363" spans="6:16" ht="12.5">
+    <row r="363" spans="6:16" ht="13.2">
       <c r="F363" s="3"/>
       <c r="I363" s="4"/>
       <c r="J363" s="4"/>
@@ -4560,7 +4589,7 @@
       <c r="L363" s="3"/>
       <c r="P363" s="3"/>
     </row>
-    <row r="364" spans="6:16" ht="12.5">
+    <row r="364" spans="6:16" ht="13.2">
       <c r="F364" s="3"/>
       <c r="I364" s="4"/>
       <c r="J364" s="4"/>
@@ -4568,7 +4597,7 @@
       <c r="L364" s="3"/>
       <c r="P364" s="3"/>
     </row>
-    <row r="365" spans="6:16" ht="12.5">
+    <row r="365" spans="6:16" ht="13.2">
       <c r="F365" s="3"/>
       <c r="I365" s="4"/>
       <c r="J365" s="4"/>
@@ -4576,7 +4605,7 @@
       <c r="L365" s="3"/>
       <c r="P365" s="3"/>
     </row>
-    <row r="366" spans="6:16" ht="12.5">
+    <row r="366" spans="6:16" ht="13.2">
       <c r="F366" s="3"/>
       <c r="I366" s="4"/>
       <c r="J366" s="4"/>
@@ -4584,7 +4613,7 @@
       <c r="L366" s="3"/>
       <c r="P366" s="3"/>
     </row>
-    <row r="367" spans="6:16" ht="12.5">
+    <row r="367" spans="6:16" ht="13.2">
       <c r="F367" s="3"/>
       <c r="I367" s="4"/>
       <c r="J367" s="4"/>
@@ -4592,7 +4621,7 @@
       <c r="L367" s="3"/>
       <c r="P367" s="3"/>
     </row>
-    <row r="368" spans="6:16" ht="12.5">
+    <row r="368" spans="6:16" ht="13.2">
       <c r="F368" s="3"/>
       <c r="I368" s="4"/>
       <c r="J368" s="4"/>
@@ -4600,7 +4629,7 @@
       <c r="L368" s="3"/>
       <c r="P368" s="3"/>
     </row>
-    <row r="369" spans="6:16" ht="12.5">
+    <row r="369" spans="6:16" ht="13.2">
       <c r="F369" s="3"/>
       <c r="I369" s="4"/>
       <c r="J369" s="4"/>
@@ -4608,7 +4637,7 @@
       <c r="L369" s="3"/>
       <c r="P369" s="3"/>
     </row>
-    <row r="370" spans="6:16" ht="12.5">
+    <row r="370" spans="6:16" ht="13.2">
       <c r="F370" s="3"/>
       <c r="I370" s="4"/>
       <c r="J370" s="4"/>
@@ -4616,7 +4645,7 @@
       <c r="L370" s="3"/>
       <c r="P370" s="3"/>
     </row>
-    <row r="371" spans="6:16" ht="12.5">
+    <row r="371" spans="6:16" ht="13.2">
       <c r="F371" s="3"/>
       <c r="I371" s="4"/>
       <c r="J371" s="4"/>
@@ -4624,7 +4653,7 @@
       <c r="L371" s="3"/>
       <c r="P371" s="3"/>
     </row>
-    <row r="372" spans="6:16" ht="12.5">
+    <row r="372" spans="6:16" ht="13.2">
       <c r="F372" s="3"/>
       <c r="I372" s="4"/>
       <c r="J372" s="4"/>
@@ -4632,7 +4661,7 @@
       <c r="L372" s="3"/>
       <c r="P372" s="3"/>
     </row>
-    <row r="373" spans="6:16" ht="12.5">
+    <row r="373" spans="6:16" ht="13.2">
       <c r="F373" s="3"/>
       <c r="I373" s="4"/>
       <c r="J373" s="4"/>
@@ -4640,7 +4669,7 @@
       <c r="L373" s="3"/>
       <c r="P373" s="3"/>
     </row>
-    <row r="374" spans="6:16" ht="12.5">
+    <row r="374" spans="6:16" ht="13.2">
       <c r="F374" s="3"/>
       <c r="I374" s="4"/>
       <c r="J374" s="4"/>
@@ -4648,7 +4677,7 @@
       <c r="L374" s="3"/>
       <c r="P374" s="3"/>
     </row>
-    <row r="375" spans="6:16" ht="12.5">
+    <row r="375" spans="6:16" ht="13.2">
       <c r="F375" s="3"/>
       <c r="I375" s="4"/>
       <c r="J375" s="4"/>
@@ -4656,7 +4685,7 @@
       <c r="L375" s="3"/>
       <c r="P375" s="3"/>
     </row>
-    <row r="376" spans="6:16" ht="12.5">
+    <row r="376" spans="6:16" ht="13.2">
       <c r="F376" s="3"/>
       <c r="I376" s="4"/>
       <c r="J376" s="4"/>
@@ -4664,7 +4693,7 @@
       <c r="L376" s="3"/>
       <c r="P376" s="3"/>
     </row>
-    <row r="377" spans="6:16" ht="12.5">
+    <row r="377" spans="6:16" ht="13.2">
       <c r="F377" s="3"/>
       <c r="I377" s="4"/>
       <c r="J377" s="4"/>
@@ -4672,7 +4701,7 @@
       <c r="L377" s="3"/>
       <c r="P377" s="3"/>
     </row>
-    <row r="378" spans="6:16" ht="12.5">
+    <row r="378" spans="6:16" ht="13.2">
       <c r="F378" s="3"/>
       <c r="I378" s="4"/>
       <c r="J378" s="4"/>
@@ -4680,7 +4709,7 @@
       <c r="L378" s="3"/>
       <c r="P378" s="3"/>
     </row>
-    <row r="379" spans="6:16" ht="12.5">
+    <row r="379" spans="6:16" ht="13.2">
       <c r="F379" s="3"/>
       <c r="I379" s="4"/>
       <c r="J379" s="4"/>
@@ -4688,7 +4717,7 @@
       <c r="L379" s="3"/>
       <c r="P379" s="3"/>
     </row>
-    <row r="380" spans="6:16" ht="12.5">
+    <row r="380" spans="6:16" ht="13.2">
       <c r="F380" s="3"/>
       <c r="I380" s="4"/>
       <c r="J380" s="4"/>
@@ -4696,7 +4725,7 @@
       <c r="L380" s="3"/>
       <c r="P380" s="3"/>
     </row>
-    <row r="381" spans="6:16" ht="12.5">
+    <row r="381" spans="6:16" ht="13.2">
       <c r="F381" s="3"/>
       <c r="I381" s="4"/>
       <c r="J381" s="4"/>
@@ -4704,7 +4733,7 @@
       <c r="L381" s="3"/>
       <c r="P381" s="3"/>
     </row>
-    <row r="382" spans="6:16" ht="12.5">
+    <row r="382" spans="6:16" ht="13.2">
       <c r="F382" s="3"/>
       <c r="I382" s="4"/>
       <c r="J382" s="4"/>
@@ -4712,7 +4741,7 @@
       <c r="L382" s="3"/>
       <c r="P382" s="3"/>
     </row>
-    <row r="383" spans="6:16" ht="12.5">
+    <row r="383" spans="6:16" ht="13.2">
       <c r="F383" s="3"/>
       <c r="I383" s="4"/>
       <c r="J383" s="4"/>
@@ -4720,7 +4749,7 @@
       <c r="L383" s="3"/>
       <c r="P383" s="3"/>
     </row>
-    <row r="384" spans="6:16" ht="12.5">
+    <row r="384" spans="6:16" ht="13.2">
       <c r="F384" s="3"/>
       <c r="I384" s="4"/>
       <c r="J384" s="4"/>
@@ -4728,7 +4757,7 @@
       <c r="L384" s="3"/>
       <c r="P384" s="3"/>
     </row>
-    <row r="385" spans="6:16" ht="12.5">
+    <row r="385" spans="6:16" ht="13.2">
       <c r="F385" s="3"/>
       <c r="I385" s="4"/>
       <c r="J385" s="4"/>
@@ -4736,7 +4765,7 @@
       <c r="L385" s="3"/>
       <c r="P385" s="3"/>
     </row>
-    <row r="386" spans="6:16" ht="12.5">
+    <row r="386" spans="6:16" ht="13.2">
       <c r="F386" s="3"/>
       <c r="I386" s="4"/>
       <c r="J386" s="4"/>
@@ -4744,7 +4773,7 @@
       <c r="L386" s="3"/>
       <c r="P386" s="3"/>
     </row>
-    <row r="387" spans="6:16" ht="12.5">
+    <row r="387" spans="6:16" ht="13.2">
       <c r="F387" s="3"/>
       <c r="I387" s="4"/>
       <c r="J387" s="4"/>
@@ -4752,7 +4781,7 @@
       <c r="L387" s="3"/>
       <c r="P387" s="3"/>
     </row>
-    <row r="388" spans="6:16" ht="12.5">
+    <row r="388" spans="6:16" ht="13.2">
       <c r="F388" s="3"/>
       <c r="I388" s="4"/>
       <c r="J388" s="4"/>
@@ -4760,7 +4789,7 @@
       <c r="L388" s="3"/>
       <c r="P388" s="3"/>
     </row>
-    <row r="389" spans="6:16" ht="12.5">
+    <row r="389" spans="6:16" ht="13.2">
       <c r="F389" s="3"/>
       <c r="I389" s="4"/>
       <c r="J389" s="4"/>
@@ -4768,7 +4797,7 @@
       <c r="L389" s="3"/>
       <c r="P389" s="3"/>
     </row>
-    <row r="390" spans="6:16" ht="12.5">
+    <row r="390" spans="6:16" ht="13.2">
       <c r="F390" s="3"/>
       <c r="I390" s="4"/>
       <c r="J390" s="4"/>
@@ -4776,7 +4805,7 @@
       <c r="L390" s="3"/>
       <c r="P390" s="3"/>
     </row>
-    <row r="391" spans="6:16" ht="12.5">
+    <row r="391" spans="6:16" ht="13.2">
       <c r="F391" s="3"/>
       <c r="I391" s="4"/>
       <c r="J391" s="4"/>
@@ -4784,7 +4813,7 @@
       <c r="L391" s="3"/>
       <c r="P391" s="3"/>
     </row>
-    <row r="392" spans="6:16" ht="12.5">
+    <row r="392" spans="6:16" ht="13.2">
       <c r="F392" s="3"/>
       <c r="I392" s="4"/>
       <c r="J392" s="4"/>
@@ -4792,7 +4821,7 @@
       <c r="L392" s="3"/>
       <c r="P392" s="3"/>
     </row>
-    <row r="393" spans="6:16" ht="12.5">
+    <row r="393" spans="6:16" ht="13.2">
       <c r="F393" s="3"/>
       <c r="I393" s="4"/>
       <c r="J393" s="4"/>
@@ -4800,7 +4829,7 @@
       <c r="L393" s="3"/>
       <c r="P393" s="3"/>
     </row>
-    <row r="394" spans="6:16" ht="12.5">
+    <row r="394" spans="6:16" ht="13.2">
       <c r="F394" s="3"/>
       <c r="I394" s="4"/>
       <c r="J394" s="4"/>
@@ -4808,7 +4837,7 @@
       <c r="L394" s="3"/>
       <c r="P394" s="3"/>
     </row>
-    <row r="395" spans="6:16" ht="12.5">
+    <row r="395" spans="6:16" ht="13.2">
       <c r="F395" s="3"/>
       <c r="I395" s="4"/>
       <c r="J395" s="4"/>
@@ -4816,7 +4845,7 @@
       <c r="L395" s="3"/>
       <c r="P395" s="3"/>
     </row>
-    <row r="396" spans="6:16" ht="12.5">
+    <row r="396" spans="6:16" ht="13.2">
       <c r="F396" s="3"/>
       <c r="I396" s="4"/>
       <c r="J396" s="4"/>
@@ -4824,7 +4853,7 @@
       <c r="L396" s="3"/>
       <c r="P396" s="3"/>
     </row>
-    <row r="397" spans="6:16" ht="12.5">
+    <row r="397" spans="6:16" ht="13.2">
       <c r="F397" s="3"/>
       <c r="I397" s="4"/>
       <c r="J397" s="4"/>
@@ -4832,7 +4861,7 @@
       <c r="L397" s="3"/>
       <c r="P397" s="3"/>
     </row>
-    <row r="398" spans="6:16" ht="12.5">
+    <row r="398" spans="6:16" ht="13.2">
       <c r="F398" s="3"/>
       <c r="I398" s="4"/>
       <c r="J398" s="4"/>
@@ -4840,7 +4869,7 @@
       <c r="L398" s="3"/>
       <c r="P398" s="3"/>
     </row>
-    <row r="399" spans="6:16" ht="12.5">
+    <row r="399" spans="6:16" ht="13.2">
       <c r="F399" s="3"/>
       <c r="I399" s="4"/>
       <c r="J399" s="4"/>
@@ -4848,7 +4877,7 @@
       <c r="L399" s="3"/>
       <c r="P399" s="3"/>
     </row>
-    <row r="400" spans="6:16" ht="12.5">
+    <row r="400" spans="6:16" ht="13.2">
       <c r="F400" s="3"/>
       <c r="I400" s="4"/>
       <c r="J400" s="4"/>
@@ -4856,7 +4885,7 @@
       <c r="L400" s="3"/>
       <c r="P400" s="3"/>
     </row>
-    <row r="401" spans="6:16" ht="12.5">
+    <row r="401" spans="6:16" ht="13.2">
       <c r="F401" s="3"/>
       <c r="I401" s="4"/>
       <c r="J401" s="4"/>
@@ -4864,7 +4893,7 @@
       <c r="L401" s="3"/>
       <c r="P401" s="3"/>
     </row>
-    <row r="402" spans="6:16" ht="12.5">
+    <row r="402" spans="6:16" ht="13.2">
       <c r="F402" s="3"/>
       <c r="I402" s="4"/>
       <c r="J402" s="4"/>
@@ -4872,7 +4901,7 @@
       <c r="L402" s="3"/>
       <c r="P402" s="3"/>
     </row>
-    <row r="403" spans="6:16" ht="12.5">
+    <row r="403" spans="6:16" ht="13.2">
       <c r="F403" s="3"/>
       <c r="I403" s="4"/>
       <c r="J403" s="4"/>
@@ -4880,7 +4909,7 @@
       <c r="L403" s="3"/>
       <c r="P403" s="3"/>
     </row>
-    <row r="404" spans="6:16" ht="12.5">
+    <row r="404" spans="6:16" ht="13.2">
       <c r="F404" s="3"/>
       <c r="I404" s="4"/>
       <c r="J404" s="4"/>
@@ -4888,7 +4917,7 @@
       <c r="L404" s="3"/>
       <c r="P404" s="3"/>
     </row>
-    <row r="405" spans="6:16" ht="12.5">
+    <row r="405" spans="6:16" ht="13.2">
       <c r="F405" s="3"/>
       <c r="I405" s="4"/>
       <c r="J405" s="4"/>
@@ -4896,7 +4925,7 @@
       <c r="L405" s="3"/>
       <c r="P405" s="3"/>
     </row>
-    <row r="406" spans="6:16" ht="12.5">
+    <row r="406" spans="6:16" ht="13.2">
       <c r="F406" s="3"/>
       <c r="I406" s="4"/>
       <c r="J406" s="4"/>
@@ -4904,7 +4933,7 @@
       <c r="L406" s="3"/>
       <c r="P406" s="3"/>
     </row>
-    <row r="407" spans="6:16" ht="12.5">
+    <row r="407" spans="6:16" ht="13.2">
       <c r="F407" s="3"/>
       <c r="I407" s="4"/>
       <c r="J407" s="4"/>
@@ -4912,7 +4941,7 @@
       <c r="L407" s="3"/>
       <c r="P407" s="3"/>
     </row>
-    <row r="408" spans="6:16" ht="12.5">
+    <row r="408" spans="6:16" ht="13.2">
       <c r="F408" s="3"/>
       <c r="I408" s="4"/>
       <c r="J408" s="4"/>
@@ -4920,7 +4949,7 @@
       <c r="L408" s="3"/>
       <c r="P408" s="3"/>
     </row>
-    <row r="409" spans="6:16" ht="12.5">
+    <row r="409" spans="6:16" ht="13.2">
       <c r="F409" s="3"/>
       <c r="I409" s="4"/>
       <c r="J409" s="4"/>
@@ -4928,7 +4957,7 @@
       <c r="L409" s="3"/>
       <c r="P409" s="3"/>
     </row>
-    <row r="410" spans="6:16" ht="12.5">
+    <row r="410" spans="6:16" ht="13.2">
       <c r="F410" s="3"/>
       <c r="I410" s="4"/>
       <c r="J410" s="4"/>
@@ -4936,7 +4965,7 @@
       <c r="L410" s="3"/>
       <c r="P410" s="3"/>
     </row>
-    <row r="411" spans="6:16" ht="12.5">
+    <row r="411" spans="6:16" ht="13.2">
       <c r="F411" s="3"/>
       <c r="I411" s="4"/>
       <c r="J411" s="4"/>
@@ -4944,7 +4973,7 @@
       <c r="L411" s="3"/>
       <c r="P411" s="3"/>
     </row>
-    <row r="412" spans="6:16" ht="12.5">
+    <row r="412" spans="6:16" ht="13.2">
       <c r="F412" s="3"/>
       <c r="I412" s="4"/>
       <c r="J412" s="4"/>
@@ -4952,7 +4981,7 @@
       <c r="L412" s="3"/>
       <c r="P412" s="3"/>
     </row>
-    <row r="413" spans="6:16" ht="12.5">
+    <row r="413" spans="6:16" ht="13.2">
       <c r="F413" s="3"/>
       <c r="I413" s="4"/>
       <c r="J413" s="4"/>
@@ -4960,7 +4989,7 @@
       <c r="L413" s="3"/>
       <c r="P413" s="3"/>
     </row>
-    <row r="414" spans="6:16" ht="12.5">
+    <row r="414" spans="6:16" ht="13.2">
       <c r="F414" s="3"/>
       <c r="I414" s="4"/>
       <c r="J414" s="4"/>
@@ -4968,7 +4997,7 @@
       <c r="L414" s="3"/>
       <c r="P414" s="3"/>
     </row>
-    <row r="415" spans="6:16" ht="12.5">
+    <row r="415" spans="6:16" ht="13.2">
       <c r="F415" s="3"/>
       <c r="I415" s="4"/>
       <c r="J415" s="4"/>
@@ -4976,7 +5005,7 @@
       <c r="L415" s="3"/>
       <c r="P415" s="3"/>
     </row>
-    <row r="416" spans="6:16" ht="12.5">
+    <row r="416" spans="6:16" ht="13.2">
       <c r="F416" s="3"/>
       <c r="I416" s="4"/>
       <c r="J416" s="4"/>
@@ -4984,7 +5013,7 @@
       <c r="L416" s="3"/>
       <c r="P416" s="3"/>
     </row>
-    <row r="417" spans="6:16" ht="12.5">
+    <row r="417" spans="6:16" ht="13.2">
       <c r="F417" s="3"/>
       <c r="I417" s="4"/>
       <c r="J417" s="4"/>
@@ -4992,7 +5021,7 @@
       <c r="L417" s="3"/>
       <c r="P417" s="3"/>
     </row>
-    <row r="418" spans="6:16" ht="12.5">
+    <row r="418" spans="6:16" ht="13.2">
       <c r="F418" s="3"/>
       <c r="I418" s="4"/>
       <c r="J418" s="4"/>
@@ -5000,7 +5029,7 @@
       <c r="L418" s="3"/>
       <c r="P418" s="3"/>
     </row>
-    <row r="419" spans="6:16" ht="12.5">
+    <row r="419" spans="6:16" ht="13.2">
       <c r="F419" s="3"/>
       <c r="I419" s="4"/>
       <c r="J419" s="4"/>
@@ -5008,7 +5037,7 @@
       <c r="L419" s="3"/>
       <c r="P419" s="3"/>
     </row>
-    <row r="420" spans="6:16" ht="12.5">
+    <row r="420" spans="6:16" ht="13.2">
       <c r="F420" s="3"/>
       <c r="I420" s="4"/>
       <c r="J420" s="4"/>
@@ -5016,7 +5045,7 @@
       <c r="L420" s="3"/>
       <c r="P420" s="3"/>
     </row>
-    <row r="421" spans="6:16" ht="12.5">
+    <row r="421" spans="6:16" ht="13.2">
       <c r="F421" s="3"/>
       <c r="I421" s="4"/>
       <c r="J421" s="4"/>
@@ -5024,7 +5053,7 @@
       <c r="L421" s="3"/>
       <c r="P421" s="3"/>
     </row>
-    <row r="422" spans="6:16" ht="12.5">
+    <row r="422" spans="6:16" ht="13.2">
       <c r="F422" s="3"/>
       <c r="I422" s="4"/>
       <c r="J422" s="4"/>
@@ -5032,7 +5061,7 @@
       <c r="L422" s="3"/>
       <c r="P422" s="3"/>
     </row>
-    <row r="423" spans="6:16" ht="12.5">
+    <row r="423" spans="6:16" ht="13.2">
       <c r="F423" s="3"/>
       <c r="I423" s="4"/>
       <c r="J423" s="4"/>
@@ -5040,7 +5069,7 @@
       <c r="L423" s="3"/>
       <c r="P423" s="3"/>
     </row>
-    <row r="424" spans="6:16" ht="12.5">
+    <row r="424" spans="6:16" ht="13.2">
       <c r="F424" s="3"/>
       <c r="I424" s="4"/>
       <c r="J424" s="4"/>
@@ -5048,7 +5077,7 @@
       <c r="L424" s="3"/>
       <c r="P424" s="3"/>
     </row>
-    <row r="425" spans="6:16" ht="12.5">
+    <row r="425" spans="6:16" ht="13.2">
       <c r="F425" s="3"/>
       <c r="I425" s="4"/>
       <c r="J425" s="4"/>
@@ -5056,7 +5085,7 @@
       <c r="L425" s="3"/>
       <c r="P425" s="3"/>
     </row>
-    <row r="426" spans="6:16" ht="12.5">
+    <row r="426" spans="6:16" ht="13.2">
       <c r="F426" s="3"/>
       <c r="I426" s="4"/>
       <c r="J426" s="4"/>
@@ -5064,7 +5093,7 @@
       <c r="L426" s="3"/>
       <c r="P426" s="3"/>
     </row>
-    <row r="427" spans="6:16" ht="12.5">
+    <row r="427" spans="6:16" ht="13.2">
       <c r="F427" s="3"/>
       <c r="I427" s="4"/>
       <c r="J427" s="4"/>
@@ -5072,7 +5101,7 @@
       <c r="L427" s="3"/>
       <c r="P427" s="3"/>
     </row>
-    <row r="428" spans="6:16" ht="12.5">
+    <row r="428" spans="6:16" ht="13.2">
       <c r="F428" s="3"/>
       <c r="I428" s="4"/>
       <c r="J428" s="4"/>
@@ -5080,7 +5109,7 @@
       <c r="L428" s="3"/>
       <c r="P428" s="3"/>
     </row>
-    <row r="429" spans="6:16" ht="12.5">
+    <row r="429" spans="6:16" ht="13.2">
       <c r="F429" s="3"/>
       <c r="I429" s="4"/>
       <c r="J429" s="4"/>
@@ -5088,7 +5117,7 @@
       <c r="L429" s="3"/>
       <c r="P429" s="3"/>
     </row>
-    <row r="430" spans="6:16" ht="12.5">
+    <row r="430" spans="6:16" ht="13.2">
       <c r="F430" s="3"/>
       <c r="I430" s="4"/>
       <c r="J430" s="4"/>
@@ -5096,7 +5125,7 @@
       <c r="L430" s="3"/>
       <c r="P430" s="3"/>
     </row>
-    <row r="431" spans="6:16" ht="12.5">
+    <row r="431" spans="6:16" ht="13.2">
       <c r="F431" s="3"/>
       <c r="I431" s="4"/>
       <c r="J431" s="4"/>
@@ -5104,7 +5133,7 @@
       <c r="L431" s="3"/>
       <c r="P431" s="3"/>
     </row>
-    <row r="432" spans="6:16" ht="12.5">
+    <row r="432" spans="6:16" ht="13.2">
       <c r="F432" s="3"/>
       <c r="I432" s="4"/>
       <c r="J432" s="4"/>
@@ -5112,7 +5141,7 @@
       <c r="L432" s="3"/>
       <c r="P432" s="3"/>
     </row>
-    <row r="433" spans="6:16" ht="12.5">
+    <row r="433" spans="6:16" ht="13.2">
       <c r="F433" s="3"/>
       <c r="I433" s="4"/>
       <c r="J433" s="4"/>
@@ -5120,7 +5149,7 @@
       <c r="L433" s="3"/>
       <c r="P433" s="3"/>
     </row>
-    <row r="434" spans="6:16" ht="12.5">
+    <row r="434" spans="6:16" ht="13.2">
       <c r="F434" s="3"/>
       <c r="I434" s="4"/>
       <c r="J434" s="4"/>
@@ -5128,7 +5157,7 @@
       <c r="L434" s="3"/>
       <c r="P434" s="3"/>
     </row>
-    <row r="435" spans="6:16" ht="12.5">
+    <row r="435" spans="6:16" ht="13.2">
       <c r="F435" s="3"/>
       <c r="I435" s="4"/>
       <c r="J435" s="4"/>
@@ -5136,7 +5165,7 @@
       <c r="L435" s="3"/>
       <c r="P435" s="3"/>
     </row>
-    <row r="436" spans="6:16" ht="12.5">
+    <row r="436" spans="6:16" ht="13.2">
       <c r="F436" s="3"/>
       <c r="I436" s="4"/>
       <c r="J436" s="4"/>
@@ -5144,7 +5173,7 @@
       <c r="L436" s="3"/>
       <c r="P436" s="3"/>
     </row>
-    <row r="437" spans="6:16" ht="12.5">
+    <row r="437" spans="6:16" ht="13.2">
       <c r="F437" s="3"/>
       <c r="I437" s="4"/>
       <c r="J437" s="4"/>
@@ -5152,7 +5181,7 @@
       <c r="L437" s="3"/>
       <c r="P437" s="3"/>
     </row>
-    <row r="438" spans="6:16" ht="12.5">
+    <row r="438" spans="6:16" ht="13.2">
       <c r="F438" s="3"/>
       <c r="I438" s="4"/>
       <c r="J438" s="4"/>
@@ -5160,7 +5189,7 @@
       <c r="L438" s="3"/>
       <c r="P438" s="3"/>
     </row>
-    <row r="439" spans="6:16" ht="12.5">
+    <row r="439" spans="6:16" ht="13.2">
       <c r="F439" s="3"/>
       <c r="I439" s="4"/>
       <c r="J439" s="4"/>
@@ -5168,7 +5197,7 @@
       <c r="L439" s="3"/>
       <c r="P439" s="3"/>
     </row>
-    <row r="440" spans="6:16" ht="12.5">
+    <row r="440" spans="6:16" ht="13.2">
       <c r="F440" s="3"/>
       <c r="I440" s="4"/>
       <c r="J440" s="4"/>
@@ -5176,7 +5205,7 @@
       <c r="L440" s="3"/>
       <c r="P440" s="3"/>
     </row>
-    <row r="441" spans="6:16" ht="12.5">
+    <row r="441" spans="6:16" ht="13.2">
       <c r="F441" s="3"/>
       <c r="I441" s="4"/>
       <c r="J441" s="4"/>
@@ -5184,7 +5213,7 @@
       <c r="L441" s="3"/>
       <c r="P441" s="3"/>
     </row>
-    <row r="442" spans="6:16" ht="12.5">
+    <row r="442" spans="6:16" ht="13.2">
       <c r="F442" s="3"/>
       <c r="I442" s="4"/>
       <c r="J442" s="4"/>
@@ -5192,7 +5221,7 @@
       <c r="L442" s="3"/>
       <c r="P442" s="3"/>
     </row>
-    <row r="443" spans="6:16" ht="12.5">
+    <row r="443" spans="6:16" ht="13.2">
       <c r="F443" s="3"/>
       <c r="I443" s="4"/>
       <c r="J443" s="4"/>
@@ -5200,7 +5229,7 @@
       <c r="L443" s="3"/>
       <c r="P443" s="3"/>
     </row>
-    <row r="444" spans="6:16" ht="12.5">
+    <row r="444" spans="6:16" ht="13.2">
       <c r="F444" s="3"/>
       <c r="I444" s="4"/>
       <c r="J444" s="4"/>
@@ -5208,7 +5237,7 @@
       <c r="L444" s="3"/>
       <c r="P444" s="3"/>
     </row>
-    <row r="445" spans="6:16" ht="12.5">
+    <row r="445" spans="6:16" ht="13.2">
       <c r="F445" s="3"/>
       <c r="I445" s="4"/>
       <c r="J445" s="4"/>
@@ -5216,7 +5245,7 @@
       <c r="L445" s="3"/>
       <c r="P445" s="3"/>
     </row>
-    <row r="446" spans="6:16" ht="12.5">
+    <row r="446" spans="6:16" ht="13.2">
       <c r="F446" s="3"/>
       <c r="I446" s="4"/>
       <c r="J446" s="4"/>
@@ -5224,7 +5253,7 @@
       <c r="L446" s="3"/>
       <c r="P446" s="3"/>
     </row>
-    <row r="447" spans="6:16" ht="12.5">
+    <row r="447" spans="6:16" ht="13.2">
       <c r="F447" s="3"/>
       <c r="I447" s="4"/>
       <c r="J447" s="4"/>
@@ -5232,7 +5261,7 @@
       <c r="L447" s="3"/>
       <c r="P447" s="3"/>
     </row>
-    <row r="448" spans="6:16" ht="12.5">
+    <row r="448" spans="6:16" ht="13.2">
       <c r="F448" s="3"/>
       <c r="I448" s="4"/>
       <c r="J448" s="4"/>
@@ -5240,7 +5269,7 @@
       <c r="L448" s="3"/>
       <c r="P448" s="3"/>
     </row>
-    <row r="449" spans="6:16" ht="12.5">
+    <row r="449" spans="6:16" ht="13.2">
       <c r="F449" s="3"/>
       <c r="I449" s="4"/>
       <c r="J449" s="4"/>
@@ -5248,7 +5277,7 @@
       <c r="L449" s="3"/>
       <c r="P449" s="3"/>
     </row>
-    <row r="450" spans="6:16" ht="12.5">
+    <row r="450" spans="6:16" ht="13.2">
       <c r="F450" s="3"/>
       <c r="I450" s="4"/>
       <c r="J450" s="4"/>
@@ -5256,7 +5285,7 @@
       <c r="L450" s="3"/>
       <c r="P450" s="3"/>
     </row>
-    <row r="451" spans="6:16" ht="12.5">
+    <row r="451" spans="6:16" ht="13.2">
       <c r="F451" s="3"/>
       <c r="I451" s="4"/>
       <c r="J451" s="4"/>
@@ -5264,7 +5293,7 @@
       <c r="L451" s="3"/>
       <c r="P451" s="3"/>
     </row>
-    <row r="452" spans="6:16" ht="12.5">
+    <row r="452" spans="6:16" ht="13.2">
       <c r="F452" s="3"/>
       <c r="I452" s="4"/>
       <c r="J452" s="4"/>
@@ -5272,7 +5301,7 @@
       <c r="L452" s="3"/>
       <c r="P452" s="3"/>
     </row>
-    <row r="453" spans="6:16" ht="12.5">
+    <row r="453" spans="6:16" ht="13.2">
       <c r="F453" s="3"/>
       <c r="I453" s="4"/>
       <c r="J453" s="4"/>
@@ -5280,7 +5309,7 @@
       <c r="L453" s="3"/>
       <c r="P453" s="3"/>
     </row>
-    <row r="454" spans="6:16" ht="12.5">
+    <row r="454" spans="6:16" ht="13.2">
       <c r="F454" s="3"/>
       <c r="I454" s="4"/>
       <c r="J454" s="4"/>
@@ -5288,7 +5317,7 @@
       <c r="L454" s="3"/>
       <c r="P454" s="3"/>
     </row>
-    <row r="455" spans="6:16" ht="12.5">
+    <row r="455" spans="6:16" ht="13.2">
       <c r="F455" s="3"/>
       <c r="I455" s="4"/>
       <c r="J455" s="4"/>
@@ -5296,7 +5325,7 @@
       <c r="L455" s="3"/>
       <c r="P455" s="3"/>
     </row>
-    <row r="456" spans="6:16" ht="12.5">
+    <row r="456" spans="6:16" ht="13.2">
       <c r="F456" s="3"/>
       <c r="I456" s="4"/>
       <c r="J456" s="4"/>
@@ -5304,7 +5333,7 @@
       <c r="L456" s="3"/>
       <c r="P456" s="3"/>
     </row>
-    <row r="457" spans="6:16" ht="12.5">
+    <row r="457" spans="6:16" ht="13.2">
       <c r="F457" s="3"/>
       <c r="I457" s="4"/>
       <c r="J457" s="4"/>
@@ -5312,7 +5341,7 @@
       <c r="L457" s="3"/>
       <c r="P457" s="3"/>
     </row>
-    <row r="458" spans="6:16" ht="12.5">
+    <row r="458" spans="6:16" ht="13.2">
       <c r="F458" s="3"/>
       <c r="I458" s="4"/>
       <c r="J458" s="4"/>
@@ -5320,7 +5349,7 @@
       <c r="L458" s="3"/>
       <c r="P458" s="3"/>
     </row>
-    <row r="459" spans="6:16" ht="12.5">
+    <row r="459" spans="6:16" ht="13.2">
       <c r="F459" s="3"/>
       <c r="I459" s="4"/>
       <c r="J459" s="4"/>
@@ -5328,7 +5357,7 @@
       <c r="L459" s="3"/>
       <c r="P459" s="3"/>
     </row>
-    <row r="460" spans="6:16" ht="12.5">
+    <row r="460" spans="6:16" ht="13.2">
       <c r="F460" s="3"/>
       <c r="I460" s="4"/>
       <c r="J460" s="4"/>
@@ -5336,7 +5365,7 @@
       <c r="L460" s="3"/>
       <c r="P460" s="3"/>
     </row>
-    <row r="461" spans="6:16" ht="12.5">
+    <row r="461" spans="6:16" ht="13.2">
       <c r="F461" s="3"/>
       <c r="I461" s="4"/>
       <c r="J461" s="4"/>
@@ -5344,7 +5373,7 @@
       <c r="L461" s="3"/>
       <c r="P461" s="3"/>
     </row>
-    <row r="462" spans="6:16" ht="12.5">
+    <row r="462" spans="6:16" ht="13.2">
       <c r="F462" s="3"/>
       <c r="I462" s="4"/>
       <c r="J462" s="4"/>
@@ -5352,7 +5381,7 @@
       <c r="L462" s="3"/>
       <c r="P462" s="3"/>
     </row>
-    <row r="463" spans="6:16" ht="12.5">
+    <row r="463" spans="6:16" ht="13.2">
       <c r="F463" s="3"/>
       <c r="I463" s="4"/>
       <c r="J463" s="4"/>
@@ -5360,7 +5389,7 @@
       <c r="L463" s="3"/>
       <c r="P463" s="3"/>
     </row>
-    <row r="464" spans="6:16" ht="12.5">
+    <row r="464" spans="6:16" ht="13.2">
       <c r="F464" s="3"/>
       <c r="I464" s="4"/>
       <c r="J464" s="4"/>
@@ -5368,7 +5397,7 @@
       <c r="L464" s="3"/>
       <c r="P464" s="3"/>
     </row>
-    <row r="465" spans="6:16" ht="12.5">
+    <row r="465" spans="6:16" ht="13.2">
       <c r="F465" s="3"/>
       <c r="I465" s="4"/>
       <c r="J465" s="4"/>
@@ -5376,7 +5405,7 @@
       <c r="L465" s="3"/>
       <c r="P465" s="3"/>
     </row>
-    <row r="466" spans="6:16" ht="12.5">
+    <row r="466" spans="6:16" ht="13.2">
       <c r="F466" s="3"/>
       <c r="I466" s="4"/>
       <c r="J466" s="4"/>
@@ -5384,7 +5413,7 @@
       <c r="L466" s="3"/>
       <c r="P466" s="3"/>
     </row>
-    <row r="467" spans="6:16" ht="12.5">
+    <row r="467" spans="6:16" ht="13.2">
       <c r="F467" s="3"/>
       <c r="I467" s="4"/>
       <c r="J467" s="4"/>
@@ -5392,7 +5421,7 @@
       <c r="L467" s="3"/>
       <c r="P467" s="3"/>
     </row>
-    <row r="468" spans="6:16" ht="12.5">
+    <row r="468" spans="6:16" ht="13.2">
       <c r="F468" s="3"/>
       <c r="I468" s="4"/>
       <c r="J468" s="4"/>
@@ -5400,7 +5429,7 @@
       <c r="L468" s="3"/>
       <c r="P468" s="3"/>
     </row>
-    <row r="469" spans="6:16" ht="12.5">
+    <row r="469" spans="6:16" ht="13.2">
       <c r="F469" s="3"/>
       <c r="I469" s="4"/>
       <c r="J469" s="4"/>
@@ -5408,7 +5437,7 @@
       <c r="L469" s="3"/>
       <c r="P469" s="3"/>
     </row>
-    <row r="470" spans="6:16" ht="12.5">
+    <row r="470" spans="6:16" ht="13.2">
       <c r="F470" s="3"/>
       <c r="I470" s="4"/>
       <c r="J470" s="4"/>
@@ -5416,7 +5445,7 @@
       <c r="L470" s="3"/>
       <c r="P470" s="3"/>
     </row>
-    <row r="471" spans="6:16" ht="12.5">
+    <row r="471" spans="6:16" ht="13.2">
       <c r="F471" s="3"/>
       <c r="I471" s="4"/>
       <c r="J471" s="4"/>
@@ -5424,7 +5453,7 @@
       <c r="L471" s="3"/>
       <c r="P471" s="3"/>
     </row>
-    <row r="472" spans="6:16" ht="12.5">
+    <row r="472" spans="6:16" ht="13.2">
       <c r="F472" s="3"/>
       <c r="I472" s="4"/>
       <c r="J472" s="4"/>
@@ -5432,7 +5461,7 @@
       <c r="L472" s="3"/>
       <c r="P472" s="3"/>
     </row>
-    <row r="473" spans="6:16" ht="12.5">
+    <row r="473" spans="6:16" ht="13.2">
       <c r="F473" s="3"/>
       <c r="I473" s="4"/>
       <c r="J473" s="4"/>
@@ -5440,7 +5469,7 @@
       <c r="L473" s="3"/>
       <c r="P473" s="3"/>
     </row>
-    <row r="474" spans="6:16" ht="12.5">
+    <row r="474" spans="6:16" ht="13.2">
       <c r="F474" s="3"/>
       <c r="I474" s="4"/>
       <c r="J474" s="4"/>
@@ -5448,7 +5477,7 @@
       <c r="L474" s="3"/>
       <c r="P474" s="3"/>
     </row>
-    <row r="475" spans="6:16" ht="12.5">
+    <row r="475" spans="6:16" ht="13.2">
       <c r="F475" s="3"/>
       <c r="I475" s="4"/>
       <c r="J475" s="4"/>
@@ -5456,7 +5485,7 @@
       <c r="L475" s="3"/>
       <c r="P475" s="3"/>
     </row>
-    <row r="476" spans="6:16" ht="12.5">
+    <row r="476" spans="6:16" ht="13.2">
       <c r="F476" s="3"/>
       <c r="I476" s="4"/>
       <c r="J476" s="4"/>
@@ -5464,7 +5493,7 @@
       <c r="L476" s="3"/>
       <c r="P476" s="3"/>
     </row>
-    <row r="477" spans="6:16" ht="12.5">
+    <row r="477" spans="6:16" ht="13.2">
       <c r="F477" s="3"/>
       <c r="I477" s="4"/>
       <c r="J477" s="4"/>
@@ -5472,7 +5501,7 @@
       <c r="L477" s="3"/>
       <c r="P477" s="3"/>
     </row>
-    <row r="478" spans="6:16" ht="12.5">
+    <row r="478" spans="6:16" ht="13.2">
       <c r="F478" s="3"/>
       <c r="I478" s="4"/>
       <c r="J478" s="4"/>
@@ -5480,7 +5509,7 @@
       <c r="L478" s="3"/>
       <c r="P478" s="3"/>
     </row>
-    <row r="479" spans="6:16" ht="12.5">
+    <row r="479" spans="6:16" ht="13.2">
       <c r="F479" s="3"/>
       <c r="I479" s="4"/>
       <c r="J479" s="4"/>
@@ -5488,7 +5517,7 @@
       <c r="L479" s="3"/>
       <c r="P479" s="3"/>
     </row>
-    <row r="480" spans="6:16" ht="12.5">
+    <row r="480" spans="6:16" ht="13.2">
       <c r="F480" s="3"/>
       <c r="I480" s="4"/>
       <c r="J480" s="4"/>
@@ -5496,7 +5525,7 @@
       <c r="L480" s="3"/>
       <c r="P480" s="3"/>
     </row>
-    <row r="481" spans="6:16" ht="12.5">
+    <row r="481" spans="6:16" ht="13.2">
       <c r="F481" s="3"/>
       <c r="I481" s="4"/>
       <c r="J481" s="4"/>
@@ -5504,7 +5533,7 @@
       <c r="L481" s="3"/>
       <c r="P481" s="3"/>
     </row>
-    <row r="482" spans="6:16" ht="12.5">
+    <row r="482" spans="6:16" ht="13.2">
       <c r="F482" s="3"/>
       <c r="I482" s="4"/>
       <c r="J482" s="4"/>
@@ -5512,7 +5541,7 @@
       <c r="L482" s="3"/>
       <c r="P482" s="3"/>
     </row>
-    <row r="483" spans="6:16" ht="12.5">
+    <row r="483" spans="6:16" ht="13.2">
       <c r="F483" s="3"/>
       <c r="I483" s="4"/>
       <c r="J483" s="4"/>
@@ -5520,7 +5549,7 @@
       <c r="L483" s="3"/>
       <c r="P483" s="3"/>
     </row>
-    <row r="484" spans="6:16" ht="12.5">
+    <row r="484" spans="6:16" ht="13.2">
       <c r="F484" s="3"/>
       <c r="I484" s="4"/>
       <c r="J484" s="4"/>
@@ -5528,7 +5557,7 @@
       <c r="L484" s="3"/>
       <c r="P484" s="3"/>
     </row>
-    <row r="485" spans="6:16" ht="12.5">
+    <row r="485" spans="6:16" ht="13.2">
       <c r="F485" s="3"/>
       <c r="I485" s="4"/>
       <c r="J485" s="4"/>
@@ -5536,7 +5565,7 @@
       <c r="L485" s="3"/>
       <c r="P485" s="3"/>
     </row>
-    <row r="486" spans="6:16" ht="12.5">
+    <row r="486" spans="6:16" ht="13.2">
       <c r="F486" s="3"/>
       <c r="I486" s="4"/>
       <c r="J486" s="4"/>
@@ -5544,7 +5573,7 @@
       <c r="L486" s="3"/>
       <c r="P486" s="3"/>
     </row>
-    <row r="487" spans="6:16" ht="12.5">
+    <row r="487" spans="6:16" ht="13.2">
       <c r="F487" s="3"/>
       <c r="I487" s="4"/>
       <c r="J487" s="4"/>
@@ -5552,7 +5581,7 @@
       <c r="L487" s="3"/>
       <c r="P487" s="3"/>
     </row>
-    <row r="488" spans="6:16" ht="12.5">
+    <row r="488" spans="6:16" ht="13.2">
       <c r="F488" s="3"/>
       <c r="I488" s="4"/>
       <c r="J488" s="4"/>
@@ -5560,7 +5589,7 @@
       <c r="L488" s="3"/>
       <c r="P488" s="3"/>
     </row>
-    <row r="489" spans="6:16" ht="12.5">
+    <row r="489" spans="6:16" ht="13.2">
       <c r="F489" s="3"/>
       <c r="I489" s="4"/>
       <c r="J489" s="4"/>
@@ -5568,7 +5597,7 @@
       <c r="L489" s="3"/>
       <c r="P489" s="3"/>
     </row>
-    <row r="490" spans="6:16" ht="12.5">
+    <row r="490" spans="6:16" ht="13.2">
       <c r="F490" s="3"/>
       <c r="I490" s="4"/>
       <c r="J490" s="4"/>
@@ -5576,7 +5605,7 @@
       <c r="L490" s="3"/>
       <c r="P490" s="3"/>
     </row>
-    <row r="491" spans="6:16" ht="12.5">
+    <row r="491" spans="6:16" ht="13.2">
       <c r="F491" s="3"/>
       <c r="I491" s="4"/>
       <c r="J491" s="4"/>
@@ -5584,7 +5613,7 @@
       <c r="L491" s="3"/>
       <c r="P491" s="3"/>
     </row>
-    <row r="492" spans="6:16" ht="12.5">
+    <row r="492" spans="6:16" ht="13.2">
       <c r="F492" s="3"/>
       <c r="I492" s="4"/>
       <c r="J492" s="4"/>
@@ -5592,7 +5621,7 @@
       <c r="L492" s="3"/>
       <c r="P492" s="3"/>
     </row>
-    <row r="493" spans="6:16" ht="12.5">
+    <row r="493" spans="6:16" ht="13.2">
       <c r="F493" s="3"/>
       <c r="I493" s="4"/>
       <c r="J493" s="4"/>
@@ -5600,7 +5629,7 @@
       <c r="L493" s="3"/>
       <c r="P493" s="3"/>
     </row>
-    <row r="494" spans="6:16" ht="12.5">
+    <row r="494" spans="6:16" ht="13.2">
       <c r="F494" s="3"/>
       <c r="I494" s="4"/>
       <c r="J494" s="4"/>
@@ -5608,7 +5637,7 @@
       <c r="L494" s="3"/>
       <c r="P494" s="3"/>
     </row>
-    <row r="495" spans="6:16" ht="12.5">
+    <row r="495" spans="6:16" ht="13.2">
       <c r="F495" s="3"/>
       <c r="I495" s="4"/>
       <c r="J495" s="4"/>
@@ -5616,7 +5645,7 @@
       <c r="L495" s="3"/>
       <c r="P495" s="3"/>
     </row>
-    <row r="496" spans="6:16" ht="12.5">
+    <row r="496" spans="6:16" ht="13.2">
       <c r="F496" s="3"/>
       <c r="I496" s="4"/>
       <c r="J496" s="4"/>
@@ -5624,7 +5653,7 @@
       <c r="L496" s="3"/>
       <c r="P496" s="3"/>
     </row>
-    <row r="497" spans="6:16" ht="12.5">
+    <row r="497" spans="6:16" ht="13.2">
       <c r="F497" s="3"/>
       <c r="I497" s="4"/>
       <c r="J497" s="4"/>
@@ -5632,7 +5661,7 @@
       <c r="L497" s="3"/>
       <c r="P497" s="3"/>
     </row>
-    <row r="498" spans="6:16" ht="12.5">
+    <row r="498" spans="6:16" ht="13.2">
       <c r="F498" s="3"/>
       <c r="I498" s="4"/>
       <c r="J498" s="4"/>
@@ -5640,7 +5669,7 @@
       <c r="L498" s="3"/>
       <c r="P498" s="3"/>
     </row>
-    <row r="499" spans="6:16" ht="12.5">
+    <row r="499" spans="6:16" ht="13.2">
       <c r="F499" s="3"/>
       <c r="I499" s="4"/>
       <c r="J499" s="4"/>
@@ -5648,7 +5677,7 @@
       <c r="L499" s="3"/>
       <c r="P499" s="3"/>
     </row>
-    <row r="500" spans="6:16" ht="12.5">
+    <row r="500" spans="6:16" ht="13.2">
       <c r="F500" s="3"/>
       <c r="I500" s="4"/>
       <c r="J500" s="4"/>
@@ -5656,7 +5685,7 @@
       <c r="L500" s="3"/>
       <c r="P500" s="3"/>
     </row>
-    <row r="501" spans="6:16" ht="12.5">
+    <row r="501" spans="6:16" ht="13.2">
       <c r="F501" s="3"/>
       <c r="I501" s="4"/>
       <c r="J501" s="4"/>
@@ -5664,7 +5693,7 @@
       <c r="L501" s="3"/>
       <c r="P501" s="3"/>
     </row>
-    <row r="502" spans="6:16" ht="12.5">
+    <row r="502" spans="6:16" ht="13.2">
       <c r="F502" s="3"/>
       <c r="I502" s="4"/>
       <c r="J502" s="4"/>
@@ -5672,7 +5701,7 @@
       <c r="L502" s="3"/>
       <c r="P502" s="3"/>
     </row>
-    <row r="503" spans="6:16" ht="12.5">
+    <row r="503" spans="6:16" ht="13.2">
       <c r="F503" s="3"/>
       <c r="I503" s="4"/>
       <c r="J503" s="4"/>
@@ -5680,7 +5709,7 @@
       <c r="L503" s="3"/>
       <c r="P503" s="3"/>
     </row>
-    <row r="504" spans="6:16" ht="12.5">
+    <row r="504" spans="6:16" ht="13.2">
       <c r="F504" s="3"/>
       <c r="I504" s="4"/>
       <c r="J504" s="4"/>
@@ -5688,7 +5717,7 @@
       <c r="L504" s="3"/>
       <c r="P504" s="3"/>
     </row>
-    <row r="505" spans="6:16" ht="12.5">
+    <row r="505" spans="6:16" ht="13.2">
       <c r="F505" s="3"/>
       <c r="I505" s="4"/>
       <c r="J505" s="4"/>
@@ -5696,7 +5725,7 @@
       <c r="L505" s="3"/>
       <c r="P505" s="3"/>
     </row>
-    <row r="506" spans="6:16" ht="12.5">
+    <row r="506" spans="6:16" ht="13.2">
       <c r="F506" s="3"/>
       <c r="I506" s="4"/>
       <c r="J506" s="4"/>
@@ -5704,7 +5733,7 @@
       <c r="L506" s="3"/>
       <c r="P506" s="3"/>
     </row>
-    <row r="507" spans="6:16" ht="12.5">
+    <row r="507" spans="6:16" ht="13.2">
       <c r="F507" s="3"/>
       <c r="I507" s="4"/>
       <c r="J507" s="4"/>
@@ -5712,7 +5741,7 @@
       <c r="L507" s="3"/>
       <c r="P507" s="3"/>
     </row>
-    <row r="508" spans="6:16" ht="12.5">
+    <row r="508" spans="6:16" ht="13.2">
       <c r="F508" s="3"/>
       <c r="I508" s="4"/>
       <c r="J508" s="4"/>
@@ -5720,7 +5749,7 @@
       <c r="L508" s="3"/>
       <c r="P508" s="3"/>
     </row>
-    <row r="509" spans="6:16" ht="12.5">
+    <row r="509" spans="6:16" ht="13.2">
       <c r="F509" s="3"/>
       <c r="I509" s="4"/>
       <c r="J509" s="4"/>
@@ -5728,7 +5757,7 @@
       <c r="L509" s="3"/>
       <c r="P509" s="3"/>
     </row>
-    <row r="510" spans="6:16" ht="12.5">
+    <row r="510" spans="6:16" ht="13.2">
       <c r="F510" s="3"/>
       <c r="I510" s="4"/>
       <c r="J510" s="4"/>
@@ -5736,7 +5765,7 @@
       <c r="L510" s="3"/>
       <c r="P510" s="3"/>
     </row>
-    <row r="511" spans="6:16" ht="12.5">
+    <row r="511" spans="6:16" ht="13.2">
       <c r="F511" s="3"/>
       <c r="I511" s="4"/>
       <c r="J511" s="4"/>
@@ -5744,7 +5773,7 @@
       <c r="L511" s="3"/>
       <c r="P511" s="3"/>
     </row>
-    <row r="512" spans="6:16" ht="12.5">
+    <row r="512" spans="6:16" ht="13.2">
       <c r="F512" s="3"/>
       <c r="I512" s="4"/>
       <c r="J512" s="4"/>
@@ -5752,7 +5781,7 @@
       <c r="L512" s="3"/>
       <c r="P512" s="3"/>
     </row>
-    <row r="513" spans="6:16" ht="12.5">
+    <row r="513" spans="6:16" ht="13.2">
       <c r="F513" s="3"/>
       <c r="I513" s="4"/>
       <c r="J513" s="4"/>
@@ -5760,7 +5789,7 @@
       <c r="L513" s="3"/>
       <c r="P513" s="3"/>
     </row>
-    <row r="514" spans="6:16" ht="12.5">
+    <row r="514" spans="6:16" ht="13.2">
       <c r="F514" s="3"/>
       <c r="I514" s="4"/>
       <c r="J514" s="4"/>
@@ -5768,7 +5797,7 @@
       <c r="L514" s="3"/>
       <c r="P514" s="3"/>
     </row>
-    <row r="515" spans="6:16" ht="12.5">
+    <row r="515" spans="6:16" ht="13.2">
       <c r="F515" s="3"/>
       <c r="I515" s="4"/>
       <c r="J515" s="4"/>
@@ -5776,7 +5805,7 @@
       <c r="L515" s="3"/>
       <c r="P515" s="3"/>
     </row>
-    <row r="516" spans="6:16" ht="12.5">
+    <row r="516" spans="6:16" ht="13.2">
       <c r="F516" s="3"/>
       <c r="I516" s="4"/>
       <c r="J516" s="4"/>
@@ -5784,7 +5813,7 @@
       <c r="L516" s="3"/>
       <c r="P516" s="3"/>
     </row>
-    <row r="517" spans="6:16" ht="12.5">
+    <row r="517" spans="6:16" ht="13.2">
       <c r="F517" s="3"/>
       <c r="I517" s="4"/>
       <c r="J517" s="4"/>
@@ -5792,7 +5821,7 @@
       <c r="L517" s="3"/>
       <c r="P517" s="3"/>
     </row>
-    <row r="518" spans="6:16" ht="12.5">
+    <row r="518" spans="6:16" ht="13.2">
       <c r="F518" s="3"/>
       <c r="I518" s="4"/>
       <c r="J518" s="4"/>
@@ -5800,7 +5829,7 @@
       <c r="L518" s="3"/>
       <c r="P518" s="3"/>
     </row>
-    <row r="519" spans="6:16" ht="12.5">
+    <row r="519" spans="6:16" ht="13.2">
       <c r="F519" s="3"/>
       <c r="I519" s="4"/>
       <c r="J519" s="4"/>
@@ -5808,7 +5837,7 @@
       <c r="L519" s="3"/>
       <c r="P519" s="3"/>
     </row>
-    <row r="520" spans="6:16" ht="12.5">
+    <row r="520" spans="6:16" ht="13.2">
       <c r="F520" s="3"/>
       <c r="I520" s="4"/>
       <c r="J520" s="4"/>
@@ -5816,7 +5845,7 @@
       <c r="L520" s="3"/>
       <c r="P520" s="3"/>
     </row>
-    <row r="521" spans="6:16" ht="12.5">
+    <row r="521" spans="6:16" ht="13.2">
       <c r="F521" s="3"/>
       <c r="I521" s="4"/>
       <c r="J521" s="4"/>
@@ -5824,7 +5853,7 @@
       <c r="L521" s="3"/>
       <c r="P521" s="3"/>
     </row>
-    <row r="522" spans="6:16" ht="12.5">
+    <row r="522" spans="6:16" ht="13.2">
       <c r="F522" s="3"/>
       <c r="I522" s="4"/>
       <c r="J522" s="4"/>
@@ -5832,7 +5861,7 @@
       <c r="L522" s="3"/>
       <c r="P522" s="3"/>
     </row>
-    <row r="523" spans="6:16" ht="12.5">
+    <row r="523" spans="6:16" ht="13.2">
       <c r="F523" s="3"/>
       <c r="I523" s="4"/>
       <c r="J523" s="4"/>
@@ -5840,7 +5869,7 @@
       <c r="L523" s="3"/>
       <c r="P523" s="3"/>
     </row>
-    <row r="524" spans="6:16" ht="12.5">
+    <row r="524" spans="6:16" ht="13.2">
       <c r="F524" s="3"/>
       <c r="I524" s="4"/>
       <c r="J524" s="4"/>
@@ -5848,7 +5877,7 @@
       <c r="L524" s="3"/>
       <c r="P524" s="3"/>
     </row>
-    <row r="525" spans="6:16" ht="12.5">
+    <row r="525" spans="6:16" ht="13.2">
       <c r="F525" s="3"/>
       <c r="I525" s="4"/>
       <c r="J525" s="4"/>
@@ -5856,7 +5885,7 @@
       <c r="L525" s="3"/>
       <c r="P525" s="3"/>
     </row>
-    <row r="526" spans="6:16" ht="12.5">
+    <row r="526" spans="6:16" ht="13.2">
       <c r="F526" s="3"/>
       <c r="I526" s="4"/>
       <c r="J526" s="4"/>
@@ -5864,7 +5893,7 @@
       <c r="L526" s="3"/>
       <c r="P526" s="3"/>
     </row>
-    <row r="527" spans="6:16" ht="12.5">
+    <row r="527" spans="6:16" ht="13.2">
       <c r="F527" s="3"/>
       <c r="I527" s="4"/>
       <c r="J527" s="4"/>
@@ -5872,7 +5901,7 @@
       <c r="L527" s="3"/>
       <c r="P527" s="3"/>
     </row>
-    <row r="528" spans="6:16" ht="12.5">
+    <row r="528" spans="6:16" ht="13.2">
       <c r="F528" s="3"/>
       <c r="I528" s="4"/>
       <c r="J528" s="4"/>
@@ -5880,7 +5909,7 @@
       <c r="L528" s="3"/>
       <c r="P528" s="3"/>
     </row>
-    <row r="529" spans="6:16" ht="12.5">
+    <row r="529" spans="6:16" ht="13.2">
       <c r="F529" s="3"/>
       <c r="I529" s="4"/>
       <c r="J529" s="4"/>
@@ -5888,7 +5917,7 @@
       <c r="L529" s="3"/>
       <c r="P529" s="3"/>
     </row>
-    <row r="530" spans="6:16" ht="12.5">
+    <row r="530" spans="6:16" ht="13.2">
       <c r="F530" s="3"/>
       <c r="I530" s="4"/>
       <c r="J530" s="4"/>
@@ -5896,7 +5925,7 @@
       <c r="L530" s="3"/>
       <c r="P530" s="3"/>
     </row>
-    <row r="531" spans="6:16" ht="12.5">
+    <row r="531" spans="6:16" ht="13.2">
       <c r="F531" s="3"/>
       <c r="I531" s="4"/>
       <c r="J531" s="4"/>
@@ -5904,7 +5933,7 @@
       <c r="L531" s="3"/>
       <c r="P531" s="3"/>
     </row>
-    <row r="532" spans="6:16" ht="12.5">
+    <row r="532" spans="6:16" ht="13.2">
       <c r="F532" s="3"/>
       <c r="I532" s="4"/>
       <c r="J532" s="4"/>
@@ -5912,7 +5941,7 @@
       <c r="L532" s="3"/>
       <c r="P532" s="3"/>
     </row>
-    <row r="533" spans="6:16" ht="12.5">
+    <row r="533" spans="6:16" ht="13.2">
       <c r="F533" s="3"/>
       <c r="I533" s="4"/>
       <c r="J533" s="4"/>
@@ -5920,7 +5949,7 @@
       <c r="L533" s="3"/>
       <c r="P533" s="3"/>
     </row>
-    <row r="534" spans="6:16" ht="12.5">
+    <row r="534" spans="6:16" ht="13.2">
       <c r="F534" s="3"/>
       <c r="I534" s="4"/>
       <c r="J534" s="4"/>
@@ -5928,7 +5957,7 @@
       <c r="L534" s="3"/>
       <c r="P534" s="3"/>
     </row>
-    <row r="535" spans="6:16" ht="12.5">
+    <row r="535" spans="6:16" ht="13.2">
       <c r="F535" s="3"/>
       <c r="I535" s="4"/>
       <c r="J535" s="4"/>
@@ -5936,7 +5965,7 @@
       <c r="L535" s="3"/>
       <c r="P535" s="3"/>
     </row>
-    <row r="536" spans="6:16" ht="12.5">
+    <row r="536" spans="6:16" ht="13.2">
       <c r="F536" s="3"/>
       <c r="I536" s="4"/>
       <c r="J536" s="4"/>
@@ -5944,7 +5973,7 @@
       <c r="L536" s="3"/>
       <c r="P536" s="3"/>
     </row>
-    <row r="537" spans="6:16" ht="12.5">
+    <row r="537" spans="6:16" ht="13.2">
       <c r="F537" s="3"/>
       <c r="I537" s="4"/>
       <c r="J537" s="4"/>
@@ -5952,7 +5981,7 @@
       <c r="L537" s="3"/>
       <c r="P537" s="3"/>
     </row>
-    <row r="538" spans="6:16" ht="12.5">
+    <row r="538" spans="6:16" ht="13.2">
       <c r="F538" s="3"/>
       <c r="I538" s="4"/>
       <c r="J538" s="4"/>
@@ -5960,7 +5989,7 @@
       <c r="L538" s="3"/>
       <c r="P538" s="3"/>
     </row>
-    <row r="539" spans="6:16" ht="12.5">
+    <row r="539" spans="6:16" ht="13.2">
       <c r="F539" s="3"/>
       <c r="I539" s="4"/>
       <c r="J539" s="4"/>
@@ -5968,7 +5997,7 @@
       <c r="L539" s="3"/>
       <c r="P539" s="3"/>
     </row>
-    <row r="540" spans="6:16" ht="12.5">
+    <row r="540" spans="6:16" ht="13.2">
       <c r="F540" s="3"/>
       <c r="I540" s="4"/>
       <c r="J540" s="4"/>
@@ -5976,7 +6005,7 @@
       <c r="L540" s="3"/>
       <c r="P540" s="3"/>
     </row>
-    <row r="541" spans="6:16" ht="12.5">
+    <row r="541" spans="6:16" ht="13.2">
       <c r="F541" s="3"/>
       <c r="I541" s="4"/>
       <c r="J541" s="4"/>
@@ -5984,7 +6013,7 @@
       <c r="L541" s="3"/>
       <c r="P541" s="3"/>
     </row>
-    <row r="542" spans="6:16" ht="12.5">
+    <row r="542" spans="6:16" ht="13.2">
       <c r="F542" s="3"/>
       <c r="I542" s="4"/>
       <c r="J542" s="4"/>
@@ -5992,7 +6021,7 @@
       <c r="L542" s="3"/>
       <c r="P542" s="3"/>
     </row>
-    <row r="543" spans="6:16" ht="12.5">
+    <row r="543" spans="6:16" ht="13.2">
       <c r="F543" s="3"/>
       <c r="I543" s="4"/>
       <c r="J543" s="4"/>
@@ -6000,7 +6029,7 @@
       <c r="L543" s="3"/>
       <c r="P543" s="3"/>
     </row>
-    <row r="544" spans="6:16" ht="12.5">
+    <row r="544" spans="6:16" ht="13.2">
       <c r="F544" s="3"/>
       <c r="I544" s="4"/>
       <c r="J544" s="4"/>
@@ -6008,7 +6037,7 @@
       <c r="L544" s="3"/>
       <c r="P544" s="3"/>
     </row>
-    <row r="545" spans="6:16" ht="12.5">
+    <row r="545" spans="6:16" ht="13.2">
       <c r="F545" s="3"/>
       <c r="I545" s="4"/>
       <c r="J545" s="4"/>
@@ -6016,7 +6045,7 @@
       <c r="L545" s="3"/>
       <c r="P545" s="3"/>
     </row>
-    <row r="546" spans="6:16" ht="12.5">
+    <row r="546" spans="6:16" ht="13.2">
       <c r="F546" s="3"/>
       <c r="I546" s="4"/>
       <c r="J546" s="4"/>
@@ -6024,7 +6053,7 @@
       <c r="L546" s="3"/>
       <c r="P546" s="3"/>
     </row>
-    <row r="547" spans="6:16" ht="12.5">
+    <row r="547" spans="6:16" ht="13.2">
       <c r="F547" s="3"/>
       <c r="I547" s="4"/>
       <c r="J547" s="4"/>
@@ -6032,7 +6061,7 @@
       <c r="L547" s="3"/>
       <c r="P547" s="3"/>
     </row>
-    <row r="548" spans="6:16" ht="12.5">
+    <row r="548" spans="6:16" ht="13.2">
       <c r="F548" s="3"/>
       <c r="I548" s="4"/>
       <c r="J548" s="4"/>
@@ -6040,7 +6069,7 @@
       <c r="L548" s="3"/>
       <c r="P548" s="3"/>
     </row>
-    <row r="549" spans="6:16" ht="12.5">
+    <row r="549" spans="6:16" ht="13.2">
       <c r="F549" s="3"/>
       <c r="I549" s="4"/>
       <c r="J549" s="4"/>
@@ -6048,7 +6077,7 @@
       <c r="L549" s="3"/>
       <c r="P549" s="3"/>
     </row>
-    <row r="550" spans="6:16" ht="12.5">
+    <row r="550" spans="6:16" ht="13.2">
       <c r="F550" s="3"/>
       <c r="I550" s="4"/>
       <c r="J550" s="4"/>
@@ -6056,7 +6085,7 @@
       <c r="L550" s="3"/>
       <c r="P550" s="3"/>
     </row>
-    <row r="551" spans="6:16" ht="12.5">
+    <row r="551" spans="6:16" ht="13.2">
       <c r="F551" s="3"/>
       <c r="I551" s="4"/>
       <c r="J551" s="4"/>
@@ -6064,7 +6093,7 @@
       <c r="L551" s="3"/>
       <c r="P551" s="3"/>
     </row>
-    <row r="552" spans="6:16" ht="12.5">
+    <row r="552" spans="6:16" ht="13.2">
       <c r="F552" s="3"/>
       <c r="I552" s="4"/>
       <c r="J552" s="4"/>
@@ -6072,7 +6101,7 @@
       <c r="L552" s="3"/>
       <c r="P552" s="3"/>
     </row>
-    <row r="553" spans="6:16" ht="12.5">
+    <row r="553" spans="6:16" ht="13.2">
       <c r="F553" s="3"/>
       <c r="I553" s="4"/>
       <c r="J553" s="4"/>
@@ -6080,7 +6109,7 @@
       <c r="L553" s="3"/>
       <c r="P553" s="3"/>
     </row>
-    <row r="554" spans="6:16" ht="12.5">
+    <row r="554" spans="6:16" ht="13.2">
       <c r="F554" s="3"/>
       <c r="I554" s="4"/>
       <c r="J554" s="4"/>
@@ -6088,7 +6117,7 @@
       <c r="L554" s="3"/>
       <c r="P554" s="3"/>
     </row>
-    <row r="555" spans="6:16" ht="12.5">
+    <row r="555" spans="6:16" ht="13.2">
       <c r="F555" s="3"/>
       <c r="I555" s="4"/>
       <c r="J555" s="4"/>
@@ -6096,7 +6125,7 @@
       <c r="L555" s="3"/>
       <c r="P555" s="3"/>
     </row>
-    <row r="556" spans="6:16" ht="12.5">
+    <row r="556" spans="6:16" ht="13.2">
       <c r="F556" s="3"/>
       <c r="I556" s="4"/>
       <c r="J556" s="4"/>
@@ -6104,7 +6133,7 @@
       <c r="L556" s="3"/>
       <c r="P556" s="3"/>
     </row>
-    <row r="557" spans="6:16" ht="12.5">
+    <row r="557" spans="6:16" ht="13.2">
       <c r="F557" s="3"/>
       <c r="I557" s="4"/>
       <c r="J557" s="4"/>
@@ -6112,7 +6141,7 @@
       <c r="L557" s="3"/>
       <c r="P557" s="3"/>
     </row>
-    <row r="558" spans="6:16" ht="12.5">
+    <row r="558" spans="6:16" ht="13.2">
       <c r="F558" s="3"/>
       <c r="I558" s="4"/>
       <c r="J558" s="4"/>
@@ -6120,7 +6149,7 @@
       <c r="L558" s="3"/>
       <c r="P558" s="3"/>
     </row>
-    <row r="559" spans="6:16" ht="12.5">
+    <row r="559" spans="6:16" ht="13.2">
       <c r="F559" s="3"/>
       <c r="I559" s="4"/>
       <c r="J559" s="4"/>
@@ -6128,7 +6157,7 @@
       <c r="L559" s="3"/>
       <c r="P559" s="3"/>
     </row>
-    <row r="560" spans="6:16" ht="12.5">
+    <row r="560" spans="6:16" ht="13.2">
       <c r="F560" s="3"/>
       <c r="I560" s="4"/>
       <c r="J560" s="4"/>
@@ -6136,7 +6165,7 @@
       <c r="L560" s="3"/>
       <c r="P560" s="3"/>
     </row>
-    <row r="561" spans="6:16" ht="12.5">
+    <row r="561" spans="6:16" ht="13.2">
       <c r="F561" s="3"/>
       <c r="I561" s="4"/>
       <c r="J561" s="4"/>
@@ -6144,7 +6173,7 @@
       <c r="L561" s="3"/>
       <c r="P561" s="3"/>
     </row>
-    <row r="562" spans="6:16" ht="12.5">
+    <row r="562" spans="6:16" ht="13.2">
       <c r="F562" s="3"/>
       <c r="I562" s="4"/>
       <c r="J562" s="4"/>
@@ -6152,7 +6181,7 @@
       <c r="L562" s="3"/>
       <c r="P562" s="3"/>
     </row>
-    <row r="563" spans="6:16" ht="12.5">
+    <row r="563" spans="6:16" ht="13.2">
       <c r="F563" s="3"/>
       <c r="I563" s="4"/>
       <c r="J563" s="4"/>
@@ -6160,7 +6189,7 @@
       <c r="L563" s="3"/>
       <c r="P563" s="3"/>
     </row>
-    <row r="564" spans="6:16" ht="12.5">
+    <row r="564" spans="6:16" ht="13.2">
       <c r="F564" s="3"/>
       <c r="I564" s="4"/>
       <c r="J564" s="4"/>
@@ -6168,7 +6197,7 @@
       <c r="L564" s="3"/>
       <c r="P564" s="3"/>
     </row>
-    <row r="565" spans="6:16" ht="12.5">
+    <row r="565" spans="6:16" ht="13.2">
       <c r="F565" s="3"/>
       <c r="I565" s="4"/>
       <c r="J565" s="4"/>
@@ -6176,7 +6205,7 @@
       <c r="L565" s="3"/>
       <c r="P565" s="3"/>
     </row>
-    <row r="566" spans="6:16" ht="12.5">
+    <row r="566" spans="6:16" ht="13.2">
       <c r="F566" s="3"/>
       <c r="I566" s="4"/>
       <c r="J566" s="4"/>
@@ -6184,7 +6213,7 @@
       <c r="L566" s="3"/>
       <c r="P566" s="3"/>
     </row>
-    <row r="567" spans="6:16" ht="12.5">
+    <row r="567" spans="6:16" ht="13.2">
       <c r="F567" s="3"/>
       <c r="I567" s="4"/>
       <c r="J567" s="4"/>
@@ -6192,7 +6221,7 @@
       <c r="L567" s="3"/>
       <c r="P567" s="3"/>
     </row>
-    <row r="568" spans="6:16" ht="12.5">
+    <row r="568" spans="6:16" ht="13.2">
       <c r="F568" s="3"/>
       <c r="I568" s="4"/>
       <c r="J568" s="4"/>
@@ -6200,7 +6229,7 @@
       <c r="L568" s="3"/>
       <c r="P568" s="3"/>
     </row>
-    <row r="569" spans="6:16" ht="12.5">
+    <row r="569" spans="6:16" ht="13.2">
       <c r="F569" s="3"/>
       <c r="I569" s="4"/>
       <c r="J569" s="4"/>
@@ -6208,7 +6237,7 @@
       <c r="L569" s="3"/>
       <c r="P569" s="3"/>
     </row>
-    <row r="570" spans="6:16" ht="12.5">
+    <row r="570" spans="6:16" ht="13.2">
       <c r="F570" s="3"/>
       <c r="I570" s="4"/>
       <c r="J570" s="4"/>
@@ -6216,7 +6245,7 @@
       <c r="L570" s="3"/>
       <c r="P570" s="3"/>
     </row>
-    <row r="571" spans="6:16" ht="12.5">
+    <row r="571" spans="6:16" ht="13.2">
       <c r="F571" s="3"/>
       <c r="I571" s="4"/>
       <c r="J571" s="4"/>
@@ -6224,7 +6253,7 @@
       <c r="L571" s="3"/>
       <c r="P571" s="3"/>
     </row>
-    <row r="572" spans="6:16" ht="12.5">
+    <row r="572" spans="6:16" ht="13.2">
       <c r="F572" s="3"/>
       <c r="I572" s="4"/>
       <c r="J572" s="4"/>
@@ -6232,7 +6261,7 @@
       <c r="L572" s="3"/>
       <c r="P572" s="3"/>
     </row>
-    <row r="573" spans="6:16" ht="12.5">
+    <row r="573" spans="6:16" ht="13.2">
       <c r="F573" s="3"/>
       <c r="I573" s="4"/>
       <c r="J573" s="4"/>
@@ -6240,7 +6269,7 @@
       <c r="L573" s="3"/>
       <c r="P573" s="3"/>
     </row>
-    <row r="574" spans="6:16" ht="12.5">
+    <row r="574" spans="6:16" ht="13.2">
       <c r="F574" s="3"/>
       <c r="I574" s="4"/>
       <c r="J574" s="4"/>
@@ -6248,7 +6277,7 @@
       <c r="L574" s="3"/>
       <c r="P574" s="3"/>
     </row>
-    <row r="575" spans="6:16" ht="12.5">
+    <row r="575" spans="6:16" ht="13.2">
       <c r="F575" s="3"/>
       <c r="I575" s="4"/>
       <c r="J575" s="4"/>
@@ -6256,7 +6285,7 @@
       <c r="L575" s="3"/>
       <c r="P575" s="3"/>
     </row>
-    <row r="576" spans="6:16" ht="12.5">
+    <row r="576" spans="6:16" ht="13.2">
       <c r="F576" s="3"/>
       <c r="I576" s="4"/>
       <c r="J576" s="4"/>
@@ -6264,7 +6293,7 @@
       <c r="L576" s="3"/>
       <c r="P576" s="3"/>
     </row>
-    <row r="577" spans="6:16" ht="12.5">
+    <row r="577" spans="6:16" ht="13.2">
       <c r="F577" s="3"/>
       <c r="I577" s="4"/>
       <c r="J577" s="4"/>
@@ -6272,7 +6301,7 @@
       <c r="L577" s="3"/>
       <c r="P577" s="3"/>
     </row>
-    <row r="578" spans="6:16" ht="12.5">
+    <row r="578" spans="6:16" ht="13.2">
       <c r="F578" s="3"/>
       <c r="I578" s="4"/>
       <c r="J578" s="4"/>
@@ -6280,7 +6309,7 @@
       <c r="L578" s="3"/>
       <c r="P578" s="3"/>
     </row>
-    <row r="579" spans="6:16" ht="12.5">
+    <row r="579" spans="6:16" ht="13.2">
       <c r="F579" s="3"/>
       <c r="I579" s="4"/>
       <c r="J579" s="4"/>
@@ -6288,7 +6317,7 @@
       <c r="L579" s="3"/>
       <c r="P579" s="3"/>
     </row>
-    <row r="580" spans="6:16" ht="12.5">
+    <row r="580" spans="6:16" ht="13.2">
       <c r="F580" s="3"/>
       <c r="I580" s="4"/>
       <c r="J580" s="4"/>
@@ -6296,7 +6325,7 @@
       <c r="L580" s="3"/>
       <c r="P580" s="3"/>
     </row>
-    <row r="581" spans="6:16" ht="12.5">
+    <row r="581" spans="6:16" ht="13.2">
       <c r="F581" s="3"/>
       <c r="I581" s="4"/>
       <c r="J581" s="4"/>
@@ -6304,7 +6333,7 @@
       <c r="L581" s="3"/>
       <c r="P581" s="3"/>
     </row>
-    <row r="582" spans="6:16" ht="12.5">
+    <row r="582" spans="6:16" ht="13.2">
       <c r="F582" s="3"/>
       <c r="I582" s="4"/>
       <c r="J582" s="4"/>
@@ -6312,7 +6341,7 @@
       <c r="L582" s="3"/>
       <c r="P582" s="3"/>
     </row>
-    <row r="583" spans="6:16" ht="12.5">
+    <row r="583" spans="6:16" ht="13.2">
       <c r="F583" s="3"/>
       <c r="I583" s="4"/>
       <c r="J583" s="4"/>
@@ -6320,7 +6349,7 @@
       <c r="L583" s="3"/>
       <c r="P583" s="3"/>
     </row>
-    <row r="584" spans="6:16" ht="12.5">
+    <row r="584" spans="6:16" ht="13.2">
       <c r="F584" s="3"/>
       <c r="I584" s="4"/>
       <c r="J584" s="4"/>
@@ -6328,7 +6357,7 @@
       <c r="L584" s="3"/>
       <c r="P584" s="3"/>
     </row>
-    <row r="585" spans="6:16" ht="12.5">
+    <row r="585" spans="6:16" ht="13.2">
       <c r="F585" s="3"/>
       <c r="I585" s="4"/>
       <c r="J585" s="4"/>
@@ -6336,7 +6365,7 @@
       <c r="L585" s="3"/>
       <c r="P585" s="3"/>
     </row>
-    <row r="586" spans="6:16" ht="12.5">
+    <row r="586" spans="6:16" ht="13.2">
       <c r="F586" s="3"/>
       <c r="I586" s="4"/>
       <c r="J586" s="4"/>
@@ -6344,7 +6373,7 @@
       <c r="L586" s="3"/>
       <c r="P586" s="3"/>
     </row>
-    <row r="587" spans="6:16" ht="12.5">
+    <row r="587" spans="6:16" ht="13.2">
       <c r="F587" s="3"/>
       <c r="I587" s="4"/>
       <c r="J587" s="4"/>
@@ -6352,7 +6381,7 @@
       <c r="L587" s="3"/>
       <c r="P587" s="3"/>
     </row>
-    <row r="588" spans="6:16" ht="12.5">
+    <row r="588" spans="6:16" ht="13.2">
       <c r="F588" s="3"/>
       <c r="I588" s="4"/>
       <c r="J588" s="4"/>
@@ -6360,7 +6389,7 @@
       <c r="L588" s="3"/>
       <c r="P588" s="3"/>
     </row>
-    <row r="589" spans="6:16" ht="12.5">
+    <row r="589" spans="6:16" ht="13.2">
       <c r="F589" s="3"/>
       <c r="I589" s="4"/>
       <c r="J589" s="4"/>
@@ -6368,7 +6397,7 @@
       <c r="L589" s="3"/>
       <c r="P589" s="3"/>
     </row>
-    <row r="590" spans="6:16" ht="12.5">
+    <row r="590" spans="6:16" ht="13.2">
       <c r="F590" s="3"/>
       <c r="I590" s="4"/>
       <c r="J590" s="4"/>
@@ -6376,7 +6405,7 @@
       <c r="L590" s="3"/>
       <c r="P590" s="3"/>
     </row>
-    <row r="591" spans="6:16" ht="12.5">
+    <row r="591" spans="6:16" ht="13.2">
       <c r="F591" s="3"/>
       <c r="I591" s="4"/>
       <c r="J591" s="4"/>
@@ -6384,7 +6413,7 @@
       <c r="L591" s="3"/>
       <c r="P591" s="3"/>
     </row>
-    <row r="592" spans="6:16" ht="12.5">
+    <row r="592" spans="6:16" ht="13.2">
       <c r="F592" s="3"/>
       <c r="I592" s="4"/>
       <c r="J592" s="4"/>
@@ -6392,7 +6421,7 @@
       <c r="L592" s="3"/>
       <c r="P592" s="3"/>
     </row>
-    <row r="593" spans="6:16" ht="12.5">
+    <row r="593" spans="6:16" ht="13.2">
       <c r="F593" s="3"/>
       <c r="I593" s="4"/>
       <c r="J593" s="4"/>
@@ -6400,7 +6429,7 @@
       <c r="L593" s="3"/>
       <c r="P593" s="3"/>
     </row>
-    <row r="594" spans="6:16" ht="12.5">
+    <row r="594" spans="6:16" ht="13.2">
       <c r="F594" s="3"/>
       <c r="I594" s="4"/>
       <c r="J594" s="4"/>
@@ -6408,7 +6437,7 @@
       <c r="L594" s="3"/>
       <c r="P594" s="3"/>
     </row>
-    <row r="595" spans="6:16" ht="12.5">
+    <row r="595" spans="6:16" ht="13.2">
       <c r="F595" s="3"/>
       <c r="I595" s="4"/>
       <c r="J595" s="4"/>
@@ -6416,7 +6445,7 @@
       <c r="L595" s="3"/>
       <c r="P595" s="3"/>
     </row>
-    <row r="596" spans="6:16" ht="12.5">
+    <row r="596" spans="6:16" ht="13.2">
       <c r="F596" s="3"/>
       <c r="I596" s="4"/>
       <c r="J596" s="4"/>
@@ -6424,7 +6453,7 @@
       <c r="L596" s="3"/>
       <c r="P596" s="3"/>
     </row>
-    <row r="597" spans="6:16" ht="12.5">
+    <row r="597" spans="6:16" ht="13.2">
       <c r="F597" s="3"/>
       <c r="I597" s="4"/>
       <c r="J597" s="4"/>
@@ -6432,7 +6461,7 @@
       <c r="L597" s="3"/>
       <c r="P597" s="3"/>
     </row>
-    <row r="598" spans="6:16" ht="12.5">
+    <row r="598" spans="6:16" ht="13.2">
       <c r="F598" s="3"/>
       <c r="I598" s="4"/>
       <c r="J598" s="4"/>
@@ -6440,7 +6469,7 @@
       <c r="L598" s="3"/>
       <c r="P598" s="3"/>
     </row>
-    <row r="599" spans="6:16" ht="12.5">
+    <row r="599" spans="6:16" ht="13.2">
       <c r="F599" s="3"/>
       <c r="I599" s="4"/>
       <c r="J599" s="4"/>
@@ -6448,7 +6477,7 @@
       <c r="L599" s="3"/>
       <c r="P599" s="3"/>
     </row>
-    <row r="600" spans="6:16" ht="12.5">
+    <row r="600" spans="6:16" ht="13.2">
       <c r="F600" s="3"/>
       <c r="I600" s="4"/>
       <c r="J600" s="4"/>
@@ -6456,7 +6485,7 @@
       <c r="L600" s="3"/>
       <c r="P600" s="3"/>
     </row>
-    <row r="601" spans="6:16" ht="12.5">
+    <row r="601" spans="6:16" ht="13.2">
       <c r="F601" s="3"/>
       <c r="I601" s="4"/>
       <c r="J601" s="4"/>
@@ -6464,7 +6493,7 @@
       <c r="L601" s="3"/>
       <c r="P601" s="3"/>
     </row>
-    <row r="602" spans="6:16" ht="12.5">
+    <row r="602" spans="6:16" ht="13.2">
       <c r="F602" s="3"/>
       <c r="I602" s="4"/>
       <c r="J602" s="4"/>
@@ -6472,7 +6501,7 @@
       <c r="L602" s="3"/>
       <c r="P602" s="3"/>
     </row>
-    <row r="603" spans="6:16" ht="12.5">
+    <row r="603" spans="6:16" ht="13.2">
       <c r="F603" s="3"/>
       <c r="I603" s="4"/>
       <c r="J603" s="4"/>
@@ -6480,7 +6509,7 @@
       <c r="L603" s="3"/>
       <c r="P603" s="3"/>
     </row>
-    <row r="604" spans="6:16" ht="12.5">
+    <row r="604" spans="6:16" ht="13.2">
       <c r="F604" s="3"/>
       <c r="I604" s="4"/>
       <c r="J604" s="4"/>
@@ -6488,7 +6517,7 @@
       <c r="L604" s="3"/>
       <c r="P604" s="3"/>
     </row>
-    <row r="605" spans="6:16" ht="12.5">
+    <row r="605" spans="6:16" ht="13.2">
       <c r="F605" s="3"/>
       <c r="I605" s="4"/>
       <c r="J605" s="4"/>
@@ -6496,7 +6525,7 @@
       <c r="L605" s="3"/>
       <c r="P605" s="3"/>
     </row>
-    <row r="606" spans="6:16" ht="12.5">
+    <row r="606" spans="6:16" ht="13.2">
       <c r="F606" s="3"/>
       <c r="I606" s="4"/>
       <c r="J606" s="4"/>
@@ -6504,7 +6533,7 @@
       <c r="L606" s="3"/>
       <c r="P606" s="3"/>
     </row>
-    <row r="607" spans="6:16" ht="12.5">
+    <row r="607" spans="6:16" ht="13.2">
       <c r="F607" s="3"/>
       <c r="I607" s="4"/>
       <c r="J607" s="4"/>
@@ -6512,7 +6541,7 @@
       <c r="L607" s="3"/>
       <c r="P607" s="3"/>
     </row>
-    <row r="608" spans="6:16" ht="12.5">
+    <row r="608" spans="6:16" ht="13.2">
       <c r="F608" s="3"/>
       <c r="I608" s="4"/>
       <c r="J608" s="4"/>
@@ -6520,7 +6549,7 @@
       <c r="L608" s="3"/>
       <c r="P608" s="3"/>
     </row>
-    <row r="609" spans="6:16" ht="12.5">
+    <row r="609" spans="6:16" ht="13.2">
       <c r="F609" s="3"/>
       <c r="I609" s="4"/>
       <c r="J609" s="4"/>
@@ -6528,7 +6557,7 @@
       <c r="L609" s="3"/>
       <c r="P609" s="3"/>
     </row>
-    <row r="610" spans="6:16" ht="12.5">
+    <row r="610" spans="6:16" ht="13.2">
       <c r="F610" s="3"/>
       <c r="I610" s="4"/>
       <c r="J610" s="4"/>
@@ -6536,7 +6565,7 @@
       <c r="L610" s="3"/>
       <c r="P610" s="3"/>
     </row>
-    <row r="611" spans="6:16" ht="12.5">
+    <row r="611" spans="6:16" ht="13.2">
       <c r="F611" s="3"/>
       <c r="I611" s="4"/>
       <c r="J611" s="4"/>
@@ -6544,7 +6573,7 @@
       <c r="L611" s="3"/>
       <c r="P611" s="3"/>
     </row>
-    <row r="612" spans="6:16" ht="12.5">
+    <row r="612" spans="6:16" ht="13.2">
       <c r="F612" s="3"/>
       <c r="I612" s="4"/>
       <c r="J612" s="4"/>
@@ -6552,7 +6581,7 @@
       <c r="L612" s="3"/>
       <c r="P612" s="3"/>
     </row>
-    <row r="613" spans="6:16" ht="12.5">
+    <row r="613" spans="6:16" ht="13.2">
       <c r="F613" s="3"/>
       <c r="I613" s="4"/>
       <c r="J613" s="4"/>
@@ -6560,7 +6589,7 @@
       <c r="L613" s="3"/>
       <c r="P613" s="3"/>
     </row>
-    <row r="614" spans="6:16" ht="12.5">
+    <row r="614" spans="6:16" ht="13.2">
       <c r="F614" s="3"/>
       <c r="I614" s="4"/>
       <c r="J614" s="4"/>
@@ -6568,7 +6597,7 @@
       <c r="L614" s="3"/>
       <c r="P614" s="3"/>
     </row>
-    <row r="615" spans="6:16" ht="12.5">
+    <row r="615" spans="6:16" ht="13.2">
       <c r="F615" s="3"/>
       <c r="I615" s="4"/>
       <c r="J615" s="4"/>
@@ -6576,7 +6605,7 @@
       <c r="L615" s="3"/>
       <c r="P615" s="3"/>
     </row>
-    <row r="616" spans="6:16" ht="12.5">
+    <row r="616" spans="6:16" ht="13.2">
       <c r="F616" s="3"/>
       <c r="I616" s="4"/>
       <c r="J616" s="4"/>
@@ -6584,7 +6613,7 @@
       <c r="L616" s="3"/>
       <c r="P616" s="3"/>
     </row>
-    <row r="617" spans="6:16" ht="12.5">
+    <row r="617" spans="6:16" ht="13.2">
       <c r="F617" s="3"/>
       <c r="I617" s="4"/>
       <c r="J617" s="4"/>
@@ -6592,7 +6621,7 @@
       <c r="L617" s="3"/>
       <c r="P617" s="3"/>
     </row>
-    <row r="618" spans="6:16" ht="12.5">
+    <row r="618" spans="6:16" ht="13.2">
       <c r="F618" s="3"/>
       <c r="I618" s="4"/>
       <c r="J618" s="4"/>
@@ -6600,7 +6629,7 @@
       <c r="L618" s="3"/>
       <c r="P618" s="3"/>
     </row>
-    <row r="619" spans="6:16" ht="12.5">
+    <row r="619" spans="6:16" ht="13.2">
       <c r="F619" s="3"/>
       <c r="I619" s="4"/>
       <c r="J619" s="4"/>
@@ -6608,7 +6637,7 @@
       <c r="L619" s="3"/>
       <c r="P619" s="3"/>
     </row>
-    <row r="620" spans="6:16" ht="12.5">
+    <row r="620" spans="6:16" ht="13.2">
       <c r="F620" s="3"/>
       <c r="I620" s="4"/>
       <c r="J620" s="4"/>
@@ -6616,7 +6645,7 @@
       <c r="L620" s="3"/>
       <c r="P620" s="3"/>
     </row>
-    <row r="621" spans="6:16" ht="12.5">
+    <row r="621" spans="6:16" ht="13.2">
       <c r="F621" s="3"/>
       <c r="I621" s="4"/>
       <c r="J621" s="4"/>
@@ -6624,7 +6653,7 @@
       <c r="L621" s="3"/>
       <c r="P621" s="3"/>
     </row>
-    <row r="622" spans="6:16" ht="12.5">
+    <row r="622" spans="6:16" ht="13.2">
       <c r="F622" s="3"/>
       <c r="I622" s="4"/>
       <c r="J622" s="4"/>
@@ -6632,7 +6661,7 @@
       <c r="L622" s="3"/>
       <c r="P622" s="3"/>
     </row>
-    <row r="623" spans="6:16" ht="12.5">
+    <row r="623" spans="6:16" ht="13.2">
       <c r="F623" s="3"/>
       <c r="I623" s="4"/>
       <c r="J623" s="4"/>
@@ -6640,7 +6669,7 @@
       <c r="L623" s="3"/>
       <c r="P623" s="3"/>
     </row>
-    <row r="624" spans="6:16" ht="12.5">
+    <row r="624" spans="6:16" ht="13.2">
       <c r="F624" s="3"/>
       <c r="I624" s="4"/>
       <c r="J624" s="4"/>
@@ -6648,7 +6677,7 @@
       <c r="L624" s="3"/>
       <c r="P624" s="3"/>
     </row>
-    <row r="625" spans="6:16" ht="12.5">
+    <row r="625" spans="6:16" ht="13.2">
       <c r="F625" s="3"/>
       <c r="I625" s="4"/>
       <c r="J625" s="4"/>
@@ -6656,7 +6685,7 @@
       <c r="L625" s="3"/>
       <c r="P625" s="3"/>
     </row>
-    <row r="626" spans="6:16" ht="12.5">
+    <row r="626" spans="6:16" ht="13.2">
       <c r="F626" s="3"/>
       <c r="I626" s="4"/>
       <c r="J626" s="4"/>
@@ -6664,7 +6693,7 @@
       <c r="L626" s="3"/>
       <c r="P626" s="3"/>
     </row>
-    <row r="627" spans="6:16" ht="12.5">
+    <row r="627" spans="6:16" ht="13.2">
       <c r="F627" s="3"/>
       <c r="I627" s="4"/>
       <c r="J627" s="4"/>
@@ -6672,7 +6701,7 @@
       <c r="L627" s="3"/>
       <c r="P627" s="3"/>
     </row>
-    <row r="628" spans="6:16" ht="12.5">
+    <row r="628" spans="6:16" ht="13.2">
       <c r="F628" s="3"/>
       <c r="I628" s="4"/>
       <c r="J628" s="4"/>
@@ -6680,7 +6709,7 @@
       <c r="L628" s="3"/>
       <c r="P628" s="3"/>
     </row>
-    <row r="629" spans="6:16" ht="12.5">
+    <row r="629" spans="6:16" ht="13.2">
       <c r="F629" s="3"/>
       <c r="I629" s="4"/>
       <c r="J629" s="4"/>
@@ -6688,7 +6717,7 @@
       <c r="L629" s="3"/>
       <c r="P629" s="3"/>
     </row>
-    <row r="630" spans="6:16" ht="12.5">
+    <row r="630" spans="6:16" ht="13.2">
       <c r="F630" s="3"/>
       <c r="I630" s="4"/>
       <c r="J630" s="4"/>
@@ -6696,7 +6725,7 @@
       <c r="L630" s="3"/>
       <c r="P630" s="3"/>
     </row>
-    <row r="631" spans="6:16" ht="12.5">
+    <row r="631" spans="6:16" ht="13.2">
       <c r="F631" s="3"/>
       <c r="I631" s="4"/>
       <c r="J631" s="4"/>
@@ -6704,7 +6733,7 @@
       <c r="L631" s="3"/>
       <c r="P631" s="3"/>
     </row>
-    <row r="632" spans="6:16" ht="12.5">
+    <row r="632" spans="6:16" ht="13.2">
       <c r="F632" s="3"/>
       <c r="I632" s="4"/>
       <c r="J632" s="4"/>
@@ -6712,7 +6741,7 @@
       <c r="L632" s="3"/>
       <c r="P632" s="3"/>
     </row>
-    <row r="633" spans="6:16" ht="12.5">
+    <row r="633" spans="6:16" ht="13.2">
       <c r="F633" s="3"/>
       <c r="I633" s="4"/>
       <c r="J633" s="4"/>
@@ -6720,7 +6749,7 @@
       <c r="L633" s="3"/>
       <c r="P633" s="3"/>
     </row>
-    <row r="634" spans="6:16" ht="12.5">
+    <row r="634" spans="6:16" ht="13.2">
       <c r="F634" s="3"/>
       <c r="I634" s="4"/>
       <c r="J634" s="4"/>
@@ -6728,7 +6757,7 @@
       <c r="L634" s="3"/>
       <c r="P634" s="3"/>
     </row>
-    <row r="635" spans="6:16" ht="12.5">
+    <row r="635" spans="6:16" ht="13.2">
       <c r="F635" s="3"/>
       <c r="I635" s="4"/>
       <c r="J635" s="4"/>
@@ -6736,7 +6765,7 @@
       <c r="L635" s="3"/>
       <c r="P635" s="3"/>
     </row>
-    <row r="636" spans="6:16" ht="12.5">
+    <row r="636" spans="6:16" ht="13.2">
       <c r="F636" s="3"/>
       <c r="I636" s="4"/>
       <c r="J636" s="4"/>
@@ -6744,7 +6773,7 @@
       <c r="L636" s="3"/>
       <c r="P636" s="3"/>
     </row>
-    <row r="637" spans="6:16" ht="12.5">
+    <row r="637" spans="6:16" ht="13.2">
       <c r="F637" s="3"/>
       <c r="I637" s="4"/>
       <c r="J637" s="4"/>
@@ -6752,7 +6781,7 @@
       <c r="L637" s="3"/>
       <c r="P637" s="3"/>
     </row>
-    <row r="638" spans="6:16" ht="12.5">
+    <row r="638" spans="6:16" ht="13.2">
       <c r="F638" s="3"/>
       <c r="I638" s="4"/>
       <c r="J638" s="4"/>
@@ -6760,7 +6789,7 @@
       <c r="L638" s="3"/>
       <c r="P638" s="3"/>
     </row>
-    <row r="639" spans="6:16" ht="12.5">
+    <row r="639" spans="6:16" ht="13.2">
       <c r="F639" s="3"/>
       <c r="I639" s="4"/>
       <c r="J639" s="4"/>
@@ -6768,7 +6797,7 @@
       <c r="L639" s="3"/>
       <c r="P639" s="3"/>
     </row>
-    <row r="640" spans="6:16" ht="12.5">
+    <row r="640" spans="6:16" ht="13.2">
       <c r="F640" s="3"/>
       <c r="I640" s="4"/>
       <c r="J640" s="4"/>
@@ -6776,7 +6805,7 @@
       <c r="L640" s="3"/>
       <c r="P640" s="3"/>
     </row>
-    <row r="641" spans="6:16" ht="12.5">
+    <row r="641" spans="6:16" ht="13.2">
       <c r="F641" s="3"/>
       <c r="I641" s="4"/>
       <c r="J641" s="4"/>
@@ -6784,7 +6813,7 @@
       <c r="L641" s="3"/>
       <c r="P641" s="3"/>
     </row>
-    <row r="642" spans="6:16" ht="12.5">
+    <row r="642" spans="6:16" ht="13.2">
       <c r="F642" s="3"/>
       <c r="I642" s="4"/>
       <c r="J642" s="4"/>
@@ -6792,7 +6821,7 @@
       <c r="L642" s="3"/>
       <c r="P642" s="3"/>
     </row>
-    <row r="643" spans="6:16" ht="12.5">
+    <row r="643" spans="6:16" ht="13.2">
       <c r="F643" s="3"/>
       <c r="I643" s="4"/>
       <c r="J643" s="4"/>
@@ -6800,7 +6829,7 @@
       <c r="L643" s="3"/>
       <c r="P643" s="3"/>
     </row>
-    <row r="644" spans="6:16" ht="12.5">
+    <row r="644" spans="6:16" ht="13.2">
       <c r="F644" s="3"/>
       <c r="I644" s="4"/>
       <c r="J644" s="4"/>
@@ -6808,7 +6837,7 @@
       <c r="L644" s="3"/>
       <c r="P644" s="3"/>
     </row>
-    <row r="645" spans="6:16" ht="12.5">
+    <row r="645" spans="6:16" ht="13.2">
       <c r="F645" s="3"/>
       <c r="I645" s="4"/>
       <c r="J645" s="4"/>
@@ -6816,7 +6845,7 @@
       <c r="L645" s="3"/>
       <c r="P645" s="3"/>
     </row>
-    <row r="646" spans="6:16" ht="12.5">
+    <row r="646" spans="6:16" ht="13.2">
       <c r="F646" s="3"/>
       <c r="I646" s="4"/>
       <c r="J646" s="4"/>
@@ -6824,7 +6853,7 @@
       <c r="L646" s="3"/>
       <c r="P646" s="3"/>
     </row>
-    <row r="647" spans="6:16" ht="12.5">
+    <row r="647" spans="6:16" ht="13.2">
       <c r="F647" s="3"/>
       <c r="I647" s="4"/>
       <c r="J647" s="4"/>
@@ -6832,7 +6861,7 @@
       <c r="L647" s="3"/>
       <c r="P647" s="3"/>
     </row>
-    <row r="648" spans="6:16" ht="12.5">
+    <row r="648" spans="6:16" ht="13.2">
       <c r="F648" s="3"/>
       <c r="I648" s="4"/>
       <c r="J648" s="4"/>
@@ -6840,7 +6869,7 @@
       <c r="L648" s="3"/>
       <c r="P648" s="3"/>
     </row>
-    <row r="649" spans="6:16" ht="12.5">
+    <row r="649" spans="6:16" ht="13.2">
       <c r="F649" s="3"/>
       <c r="I649" s="4"/>
       <c r="J649" s="4"/>
@@ -6848,7 +6877,7 @@
       <c r="L649" s="3"/>
       <c r="P649" s="3"/>
     </row>
-    <row r="650" spans="6:16" ht="12.5">
+    <row r="650" spans="6:16" ht="13.2">
       <c r="F650" s="3"/>
       <c r="I650" s="4"/>
       <c r="J650" s="4"/>
@@ -6856,7 +6885,7 @@
       <c r="L650" s="3"/>
       <c r="P650" s="3"/>
     </row>
-    <row r="651" spans="6:16" ht="12.5">
+    <row r="651" spans="6:16" ht="13.2">
       <c r="F651" s="3"/>
       <c r="I651" s="4"/>
       <c r="J651" s="4"/>
@@ -6864,7 +6893,7 @@
       <c r="L651" s="3"/>
       <c r="P651" s="3"/>
     </row>
-    <row r="652" spans="6:16" ht="12.5">
+    <row r="652" spans="6:16" ht="13.2">
       <c r="F652" s="3"/>
       <c r="I652" s="4"/>
       <c r="J652" s="4"/>
@@ -6872,7 +6901,7 @@
       <c r="L652" s="3"/>
       <c r="P652" s="3"/>
     </row>
-    <row r="653" spans="6:16" ht="12.5">
+    <row r="653" spans="6:16" ht="13.2">
       <c r="F653" s="3"/>
       <c r="I653" s="4"/>
       <c r="J653" s="4"/>
@@ -6880,7 +6909,7 @@
       <c r="L653" s="3"/>
       <c r="P653" s="3"/>
     </row>
-    <row r="654" spans="6:16" ht="12.5">
+    <row r="654" spans="6:16" ht="13.2">
       <c r="F654" s="3"/>
       <c r="I654" s="4"/>
       <c r="J654" s="4"/>
@@ -6888,7 +6917,7 @@
       <c r="L654" s="3"/>
       <c r="P654" s="3"/>
     </row>
-    <row r="655" spans="6:16" ht="12.5">
+    <row r="655" spans="6:16" ht="13.2">
       <c r="F655" s="3"/>
       <c r="I655" s="4"/>
       <c r="J655" s="4"/>
@@ -6896,7 +6925,7 @@
       <c r="L655" s="3"/>
       <c r="P655" s="3"/>
     </row>
-    <row r="656" spans="6:16" ht="12.5">
+    <row r="656" spans="6:16" ht="13.2">
       <c r="F656" s="3"/>
       <c r="I656" s="4"/>
       <c r="J656" s="4"/>
@@ -6904,7 +6933,7 @@
       <c r="L656" s="3"/>
       <c r="P656" s="3"/>
     </row>
-    <row r="657" spans="6:16" ht="12.5">
+    <row r="657" spans="6:16" ht="13.2">
       <c r="F657" s="3"/>
       <c r="I657" s="4"/>
       <c r="J657" s="4"/>
@@ -6912,7 +6941,7 @@
       <c r="L657" s="3"/>
       <c r="P657" s="3"/>
     </row>
-    <row r="658" spans="6:16" ht="12.5">
+    <row r="658" spans="6:16" ht="13.2">
       <c r="F658" s="3"/>
       <c r="I658" s="4"/>
       <c r="J658" s="4"/>
@@ -6920,7 +6949,7 @@
       <c r="L658" s="3"/>
       <c r="P658" s="3"/>
     </row>
-    <row r="659" spans="6:16" ht="12.5">
+    <row r="659" spans="6:16" ht="13.2">
       <c r="F659" s="3"/>
       <c r="I659" s="4"/>
       <c r="J659" s="4"/>
@@ -6928,7 +6957,7 @@
       <c r="L659" s="3"/>
       <c r="P659" s="3"/>
     </row>
-    <row r="660" spans="6:16" ht="12.5">
+    <row r="660" spans="6:16" ht="13.2">
       <c r="F660" s="3"/>
       <c r="I660" s="4"/>
       <c r="J660" s="4"/>
@@ -6936,7 +6965,7 @@
       <c r="L660" s="3"/>
       <c r="P660" s="3"/>
     </row>
-    <row r="661" spans="6:16" ht="12.5">
+    <row r="661" spans="6:16" ht="13.2">
       <c r="F661" s="3"/>
       <c r="I661" s="4"/>
       <c r="J661" s="4"/>
@@ -6944,7 +6973,7 @@
       <c r="L661" s="3"/>
       <c r="P661" s="3"/>
     </row>
-    <row r="662" spans="6:16" ht="12.5">
+    <row r="662" spans="6:16" ht="13.2">
       <c r="F662" s="3"/>
       <c r="I662" s="4"/>
       <c r="J662" s="4"/>
@@ -6952,7 +6981,7 @@
       <c r="L662" s="3"/>
       <c r="P662" s="3"/>
     </row>
-    <row r="663" spans="6:16" ht="12.5">
+    <row r="663" spans="6:16" ht="13.2">
       <c r="F663" s="3"/>
       <c r="I663" s="4"/>
       <c r="J663" s="4"/>
@@ -6960,7 +6989,7 @@
       <c r="L663" s="3"/>
       <c r="P663" s="3"/>
     </row>
-    <row r="664" spans="6:16" ht="12.5">
+    <row r="664" spans="6:16" ht="13.2">
       <c r="F664" s="3"/>
       <c r="I664" s="4"/>
       <c r="J664" s="4"/>
@@ -6968,7 +6997,7 @@
       <c r="L664" s="3"/>
       <c r="P664" s="3"/>
     </row>
-    <row r="665" spans="6:16" ht="12.5">
+    <row r="665" spans="6:16" ht="13.2">
       <c r="F665" s="3"/>
       <c r="I665" s="4"/>
       <c r="J665" s="4"/>
@@ -6976,7 +7005,7 @@
       <c r="L665" s="3"/>
       <c r="P665" s="3"/>
     </row>
-    <row r="666" spans="6:16" ht="12.5">
+    <row r="666" spans="6:16" ht="13.2">
       <c r="F666" s="3"/>
       <c r="I666" s="4"/>
       <c r="J666" s="4"/>
@@ -6984,7 +7013,7 @@
       <c r="L666" s="3"/>
       <c r="P666" s="3"/>
     </row>
-    <row r="667" spans="6:16" ht="12.5">
+    <row r="667" spans="6:16" ht="13.2">
       <c r="F667" s="3"/>
       <c r="I667" s="4"/>
       <c r="J667" s="4"/>
@@ -6992,7 +7021,7 @@
       <c r="L667" s="3"/>
       <c r="P667" s="3"/>
     </row>
-    <row r="668" spans="6:16" ht="12.5">
+    <row r="668" spans="6:16" ht="13.2">
       <c r="F668" s="3"/>
       <c r="I668" s="4"/>
       <c r="J668" s="4"/>
@@ -7000,7 +7029,7 @@
       <c r="L668" s="3"/>
       <c r="P668" s="3"/>
     </row>
-    <row r="669" spans="6:16" ht="12.5">
+    <row r="669" spans="6:16" ht="13.2">
       <c r="F669" s="3"/>
       <c r="I669" s="4"/>
       <c r="J669" s="4"/>
@@ -7008,7 +7037,7 @@
       <c r="L669" s="3"/>
       <c r="P669" s="3"/>
     </row>
-    <row r="670" spans="6:16" ht="12.5">
+    <row r="670" spans="6:16" ht="13.2">
       <c r="F670" s="3"/>
       <c r="I670" s="4"/>
       <c r="J670" s="4"/>
@@ -7016,7 +7045,7 @@
       <c r="L670" s="3"/>
       <c r="P670" s="3"/>
     </row>
-    <row r="671" spans="6:16" ht="12.5">
+    <row r="671" spans="6:16" ht="13.2">
       <c r="F671" s="3"/>
       <c r="I671" s="4"/>
       <c r="J671" s="4"/>
@@ -7024,7 +7053,7 @@
       <c r="L671" s="3"/>
       <c r="P671" s="3"/>
     </row>
-    <row r="672" spans="6:16" ht="12.5">
+    <row r="672" spans="6:16" ht="13.2">
       <c r="F672" s="3"/>
       <c r="I672" s="4"/>
       <c r="J672" s="4"/>
@@ -7032,7 +7061,7 @@
       <c r="L672" s="3"/>
       <c r="P672" s="3"/>
     </row>
-    <row r="673" spans="6:16" ht="12.5">
+    <row r="673" spans="6:16" ht="13.2">
       <c r="F673" s="3"/>
       <c r="I673" s="4"/>
       <c r="J673" s="4"/>
@@ -7040,7 +7069,7 @@
       <c r="L673" s="3"/>
       <c r="P673" s="3"/>
     </row>
-    <row r="674" spans="6:16" ht="12.5">
+    <row r="674" spans="6:16" ht="13.2">
       <c r="F674" s="3"/>
       <c r="I674" s="4"/>
       <c r="J674" s="4"/>
@@ -7048,7 +7077,7 @@
       <c r="L674" s="3"/>
       <c r="P674" s="3"/>
     </row>
-    <row r="675" spans="6:16" ht="12.5">
+    <row r="675" spans="6:16" ht="13.2">
       <c r="F675" s="3"/>
       <c r="I675" s="4"/>
       <c r="J675" s="4"/>
@@ -7056,7 +7085,7 @@
       <c r="L675" s="3"/>
       <c r="P675" s="3"/>
     </row>
-    <row r="676" spans="6:16" ht="12.5">
+    <row r="676" spans="6:16" ht="13.2">
       <c r="F676" s="3"/>
       <c r="I676" s="4"/>
       <c r="J676" s="4"/>
@@ -7064,7 +7093,7 @@
       <c r="L676" s="3"/>
       <c r="P676" s="3"/>
     </row>
-    <row r="677" spans="6:16" ht="12.5">
+    <row r="677" spans="6:16" ht="13.2">
       <c r="F677" s="3"/>
       <c r="I677" s="4"/>
       <c r="J677" s="4"/>
@@ -7072,7 +7101,7 @@
       <c r="L677" s="3"/>
       <c r="P677" s="3"/>
     </row>
-    <row r="678" spans="6:16" ht="12.5">
+    <row r="678" spans="6:16" ht="13.2">
       <c r="F678" s="3"/>
       <c r="I678" s="4"/>
       <c r="J678" s="4"/>
@@ -7080,7 +7109,7 @@
       <c r="L678" s="3"/>
       <c r="P678" s="3"/>
     </row>
-    <row r="679" spans="6:16" ht="12.5">
+    <row r="679" spans="6:16" ht="13.2">
       <c r="F679" s="3"/>
       <c r="I679" s="4"/>
       <c r="J679" s="4"/>
@@ -7088,7 +7117,7 @@
       <c r="L679" s="3"/>
       <c r="P679" s="3"/>
     </row>
-    <row r="680" spans="6:16" ht="12.5">
+    <row r="680" spans="6:16" ht="13.2">
       <c r="F680" s="3"/>
       <c r="I680" s="4"/>
       <c r="J680" s="4"/>
@@ -7096,7 +7125,7 @@
       <c r="L680" s="3"/>
       <c r="P680" s="3"/>
     </row>
-    <row r="681" spans="6:16" ht="12.5">
+    <row r="681" spans="6:16" ht="13.2">
       <c r="F681" s="3"/>
       <c r="I681" s="4"/>
       <c r="J681" s="4"/>
@@ -7104,7 +7133,7 @@
       <c r="L681" s="3"/>
       <c r="P681" s="3"/>
     </row>
-    <row r="682" spans="6:16" ht="12.5">
+    <row r="682" spans="6:16" ht="13.2">
       <c r="F682" s="3"/>
       <c r="I682" s="4"/>
       <c r="J682" s="4"/>
@@ -7112,7 +7141,7 @@
       <c r="L682" s="3"/>
       <c r="P682" s="3"/>
     </row>
-    <row r="683" spans="6:16" ht="12.5">
+    <row r="683" spans="6:16" ht="13.2">
       <c r="F683" s="3"/>
       <c r="I683" s="4"/>
       <c r="J683" s="4"/>
@@ -7120,7 +7149,7 @@
       <c r="L683" s="3"/>
       <c r="P683" s="3"/>
     </row>
-    <row r="684" spans="6:16" ht="12.5">
+    <row r="684" spans="6:16" ht="13.2">
       <c r="F684" s="3"/>
       <c r="I684" s="4"/>
       <c r="J684" s="4"/>
@@ -7128,7 +7157,7 @@
       <c r="L684" s="3"/>
       <c r="P684" s="3"/>
     </row>
-    <row r="685" spans="6:16" ht="12.5">
+    <row r="685" spans="6:16" ht="13.2">
       <c r="F685" s="3"/>
       <c r="I685" s="4"/>
       <c r="J685" s="4"/>
@@ -7136,7 +7165,7 @@
       <c r="L685" s="3"/>
       <c r="P685" s="3"/>
     </row>
-    <row r="686" spans="6:16" ht="12.5">
+    <row r="686" spans="6:16" ht="13.2">
       <c r="F686" s="3"/>
       <c r="I686" s="4"/>
       <c r="J686" s="4"/>
@@ -7144,7 +7173,7 @@
       <c r="L686" s="3"/>
       <c r="P686" s="3"/>
     </row>
-    <row r="687" spans="6:16" ht="12.5">
+    <row r="687" spans="6:16" ht="13.2">
       <c r="F687" s="3"/>
       <c r="I687" s="4"/>
       <c r="J687" s="4"/>
@@ -7152,7 +7181,7 @@
       <c r="L687" s="3"/>
       <c r="P687" s="3"/>
     </row>
-    <row r="688" spans="6:16" ht="12.5">
+    <row r="688" spans="6:16" ht="13.2">
       <c r="F688" s="3"/>
       <c r="I688" s="4"/>
       <c r="J688" s="4"/>
@@ -7160,7 +7189,7 @@
       <c r="L688" s="3"/>
       <c r="P688" s="3"/>
     </row>
-    <row r="689" spans="6:16" ht="12.5">
+    <row r="689" spans="6:16" ht="13.2">
       <c r="F689" s="3"/>
       <c r="I689" s="4"/>
       <c r="J689" s="4"/>
@@ -7168,7 +7197,7 @@
       <c r="L689" s="3"/>
       <c r="P689" s="3"/>
     </row>
-    <row r="690" spans="6:16" ht="12.5">
+    <row r="690" spans="6:16" ht="13.2">
       <c r="F690" s="3"/>
       <c r="I690" s="4"/>
       <c r="J690" s="4"/>
@@ -7176,7 +7205,7 @@
       <c r="L690" s="3"/>
       <c r="P690" s="3"/>
     </row>
-    <row r="691" spans="6:16" ht="12.5">
+    <row r="691" spans="6:16" ht="13.2">
       <c r="F691" s="3"/>
       <c r="I691" s="4"/>
       <c r="J691" s="4"/>
@@ -7184,7 +7213,7 @@
       <c r="L691" s="3"/>
       <c r="P691" s="3"/>
     </row>
-    <row r="692" spans="6:16" ht="12.5">
+    <row r="692" spans="6:16" ht="13.2">
       <c r="F692" s="3"/>
       <c r="I692" s="4"/>
       <c r="J692" s="4"/>
@@ -7192,7 +7221,7 @@
       <c r="L692" s="3"/>
       <c r="P692" s="3"/>
     </row>
-    <row r="693" spans="6:16" ht="12.5">
+    <row r="693" spans="6:16" ht="13.2">
       <c r="F693" s="3"/>
       <c r="I693" s="4"/>
       <c r="J693" s="4"/>
@@ -7200,7 +7229,7 @@
       <c r="L693" s="3"/>
       <c r="P693" s="3"/>
     </row>
-    <row r="694" spans="6:16" ht="12.5">
+    <row r="694" spans="6:16" ht="13.2">
       <c r="F694" s="3"/>
       <c r="I694" s="4"/>
       <c r="J694" s="4"/>
@@ -7208,7 +7237,7 @@
       <c r="L694" s="3"/>
       <c r="P694" s="3"/>
     </row>
-    <row r="695" spans="6:16" ht="12.5">
+    <row r="695" spans="6:16" ht="13.2">
       <c r="F695" s="3"/>
       <c r="I695" s="4"/>
       <c r="J695" s="4"/>
@@ -7216,7 +7245,7 @@
       <c r="L695" s="3"/>
       <c r="P695" s="3"/>
     </row>
-    <row r="696" spans="6:16" ht="12.5">
+    <row r="696" spans="6:16" ht="13.2">
       <c r="F696" s="3"/>
       <c r="I696" s="4"/>
       <c r="J696" s="4"/>
@@ -7224,7 +7253,7 @@
       <c r="L696" s="3"/>
       <c r="P696" s="3"/>
     </row>
-    <row r="697" spans="6:16" ht="12.5">
+    <row r="697" spans="6:16" ht="13.2">
       <c r="F697" s="3"/>
       <c r="I697" s="4"/>
       <c r="J697" s="4"/>
@@ -7232,7 +7261,7 @@
       <c r="L697" s="3"/>
       <c r="P697" s="3"/>
     </row>
-    <row r="698" spans="6:16" ht="12.5">
+    <row r="698" spans="6:16" ht="13.2">
       <c r="F698" s="3"/>
       <c r="I698" s="4"/>
       <c r="J698" s="4"/>
@@ -7240,7 +7269,7 @@
       <c r="L698" s="3"/>
       <c r="P698" s="3"/>
     </row>
-    <row r="699" spans="6:16" ht="12.5">
+    <row r="699" spans="6:16" ht="13.2">
       <c r="F699" s="3"/>
       <c r="I699" s="4"/>
       <c r="J699" s="4"/>
@@ -7248,7 +7277,7 @@
       <c r="L699" s="3"/>
       <c r="P699" s="3"/>
     </row>
-    <row r="700" spans="6:16" ht="12.5">
+    <row r="700" spans="6:16" ht="13.2">
       <c r="F700" s="3"/>
       <c r="I700" s="4"/>
       <c r="J700" s="4"/>
@@ -7256,7 +7285,7 @@
       <c r="L700" s="3"/>
       <c r="P700" s="3"/>
     </row>
-    <row r="701" spans="6:16" ht="12.5">
+    <row r="701" spans="6:16" ht="13.2">
       <c r="F701" s="3"/>
       <c r="I701" s="4"/>
       <c r="J701" s="4"/>
@@ -7264,7 +7293,7 @@
       <c r="L701" s="3"/>
       <c r="P701" s="3"/>
     </row>
-    <row r="702" spans="6:16" ht="12.5">
+    <row r="702" spans="6:16" ht="13.2">
       <c r="F702" s="3"/>
       <c r="I702" s="4"/>
       <c r="J702" s="4"/>
@@ -7272,7 +7301,7 @@
       <c r="L702" s="3"/>
       <c r="P702" s="3"/>
     </row>
-    <row r="703" spans="6:16" ht="12.5">
+    <row r="703" spans="6:16" ht="13.2">
       <c r="F703" s="3"/>
       <c r="I703" s="4"/>
       <c r="J703" s="4"/>
@@ -7280,7 +7309,7 @@
       <c r="L703" s="3"/>
       <c r="P703" s="3"/>
     </row>
-    <row r="704" spans="6:16" ht="12.5">
+    <row r="704" spans="6:16" ht="13.2">
       <c r="F704" s="3"/>
       <c r="I704" s="4"/>
       <c r="J704" s="4"/>
@@ -7288,7 +7317,7 @@
       <c r="L704" s="3"/>
       <c r="P704" s="3"/>
     </row>
-    <row r="705" spans="6:16" ht="12.5">
+    <row r="705" spans="6:16" ht="13.2">
       <c r="F705" s="3"/>
       <c r="I705" s="4"/>
       <c r="J705" s="4"/>
@@ -7296,7 +7325,7 @@
       <c r="L705" s="3"/>
       <c r="P705" s="3"/>
     </row>
-    <row r="706" spans="6:16" ht="12.5">
+    <row r="706" spans="6:16" ht="13.2">
       <c r="F706" s="3"/>
       <c r="I706" s="4"/>
       <c r="J706" s="4"/>
@@ -7304,7 +7333,7 @@
       <c r="L706" s="3"/>
       <c r="P706" s="3"/>
     </row>
-    <row r="707" spans="6:16" ht="12.5">
+    <row r="707" spans="6:16" ht="13.2">
       <c r="F707" s="3"/>
       <c r="I707" s="4"/>
       <c r="J707" s="4"/>
@@ -7312,7 +7341,7 @@
       <c r="L707" s="3"/>
       <c r="P707" s="3"/>
     </row>
-    <row r="708" spans="6:16" ht="12.5">
+    <row r="708" spans="6:16" ht="13.2">
       <c r="F708" s="3"/>
       <c r="I708" s="4"/>
       <c r="J708" s="4"/>
@@ -7320,7 +7349,7 @@
       <c r="L708" s="3"/>
       <c r="P708" s="3"/>
     </row>
-    <row r="709" spans="6:16" ht="12.5">
+    <row r="709" spans="6:16" ht="13.2">
       <c r="F709" s="3"/>
       <c r="I709" s="4"/>
       <c r="J709" s="4"/>
@@ -7328,7 +7357,7 @@
       <c r="L709" s="3"/>
       <c r="P709" s="3"/>
     </row>
-    <row r="710" spans="6:16" ht="12.5">
+    <row r="710" spans="6:16" ht="13.2">
       <c r="F710" s="3"/>
       <c r="I710" s="4"/>
       <c r="J710" s="4"/>
@@ -7336,7 +7365,7 @@
       <c r="L710" s="3"/>
       <c r="P710" s="3"/>
     </row>
-    <row r="711" spans="6:16" ht="12.5">
+    <row r="711" spans="6:16" ht="13.2">
       <c r="F711" s="3"/>
       <c r="I711" s="4"/>
       <c r="J711" s="4"/>
@@ -7344,7 +7373,7 @@
       <c r="L711" s="3"/>
       <c r="P711" s="3"/>
     </row>
-    <row r="712" spans="6:16" ht="12.5">
+    <row r="712" spans="6:16" ht="13.2">
       <c r="F712" s="3"/>
       <c r="I712" s="4"/>
       <c r="J712" s="4"/>
@@ -7352,7 +7381,7 @@
       <c r="L712" s="3"/>
       <c r="P712" s="3"/>
     </row>
-    <row r="713" spans="6:16" ht="12.5">
+    <row r="713" spans="6:16" ht="13.2">
       <c r="F713" s="3"/>
       <c r="I713" s="4"/>
       <c r="J713" s="4"/>
@@ -7360,7 +7389,7 @@
       <c r="L713" s="3"/>
       <c r="P713" s="3"/>
     </row>
-    <row r="714" spans="6:16" ht="12.5">
+    <row r="714" spans="6:16" ht="13.2">
       <c r="F714" s="3"/>
       <c r="I714" s="4"/>
       <c r="J714" s="4"/>
@@ -7368,7 +7397,7 @@
       <c r="L714" s="3"/>
       <c r="P714" s="3"/>
     </row>
-    <row r="715" spans="6:16" ht="12.5">
+    <row r="715" spans="6:16" ht="13.2">
       <c r="F715" s="3"/>
       <c r="I715" s="4"/>
       <c r="J715" s="4"/>
@@ -7376,7 +7405,7 @@
       <c r="L715" s="3"/>
       <c r="P715" s="3"/>
     </row>
-    <row r="716" spans="6:16" ht="12.5">
+    <row r="716" spans="6:16" ht="13.2">
       <c r="F716" s="3"/>
       <c r="I716" s="4"/>
       <c r="J716" s="4"/>
@@ -7384,7 +7413,7 @@
       <c r="L716" s="3"/>
       <c r="P716" s="3"/>
     </row>
-    <row r="717" spans="6:16" ht="12.5">
+    <row r="717" spans="6:16" ht="13.2">
       <c r="F717" s="3"/>
       <c r="I717" s="4"/>
       <c r="J717" s="4"/>
@@ -7392,7 +7421,7 @@
       <c r="L717" s="3"/>
       <c r="P717" s="3"/>
     </row>
-    <row r="718" spans="6:16" ht="12.5">
+    <row r="718" spans="6:16" ht="13.2">
       <c r="F718" s="3"/>
       <c r="I718" s="4"/>
       <c r="J718" s="4"/>
@@ -7400,7 +7429,7 @@
       <c r="L718" s="3"/>
       <c r="P718" s="3"/>
     </row>
-    <row r="719" spans="6:16" ht="12.5">
+    <row r="719" spans="6:16" ht="13.2">
       <c r="F719" s="3"/>
       <c r="I719" s="4"/>
       <c r="J719" s="4"/>
@@ -7408,7 +7437,7 @@
       <c r="L719" s="3"/>
       <c r="P719" s="3"/>
     </row>
-    <row r="720" spans="6:16" ht="12.5">
+    <row r="720" spans="6:16" ht="13.2">
       <c r="F720" s="3"/>
       <c r="I720" s="4"/>
       <c r="J720" s="4"/>
@@ -7416,7 +7445,7 @@
       <c r="L720" s="3"/>
       <c r="P720" s="3"/>
     </row>
-    <row r="721" spans="6:16" ht="12.5">
+    <row r="721" spans="6:16" ht="13.2">
       <c r="F721" s="3"/>
       <c r="I721" s="4"/>
       <c r="J721" s="4"/>
@@ -7424,7 +7453,7 @@
       <c r="L721" s="3"/>
       <c r="P721" s="3"/>
     </row>
-    <row r="722" spans="6:16" ht="12.5">
+    <row r="722" spans="6:16" ht="13.2">
       <c r="F722" s="3"/>
       <c r="I722" s="4"/>
       <c r="J722" s="4"/>
@@ -7432,7 +7461,7 @@
       <c r="L722" s="3"/>
       <c r="P722" s="3"/>
     </row>
-    <row r="723" spans="6:16" ht="12.5">
+    <row r="723" spans="6:16" ht="13.2">
       <c r="F723" s="3"/>
       <c r="I723" s="4"/>
       <c r="J723" s="4"/>
@@ -7440,7 +7469,7 @@
       <c r="L723" s="3"/>
       <c r="P723" s="3"/>
     </row>
-    <row r="724" spans="6:16" ht="12.5">
+    <row r="724" spans="6:16" ht="13.2">
       <c r="F724" s="3"/>
       <c r="I724" s="4"/>
       <c r="J724" s="4"/>
@@ -7448,7 +7477,7 @@
       <c r="L724" s="3"/>
       <c r="P724" s="3"/>
     </row>
-    <row r="725" spans="6:16" ht="12.5">
+    <row r="725" spans="6:16" ht="13.2">
       <c r="F725" s="3"/>
       <c r="I725" s="4"/>
       <c r="J725" s="4"/>
@@ -7456,7 +7485,7 @@
       <c r="L725" s="3"/>
       <c r="P725" s="3"/>
     </row>
-    <row r="726" spans="6:16" ht="12.5">
+    <row r="726" spans="6:16" ht="13.2">
       <c r="F726" s="3"/>
       <c r="I726" s="4"/>
       <c r="J726" s="4"/>
@@ -7464,7 +7493,7 @@
       <c r="L726" s="3"/>
       <c r="P726" s="3"/>
     </row>
-    <row r="727" spans="6:16" ht="12.5">
+    <row r="727" spans="6:16" ht="13.2">
       <c r="F727" s="3"/>
       <c r="I727" s="4"/>
       <c r="J727" s="4"/>
@@ -7472,7 +7501,7 @@
       <c r="L727" s="3"/>
       <c r="P727" s="3"/>
     </row>
-    <row r="728" spans="6:16" ht="12.5">
+    <row r="728" spans="6:16" ht="13.2">
       <c r="F728" s="3"/>
       <c r="I728" s="4"/>
       <c r="J728" s="4"/>
@@ -7480,7 +7509,7 @@
       <c r="L728" s="3"/>
       <c r="P728" s="3"/>
     </row>
-    <row r="729" spans="6:16" ht="12.5">
+    <row r="729" spans="6:16" ht="13.2">
       <c r="F729" s="3"/>
       <c r="I729" s="4"/>
       <c r="J729" s="4"/>
@@ -7488,7 +7517,7 @@
       <c r="L729" s="3"/>
       <c r="P729" s="3"/>
     </row>
-    <row r="730" spans="6:16" ht="12.5">
+    <row r="730" spans="6:16" ht="13.2">
       <c r="F730" s="3"/>
       <c r="I730" s="4"/>
       <c r="J730" s="4"/>
@@ -7496,7 +7525,7 @@
       <c r="L730" s="3"/>
       <c r="P730" s="3"/>
     </row>
-    <row r="731" spans="6:16" ht="12.5">
+    <row r="731" spans="6:16" ht="13.2">
       <c r="F731" s="3"/>
       <c r="I731" s="4"/>
       <c r="J731" s="4"/>
@@ -7504,7 +7533,7 @@
       <c r="L731" s="3"/>
       <c r="P731" s="3"/>
     </row>
-    <row r="732" spans="6:16" ht="12.5">
+    <row r="732" spans="6:16" ht="13.2">
       <c r="F732" s="3"/>
       <c r="I732" s="4"/>
       <c r="J732" s="4"/>
@@ -7512,7 +7541,7 @@
       <c r="L732" s="3"/>
       <c r="P732" s="3"/>
     </row>
-    <row r="733" spans="6:16" ht="12.5">
+    <row r="733" spans="6:16" ht="13.2">
       <c r="F733" s="3"/>
       <c r="I733" s="4"/>
       <c r="J733" s="4"/>
@@ -7520,7 +7549,7 @@
       <c r="L733" s="3"/>
       <c r="P733" s="3"/>
     </row>
-    <row r="734" spans="6:16" ht="12.5">
+    <row r="734" spans="6:16" ht="13.2">
       <c r="F734" s="3"/>
       <c r="I734" s="4"/>
       <c r="J734" s="4"/>
@@ -7528,7 +7557,7 @@
       <c r="L734" s="3"/>
       <c r="P734" s="3"/>
     </row>
-    <row r="735" spans="6:16" ht="12.5">
+    <row r="735" spans="6:16" ht="13.2">
       <c r="F735" s="3"/>
       <c r="I735" s="4"/>
       <c r="J735" s="4"/>
@@ -7536,7 +7565,7 @@
       <c r="L735" s="3"/>
       <c r="P735" s="3"/>
     </row>
-    <row r="736" spans="6:16" ht="12.5">
+    <row r="736" spans="6:16" ht="13.2">
       <c r="F736" s="3"/>
       <c r="I736" s="4"/>
       <c r="J736" s="4"/>
@@ -7544,7 +7573,7 @@
       <c r="L736" s="3"/>
       <c r="P736" s="3"/>
     </row>
-    <row r="737" spans="6:16" ht="12.5">
+    <row r="737" spans="6:16" ht="13.2">
       <c r="F737" s="3"/>
       <c r="I737" s="4"/>
       <c r="J737" s="4"/>
@@ -7552,7 +7581,7 @@
       <c r="L737" s="3"/>
       <c r="P737" s="3"/>
     </row>
-    <row r="738" spans="6:16" ht="12.5">
+    <row r="738" spans="6:16" ht="13.2">
       <c r="F738" s="3"/>
       <c r="I738" s="4"/>
       <c r="J738" s="4"/>
@@ -7560,7 +7589,7 @@
       <c r="L738" s="3"/>
       <c r="P738" s="3"/>
     </row>
-    <row r="739" spans="6:16" ht="12.5">
+    <row r="739" spans="6:16" ht="13.2">
       <c r="F739" s="3"/>
       <c r="I739" s="4"/>
       <c r="J739" s="4"/>
@@ -7568,7 +7597,7 @@
       <c r="L739" s="3"/>
       <c r="P739" s="3"/>
     </row>
-    <row r="740" spans="6:16" ht="12.5">
+    <row r="740" spans="6:16" ht="13.2">
       <c r="F740" s="3"/>
       <c r="I740" s="4"/>
       <c r="J740" s="4"/>
@@ -7576,7 +7605,7 @@
       <c r="L740" s="3"/>
       <c r="P740" s="3"/>
     </row>
-    <row r="741" spans="6:16" ht="12.5">
+    <row r="741" spans="6:16" ht="13.2">
       <c r="F741" s="3"/>
       <c r="I741" s="4"/>
       <c r="J741" s="4"/>
@@ -7584,7 +7613,7 @@
       <c r="L741" s="3"/>
       <c r="P741" s="3"/>
     </row>
-    <row r="742" spans="6:16" ht="12.5">
+    <row r="742" spans="6:16" ht="13.2">
       <c r="F742" s="3"/>
       <c r="I742" s="4"/>
       <c r="J742" s="4"/>
@@ -7592,7 +7621,7 @@
       <c r="L742" s="3"/>
       <c r="P742" s="3"/>
     </row>
-    <row r="743" spans="6:16" ht="12.5">
+    <row r="743" spans="6:16" ht="13.2">
       <c r="F743" s="3"/>
       <c r="I743" s="4"/>
       <c r="J743" s="4"/>
@@ -7600,7 +7629,7 @@
       <c r="L743" s="3"/>
       <c r="P743" s="3"/>
     </row>
-    <row r="744" spans="6:16" ht="12.5">
+    <row r="744" spans="6:16" ht="13.2">
       <c r="F744" s="3"/>
       <c r="I744" s="4"/>
       <c r="J744" s="4"/>
@@ -7608,7 +7637,7 @@
       <c r="L744" s="3"/>
       <c r="P744" s="3"/>
     </row>
-    <row r="745" spans="6:16" ht="12.5">
+    <row r="745" spans="6:16" ht="13.2">
       <c r="F745" s="3"/>
       <c r="I745" s="4"/>
       <c r="J745" s="4"/>
@@ -7616,7 +7645,7 @@
       <c r="L745" s="3"/>
       <c r="P745" s="3"/>
     </row>
-    <row r="746" spans="6:16" ht="12.5">
+    <row r="746" spans="6:16" ht="13.2">
       <c r="F746" s="3"/>
       <c r="I746" s="4"/>
       <c r="J746" s="4"/>
@@ -7624,7 +7653,7 @@
       <c r="L746" s="3"/>
       <c r="P746" s="3"/>
     </row>
-    <row r="747" spans="6:16" ht="12.5">
+    <row r="747" spans="6:16" ht="13.2">
       <c r="F747" s="3"/>
       <c r="I747" s="4"/>
       <c r="J747" s="4"/>
@@ -7632,7 +7661,7 @@
       <c r="L747" s="3"/>
       <c r="P747" s="3"/>
     </row>
-    <row r="748" spans="6:16" ht="12.5">
+    <row r="748" spans="6:16" ht="13.2">
       <c r="F748" s="3"/>
       <c r="I748" s="4"/>
       <c r="J748" s="4"/>
@@ -7640,7 +7669,7 @@
       <c r="L748" s="3"/>
       <c r="P748" s="3"/>
     </row>
-    <row r="749" spans="6:16" ht="12.5">
+    <row r="749" spans="6:16" ht="13.2">
       <c r="F749" s="3"/>
       <c r="I749" s="4"/>
       <c r="J749" s="4"/>
@@ -7648,7 +7677,7 @@
       <c r="L749" s="3"/>
       <c r="P749" s="3"/>
     </row>
-    <row r="750" spans="6:16" ht="12.5">
+    <row r="750" spans="6:16" ht="13.2">
       <c r="F750" s="3"/>
       <c r="I750" s="4"/>
       <c r="J750" s="4"/>
@@ -7656,7 +7685,7 @@
       <c r="L750" s="3"/>
       <c r="P750" s="3"/>
     </row>
-    <row r="751" spans="6:16" ht="12.5">
+    <row r="751" spans="6:16" ht="13.2">
       <c r="F751" s="3"/>
       <c r="I751" s="4"/>
       <c r="J751" s="4"/>
@@ -7664,7 +7693,7 @@
       <c r="L751" s="3"/>
       <c r="P751" s="3"/>
     </row>
-    <row r="752" spans="6:16" ht="12.5">
+    <row r="752" spans="6:16" ht="13.2">
       <c r="F752" s="3"/>
       <c r="I752" s="4"/>
       <c r="J752" s="4"/>
@@ -7672,7 +7701,7 @@
       <c r="L752" s="3"/>
       <c r="P752" s="3"/>
     </row>
-    <row r="753" spans="6:16" ht="12.5">
+    <row r="753" spans="6:16" ht="13.2">
       <c r="F753" s="3"/>
       <c r="I753" s="4"/>
       <c r="J753" s="4"/>
@@ -7680,7 +7709,7 @@
       <c r="L753" s="3"/>
       <c r="P753" s="3"/>
     </row>
-    <row r="754" spans="6:16" ht="12.5">
+    <row r="754" spans="6:16" ht="13.2">
       <c r="F754" s="3"/>
       <c r="I754" s="4"/>
       <c r="J754" s="4"/>
@@ -7688,7 +7717,7 @@
       <c r="L754" s="3"/>
       <c r="P754" s="3"/>
     </row>
-    <row r="755" spans="6:16" ht="12.5">
+    <row r="755" spans="6:16" ht="13.2">
       <c r="F755" s="3"/>
       <c r="I755" s="4"/>
       <c r="J755" s="4"/>
@@ -7696,7 +7725,7 @@
       <c r="L755" s="3"/>
       <c r="P755" s="3"/>
     </row>
-    <row r="756" spans="6:16" ht="12.5">
+    <row r="756" spans="6:16" ht="13.2">
       <c r="F756" s="3"/>
       <c r="I756" s="4"/>
       <c r="J756" s="4"/>
@@ -7704,7 +7733,7 @@
       <c r="L756" s="3"/>
       <c r="P756" s="3"/>
     </row>
-    <row r="757" spans="6:16" ht="12.5">
+    <row r="757" spans="6:16" ht="13.2">
       <c r="F757" s="3"/>
       <c r="I757" s="4"/>
       <c r="J757" s="4"/>
@@ -7712,7 +7741,7 @@
       <c r="L757" s="3"/>
       <c r="P757" s="3"/>
     </row>
-    <row r="758" spans="6:16" ht="12.5">
+    <row r="758" spans="6:16" ht="13.2">
       <c r="F758" s="3"/>
       <c r="I758" s="4"/>
       <c r="J758" s="4"/>
@@ -7720,7 +7749,7 @@
       <c r="L758" s="3"/>
       <c r="P758" s="3"/>
     </row>
-    <row r="759" spans="6:16" ht="12.5">
+    <row r="759" spans="6:16" ht="13.2">
       <c r="F759" s="3"/>
       <c r="I759" s="4"/>
       <c r="J759" s="4"/>
@@ -7728,7 +7757,7 @@
       <c r="L759" s="3"/>
       <c r="P759" s="3"/>
     </row>
-    <row r="760" spans="6:16" ht="12.5">
+    <row r="760" spans="6:16" ht="13.2">
       <c r="F760" s="3"/>
       <c r="I760" s="4"/>
       <c r="J760" s="4"/>
@@ -7736,7 +7765,7 @@
       <c r="L760" s="3"/>
       <c r="P760" s="3"/>
     </row>
-    <row r="761" spans="6:16" ht="12.5">
+    <row r="761" spans="6:16" ht="13.2">
       <c r="F761" s="3"/>
       <c r="I761" s="4"/>
       <c r="J761" s="4"/>
@@ -7744,7 +7773,7 @@
       <c r="L761" s="3"/>
       <c r="P761" s="3"/>
     </row>
-    <row r="762" spans="6:16" ht="12.5">
+    <row r="762" spans="6:16" ht="13.2">
       <c r="F762" s="3"/>
       <c r="I762" s="4"/>
       <c r="J762" s="4"/>
@@ -7752,7 +7781,7 @@
       <c r="L762" s="3"/>
       <c r="P762" s="3"/>
     </row>
-    <row r="763" spans="6:16" ht="12.5">
+    <row r="763" spans="6:16" ht="13.2">
       <c r="F763" s="3"/>
       <c r="I763" s="4"/>
       <c r="J763" s="4"/>
@@ -7760,7 +7789,7 @@
       <c r="L763" s="3"/>
       <c r="P763" s="3"/>
     </row>
-    <row r="764" spans="6:16" ht="12.5">
+    <row r="764" spans="6:16" ht="13.2">
       <c r="F764" s="3"/>
       <c r="I764" s="4"/>
       <c r="J764" s="4"/>
@@ -7768,7 +7797,7 @@
       <c r="L764" s="3"/>
       <c r="P764" s="3"/>
     </row>
-    <row r="765" spans="6:16" ht="12.5">
+    <row r="765" spans="6:16" ht="13.2">
       <c r="F765" s="3"/>
       <c r="I765" s="4"/>
       <c r="J765" s="4"/>
@@ -7776,7 +7805,7 @@
       <c r="L765" s="3"/>
       <c r="P765" s="3"/>
     </row>
-    <row r="766" spans="6:16" ht="12.5">
+    <row r="766" spans="6:16" ht="13.2">
       <c r="F766" s="3"/>
       <c r="I766" s="4"/>
       <c r="J766" s="4"/>
@@ -7784,7 +7813,7 @@
       <c r="L766" s="3"/>
       <c r="P766" s="3"/>
     </row>
-    <row r="767" spans="6:16" ht="12.5">
+    <row r="767" spans="6:16" ht="13.2">
       <c r="F767" s="3"/>
       <c r="I767" s="4"/>
       <c r="J767" s="4"/>
@@ -7792,7 +7821,7 @@
       <c r="L767" s="3"/>
       <c r="P767" s="3"/>
     </row>
-    <row r="768" spans="6:16" ht="12.5">
+    <row r="768" spans="6:16" ht="13.2">
       <c r="F768" s="3"/>
       <c r="I768" s="4"/>
       <c r="J768" s="4"/>
@@ -7800,7 +7829,7 @@
       <c r="L768" s="3"/>
       <c r="P768" s="3"/>
     </row>
-    <row r="769" spans="6:16" ht="12.5">
+    <row r="769" spans="6:16" ht="13.2">
       <c r="F769" s="3"/>
       <c r="I769" s="4"/>
       <c r="J769" s="4"/>
@@ -7808,7 +7837,7 @@
       <c r="L769" s="3"/>
       <c r="P769" s="3"/>
     </row>
-    <row r="770" spans="6:16" ht="12.5">
+    <row r="770" spans="6:16" ht="13.2">
       <c r="F770" s="3"/>
       <c r="I770" s="4"/>
       <c r="J770" s="4"/>
@@ -7816,7 +7845,7 @@
       <c r="L770" s="3"/>
       <c r="P770" s="3"/>
     </row>
-    <row r="771" spans="6:16" ht="12.5">
+    <row r="771" spans="6:16" ht="13.2">
       <c r="F771" s="3"/>
       <c r="I771" s="4"/>
       <c r="J771" s="4"/>
@@ -7824,7 +7853,7 @@
       <c r="L771" s="3"/>
       <c r="P771" s="3"/>
     </row>
-    <row r="772" spans="6:16" ht="12.5">
+    <row r="772" spans="6:16" ht="13.2">
       <c r="F772" s="3"/>
       <c r="I772" s="4"/>
       <c r="J772" s="4"/>
@@ -7832,7 +7861,7 @@
       <c r="L772" s="3"/>
       <c r="P772" s="3"/>
     </row>
-    <row r="773" spans="6:16" ht="12.5">
+    <row r="773" spans="6:16" ht="13.2">
       <c r="F773" s="3"/>
       <c r="I773" s="4"/>
       <c r="J773" s="4"/>
@@ -7840,7 +7869,7 @@
       <c r="L773" s="3"/>
       <c r="P773" s="3"/>
     </row>
-    <row r="774" spans="6:16" ht="12.5">
+    <row r="774" spans="6:16" ht="13.2">
       <c r="F774" s="3"/>
       <c r="I774" s="4"/>
       <c r="J774" s="4"/>
@@ -7848,7 +7877,7 @@
       <c r="L774" s="3"/>
       <c r="P774" s="3"/>
     </row>
-    <row r="775" spans="6:16" ht="12.5">
+    <row r="775" spans="6:16" ht="13.2">
       <c r="F775" s="3"/>
       <c r="I775" s="4"/>
       <c r="J775" s="4"/>
@@ -7856,7 +7885,7 @@
       <c r="L775" s="3"/>
       <c r="P775" s="3"/>
     </row>
-    <row r="776" spans="6:16" ht="12.5">
+    <row r="776" spans="6:16" ht="13.2">
       <c r="F776" s="3"/>
       <c r="I776" s="4"/>
       <c r="J776" s="4"/>
@@ -7864,7 +7893,7 @@
       <c r="L776" s="3"/>
       <c r="P776" s="3"/>
     </row>
-    <row r="777" spans="6:16" ht="12.5">
+    <row r="777" spans="6:16" ht="13.2">
       <c r="F777" s="3"/>
       <c r="I777" s="4"/>
       <c r="J777" s="4"/>
@@ -7872,7 +7901,7 @@
       <c r="L777" s="3"/>
       <c r="P777" s="3"/>
     </row>
-    <row r="778" spans="6:16" ht="12.5">
+    <row r="778" spans="6:16" ht="13.2">
       <c r="F778" s="3"/>
       <c r="I778" s="4"/>
       <c r="J778" s="4"/>
@@ -7880,7 +7909,7 @@
       <c r="L778" s="3"/>
       <c r="P778" s="3"/>
     </row>
-    <row r="779" spans="6:16" ht="12.5">
+    <row r="779" spans="6:16" ht="13.2">
       <c r="F779" s="3"/>
       <c r="I779" s="4"/>
       <c r="J779" s="4"/>
@@ -7888,7 +7917,7 @@
       <c r="L779" s="3"/>
       <c r="P779" s="3"/>
     </row>
-    <row r="780" spans="6:16" ht="12.5">
+    <row r="780" spans="6:16" ht="13.2">
       <c r="F780" s="3"/>
       <c r="I780" s="4"/>
       <c r="J780" s="4"/>
@@ -7896,7 +7925,7 @@
       <c r="L780" s="3"/>
       <c r="P780" s="3"/>
     </row>
-    <row r="781" spans="6:16" ht="12.5">
+    <row r="781" spans="6:16" ht="13.2">
       <c r="F781" s="3"/>
       <c r="I781" s="4"/>
       <c r="J781" s="4"/>
@@ -7904,7 +7933,7 @@
       <c r="L781" s="3"/>
       <c r="P781" s="3"/>
     </row>
-    <row r="782" spans="6:16" ht="12.5">
+    <row r="782" spans="6:16" ht="13.2">
       <c r="F782" s="3"/>
       <c r="I782" s="4"/>
       <c r="J782" s="4"/>
@@ -7912,7 +7941,7 @@
       <c r="L782" s="3"/>
       <c r="P782" s="3"/>
     </row>
-    <row r="783" spans="6:16" ht="12.5">
+    <row r="783" spans="6:16" ht="13.2">
       <c r="F783" s="3"/>
       <c r="I783" s="4"/>
       <c r="J783" s="4"/>
@@ -7920,7 +7949,7 @@
       <c r="L783" s="3"/>
       <c r="P783" s="3"/>
     </row>
-    <row r="784" spans="6:16" ht="12.5">
+    <row r="784" spans="6:16" ht="13.2">
       <c r="F784" s="3"/>
       <c r="I784" s="4"/>
       <c r="J784" s="4"/>
@@ -7928,7 +7957,7 @@
       <c r="L784" s="3"/>
       <c r="P784" s="3"/>
     </row>
-    <row r="785" spans="6:16" ht="12.5">
+    <row r="785" spans="6:16" ht="13.2">
       <c r="F785" s="3"/>
       <c r="I785" s="4"/>
       <c r="J785" s="4"/>
@@ -7936,7 +7965,7 @@
       <c r="L785" s="3"/>
       <c r="P785" s="3"/>
     </row>
-    <row r="786" spans="6:16" ht="12.5">
+    <row r="786" spans="6:16" ht="13.2">
       <c r="F786" s="3"/>
       <c r="I786" s="4"/>
       <c r="J786" s="4"/>
@@ -7944,7 +7973,7 @@
       <c r="L786" s="3"/>
       <c r="P786" s="3"/>
     </row>
-    <row r="787" spans="6:16" ht="12.5">
+    <row r="787" spans="6:16" ht="13.2">
       <c r="F787" s="3"/>
       <c r="I787" s="4"/>
       <c r="J787" s="4"/>
@@ -7952,7 +7981,7 @@
       <c r="L787" s="3"/>
       <c r="P787" s="3"/>
     </row>
-    <row r="788" spans="6:16" ht="12.5">
+    <row r="788" spans="6:16" ht="13.2">
       <c r="F788" s="3"/>
       <c r="I788" s="4"/>
       <c r="J788" s="4"/>
@@ -7960,7 +7989,7 @@
       <c r="L788" s="3"/>
       <c r="P788" s="3"/>
     </row>
-    <row r="789" spans="6:16" ht="12.5">
+    <row r="789" spans="6:16" ht="13.2">
       <c r="F789" s="3"/>
       <c r="I789" s="4"/>
       <c r="J789" s="4"/>
@@ -7968,7 +7997,7 @@
       <c r="L789" s="3"/>
       <c r="P789" s="3"/>
     </row>
-    <row r="790" spans="6:16" ht="12.5">
+    <row r="790" spans="6:16" ht="13.2">
       <c r="F790" s="3"/>
       <c r="I790" s="4"/>
       <c r="J790" s="4"/>
@@ -7976,7 +8005,7 @@
       <c r="L790" s="3"/>
       <c r="P790" s="3"/>
     </row>
-    <row r="791" spans="6:16" ht="12.5">
+    <row r="791" spans="6:16" ht="13.2">
       <c r="F791" s="3"/>
       <c r="I791" s="4"/>
       <c r="J791" s="4"/>
@@ -7984,7 +8013,7 @@
       <c r="L791" s="3"/>
       <c r="P791" s="3"/>
     </row>
-    <row r="792" spans="6:16" ht="12.5">
+    <row r="792" spans="6:16" ht="13.2">
       <c r="F792" s="3"/>
       <c r="I792" s="4"/>
       <c r="J792" s="4"/>
@@ -7992,7 +8021,7 @@
       <c r="L792" s="3"/>
       <c r="P792" s="3"/>
     </row>
-    <row r="793" spans="6:16" ht="12.5">
+    <row r="793" spans="6:16" ht="13.2">
       <c r="F793" s="3"/>
       <c r="I793" s="4"/>
       <c r="J793" s="4"/>
@@ -8000,7 +8029,7 @@
       <c r="L793" s="3"/>
       <c r="P793" s="3"/>
     </row>
-    <row r="794" spans="6:16" ht="12.5">
+    <row r="794" spans="6:16" ht="13.2">
       <c r="F794" s="3"/>
       <c r="I794" s="4"/>
       <c r="J794" s="4"/>
@@ -8008,7 +8037,7 @@
       <c r="L794" s="3"/>
       <c r="P794" s="3"/>
     </row>
-    <row r="795" spans="6:16" ht="12.5">
+    <row r="795" spans="6:16" ht="13.2">
       <c r="F795" s="3"/>
       <c r="I795" s="4"/>
       <c r="J795" s="4"/>
@@ -8016,7 +8045,7 @@
       <c r="L795" s="3"/>
       <c r="P795" s="3"/>
     </row>
-    <row r="796" spans="6:16" ht="12.5">
+    <row r="796" spans="6:16" ht="13.2">
       <c r="F796" s="3"/>
       <c r="I796" s="4"/>
       <c r="J796" s="4"/>
@@ -8024,7 +8053,7 @@
       <c r="L796" s="3"/>
       <c r="P796" s="3"/>
     </row>
-    <row r="797" spans="6:16" ht="12.5">
+    <row r="797" spans="6:16" ht="13.2">
       <c r="F797" s="3"/>
       <c r="I797" s="4"/>
       <c r="J797" s="4"/>
@@ -8032,7 +8061,7 @@
       <c r="L797" s="3"/>
       <c r="P797" s="3"/>
     </row>
-    <row r="798" spans="6:16" ht="12.5">
+    <row r="798" spans="6:16" ht="13.2">
       <c r="F798" s="3"/>
       <c r="I798" s="4"/>
       <c r="J798" s="4"/>
@@ -8040,7 +8069,7 @@
       <c r="L798" s="3"/>
       <c r="P798" s="3"/>
     </row>
-    <row r="799" spans="6:16" ht="12.5">
+    <row r="799" spans="6:16" ht="13.2">
       <c r="F799" s="3"/>
       <c r="I799" s="4"/>
       <c r="J799" s="4"/>
@@ -8048,7 +8077,7 @@
       <c r="L799" s="3"/>
       <c r="P799" s="3"/>
     </row>
-    <row r="800" spans="6:16" ht="12.5">
+    <row r="800" spans="6:16" ht="13.2">
       <c r="F800" s="3"/>
       <c r="I800" s="4"/>
       <c r="J800" s="4"/>
@@ -8056,7 +8085,7 @@
       <c r="L800" s="3"/>
       <c r="P800" s="3"/>
     </row>
-    <row r="801" spans="6:16" ht="12.5">
+    <row r="801" spans="6:16" ht="13.2">
       <c r="F801" s="3"/>
       <c r="I801" s="4"/>
       <c r="J801" s="4"/>
@@ -8064,7 +8093,7 @@
       <c r="L801" s="3"/>
       <c r="P801" s="3"/>
     </row>
-    <row r="802" spans="6:16" ht="12.5">
+    <row r="802" spans="6:16" ht="13.2">
       <c r="F802" s="3"/>
       <c r="I802" s="4"/>
       <c r="J802" s="4"/>
@@ -8072,7 +8101,7 @@
       <c r="L802" s="3"/>
       <c r="P802" s="3"/>
     </row>
-    <row r="803" spans="6:16" ht="12.5">
+    <row r="803" spans="6:16" ht="13.2">
       <c r="F803" s="3"/>
       <c r="I803" s="4"/>
       <c r="J803" s="4"/>
@@ -8080,7 +8109,7 @@
       <c r="L803" s="3"/>
       <c r="P803" s="3"/>
     </row>
-    <row r="804" spans="6:16" ht="12.5">
+    <row r="804" spans="6:16" ht="13.2">
       <c r="F804" s="3"/>
       <c r="I804" s="4"/>
       <c r="J804" s="4"/>
@@ -8088,7 +8117,7 @@
       <c r="L804" s="3"/>
       <c r="P804" s="3"/>
     </row>
-    <row r="805" spans="6:16" ht="12.5">
+    <row r="805" spans="6:16" ht="13.2">
       <c r="F805" s="3"/>
       <c r="I805" s="4"/>
       <c r="J805" s="4"/>
@@ -8096,7 +8125,7 @@
       <c r="L805" s="3"/>
       <c r="P805" s="3"/>
     </row>
-    <row r="806" spans="6:16" ht="12.5">
+    <row r="806" spans="6:16" ht="13.2">
       <c r="F806" s="3"/>
       <c r="I806" s="4"/>
       <c r="J806" s="4"/>
@@ -8104,7 +8133,7 @@
       <c r="L806" s="3"/>
       <c r="P806" s="3"/>
     </row>
-    <row r="807" spans="6:16" ht="12.5">
+    <row r="807" spans="6:16" ht="13.2">
       <c r="F807" s="3"/>
       <c r="I807" s="4"/>
       <c r="J807" s="4"/>
@@ -8112,7 +8141,7 @@
       <c r="L807" s="3"/>
       <c r="P807" s="3"/>
     </row>
-    <row r="808" spans="6:16" ht="12.5">
+    <row r="808" spans="6:16" ht="13.2">
       <c r="F808" s="3"/>
       <c r="I808" s="4"/>
       <c r="J808" s="4"/>
@@ -8120,7 +8149,7 @@
       <c r="L808" s="3"/>
       <c r="P808" s="3"/>
     </row>
-    <row r="809" spans="6:16" ht="12.5">
+    <row r="809" spans="6:16" ht="13.2">
       <c r="F809" s="3"/>
       <c r="I809" s="4"/>
       <c r="J809" s="4"/>
@@ -8128,7 +8157,7 @@
       <c r="L809" s="3"/>
       <c r="P809" s="3"/>
     </row>
-    <row r="810" spans="6:16" ht="12.5">
+    <row r="810" spans="6:16" ht="13.2">
       <c r="F810" s="3"/>
       <c r="I810" s="4"/>
       <c r="J810" s="4"/>
@@ -8136,7 +8165,7 @@
       <c r="L810" s="3"/>
       <c r="P810" s="3"/>
     </row>
-    <row r="811" spans="6:16" ht="12.5">
+    <row r="811" spans="6:16" ht="13.2">
       <c r="F811" s="3"/>
       <c r="I811" s="4"/>
       <c r="J811" s="4"/>
@@ -8144,7 +8173,7 @@
       <c r="L811" s="3"/>
       <c r="P811" s="3"/>
     </row>
-    <row r="812" spans="6:16" ht="12.5">
+    <row r="812" spans="6:16" ht="13.2">
       <c r="F812" s="3"/>
       <c r="I812" s="4"/>
       <c r="J812" s="4"/>
@@ -8152,7 +8181,7 @@
       <c r="L812" s="3"/>
       <c r="P812" s="3"/>
     </row>
-    <row r="813" spans="6:16" ht="12.5">
+    <row r="813" spans="6:16" ht="13.2">
       <c r="F813" s="3"/>
       <c r="I813" s="4"/>
       <c r="J813" s="4"/>
@@ -8160,7 +8189,7 @@
       <c r="L813" s="3"/>
       <c r="P813" s="3"/>
     </row>
-    <row r="814" spans="6:16" ht="12.5">
+    <row r="814" spans="6:16" ht="13.2">
       <c r="F814" s="3"/>
       <c r="I814" s="4"/>
       <c r="J814" s="4"/>
@@ -8168,7 +8197,7 @@
       <c r="L814" s="3"/>
       <c r="P814" s="3"/>
     </row>
-    <row r="815" spans="6:16" ht="12.5">
+    <row r="815" spans="6:16" ht="13.2">
       <c r="F815" s="3"/>
       <c r="I815" s="4"/>
       <c r="J815" s="4"/>
@@ -8176,7 +8205,7 @@
       <c r="L815" s="3"/>
       <c r="P815" s="3"/>
     </row>
-    <row r="816" spans="6:16" ht="12.5">
+    <row r="816" spans="6:16" ht="13.2">
       <c r="F816" s="3"/>
       <c r="I816" s="4"/>
       <c r="J816" s="4"/>
@@ -8184,7 +8213,7 @@
       <c r="L816" s="3"/>
       <c r="P816" s="3"/>
     </row>
-    <row r="817" spans="6:16" ht="12.5">
+    <row r="817" spans="6:16" ht="13.2">
       <c r="F817" s="3"/>
       <c r="I817" s="4"/>
       <c r="J817" s="4"/>
@@ -8192,7 +8221,7 @@
       <c r="L817" s="3"/>
       <c r="P817" s="3"/>
     </row>
-    <row r="818" spans="6:16" ht="12.5">
+    <row r="818" spans="6:16" ht="13.2">
       <c r="F818" s="3"/>
       <c r="I818" s="4"/>
       <c r="J818" s="4"/>
@@ -8200,7 +8229,7 @@
       <c r="L818" s="3"/>
       <c r="P818" s="3"/>
     </row>
-    <row r="819" spans="6:16" ht="12.5">
+    <row r="819" spans="6:16" ht="13.2">
       <c r="F819" s="3"/>
       <c r="I819" s="4"/>
       <c r="J819" s="4"/>
@@ -8208,7 +8237,7 @@
       <c r="L819" s="3"/>
       <c r="P819" s="3"/>
     </row>
-    <row r="820" spans="6:16" ht="12.5">
+    <row r="820" spans="6:16" ht="13.2">
       <c r="F820" s="3"/>
       <c r="I820" s="4"/>
       <c r="J820" s="4"/>
@@ -8216,7 +8245,7 @@
       <c r="L820" s="3"/>
       <c r="P820" s="3"/>
     </row>
-    <row r="821" spans="6:16" ht="12.5">
+    <row r="821" spans="6:16" ht="13.2">
       <c r="F821" s="3"/>
       <c r="I821" s="4"/>
       <c r="J821" s="4"/>
@@ -8224,7 +8253,7 @@
       <c r="L821" s="3"/>
       <c r="P821" s="3"/>
     </row>
-    <row r="822" spans="6:16" ht="12.5">
+    <row r="822" spans="6:16" ht="13.2">
       <c r="F822" s="3"/>
       <c r="I822" s="4"/>
       <c r="J822" s="4"/>
@@ -8232,7 +8261,7 @@
       <c r="L822" s="3"/>
       <c r="P822" s="3"/>
     </row>
-    <row r="823" spans="6:16" ht="12.5">
+    <row r="823" spans="6:16" ht="13.2">
       <c r="F823" s="3"/>
       <c r="I823" s="4"/>
       <c r="J823" s="4"/>
@@ -8240,7 +8269,7 @@
       <c r="L823" s="3"/>
       <c r="P823" s="3"/>
     </row>
-    <row r="824" spans="6:16" ht="12.5">
+    <row r="824" spans="6:16" ht="13.2">
       <c r="F824" s="3"/>
       <c r="I824" s="4"/>
       <c r="J824" s="4"/>
@@ -8248,7 +8277,7 @@
       <c r="L824" s="3"/>
       <c r="P824" s="3"/>
     </row>
-    <row r="825" spans="6:16" ht="12.5">
+    <row r="825" spans="6:16" ht="13.2">
       <c r="F825" s="3"/>
       <c r="I825" s="4"/>
       <c r="J825" s="4"/>
@@ -8256,7 +8285,7 @@
       <c r="L825" s="3"/>
       <c r="P825" s="3"/>
     </row>
-    <row r="826" spans="6:16" ht="12.5">
+    <row r="826" spans="6:16" ht="13.2">
       <c r="F826" s="3"/>
       <c r="I826" s="4"/>
       <c r="J826" s="4"/>
@@ -8264,7 +8293,7 @@
       <c r="L826" s="3"/>
       <c r="P826" s="3"/>
     </row>
-    <row r="827" spans="6:16" ht="12.5">
+    <row r="827" spans="6:16" ht="13.2">
       <c r="F827" s="3"/>
       <c r="I827" s="4"/>
       <c r="J827" s="4"/>
@@ -8272,7 +8301,7 @@
       <c r="L827" s="3"/>
       <c r="P827" s="3"/>
     </row>
-    <row r="828" spans="6:16" ht="12.5">
+    <row r="828" spans="6:16" ht="13.2">
       <c r="F828" s="3"/>
       <c r="I828" s="4"/>
       <c r="J828" s="4"/>
@@ -8280,7 +8309,7 @@
       <c r="L828" s="3"/>
       <c r="P828" s="3"/>
     </row>
-    <row r="829" spans="6:16" ht="12.5">
+    <row r="829" spans="6:16" ht="13.2">
       <c r="F829" s="3"/>
       <c r="I829" s="4"/>
       <c r="J829" s="4"/>
@@ -8288,7 +8317,7 @@
       <c r="L829" s="3"/>
       <c r="P829" s="3"/>
     </row>
-    <row r="830" spans="6:16" ht="12.5">
+    <row r="830" spans="6:16" ht="13.2">
       <c r="F830" s="3"/>
       <c r="I830" s="4"/>
       <c r="J830" s="4"/>
@@ -8296,7 +8325,7 @@
       <c r="L830" s="3"/>
       <c r="P830" s="3"/>
     </row>
-    <row r="831" spans="6:16" ht="12.5">
+    <row r="831" spans="6:16" ht="13.2">
       <c r="F831" s="3"/>
       <c r="I831" s="4"/>
       <c r="J831" s="4"/>
@@ -8304,7 +8333,7 @@
       <c r="L831" s="3"/>
       <c r="P831" s="3"/>
     </row>
-    <row r="832" spans="6:16" ht="12.5">
+    <row r="832" spans="6:16" ht="13.2">
       <c r="F832" s="3"/>
       <c r="I832" s="4"/>
       <c r="J832" s="4"/>
@@ -8312,7 +8341,7 @@
       <c r="L832" s="3"/>
       <c r="P832" s="3"/>
     </row>
-    <row r="833" spans="6:16" ht="12.5">
+    <row r="833" spans="6:16" ht="13.2">
       <c r="F833" s="3"/>
       <c r="I833" s="4"/>
       <c r="J833" s="4"/>
@@ -8320,7 +8349,7 @@
       <c r="L833" s="3"/>
       <c r="P833" s="3"/>
     </row>
-    <row r="834" spans="6:16" ht="12.5">
+    <row r="834" spans="6:16" ht="13.2">
       <c r="F834" s="3"/>
       <c r="I834" s="4"/>
       <c r="J834" s="4"/>
@@ -8328,7 +8357,7 @@
       <c r="L834" s="3"/>
       <c r="P834" s="3"/>
     </row>
-    <row r="835" spans="6:16" ht="12.5">
+    <row r="835" spans="6:16" ht="13.2">
       <c r="F835" s="3"/>
       <c r="I835" s="4"/>
       <c r="J835" s="4"/>
@@ -8336,7 +8365,7 @@
       <c r="L835" s="3"/>
       <c r="P835" s="3"/>
     </row>
-    <row r="836" spans="6:16" ht="12.5">
+    <row r="836" spans="6:16" ht="13.2">
       <c r="F836" s="3"/>
       <c r="I836" s="4"/>
       <c r="J836" s="4"/>
@@ -8344,7 +8373,7 @@
       <c r="L836" s="3"/>
       <c r="P836" s="3"/>
     </row>
-    <row r="837" spans="6:16" ht="12.5">
+    <row r="837" spans="6:16" ht="13.2">
       <c r="F837" s="3"/>
       <c r="I837" s="4"/>
       <c r="J837" s="4"/>
@@ -8352,7 +8381,7 @@
       <c r="L837" s="3"/>
       <c r="P837" s="3"/>
     </row>
-    <row r="838" spans="6:16" ht="12.5">
+    <row r="838" spans="6:16" ht="13.2">
       <c r="F838" s="3"/>
       <c r="I838" s="4"/>
       <c r="J838" s="4"/>
@@ -8360,7 +8389,7 @@
       <c r="L838" s="3"/>
       <c r="P838" s="3"/>
     </row>
-    <row r="839" spans="6:16" ht="12.5">
+    <row r="839" spans="6:16" ht="13.2">
       <c r="F839" s="3"/>
       <c r="I839" s="4"/>
       <c r="J839" s="4"/>
@@ -8368,7 +8397,7 @@
       <c r="L839" s="3"/>
       <c r="P839" s="3"/>
     </row>
-    <row r="840" spans="6:16" ht="12.5">
+    <row r="840" spans="6:16" ht="13.2">
       <c r="F840" s="3"/>
       <c r="I840" s="4"/>
       <c r="J840" s="4"/>
@@ -8376,7 +8405,7 @@
       <c r="L840" s="3"/>
       <c r="P840" s="3"/>
     </row>
-    <row r="841" spans="6:16" ht="12.5">
+    <row r="841" spans="6:16" ht="13.2">
       <c r="F841" s="3"/>
       <c r="I841" s="4"/>
       <c r="J841" s="4"/>
@@ -8384,7 +8413,7 @@
       <c r="L841" s="3"/>
       <c r="P841" s="3"/>
     </row>
-    <row r="842" spans="6:16" ht="12.5">
+    <row r="842" spans="6:16" ht="13.2">
       <c r="F842" s="3"/>
       <c r="I842" s="4"/>
       <c r="J842" s="4"/>
@@ -8392,7 +8421,7 @@
       <c r="L842" s="3"/>
       <c r="P842" s="3"/>
     </row>
-    <row r="843" spans="6:16" ht="12.5">
+    <row r="843" spans="6:16" ht="13.2">
       <c r="F843" s="3"/>
       <c r="I843" s="4"/>
       <c r="J843" s="4"/>
@@ -8400,7 +8429,7 @@
       <c r="L843" s="3"/>
       <c r="P843" s="3"/>
     </row>
-    <row r="844" spans="6:16" ht="12.5">
+    <row r="844" spans="6:16" ht="13.2">
       <c r="F844" s="3"/>
       <c r="I844" s="4"/>
       <c r="J844" s="4"/>
@@ -8408,7 +8437,7 @@
       <c r="L844" s="3"/>
       <c r="P844" s="3"/>
     </row>
-    <row r="845" spans="6:16" ht="12.5">
+    <row r="845" spans="6:16" ht="13.2">
       <c r="F845" s="3"/>
       <c r="I845" s="4"/>
       <c r="J845" s="4"/>
@@ -8416,7 +8445,7 @@
       <c r="L845" s="3"/>
       <c r="P845" s="3"/>
     </row>
-    <row r="846" spans="6:16" ht="12.5">
+    <row r="846" spans="6:16" ht="13.2">
       <c r="F846" s="3"/>
       <c r="I846" s="4"/>
       <c r="J846" s="4"/>
@@ -8424,7 +8453,7 @@
       <c r="L846" s="3"/>
       <c r="P846" s="3"/>
     </row>
-    <row r="847" spans="6:16" ht="12.5">
+    <row r="847" spans="6:16" ht="13.2">
       <c r="F847" s="3"/>
       <c r="I847" s="4"/>
       <c r="J847" s="4"/>
@@ -8432,7 +8461,7 @@
       <c r="L847" s="3"/>
       <c r="P847" s="3"/>
     </row>
-    <row r="848" spans="6:16" ht="12.5">
+    <row r="848" spans="6:16" ht="13.2">
       <c r="F848" s="3"/>
       <c r="I848" s="4"/>
       <c r="J848" s="4"/>
@@ -8440,7 +8469,7 @@
       <c r="L848" s="3"/>
       <c r="P848" s="3"/>
     </row>
-    <row r="849" spans="6:16" ht="12.5">
+    <row r="849" spans="6:16" ht="13.2">
       <c r="F849" s="3"/>
       <c r="I849" s="4"/>
       <c r="J849" s="4"/>
@@ -8448,7 +8477,7 @@
       <c r="L849" s="3"/>
       <c r="P849" s="3"/>
     </row>
-    <row r="850" spans="6:16" ht="12.5">
+    <row r="850" spans="6:16" ht="13.2">
       <c r="F850" s="3"/>
       <c r="I850" s="4"/>
       <c r="J850" s="4"/>
@@ -8456,7 +8485,7 @@
       <c r="L850" s="3"/>
       <c r="P850" s="3"/>
     </row>
-    <row r="851" spans="6:16" ht="12.5">
+    <row r="851" spans="6:16" ht="13.2">
       <c r="F851" s="3"/>
       <c r="I851" s="4"/>
       <c r="J851" s="4"/>
@@ -8464,7 +8493,7 @@
       <c r="L851" s="3"/>
       <c r="P851" s="3"/>
     </row>
-    <row r="852" spans="6:16" ht="12.5">
+    <row r="852" spans="6:16" ht="13.2">
       <c r="F852" s="3"/>
       <c r="I852" s="4"/>
       <c r="J852" s="4"/>
@@ -8472,7 +8501,7 @@
       <c r="L852" s="3"/>
       <c r="P852" s="3"/>
     </row>
-    <row r="853" spans="6:16" ht="12.5">
+    <row r="853" spans="6:16" ht="13.2">
       <c r="F853" s="3"/>
       <c r="I853" s="4"/>
       <c r="J853" s="4"/>
@@ -8480,7 +8509,7 @@
       <c r="L853" s="3"/>
       <c r="P853" s="3"/>
     </row>
-    <row r="854" spans="6:16" ht="12.5">
+    <row r="854" spans="6:16" ht="13.2">
       <c r="F854" s="3"/>
       <c r="I854" s="4"/>
       <c r="J854" s="4"/>
@@ -8488,7 +8517,7 @@
       <c r="L854" s="3"/>
       <c r="P854" s="3"/>
     </row>
-    <row r="855" spans="6:16" ht="12.5">
+    <row r="855" spans="6:16" ht="13.2">
       <c r="F855" s="3"/>
       <c r="I855" s="4"/>
       <c r="J855" s="4"/>
@@ -8496,7 +8525,7 @@
       <c r="L855" s="3"/>
       <c r="P855" s="3"/>
     </row>
-    <row r="856" spans="6:16" ht="12.5">
+    <row r="856" spans="6:16" ht="13.2">
       <c r="F856" s="3"/>
       <c r="I856" s="4"/>
       <c r="J856" s="4"/>
@@ -8504,7 +8533,7 @@
       <c r="L856" s="3"/>
       <c r="P856" s="3"/>
     </row>
-    <row r="857" spans="6:16" ht="12.5">
+    <row r="857" spans="6:16" ht="13.2">
       <c r="F857" s="3"/>
       <c r="I857" s="4"/>
       <c r="J857" s="4"/>
@@ -8512,7 +8541,7 @@
       <c r="L857" s="3"/>
       <c r="P857" s="3"/>
     </row>
-    <row r="858" spans="6:16" ht="12.5">
+    <row r="858" spans="6:16" ht="13.2">
       <c r="F858" s="3"/>
       <c r="I858" s="4"/>
       <c r="J858" s="4"/>
@@ -8520,7 +8549,7 @@
       <c r="L858" s="3"/>
       <c r="P858" s="3"/>
     </row>
-    <row r="859" spans="6:16" ht="12.5">
+    <row r="859" spans="6:16" ht="13.2">
       <c r="F859" s="3"/>
       <c r="I859" s="4"/>
       <c r="J859" s="4"/>
@@ -8528,7 +8557,7 @@
       <c r="L859" s="3"/>
       <c r="P859" s="3"/>
     </row>
-    <row r="860" spans="6:16" ht="12.5">
+    <row r="860" spans="6:16" ht="13.2">
       <c r="F860" s="3"/>
       <c r="I860" s="4"/>
       <c r="J860" s="4"/>
@@ -8536,7 +8565,7 @@
       <c r="L860" s="3"/>
       <c r="P860" s="3"/>
     </row>
-    <row r="861" spans="6:16" ht="12.5">
+    <row r="861" spans="6:16" ht="13.2">
       <c r="F861" s="3"/>
       <c r="I861" s="4"/>
       <c r="J861" s="4"/>
@@ -8544,7 +8573,7 @@
       <c r="L861" s="3"/>
       <c r="P861" s="3"/>
     </row>
-    <row r="862" spans="6:16" ht="12.5">
+    <row r="862" spans="6:16" ht="13.2">
       <c r="F862" s="3"/>
       <c r="I862" s="4"/>
       <c r="J862" s="4"/>
@@ -8552,7 +8581,7 @@
       <c r="L862" s="3"/>
       <c r="P862" s="3"/>
     </row>
-    <row r="863" spans="6:16" ht="12.5">
+    <row r="863" spans="6:16" ht="13.2">
       <c r="F863" s="3"/>
       <c r="I863" s="4"/>
       <c r="J863" s="4"/>
@@ -8560,7 +8589,7 @@
       <c r="L863" s="3"/>
       <c r="P863" s="3"/>
     </row>
-    <row r="864" spans="6:16" ht="12.5">
+    <row r="864" spans="6:16" ht="13.2">
       <c r="F864" s="3"/>
       <c r="I864" s="4"/>
       <c r="J864" s="4"/>
@@ -8568,7 +8597,7 @@
       <c r="L864" s="3"/>
       <c r="P864" s="3"/>
     </row>
-    <row r="865" spans="6:16" ht="12.5">
+    <row r="865" spans="6:16" ht="13.2">
       <c r="F865" s="3"/>
       <c r="I865" s="4"/>
       <c r="J865" s="4"/>
@@ -8576,7 +8605,7 @@
       <c r="L865" s="3"/>
       <c r="P865" s="3"/>
     </row>
-    <row r="866" spans="6:16" ht="12.5">
+    <row r="866" spans="6:16" ht="13.2">
       <c r="F866" s="3"/>
       <c r="I866" s="4"/>
       <c r="J866" s="4"/>
@@ -8584,7 +8613,7 @@
       <c r="L866" s="3"/>
       <c r="P866" s="3"/>
     </row>
-    <row r="867" spans="6:16" ht="12.5">
+    <row r="867" spans="6:16" ht="13.2">
       <c r="F867" s="3"/>
       <c r="I867" s="4"/>
       <c r="J867" s="4"/>
@@ -8592,7 +8621,7 @@
       <c r="L867" s="3"/>
       <c r="P867" s="3"/>
     </row>
-    <row r="868" spans="6:16" ht="12.5">
+    <row r="868" spans="6:16" ht="13.2">
       <c r="F868" s="3"/>
       <c r="I868" s="4"/>
       <c r="J868" s="4"/>
@@ -8600,7 +8629,7 @@
       <c r="L868" s="3"/>
       <c r="P868" s="3"/>
     </row>
-    <row r="869" spans="6:16" ht="12.5">
+    <row r="869" spans="6:16" ht="13.2">
       <c r="F869" s="3"/>
       <c r="I869" s="4"/>
       <c r="J869" s="4"/>
@@ -8608,7 +8637,7 @@
       <c r="L869" s="3"/>
       <c r="P869" s="3"/>
     </row>
-    <row r="870" spans="6:16" ht="12.5">
+    <row r="870" spans="6:16" ht="13.2">
       <c r="F870" s="3"/>
       <c r="I870" s="4"/>
       <c r="J870" s="4"/>
@@ -8616,7 +8645,7 @@
       <c r="L870" s="3"/>
       <c r="P870" s="3"/>
     </row>
-    <row r="871" spans="6:16" ht="12.5">
+    <row r="871" spans="6:16" ht="13.2">
       <c r="F871" s="3"/>
       <c r="I871" s="4"/>
       <c r="J871" s="4"/>
@@ -8624,7 +8653,7 @@
       <c r="L871" s="3"/>
       <c r="P871" s="3"/>
     </row>
-    <row r="872" spans="6:16" ht="12.5">
+    <row r="872" spans="6:16" ht="13.2">
       <c r="F872" s="3"/>
       <c r="I872" s="4"/>
       <c r="J872" s="4"/>
@@ -8632,7 +8661,7 @@
       <c r="L872" s="3"/>
       <c r="P872" s="3"/>
     </row>
-    <row r="873" spans="6:16" ht="12.5">
+    <row r="873" spans="6:16" ht="13.2">
       <c r="F873" s="3"/>
       <c r="I873" s="4"/>
       <c r="J873" s="4"/>
@@ -8640,7 +8669,7 @@
       <c r="L873" s="3"/>
       <c r="P873" s="3"/>
     </row>
-    <row r="874" spans="6:16" ht="12.5">
+    <row r="874" spans="6:16" ht="13.2">
       <c r="F874" s="3"/>
       <c r="I874" s="4"/>
       <c r="J874" s="4"/>
@@ -8648,7 +8677,7 @@
       <c r="L874" s="3"/>
       <c r="P874" s="3"/>
     </row>
-    <row r="875" spans="6:16" ht="12.5">
+    <row r="875" spans="6:16" ht="13.2">
       <c r="F875" s="3"/>
       <c r="I875" s="4"/>
       <c r="J875" s="4"/>
@@ -8656,7 +8685,7 @@
       <c r="L875" s="3"/>
       <c r="P875" s="3"/>
     </row>
-    <row r="876" spans="6:16" ht="12.5">
+    <row r="876" spans="6:16" ht="13.2">
       <c r="F876" s="3"/>
       <c r="I876" s="4"/>
       <c r="J876" s="4"/>
@@ -8664,7 +8693,7 @@
       <c r="L876" s="3"/>
       <c r="P876" s="3"/>
     </row>
-    <row r="877" spans="6:16" ht="12.5">
+    <row r="877" spans="6:16" ht="13.2">
       <c r="F877" s="3"/>
       <c r="I877" s="4"/>
       <c r="J877" s="4"/>
@@ -8672,7 +8701,7 @@
       <c r="L877" s="3"/>
       <c r="P877" s="3"/>
     </row>
-    <row r="878" spans="6:16" ht="12.5">
+    <row r="878" spans="6:16" ht="13.2">
       <c r="F878" s="3"/>
       <c r="I878" s="4"/>
       <c r="J878" s="4"/>
@@ -8680,7 +8709,7 @@
       <c r="L878" s="3"/>
       <c r="P878" s="3"/>
     </row>
-    <row r="879" spans="6:16" ht="12.5">
+    <row r="879" spans="6:16" ht="13.2">
       <c r="F879" s="3"/>
       <c r="I879" s="4"/>
       <c r="J879" s="4"/>
@@ -8688,7 +8717,7 @@
       <c r="L879" s="3"/>
       <c r="P879" s="3"/>
     </row>
-    <row r="880" spans="6:16" ht="12.5">
+    <row r="880" spans="6:16" ht="13.2">
       <c r="F880" s="3"/>
       <c r="I880" s="4"/>
       <c r="J880" s="4"/>
@@ -8696,7 +8725,7 @@
       <c r="L880" s="3"/>
       <c r="P880" s="3"/>
     </row>
-    <row r="881" spans="6:16" ht="12.5">
+    <row r="881" spans="6:16" ht="13.2">
       <c r="F881" s="3"/>
       <c r="I881" s="4"/>
       <c r="J881" s="4"/>
@@ -8704,7 +8733,7 @@
       <c r="L881" s="3"/>
       <c r="P881" s="3"/>
     </row>
-    <row r="882" spans="6:16" ht="12.5">
+    <row r="882" spans="6:16" ht="13.2">
       <c r="F882" s="3"/>
       <c r="I882" s="4"/>
       <c r="J882" s="4"/>
@@ -8712,7 +8741,7 @@
       <c r="L882" s="3"/>
       <c r="P882" s="3"/>
     </row>
-    <row r="883" spans="6:16" ht="12.5">
+    <row r="883" spans="6:16" ht="13.2">
       <c r="F883" s="3"/>
       <c r="I883" s="4"/>
       <c r="J883" s="4"/>
@@ -8720,7 +8749,7 @@
       <c r="L883" s="3"/>
       <c r="P883" s="3"/>
     </row>
-    <row r="884" spans="6:16" ht="12.5">
+    <row r="884" spans="6:16" ht="13.2">
       <c r="F884" s="3"/>
       <c r="I884" s="4"/>
       <c r="J884" s="4"/>
@@ -8728,7 +8757,7 @@
       <c r="L884" s="3"/>
       <c r="P884" s="3"/>
     </row>
-    <row r="885" spans="6:16" ht="12.5">
+    <row r="885" spans="6:16" ht="13.2">
       <c r="F885" s="3"/>
       <c r="I885" s="4"/>
       <c r="J885" s="4"/>
@@ -8736,7 +8765,7 @@
       <c r="L885" s="3"/>
       <c r="P885" s="3"/>
     </row>
-    <row r="886" spans="6:16" ht="12.5">
+    <row r="886" spans="6:16" ht="13.2">
       <c r="F886" s="3"/>
       <c r="I886" s="4"/>
       <c r="J886" s="4"/>
@@ -8744,7 +8773,7 @@
       <c r="L886" s="3"/>
       <c r="P886" s="3"/>
     </row>
-    <row r="887" spans="6:16" ht="12.5">
+    <row r="887" spans="6:16" ht="13.2">
       <c r="F887" s="3"/>
       <c r="I887" s="4"/>
       <c r="J887" s="4"/>
@@ -8752,7 +8781,7 @@
       <c r="L887" s="3"/>
       <c r="P887" s="3"/>
     </row>
-    <row r="888" spans="6:16" ht="12.5">
+    <row r="888" spans="6:16" ht="13.2">
       <c r="F888" s="3"/>
       <c r="I888" s="4"/>
       <c r="J888" s="4"/>
@@ -8760,7 +8789,7 @@
       <c r="L888" s="3"/>
       <c r="P888" s="3"/>
     </row>
-    <row r="889" spans="6:16" ht="12.5">
+    <row r="889" spans="6:16" ht="13.2">
       <c r="F889" s="3"/>
       <c r="I889" s="4"/>
       <c r="J889" s="4"/>
@@ -8768,7 +8797,7 @@
       <c r="L889" s="3"/>
       <c r="P889" s="3"/>
     </row>
-    <row r="890" spans="6:16" ht="12.5">
+    <row r="890" spans="6:16" ht="13.2">
       <c r="F890" s="3"/>
       <c r="I890" s="4"/>
       <c r="J890" s="4"/>
@@ -8776,7 +8805,7 @@
       <c r="L890" s="3"/>
       <c r="P890" s="3"/>
     </row>
-    <row r="891" spans="6:16" ht="12.5">
+    <row r="891" spans="6:16" ht="13.2">
       <c r="F891" s="3"/>
       <c r="I891" s="4"/>
       <c r="J891" s="4"/>
@@ -8784,7 +8813,7 @@
       <c r="L891" s="3"/>
       <c r="P891" s="3"/>
     </row>
-    <row r="892" spans="6:16" ht="12.5">
+    <row r="892" spans="6:16" ht="13.2">
       <c r="F892" s="3"/>
       <c r="I892" s="4"/>
       <c r="J892" s="4"/>
@@ -8792,7 +8821,7 @@
       <c r="L892" s="3"/>
       <c r="P892" s="3"/>
     </row>
-    <row r="893" spans="6:16" ht="12.5">
+    <row r="893" spans="6:16" ht="13.2">
       <c r="F893" s="3"/>
       <c r="I893" s="4"/>
       <c r="J893" s="4"/>
@@ -8800,7 +8829,7 @@
       <c r="L893" s="3"/>
       <c r="P893" s="3"/>
     </row>
-    <row r="894" spans="6:16" ht="12.5">
+    <row r="894" spans="6:16" ht="13.2">
       <c r="F894" s="3"/>
       <c r="I894" s="4"/>
       <c r="J894" s="4"/>
@@ -8808,7 +8837,7 @@
       <c r="L894" s="3"/>
       <c r="P894" s="3"/>
     </row>
-    <row r="895" spans="6:16" ht="12.5">
+    <row r="895" spans="6:16" ht="13.2">
       <c r="F895" s="3"/>
       <c r="I895" s="4"/>
       <c r="J895" s="4"/>
@@ -8816,7 +8845,7 @@
       <c r="L895" s="3"/>
       <c r="P895" s="3"/>
     </row>
-    <row r="896" spans="6:16" ht="12.5">
+    <row r="896" spans="6:16" ht="13.2">
       <c r="F896" s="3"/>
       <c r="I896" s="4"/>
       <c r="J896" s="4"/>
@@ -8824,7 +8853,7 @@
       <c r="L896" s="3"/>
       <c r="P896" s="3"/>
     </row>
-    <row r="897" spans="6:16" ht="12.5">
+    <row r="897" spans="6:16" ht="13.2">
       <c r="F897" s="3"/>
       <c r="I897" s="4"/>
       <c r="J897" s="4"/>
@@ -8832,7 +8861,7 @@
       <c r="L897" s="3"/>
       <c r="P897" s="3"/>
     </row>
-    <row r="898" spans="6:16" ht="12.5">
+    <row r="898" spans="6:16" ht="13.2">
       <c r="F898" s="3"/>
       <c r="I898" s="4"/>
       <c r="J898" s="4"/>
@@ -8840,7 +8869,7 @@
       <c r="L898" s="3"/>
       <c r="P898" s="3"/>
     </row>
-    <row r="899" spans="6:16" ht="12.5">
+    <row r="899" spans="6:16" ht="13.2">
       <c r="F899" s="3"/>
       <c r="I899" s="4"/>
       <c r="J899" s="4"/>
@@ -8848,7 +8877,7 @@
       <c r="L899" s="3"/>
       <c r="P899" s="3"/>
     </row>
-    <row r="900" spans="6:16" ht="12.5">
+    <row r="900" spans="6:16" ht="13.2">
       <c r="F900" s="3"/>
       <c r="I900" s="4"/>
       <c r="J900" s="4"/>
@@ -8856,7 +8885,7 @@
       <c r="L900" s="3"/>
       <c r="P900" s="3"/>
     </row>
-    <row r="901" spans="6:16" ht="12.5">
+    <row r="901" spans="6:16" ht="13.2">
       <c r="F901" s="3"/>
       <c r="I901" s="4"/>
       <c r="J901" s="4"/>
@@ -8864,7 +8893,7 @@
       <c r="L901" s="3"/>
       <c r="P901" s="3"/>
     </row>
-    <row r="902" spans="6:16" ht="12.5">
+    <row r="902" spans="6:16" ht="13.2">
       <c r="F902" s="3"/>
       <c r="I902" s="4"/>
       <c r="J902" s="4"/>
@@ -8872,7 +8901,7 @@
       <c r="L902" s="3"/>
       <c r="P902" s="3"/>
     </row>
-    <row r="903" spans="6:16" ht="12.5">
+    <row r="903" spans="6:16" ht="13.2">
       <c r="F903" s="3"/>
       <c r="I903" s="4"/>
       <c r="J903" s="4"/>
@@ -8880,7 +8909,7 @@
       <c r="L903" s="3"/>
       <c r="P903" s="3"/>
     </row>
-    <row r="904" spans="6:16" ht="12.5">
+    <row r="904" spans="6:16" ht="13.2">
       <c r="F904" s="3"/>
       <c r="I904" s="4"/>
       <c r="J904" s="4"/>
@@ -8888,7 +8917,7 @@
       <c r="L904" s="3"/>
       <c r="P904" s="3"/>
     </row>
-    <row r="905" spans="6:16" ht="12.5">
+    <row r="905" spans="6:16" ht="13.2">
       <c r="F905" s="3"/>
       <c r="I905" s="4"/>
       <c r="J905" s="4"/>
@@ -8896,7 +8925,7 @@
       <c r="L905" s="3"/>
       <c r="P905" s="3"/>
     </row>
-    <row r="906" spans="6:16" ht="12.5">
+    <row r="906" spans="6:16" ht="13.2">
       <c r="F906" s="3"/>
       <c r="I906" s="4"/>
       <c r="J906" s="4"/>
@@ -8904,7 +8933,7 @@
       <c r="L906" s="3"/>
       <c r="P906" s="3"/>
     </row>
-    <row r="907" spans="6:16" ht="12.5">
+    <row r="907" spans="6:16" ht="13.2">
       <c r="F907" s="3"/>
       <c r="I907" s="4"/>
       <c r="J907" s="4"/>
@@ -8912,7 +8941,7 @@
       <c r="L907" s="3"/>
       <c r="P907" s="3"/>
     </row>
-    <row r="908" spans="6:16" ht="12.5">
+    <row r="908" spans="6:16" ht="13.2">
       <c r="F908" s="3"/>
       <c r="I908" s="4"/>
       <c r="J908" s="4"/>
@@ -8920,7 +8949,7 @@
       <c r="L908" s="3"/>
       <c r="P908" s="3"/>
     </row>
-    <row r="909" spans="6:16" ht="12.5">
+    <row r="909" spans="6:16" ht="13.2">
       <c r="F909" s="3"/>
       <c r="I909" s="4"/>
       <c r="J909" s="4"/>
@@ -8928,7 +8957,7 @@
       <c r="L909" s="3"/>
       <c r="P909" s="3"/>
     </row>
-    <row r="910" spans="6:16" ht="12.5">
+    <row r="910" spans="6:16" ht="13.2">
       <c r="F910" s="3"/>
       <c r="I910" s="4"/>
       <c r="J910" s="4"/>
@@ -8936,7 +8965,7 @@
       <c r="L910" s="3"/>
       <c r="P910" s="3"/>
     </row>
-    <row r="911" spans="6:16" ht="12.5">
+    <row r="911" spans="6:16" ht="13.2">
       <c r="F911" s="3"/>
       <c r="I911" s="4"/>
       <c r="J911" s="4"/>
@@ -8944,7 +8973,7 @@
       <c r="L911" s="3"/>
       <c r="P911" s="3"/>
     </row>
-    <row r="912" spans="6:16" ht="12.5">
+    <row r="912" spans="6:16" ht="13.2">
       <c r="F912" s="3"/>
       <c r="I912" s="4"/>
       <c r="J912" s="4"/>
@@ -8952,7 +8981,7 @@
       <c r="L912" s="3"/>
       <c r="P912" s="3"/>
     </row>
-    <row r="913" spans="6:16" ht="12.5">
+    <row r="913" spans="6:16" ht="13.2">
       <c r="F913" s="3"/>
       <c r="I913" s="4"/>
       <c r="J913" s="4"/>
@@ -8960,7 +8989,7 @@
       <c r="L913" s="3"/>
       <c r="P913" s="3"/>
     </row>
-    <row r="914" spans="6:16" ht="12.5">
+    <row r="914" spans="6:16" ht="13.2">
       <c r="F914" s="3"/>
       <c r="I914" s="4"/>
       <c r="J914" s="4"/>
@@ -8968,7 +8997,7 @@
       <c r="L914" s="3"/>
       <c r="P914" s="3"/>
     </row>
-    <row r="915" spans="6:16" ht="12.5">
+    <row r="915" spans="6:16" ht="13.2">
       <c r="F915" s="3"/>
       <c r="I915" s="4"/>
       <c r="J915" s="4"/>
@@ -8976,7 +9005,7 @@
       <c r="L915" s="3"/>
       <c r="P915" s="3"/>
     </row>
-    <row r="916" spans="6:16" ht="12.5">
+    <row r="916" spans="6:16" ht="13.2">
       <c r="F916" s="3"/>
       <c r="I916" s="4"/>
       <c r="J916" s="4"/>
@@ -8984,7 +9013,7 @@
       <c r="L916" s="3"/>
       <c r="P916" s="3"/>
     </row>
-    <row r="917" spans="6:16" ht="12.5">
+    <row r="917" spans="6:16" ht="13.2">
       <c r="F917" s="3"/>
       <c r="I917" s="4"/>
       <c r="J917" s="4"/>
@@ -8992,7 +9021,7 @@
       <c r="L917" s="3"/>
       <c r="P917" s="3"/>
     </row>
-    <row r="918" spans="6:16" ht="12.5">
+    <row r="918" spans="6:16" ht="13.2">
       <c r="F918" s="3"/>
       <c r="I918" s="4"/>
       <c r="J918" s="4"/>
@@ -9000,7 +9029,7 @@
       <c r="L918" s="3"/>
       <c r="P918" s="3"/>
     </row>
-    <row r="919" spans="6:16" ht="12.5">
+    <row r="919" spans="6:16" ht="13.2">
       <c r="F919" s="3"/>
       <c r="I919" s="4"/>
       <c r="J919" s="4"/>
@@ -9008,7 +9037,7 @@
       <c r="L919" s="3"/>
       <c r="P919" s="3"/>
     </row>
-    <row r="920" spans="6:16" ht="12.5">
+    <row r="920" spans="6:16" ht="13.2">
       <c r="F920" s="3"/>
       <c r="I920" s="4"/>
       <c r="J920" s="4"/>
@@ -9016,7 +9045,7 @@
       <c r="L920" s="3"/>
       <c r="P920" s="3"/>
     </row>
-    <row r="921" spans="6:16" ht="12.5">
+    <row r="921" spans="6:16" ht="13.2">
       <c r="F921" s="3"/>
       <c r="I921" s="4"/>
       <c r="J921" s="4"/>
@@ -9024,7 +9053,7 @@
       <c r="L921" s="3"/>
       <c r="P921" s="3"/>
     </row>
-    <row r="922" spans="6:16" ht="12.5">
+    <row r="922" spans="6:16" ht="13.2">
       <c r="F922" s="3"/>
       <c r="I922" s="4"/>
       <c r="J922" s="4"/>
@@ -9032,7 +9061,7 @@
       <c r="L922" s="3"/>
       <c r="P922" s="3"/>
     </row>
-    <row r="923" spans="6:16" ht="12.5">
+    <row r="923" spans="6:16" ht="13.2">
       <c r="F923" s="3"/>
       <c r="I923" s="4"/>
       <c r="J923" s="4"/>
@@ -9040,7 +9069,7 @@
       <c r="L923" s="3"/>
       <c r="P923" s="3"/>
     </row>
-    <row r="924" spans="6:16" ht="12.5">
+    <row r="924" spans="6:16" ht="13.2">
       <c r="F924" s="3"/>
       <c r="I924" s="4"/>
       <c r="J924" s="4"/>
@@ -9048,7 +9077,7 @@
       <c r="L924" s="3"/>
       <c r="P924" s="3"/>
     </row>
-    <row r="925" spans="6:16" ht="12.5">
+    <row r="925" spans="6:16" ht="13.2">
       <c r="F925" s="3"/>
       <c r="I925" s="4"/>
       <c r="J925" s="4"/>
@@ -9056,7 +9085,7 @@
       <c r="L925" s="3"/>
       <c r="P925" s="3"/>
     </row>
-    <row r="926" spans="6:16" ht="12.5">
+    <row r="926" spans="6:16" ht="13.2">
       <c r="F926" s="3"/>
       <c r="I926" s="4"/>
       <c r="J926" s="4"/>
@@ -9064,7 +9093,7 @@
       <c r="L926" s="3"/>
       <c r="P926" s="3"/>
     </row>
-    <row r="927" spans="6:16" ht="12.5">
+    <row r="927" spans="6:16" ht="13.2">
       <c r="F927" s="3"/>
       <c r="I927" s="4"/>
       <c r="J927" s="4"/>
@@ -9072,7 +9101,7 @@
       <c r="L927" s="3"/>
       <c r="P927" s="3"/>
     </row>
-    <row r="928" spans="6:16" ht="12.5">
+    <row r="928" spans="6:16" ht="13.2">
       <c r="F928" s="3"/>
       <c r="I928" s="4"/>
       <c r="J928" s="4"/>
@@ -9080,7 +9109,7 @@
       <c r="L928" s="3"/>
       <c r="P928" s="3"/>
     </row>
-    <row r="929" spans="6:16" ht="12.5">
+    <row r="929" spans="6:16" ht="13.2">
       <c r="F929" s="3"/>
       <c r="I929" s="4"/>
       <c r="J929" s="4"/>
@@ -9088,7 +9117,7 @@
       <c r="L929" s="3"/>
       <c r="P929" s="3"/>
     </row>
-    <row r="930" spans="6:16" ht="12.5">
+    <row r="930" spans="6:16" ht="13.2">
       <c r="F930" s="3"/>
       <c r="I930" s="4"/>
       <c r="J930" s="4"/>
@@ -9096,7 +9125,7 @@
       <c r="L930" s="3"/>
       <c r="P930" s="3"/>
     </row>
-    <row r="931" spans="6:16" ht="12.5">
+    <row r="931" spans="6:16" ht="13.2">
       <c r="F931" s="3"/>
       <c r="I931" s="4"/>
       <c r="J931" s="4"/>
@@ -9104,7 +9133,7 @@
       <c r="L931" s="3"/>
       <c r="P931" s="3"/>
     </row>
-    <row r="932" spans="6:16" ht="12.5">
+    <row r="932" spans="6:16" ht="13.2">
       <c r="F932" s="3"/>
       <c r="I932" s="4"/>
       <c r="J932" s="4"/>
@@ -9112,7 +9141,7 @@
       <c r="L932" s="3"/>
       <c r="P932" s="3"/>
     </row>
-    <row r="933" spans="6:16" ht="12.5">
+    <row r="933" spans="6:16" ht="13.2">
       <c r="F933" s="3"/>
       <c r="I933" s="4"/>
       <c r="J933" s="4"/>
@@ -9120,7 +9149,7 @@
       <c r="L933" s="3"/>
       <c r="P933" s="3"/>
     </row>
-    <row r="934" spans="6:16" ht="12.5">
+    <row r="934" spans="6:16" ht="13.2">
       <c r="F934" s="3"/>
       <c r="I934" s="4"/>
       <c r="J934" s="4"/>
@@ -9128,7 +9157,7 @@
       <c r="L934" s="3"/>
       <c r="P934" s="3"/>
     </row>
-    <row r="935" spans="6:16" ht="12.5">
+    <row r="935" spans="6:16" ht="13.2">
       <c r="F935" s="3"/>
       <c r="I935" s="4"/>
       <c r="J935" s="4"/>
@@ -9136,7 +9165,7 @@
       <c r="L935" s="3"/>
       <c r="P935" s="3"/>
     </row>
-    <row r="936" spans="6:16" ht="12.5">
+    <row r="936" spans="6:16" ht="13.2">
       <c r="F936" s="3"/>
       <c r="I936" s="4"/>
       <c r="J936" s="4"/>
@@ -9144,7 +9173,7 @@
       <c r="L936" s="3"/>
       <c r="P936" s="3"/>
     </row>
-    <row r="937" spans="6:16" ht="12.5">
+    <row r="937" spans="6:16" ht="13.2">
       <c r="F937" s="3"/>
       <c r="I937" s="4"/>
       <c r="J937" s="4"/>
@@ -9152,7 +9181,7 @@
       <c r="L937" s="3"/>
       <c r="P937" s="3"/>
     </row>
-    <row r="938" spans="6:16" ht="12.5">
+    <row r="938" spans="6:16" ht="13.2">
       <c r="F938" s="3"/>
       <c r="I938" s="4"/>
       <c r="J938" s="4"/>
@@ -9160,7 +9189,7 @@
       <c r="L938" s="3"/>
       <c r="P938" s="3"/>
     </row>
-    <row r="939" spans="6:16" ht="12.5">
+    <row r="939" spans="6:16" ht="13.2">
       <c r="F939" s="3"/>
       <c r="I939" s="4"/>
       <c r="J939" s="4"/>
@@ -9168,7 +9197,7 @@
       <c r="L939" s="3"/>
       <c r="P939" s="3"/>
     </row>
-    <row r="940" spans="6:16" ht="12.5">
+    <row r="940" spans="6:16" ht="13.2">
       <c r="F940" s="3"/>
       <c r="I940" s="4"/>
       <c r="J940" s="4"/>
@@ -9176,7 +9205,7 @@
       <c r="L940" s="3"/>
       <c r="P940" s="3"/>
     </row>
-    <row r="941" spans="6:16" ht="12.5">
+    <row r="941" spans="6:16" ht="13.2">
       <c r="F941" s="3"/>
       <c r="I941" s="4"/>
       <c r="J941" s="4"/>
@@ -9184,7 +9213,7 @@
       <c r="L941" s="3"/>
       <c r="P941" s="3"/>
     </row>
-    <row r="942" spans="6:16" ht="12.5">
+    <row r="942" spans="6:16" ht="13.2">
       <c r="F942" s="3"/>
       <c r="I942" s="4"/>
       <c r="J942" s="4"/>
@@ -9192,7 +9221,7 @@
       <c r="L942" s="3"/>
       <c r="P942" s="3"/>
     </row>
-    <row r="943" spans="6:16" ht="12.5">
+    <row r="943" spans="6:16" ht="13.2">
       <c r="F943" s="3"/>
       <c r="I943" s="4"/>
       <c r="J943" s="4"/>
@@ -9200,7 +9229,7 @@
       <c r="L943" s="3"/>
       <c r="P943" s="3"/>
     </row>
-    <row r="944" spans="6:16" ht="12.5">
+    <row r="944" spans="6:16" ht="13.2">
       <c r="F944" s="3"/>
       <c r="I944" s="4"/>
       <c r="J944" s="4"/>
@@ -9208,7 +9237,7 @@
       <c r="L944" s="3"/>
       <c r="P944" s="3"/>
     </row>
-    <row r="945" spans="6:16" ht="12.5">
+    <row r="945" spans="6:16" ht="13.2">
       <c r="F945" s="3"/>
       <c r="I945" s="4"/>
       <c r="J945" s="4"/>
@@ -9216,7 +9245,7 @@
       <c r="L945" s="3"/>
       <c r="P945" s="3"/>
     </row>
-    <row r="946" spans="6:16" ht="12.5">
+    <row r="946" spans="6:16" ht="13.2">
       <c r="F946" s="3"/>
       <c r="I946" s="4"/>
       <c r="J946" s="4"/>
@@ -9224,7 +9253,7 @@
       <c r="L946" s="3"/>
       <c r="P946" s="3"/>
     </row>
-    <row r="947" spans="6:16" ht="12.5">
+    <row r="947" spans="6:16" ht="13.2">
       <c r="F947" s="3"/>
       <c r="I947" s="4"/>
       <c r="J947" s="4"/>
@@ -9232,7 +9261,7 @@
       <c r="L947" s="3"/>
       <c r="P947" s="3"/>
     </row>
-    <row r="948" spans="6:16" ht="12.5">
+    <row r="948" spans="6:16" ht="13.2">
       <c r="F948" s="3"/>
       <c r="I948" s="4"/>
       <c r="J948" s="4"/>
@@ -9240,7 +9269,7 @@
       <c r="L948" s="3"/>
       <c r="P948" s="3"/>
     </row>
-    <row r="949" spans="6:16" ht="12.5">
+    <row r="949" spans="6:16" ht="13.2">
       <c r="F949" s="3"/>
       <c r="I949" s="4"/>
       <c r="J949" s="4"/>
@@ -9248,7 +9277,7 @@
       <c r="L949" s="3"/>
       <c r="P949" s="3"/>
     </row>
-    <row r="950" spans="6:16" ht="12.5">
+    <row r="950" spans="6:16" ht="13.2">
       <c r="F950" s="3"/>
       <c r="I950" s="4"/>
       <c r="J950" s="4"/>
@@ -9256,7 +9285,7 @@
       <c r="L950" s="3"/>
       <c r="P950" s="3"/>
     </row>
-    <row r="951" spans="6:16" ht="12.5">
+    <row r="951" spans="6:16" ht="13.2">
       <c r="F951" s="3"/>
       <c r="I951" s="4"/>
       <c r="J951" s="4"/>
@@ -9264,7 +9293,7 @@
       <c r="L951" s="3"/>
       <c r="P951" s="3"/>
     </row>
-    <row r="952" spans="6:16" ht="12.5">
+    <row r="952" spans="6:16" ht="13.2">
       <c r="F952" s="3"/>
       <c r="I952" s="4"/>
       <c r="J952" s="4"/>
@@ -9272,7 +9301,7 @@
       <c r="L952" s="3"/>
       <c r="P952" s="3"/>
     </row>
-    <row r="953" spans="6:16" ht="12.5">
+    <row r="953" spans="6:16" ht="13.2">
       <c r="F953" s="3"/>
       <c r="I953" s="4"/>
       <c r="J953" s="4"/>
@@ -9280,7 +9309,7 @@
       <c r="L953" s="3"/>
       <c r="P953" s="3"/>
     </row>
-    <row r="954" spans="6:16" ht="12.5">
+    <row r="954" spans="6:16" ht="13.2">
       <c r="F954" s="3"/>
       <c r="I954" s="4"/>
       <c r="J954" s="4"/>
@@ -9288,7 +9317,7 @@
       <c r="L954" s="3"/>
       <c r="P954" s="3"/>
     </row>
-    <row r="955" spans="6:16" ht="12.5">
+    <row r="955" spans="6:16" ht="13.2">
       <c r="F955" s="3"/>
       <c r="I955" s="4"/>
       <c r="J955" s="4"/>
@@ -9296,7 +9325,7 @@
       <c r="L955" s="3"/>
       <c r="P955" s="3"/>
     </row>
-    <row r="956" spans="6:16" ht="12.5">
+    <row r="956" spans="6:16" ht="13.2">
       <c r="F956" s="3"/>
       <c r="I956" s="4"/>
       <c r="J956" s="4"/>
@@ -9304,7 +9333,7 @@
       <c r="L956" s="3"/>
       <c r="P956" s="3"/>
     </row>
-    <row r="957" spans="6:16" ht="12.5">
+    <row r="957" spans="6:16" ht="13.2">
       <c r="F957" s="3"/>
       <c r="I957" s="4"/>
       <c r="J957" s="4"/>
@@ -9312,7 +9341,7 @@
       <c r="L957" s="3"/>
       <c r="P957" s="3"/>
     </row>
-    <row r="958" spans="6:16" ht="12.5">
+    <row r="958" spans="6:16" ht="13.2">
       <c r="F958" s="3"/>
       <c r="I958" s="4"/>
       <c r="J958" s="4"/>
@@ -9320,7 +9349,7 @@
       <c r="L958" s="3"/>
       <c r="P958" s="3"/>
     </row>
-    <row r="959" spans="6:16" ht="12.5">
+    <row r="959" spans="6:16" ht="13.2">
       <c r="F959" s="3"/>
       <c r="I959" s="4"/>
       <c r="J959" s="4"/>
@@ -9328,7 +9357,7 @@
       <c r="L959" s="3"/>
       <c r="P959" s="3"/>
     </row>
-    <row r="960" spans="6:16" ht="12.5">
+    <row r="960" spans="6:16" ht="13.2">
       <c r="F960" s="3"/>
       <c r="I960" s="4"/>
       <c r="J960" s="4"/>
@@ -9336,7 +9365,7 @@
       <c r="L960" s="3"/>
       <c r="P960" s="3"/>
     </row>
-    <row r="961" spans="6:16" ht="12.5">
+    <row r="961" spans="6:16" ht="13.2">
       <c r="F961" s="3"/>
       <c r="I961" s="4"/>
       <c r="J961" s="4"/>
@@ -9344,7 +9373,7 @@
       <c r="L961" s="3"/>
       <c r="P961" s="3"/>
     </row>
-    <row r="962" spans="6:16" ht="12.5">
+    <row r="962" spans="6:16" ht="13.2">
       <c r="F962" s="3"/>
       <c r="I962" s="4"/>
       <c r="J962" s="4"/>
@@ -9352,7 +9381,7 @@
       <c r="L962" s="3"/>
       <c r="P962" s="3"/>
     </row>
-    <row r="963" spans="6:16" ht="12.5">
+    <row r="963" spans="6:16" ht="13.2">
       <c r="F963" s="3"/>
       <c r="I963" s="4"/>
       <c r="J963" s="4"/>
@@ -9360,7 +9389,7 @@
       <c r="L963" s="3"/>
       <c r="P963" s="3"/>
     </row>
-    <row r="964" spans="6:16" ht="12.5">
+    <row r="964" spans="6:16" ht="13.2">
       <c r="F964" s="3"/>
       <c r="I964" s="4"/>
       <c r="J964" s="4"/>
@@ -9368,7 +9397,7 @@
       <c r="L964" s="3"/>
       <c r="P964" s="3"/>
     </row>
-    <row r="965" spans="6:16" ht="12.5">
+    <row r="965" spans="6:16" ht="13.2">
       <c r="F965" s="3"/>
       <c r="I965" s="4"/>
       <c r="J965" s="4"/>
@@ -9376,7 +9405,7 @@
       <c r="L965" s="3"/>
       <c r="P965" s="3"/>
     </row>
-    <row r="966" spans="6:16" ht="12.5">
+    <row r="966" spans="6:16" ht="13.2">
       <c r="F966" s="3"/>
       <c r="I966" s="4"/>
       <c r="J966" s="4"/>
@@ -9384,7 +9413,7 @@
       <c r="L966" s="3"/>
       <c r="P966" s="3"/>
     </row>
-    <row r="967" spans="6:16" ht="12.5">
+    <row r="967" spans="6:16" ht="13.2">
       <c r="F967" s="3"/>
       <c r="I967" s="4"/>
       <c r="J967" s="4"/>
@@ -9392,7 +9421,7 @@
       <c r="L967" s="3"/>
       <c r="P967" s="3"/>
     </row>
-    <row r="968" spans="6:16" ht="12.5">
+    <row r="968" spans="6:16" ht="13.2">
       <c r="F968" s="3"/>
       <c r="I968" s="4"/>
       <c r="J968" s="4"/>
@@ -9400,7 +9429,7 @@
       <c r="L968" s="3"/>
       <c r="P968" s="3"/>
     </row>
-    <row r="969" spans="6:16" ht="12.5">
+    <row r="969" spans="6:16" ht="13.2">
       <c r="F969" s="3"/>
       <c r="I969" s="4"/>
       <c r="J969" s="4"/>
@@ -9408,7 +9437,7 @@
       <c r="L969" s="3"/>
       <c r="P969" s="3"/>
     </row>
-    <row r="970" spans="6:16" ht="12.5">
+    <row r="970" spans="6:16" ht="13.2">
       <c r="F970" s="3"/>
       <c r="I970" s="4"/>
       <c r="J970" s="4"/>
@@ -9416,7 +9445,7 @@
       <c r="L970" s="3"/>
       <c r="P970" s="3"/>
     </row>
-    <row r="971" spans="6:16" ht="12.5">
+    <row r="971" spans="6:16" ht="13.2">
       <c r="F971" s="3"/>
       <c r="I971" s="4"/>
       <c r="J971" s="4"/>
@@ -9424,7 +9453,7 @@
       <c r="L971" s="3"/>
       <c r="P971" s="3"/>
     </row>
-    <row r="972" spans="6:16" ht="12.5">
+    <row r="972" spans="6:16" ht="13.2">
       <c r="F972" s="3"/>
       <c r="I972" s="4"/>
       <c r="J972" s="4"/>
@@ -9432,7 +9461,7 @@
       <c r="L972" s="3"/>
       <c r="P972" s="3"/>
     </row>
-    <row r="973" spans="6:16" ht="12.5">
+    <row r="973" spans="6:16" ht="13.2">
       <c r="F973" s="3"/>
       <c r="I973" s="4"/>
       <c r="J973" s="4"/>
@@ -9440,7 +9469,7 @@
       <c r="L973" s="3"/>
       <c r="P973" s="3"/>
     </row>
-    <row r="974" spans="6:16" ht="12.5">
+    <row r="974" spans="6:16" ht="13.2">
       <c r="F974" s="3"/>
       <c r="I974" s="4"/>
       <c r="J974" s="4"/>
@@ -9448,7 +9477,7 @@
       <c r="L974" s="3"/>
       <c r="P974" s="3"/>
     </row>
-    <row r="975" spans="6:16" ht="12.5">
+    <row r="975" spans="6:16" ht="13.2">
       <c r="F975" s="3"/>
       <c r="I975" s="4"/>
       <c r="J975" s="4"/>
@@ -9456,7 +9485,7 @@
       <c r="L975" s="3"/>
       <c r="P975" s="3"/>
     </row>
-    <row r="976" spans="6:16" ht="12.5">
+    <row r="976" spans="6:16" ht="13.2">
       <c r="F976" s="3"/>
       <c r="I976" s="4"/>
       <c r="J976" s="4"/>
@@ -9464,7 +9493,7 @@
       <c r="L976" s="3"/>
       <c r="P976" s="3"/>
     </row>
-    <row r="977" spans="6:16" ht="12.5">
+    <row r="977" spans="6:16" ht="13.2">
       <c r="F977" s="3"/>
       <c r="I977" s="4"/>
       <c r="J977" s="4"/>
@@ -9472,7 +9501,7 @@
       <c r="L977" s="3"/>
       <c r="P977" s="3"/>
     </row>
-    <row r="978" spans="6:16" ht="12.5">
+    <row r="978" spans="6:16" ht="13.2">
       <c r="F978" s="3"/>
       <c r="I978" s="4"/>
       <c r="J978" s="4"/>
@@ -9480,7 +9509,7 @@
       <c r="L978" s="3"/>
       <c r="P978" s="3"/>
     </row>
-    <row r="979" spans="6:16" ht="12.5">
+    <row r="979" spans="6:16" ht="13.2">
       <c r="F979" s="3"/>
       <c r="I979" s="4"/>
       <c r="J979" s="4"/>
@@ -9488,7 +9517,7 @@
       <c r="L979" s="3"/>
       <c r="P979" s="3"/>
     </row>
-    <row r="980" spans="6:16" ht="12.5">
+    <row r="980" spans="6:16" ht="13.2">
       <c r="F980" s="3"/>
       <c r="I980" s="4"/>
       <c r="J980" s="4"/>
@@ -9496,7 +9525,7 @@
       <c r="L980" s="3"/>
       <c r="P980" s="3"/>
     </row>
-    <row r="981" spans="6:16" ht="12.5">
+    <row r="981" spans="6:16" ht="13.2">
       <c r="F981" s="3"/>
       <c r="I981" s="4"/>
       <c r="J981" s="4"/>
@@ -9504,7 +9533,7 @@
       <c r="L981" s="3"/>
       <c r="P981" s="3"/>
     </row>
-    <row r="982" spans="6:16" ht="12.5">
+    <row r="982" spans="6:16" ht="13.2">
       <c r="F982" s="3"/>
       <c r="I982" s="4"/>
       <c r="J982" s="4"/>
@@ -9512,7 +9541,7 @@
       <c r="L982" s="3"/>
       <c r="P982" s="3"/>
     </row>
-    <row r="983" spans="6:16" ht="12.5">
+    <row r="983" spans="6:16" ht="13.2">
       <c r="F983" s="3"/>
       <c r="I983" s="4"/>
       <c r="J983" s="4"/>
@@ -9520,7 +9549,7 @@
       <c r="L983" s="3"/>
       <c r="P983" s="3"/>
     </row>
-    <row r="984" spans="6:16" ht="12.5">
+    <row r="984" spans="6:16" ht="13.2">
       <c r="F984" s="3"/>
       <c r="I984" s="4"/>
       <c r="J984" s="4"/>
@@ -9528,7 +9557,7 @@
       <c r="L984" s="3"/>
       <c r="P984" s="3"/>
     </row>
-    <row r="985" spans="6:16" ht="12.5">
+    <row r="985" spans="6:16" ht="13.2">
       <c r="F985" s="3"/>
       <c r="I985" s="4"/>
       <c r="J985" s="4"/>
@@ -9536,7 +9565,7 @@
       <c r="L985" s="3"/>
       <c r="P985" s="3"/>
     </row>
-    <row r="986" spans="6:16" ht="12.5">
+    <row r="986" spans="6:16" ht="13.2">
       <c r="F986" s="3"/>
       <c r="I986" s="4"/>
       <c r="J986" s="4"/>
@@ -9544,7 +9573,7 @@
       <c r="L986" s="3"/>
       <c r="P986" s="3"/>
     </row>
-    <row r="987" spans="6:16" ht="12.5">
+    <row r="987" spans="6:16" ht="13.2">
       <c r="F987" s="3"/>
       <c r="I987" s="4"/>
       <c r="J987" s="4"/>
@@ -9552,7 +9581,7 @@
       <c r="L987" s="3"/>
       <c r="P987" s="3"/>
     </row>
-    <row r="988" spans="6:16" ht="12.5">
+    <row r="988" spans="6:16" ht="13.2">
       <c r="F988" s="3"/>
       <c r="I988" s="4"/>
       <c r="J988" s="4"/>
@@ -9560,7 +9589,7 @@
       <c r="L988" s="3"/>
       <c r="P988" s="3"/>
     </row>
-    <row r="989" spans="6:16" ht="12.5">
+    <row r="989" spans="6:16" ht="13.2">
       <c r="F989" s="3"/>
       <c r="I989" s="4"/>
       <c r="J989" s="4"/>
@@ -9568,7 +9597,7 @@
       <c r="L989" s="3"/>
       <c r="P989" s="3"/>
     </row>
-    <row r="990" spans="6:16" ht="12.5">
+    <row r="990" spans="6:16" ht="13.2">
       <c r="F990" s="3"/>
       <c r="I990" s="4"/>
       <c r="J990" s="4"/>
@@ -9577,18 +9606,12 @@
       <c r="P990" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:AM19" xr:uid="{00000000-0009-0000-0000-000006000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Blog"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B1:AM19" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576 T2:T1048576" xr:uid="{C4627515-2A22-4082-A750-A6A1D7F387B7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576 T2:T11 T13:T1048576" xr:uid="{C4627515-2A22-4082-A750-A6A1D7F387B7}">
       <formula1>"Juan Manuel,Santiago,Manuela"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 O2:O1048576" xr:uid="{39B9776E-52EE-404B-ABA6-3F1ED047FC1F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 U2:U1048576" xr:uid="{39B9776E-52EE-404B-ABA6-3F1ED047FC1F}">
       <formula1>"15,30,45,60,90,120,180"</formula1>
     </dataValidation>
   </dataValidations>
